--- a/public/templates/crechely-children-template.xlsx
+++ b/public/templates/crechely-children-template.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y500"/>
+  <dimension ref="A1:AB500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -484,23 +484,26 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="25" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="28" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -544,87 +547,102 @@
           <t>Allergies</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Home Address</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 Name</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 Surname</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 Relationship</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 ID</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 Phone</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 Email</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Parent 1 Occupation</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Parent 1 Address</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 Name</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 Surname</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 Relationship</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 ID</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 Phone</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 Email</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Parent 2 Occupation</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Parent 2 Address</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Emergency Contact Name</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Emergency Contact Relationship</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>Emergency Contact Phone</t>
         </is>
@@ -663,83 +681,90 @@
           <t>Peanuts</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>12 Example Street, Garsfontein, Pretoria</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>1234567890123</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>082 000 0000</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>parent@example.com</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Nurse</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="Q2" s="6" t="n"/>
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="U2" s="6" t="inlineStr">
         <is>
           <t>1234567890123</t>
         </is>
       </c>
-      <c r="T2" s="6" t="inlineStr">
+      <c r="V2" s="6" t="inlineStr">
         <is>
           <t>083 000 0000</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr">
         <is>
           <t>Teacher</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="Y2" s="6" t="n"/>
+      <c r="Z2" s="5" t="inlineStr">
         <is>
           <t>Example Contact</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr">
+      <c r="AA2" s="5" t="inlineStr">
         <is>
           <t>Grandmother</t>
         </is>
       </c>
-      <c r="Y2" s="6" t="inlineStr">
+      <c r="AB2" s="6" t="inlineStr">
         <is>
           <t>084 000 0000</t>
         </is>
@@ -749,4981 +774,6475 @@
       <c r="C3" s="7" t="n"/>
       <c r="E3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
       <c r="M3" s="7" t="n"/>
-      <c r="S3" s="7" t="n"/>
-      <c r="T3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+      <c r="U3" s="7" t="n"/>
+      <c r="V3" s="7" t="n"/>
       <c r="Y3" s="7" t="n"/>
+      <c r="AB3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="C4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
       <c r="M4" s="7" t="n"/>
-      <c r="S4" s="7" t="n"/>
-      <c r="T4" s="7" t="n"/>
+      <c r="N4" s="7" t="n"/>
+      <c r="Q4" s="7" t="n"/>
+      <c r="U4" s="7" t="n"/>
+      <c r="V4" s="7" t="n"/>
       <c r="Y4" s="7" t="n"/>
+      <c r="AB4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
       <c r="M5" s="7" t="n"/>
-      <c r="S5" s="7" t="n"/>
-      <c r="T5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+      <c r="U5" s="7" t="n"/>
+      <c r="V5" s="7" t="n"/>
       <c r="Y5" s="7" t="n"/>
+      <c r="AB5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
       <c r="M6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
+      <c r="N6" s="7" t="n"/>
+      <c r="Q6" s="7" t="n"/>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="7" t="n"/>
       <c r="Y6" s="7" t="n"/>
+      <c r="AB6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
       <c r="Y7" s="7" t="n"/>
+      <c r="AB7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
       <c r="Y8" s="7" t="n"/>
+      <c r="AB8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
-      <c r="S9" s="7" t="n"/>
-      <c r="T9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
       <c r="Y9" s="7" t="n"/>
+      <c r="AB9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
       <c r="M10" s="7" t="n"/>
-      <c r="S10" s="7" t="n"/>
-      <c r="T10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
       <c r="Y10" s="7" t="n"/>
+      <c r="AB10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
       <c r="M11" s="7" t="n"/>
-      <c r="S11" s="7" t="n"/>
-      <c r="T11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
       <c r="Y11" s="7" t="n"/>
+      <c r="AB11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
-      <c r="S12" s="7" t="n"/>
-      <c r="T12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
       <c r="Y12" s="7" t="n"/>
+      <c r="AB12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
-      <c r="S13" s="7" t="n"/>
-      <c r="T13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
       <c r="Y13" s="7" t="n"/>
+      <c r="AB13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
-      <c r="S14" s="7" t="n"/>
-      <c r="T14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
       <c r="Y14" s="7" t="n"/>
+      <c r="AB14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
-      <c r="S15" s="7" t="n"/>
-      <c r="T15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
       <c r="Y15" s="7" t="n"/>
+      <c r="AB15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
-      <c r="S16" s="7" t="n"/>
-      <c r="T16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
       <c r="Y16" s="7" t="n"/>
+      <c r="AB16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
-      <c r="S17" s="7" t="n"/>
-      <c r="T17" s="7" t="n"/>
+      <c r="N17" s="7" t="n"/>
+      <c r="Q17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="Y17" s="7" t="n"/>
+      <c r="AB17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
-      <c r="S18" s="7" t="n"/>
-      <c r="T18" s="7" t="n"/>
+      <c r="N18" s="7" t="n"/>
+      <c r="Q18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
       <c r="Y18" s="7" t="n"/>
+      <c r="AB18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="C19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
-      <c r="S19" s="7" t="n"/>
-      <c r="T19" s="7" t="n"/>
+      <c r="N19" s="7" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
       <c r="Y19" s="7" t="n"/>
+      <c r="AB19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
-      <c r="S20" s="7" t="n"/>
-      <c r="T20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="Q20" s="7" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
       <c r="Y20" s="7" t="n"/>
+      <c r="AB20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
-      <c r="S21" s="7" t="n"/>
-      <c r="T21" s="7" t="n"/>
+      <c r="N21" s="7" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
       <c r="Y21" s="7" t="n"/>
+      <c r="AB21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
-      <c r="S22" s="7" t="n"/>
-      <c r="T22" s="7" t="n"/>
+      <c r="N22" s="7" t="n"/>
+      <c r="Q22" s="7" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="7" t="n"/>
       <c r="Y22" s="7" t="n"/>
+      <c r="AB22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="C23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
       <c r="M23" s="7" t="n"/>
-      <c r="S23" s="7" t="n"/>
-      <c r="T23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="Q23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
       <c r="Y23" s="7" t="n"/>
+      <c r="AB23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="C24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
       <c r="M24" s="7" t="n"/>
-      <c r="S24" s="7" t="n"/>
-      <c r="T24" s="7" t="n"/>
+      <c r="N24" s="7" t="n"/>
+      <c r="Q24" s="7" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="7" t="n"/>
       <c r="Y24" s="7" t="n"/>
+      <c r="AB24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="C25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
-      <c r="S25" s="7" t="n"/>
-      <c r="T25" s="7" t="n"/>
+      <c r="N25" s="7" t="n"/>
+      <c r="Q25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
       <c r="Y25" s="7" t="n"/>
+      <c r="AB25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="C26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
-      <c r="S26" s="7" t="n"/>
-      <c r="T26" s="7" t="n"/>
+      <c r="N26" s="7" t="n"/>
+      <c r="Q26" s="7" t="n"/>
+      <c r="U26" s="7" t="n"/>
+      <c r="V26" s="7" t="n"/>
       <c r="Y26" s="7" t="n"/>
+      <c r="AB26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="C27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
-      <c r="S27" s="7" t="n"/>
-      <c r="T27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
       <c r="Y27" s="7" t="n"/>
+      <c r="AB27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="C28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
-      <c r="S28" s="7" t="n"/>
-      <c r="T28" s="7" t="n"/>
+      <c r="N28" s="7" t="n"/>
+      <c r="Q28" s="7" t="n"/>
+      <c r="U28" s="7" t="n"/>
+      <c r="V28" s="7" t="n"/>
       <c r="Y28" s="7" t="n"/>
+      <c r="AB28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="C29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
-      <c r="S29" s="7" t="n"/>
-      <c r="T29" s="7" t="n"/>
+      <c r="N29" s="7" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+      <c r="U29" s="7" t="n"/>
+      <c r="V29" s="7" t="n"/>
       <c r="Y29" s="7" t="n"/>
+      <c r="AB29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="C30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
       <c r="M30" s="7" t="n"/>
-      <c r="S30" s="7" t="n"/>
-      <c r="T30" s="7" t="n"/>
+      <c r="N30" s="7" t="n"/>
+      <c r="Q30" s="7" t="n"/>
+      <c r="U30" s="7" t="n"/>
+      <c r="V30" s="7" t="n"/>
       <c r="Y30" s="7" t="n"/>
+      <c r="AB30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="C31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
       <c r="M31" s="7" t="n"/>
-      <c r="S31" s="7" t="n"/>
-      <c r="T31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+      <c r="U31" s="7" t="n"/>
+      <c r="V31" s="7" t="n"/>
       <c r="Y31" s="7" t="n"/>
+      <c r="AB31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="C32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
       <c r="M32" s="7" t="n"/>
-      <c r="S32" s="7" t="n"/>
-      <c r="T32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+      <c r="U32" s="7" t="n"/>
+      <c r="V32" s="7" t="n"/>
       <c r="Y32" s="7" t="n"/>
+      <c r="AB32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="C33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
-      <c r="S33" s="7" t="n"/>
-      <c r="T33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="Q33" s="7" t="n"/>
+      <c r="U33" s="7" t="n"/>
+      <c r="V33" s="7" t="n"/>
       <c r="Y33" s="7" t="n"/>
+      <c r="AB33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="C34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
-      <c r="S34" s="7" t="n"/>
-      <c r="T34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="Q34" s="7" t="n"/>
+      <c r="U34" s="7" t="n"/>
+      <c r="V34" s="7" t="n"/>
       <c r="Y34" s="7" t="n"/>
+      <c r="AB34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="C35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
-      <c r="S35" s="7" t="n"/>
-      <c r="T35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="Q35" s="7" t="n"/>
+      <c r="U35" s="7" t="n"/>
+      <c r="V35" s="7" t="n"/>
       <c r="Y35" s="7" t="n"/>
+      <c r="AB35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="C36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
-      <c r="S36" s="7" t="n"/>
-      <c r="T36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+      <c r="U36" s="7" t="n"/>
+      <c r="V36" s="7" t="n"/>
       <c r="Y36" s="7" t="n"/>
+      <c r="AB36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="C37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
       <c r="M37" s="7" t="n"/>
-      <c r="S37" s="7" t="n"/>
-      <c r="T37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+      <c r="U37" s="7" t="n"/>
+      <c r="V37" s="7" t="n"/>
       <c r="Y37" s="7" t="n"/>
+      <c r="AB37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="C38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
       <c r="M38" s="7" t="n"/>
-      <c r="S38" s="7" t="n"/>
-      <c r="T38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+      <c r="U38" s="7" t="n"/>
+      <c r="V38" s="7" t="n"/>
       <c r="Y38" s="7" t="n"/>
+      <c r="AB38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="C39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
-      <c r="L39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
       <c r="M39" s="7" t="n"/>
-      <c r="S39" s="7" t="n"/>
-      <c r="T39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+      <c r="Q39" s="7" t="n"/>
+      <c r="U39" s="7" t="n"/>
+      <c r="V39" s="7" t="n"/>
       <c r="Y39" s="7" t="n"/>
+      <c r="AB39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="C40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
-      <c r="L40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
-      <c r="S40" s="7" t="n"/>
-      <c r="T40" s="7" t="n"/>
+      <c r="N40" s="7" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+      <c r="U40" s="7" t="n"/>
+      <c r="V40" s="7" t="n"/>
       <c r="Y40" s="7" t="n"/>
+      <c r="AB40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="C41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
       <c r="M41" s="7" t="n"/>
-      <c r="S41" s="7" t="n"/>
-      <c r="T41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+      <c r="Q41" s="7" t="n"/>
+      <c r="U41" s="7" t="n"/>
+      <c r="V41" s="7" t="n"/>
       <c r="Y41" s="7" t="n"/>
+      <c r="AB41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="C42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
-      <c r="L42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
-      <c r="S42" s="7" t="n"/>
-      <c r="T42" s="7" t="n"/>
+      <c r="N42" s="7" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+      <c r="U42" s="7" t="n"/>
+      <c r="V42" s="7" t="n"/>
       <c r="Y42" s="7" t="n"/>
+      <c r="AB42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="C43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
-      <c r="L43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
-      <c r="S43" s="7" t="n"/>
-      <c r="T43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="Q43" s="7" t="n"/>
+      <c r="U43" s="7" t="n"/>
+      <c r="V43" s="7" t="n"/>
       <c r="Y43" s="7" t="n"/>
+      <c r="AB43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="C44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
-      <c r="L44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
       <c r="M44" s="7" t="n"/>
-      <c r="S44" s="7" t="n"/>
-      <c r="T44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="U44" s="7" t="n"/>
+      <c r="V44" s="7" t="n"/>
       <c r="Y44" s="7" t="n"/>
+      <c r="AB44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="C45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
-      <c r="L45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
       <c r="M45" s="7" t="n"/>
-      <c r="S45" s="7" t="n"/>
-      <c r="T45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
       <c r="Y45" s="7" t="n"/>
+      <c r="AB45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="C46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
       <c r="M46" s="7" t="n"/>
-      <c r="S46" s="7" t="n"/>
-      <c r="T46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="U46" s="7" t="n"/>
+      <c r="V46" s="7" t="n"/>
       <c r="Y46" s="7" t="n"/>
+      <c r="AB46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="C47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
-      <c r="L47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
       <c r="M47" s="7" t="n"/>
-      <c r="S47" s="7" t="n"/>
-      <c r="T47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
       <c r="Y47" s="7" t="n"/>
+      <c r="AB47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="C48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
-      <c r="L48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
       <c r="M48" s="7" t="n"/>
-      <c r="S48" s="7" t="n"/>
-      <c r="T48" s="7" t="n"/>
+      <c r="N48" s="7" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+      <c r="U48" s="7" t="n"/>
+      <c r="V48" s="7" t="n"/>
       <c r="Y48" s="7" t="n"/>
+      <c r="AB48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="C49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
-      <c r="L49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
-      <c r="S49" s="7" t="n"/>
-      <c r="T49" s="7" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
       <c r="Y49" s="7" t="n"/>
+      <c r="AB49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="C50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
-      <c r="L50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
-      <c r="S50" s="7" t="n"/>
-      <c r="T50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="7" t="n"/>
       <c r="Y50" s="7" t="n"/>
+      <c r="AB50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="C51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
       <c r="M51" s="7" t="n"/>
-      <c r="S51" s="7" t="n"/>
-      <c r="T51" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
+      <c r="Q51" s="7" t="n"/>
+      <c r="U51" s="7" t="n"/>
+      <c r="V51" s="7" t="n"/>
       <c r="Y51" s="7" t="n"/>
+      <c r="AB51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="C52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
-      <c r="L52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
       <c r="M52" s="7" t="n"/>
-      <c r="S52" s="7" t="n"/>
-      <c r="T52" s="7" t="n"/>
+      <c r="N52" s="7" t="n"/>
+      <c r="Q52" s="7" t="n"/>
+      <c r="U52" s="7" t="n"/>
+      <c r="V52" s="7" t="n"/>
       <c r="Y52" s="7" t="n"/>
+      <c r="AB52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="C53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
-      <c r="L53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
       <c r="M53" s="7" t="n"/>
-      <c r="S53" s="7" t="n"/>
-      <c r="T53" s="7" t="n"/>
+      <c r="N53" s="7" t="n"/>
+      <c r="Q53" s="7" t="n"/>
+      <c r="U53" s="7" t="n"/>
+      <c r="V53" s="7" t="n"/>
       <c r="Y53" s="7" t="n"/>
+      <c r="AB53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="C54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
-      <c r="L54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
       <c r="M54" s="7" t="n"/>
-      <c r="S54" s="7" t="n"/>
-      <c r="T54" s="7" t="n"/>
+      <c r="N54" s="7" t="n"/>
+      <c r="Q54" s="7" t="n"/>
+      <c r="U54" s="7" t="n"/>
+      <c r="V54" s="7" t="n"/>
       <c r="Y54" s="7" t="n"/>
+      <c r="AB54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="C55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
-      <c r="L55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
       <c r="M55" s="7" t="n"/>
-      <c r="S55" s="7" t="n"/>
-      <c r="T55" s="7" t="n"/>
+      <c r="N55" s="7" t="n"/>
+      <c r="Q55" s="7" t="n"/>
+      <c r="U55" s="7" t="n"/>
+      <c r="V55" s="7" t="n"/>
       <c r="Y55" s="7" t="n"/>
+      <c r="AB55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="C56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
-      <c r="L56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
       <c r="M56" s="7" t="n"/>
-      <c r="S56" s="7" t="n"/>
-      <c r="T56" s="7" t="n"/>
+      <c r="N56" s="7" t="n"/>
+      <c r="Q56" s="7" t="n"/>
+      <c r="U56" s="7" t="n"/>
+      <c r="V56" s="7" t="n"/>
       <c r="Y56" s="7" t="n"/>
+      <c r="AB56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="C57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
-      <c r="L57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
       <c r="M57" s="7" t="n"/>
-      <c r="S57" s="7" t="n"/>
-      <c r="T57" s="7" t="n"/>
+      <c r="N57" s="7" t="n"/>
+      <c r="Q57" s="7" t="n"/>
+      <c r="U57" s="7" t="n"/>
+      <c r="V57" s="7" t="n"/>
       <c r="Y57" s="7" t="n"/>
+      <c r="AB57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="C58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
-      <c r="L58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
       <c r="M58" s="7" t="n"/>
-      <c r="S58" s="7" t="n"/>
-      <c r="T58" s="7" t="n"/>
+      <c r="N58" s="7" t="n"/>
+      <c r="Q58" s="7" t="n"/>
+      <c r="U58" s="7" t="n"/>
+      <c r="V58" s="7" t="n"/>
       <c r="Y58" s="7" t="n"/>
+      <c r="AB58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="C59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
-      <c r="L59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
       <c r="M59" s="7" t="n"/>
-      <c r="S59" s="7" t="n"/>
-      <c r="T59" s="7" t="n"/>
+      <c r="N59" s="7" t="n"/>
+      <c r="Q59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
       <c r="Y59" s="7" t="n"/>
+      <c r="AB59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
-      <c r="L60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
       <c r="M60" s="7" t="n"/>
-      <c r="S60" s="7" t="n"/>
-      <c r="T60" s="7" t="n"/>
+      <c r="N60" s="7" t="n"/>
+      <c r="Q60" s="7" t="n"/>
+      <c r="U60" s="7" t="n"/>
+      <c r="V60" s="7" t="n"/>
       <c r="Y60" s="7" t="n"/>
+      <c r="AB60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="C61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
       <c r="M61" s="7" t="n"/>
-      <c r="S61" s="7" t="n"/>
-      <c r="T61" s="7" t="n"/>
+      <c r="N61" s="7" t="n"/>
+      <c r="Q61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
       <c r="Y61" s="7" t="n"/>
+      <c r="AB61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="C62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
-      <c r="L62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
       <c r="M62" s="7" t="n"/>
-      <c r="S62" s="7" t="n"/>
-      <c r="T62" s="7" t="n"/>
+      <c r="N62" s="7" t="n"/>
+      <c r="Q62" s="7" t="n"/>
+      <c r="U62" s="7" t="n"/>
+      <c r="V62" s="7" t="n"/>
       <c r="Y62" s="7" t="n"/>
+      <c r="AB62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="C63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
-      <c r="L63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
-      <c r="S63" s="7" t="n"/>
-      <c r="T63" s="7" t="n"/>
+      <c r="N63" s="7" t="n"/>
+      <c r="Q63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
       <c r="Y63" s="7" t="n"/>
+      <c r="AB63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="C64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
-      <c r="L64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
-      <c r="S64" s="7" t="n"/>
-      <c r="T64" s="7" t="n"/>
+      <c r="N64" s="7" t="n"/>
+      <c r="Q64" s="7" t="n"/>
+      <c r="U64" s="7" t="n"/>
+      <c r="V64" s="7" t="n"/>
       <c r="Y64" s="7" t="n"/>
+      <c r="AB64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="C65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
-      <c r="L65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
       <c r="M65" s="7" t="n"/>
-      <c r="S65" s="7" t="n"/>
-      <c r="T65" s="7" t="n"/>
+      <c r="N65" s="7" t="n"/>
+      <c r="Q65" s="7" t="n"/>
+      <c r="U65" s="7" t="n"/>
+      <c r="V65" s="7" t="n"/>
       <c r="Y65" s="7" t="n"/>
+      <c r="AB65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="C66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
-      <c r="L66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
       <c r="M66" s="7" t="n"/>
-      <c r="S66" s="7" t="n"/>
-      <c r="T66" s="7" t="n"/>
+      <c r="N66" s="7" t="n"/>
+      <c r="Q66" s="7" t="n"/>
+      <c r="U66" s="7" t="n"/>
+      <c r="V66" s="7" t="n"/>
       <c r="Y66" s="7" t="n"/>
+      <c r="AB66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="C67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
-      <c r="L67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
       <c r="M67" s="7" t="n"/>
-      <c r="S67" s="7" t="n"/>
-      <c r="T67" s="7" t="n"/>
+      <c r="N67" s="7" t="n"/>
+      <c r="Q67" s="7" t="n"/>
+      <c r="U67" s="7" t="n"/>
+      <c r="V67" s="7" t="n"/>
       <c r="Y67" s="7" t="n"/>
+      <c r="AB67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="C68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
-      <c r="L68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
       <c r="M68" s="7" t="n"/>
-      <c r="S68" s="7" t="n"/>
-      <c r="T68" s="7" t="n"/>
+      <c r="N68" s="7" t="n"/>
+      <c r="Q68" s="7" t="n"/>
+      <c r="U68" s="7" t="n"/>
+      <c r="V68" s="7" t="n"/>
       <c r="Y68" s="7" t="n"/>
+      <c r="AB68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="C69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
-      <c r="L69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
       <c r="M69" s="7" t="n"/>
-      <c r="S69" s="7" t="n"/>
-      <c r="T69" s="7" t="n"/>
+      <c r="N69" s="7" t="n"/>
+      <c r="Q69" s="7" t="n"/>
+      <c r="U69" s="7" t="n"/>
+      <c r="V69" s="7" t="n"/>
       <c r="Y69" s="7" t="n"/>
+      <c r="AB69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="C70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
-      <c r="L70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
-      <c r="S70" s="7" t="n"/>
-      <c r="T70" s="7" t="n"/>
+      <c r="N70" s="7" t="n"/>
+      <c r="Q70" s="7" t="n"/>
+      <c r="U70" s="7" t="n"/>
+      <c r="V70" s="7" t="n"/>
       <c r="Y70" s="7" t="n"/>
+      <c r="AB70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="C71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
-      <c r="L71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
-      <c r="S71" s="7" t="n"/>
-      <c r="T71" s="7" t="n"/>
+      <c r="N71" s="7" t="n"/>
+      <c r="Q71" s="7" t="n"/>
+      <c r="U71" s="7" t="n"/>
+      <c r="V71" s="7" t="n"/>
       <c r="Y71" s="7" t="n"/>
+      <c r="AB71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="C72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
-      <c r="L72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
       <c r="M72" s="7" t="n"/>
-      <c r="S72" s="7" t="n"/>
-      <c r="T72" s="7" t="n"/>
+      <c r="N72" s="7" t="n"/>
+      <c r="Q72" s="7" t="n"/>
+      <c r="U72" s="7" t="n"/>
+      <c r="V72" s="7" t="n"/>
       <c r="Y72" s="7" t="n"/>
+      <c r="AB72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="C73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
-      <c r="L73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
       <c r="M73" s="7" t="n"/>
-      <c r="S73" s="7" t="n"/>
-      <c r="T73" s="7" t="n"/>
+      <c r="N73" s="7" t="n"/>
+      <c r="Q73" s="7" t="n"/>
+      <c r="U73" s="7" t="n"/>
+      <c r="V73" s="7" t="n"/>
       <c r="Y73" s="7" t="n"/>
+      <c r="AB73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="C74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
-      <c r="L74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
       <c r="M74" s="7" t="n"/>
-      <c r="S74" s="7" t="n"/>
-      <c r="T74" s="7" t="n"/>
+      <c r="N74" s="7" t="n"/>
+      <c r="Q74" s="7" t="n"/>
+      <c r="U74" s="7" t="n"/>
+      <c r="V74" s="7" t="n"/>
       <c r="Y74" s="7" t="n"/>
+      <c r="AB74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="C75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
-      <c r="L75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
       <c r="M75" s="7" t="n"/>
-      <c r="S75" s="7" t="n"/>
-      <c r="T75" s="7" t="n"/>
+      <c r="N75" s="7" t="n"/>
+      <c r="Q75" s="7" t="n"/>
+      <c r="U75" s="7" t="n"/>
+      <c r="V75" s="7" t="n"/>
       <c r="Y75" s="7" t="n"/>
+      <c r="AB75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="C76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
-      <c r="L76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
       <c r="M76" s="7" t="n"/>
-      <c r="S76" s="7" t="n"/>
-      <c r="T76" s="7" t="n"/>
+      <c r="N76" s="7" t="n"/>
+      <c r="Q76" s="7" t="n"/>
+      <c r="U76" s="7" t="n"/>
+      <c r="V76" s="7" t="n"/>
       <c r="Y76" s="7" t="n"/>
+      <c r="AB76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="C77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
-      <c r="L77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
-      <c r="S77" s="7" t="n"/>
-      <c r="T77" s="7" t="n"/>
+      <c r="N77" s="7" t="n"/>
+      <c r="Q77" s="7" t="n"/>
+      <c r="U77" s="7" t="n"/>
+      <c r="V77" s="7" t="n"/>
       <c r="Y77" s="7" t="n"/>
+      <c r="AB77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="C78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
-      <c r="L78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
-      <c r="S78" s="7" t="n"/>
-      <c r="T78" s="7" t="n"/>
+      <c r="N78" s="7" t="n"/>
+      <c r="Q78" s="7" t="n"/>
+      <c r="U78" s="7" t="n"/>
+      <c r="V78" s="7" t="n"/>
       <c r="Y78" s="7" t="n"/>
+      <c r="AB78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="C79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
-      <c r="L79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
       <c r="M79" s="7" t="n"/>
-      <c r="S79" s="7" t="n"/>
-      <c r="T79" s="7" t="n"/>
+      <c r="N79" s="7" t="n"/>
+      <c r="Q79" s="7" t="n"/>
+      <c r="U79" s="7" t="n"/>
+      <c r="V79" s="7" t="n"/>
       <c r="Y79" s="7" t="n"/>
+      <c r="AB79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="C80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
-      <c r="L80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
       <c r="M80" s="7" t="n"/>
-      <c r="S80" s="7" t="n"/>
-      <c r="T80" s="7" t="n"/>
+      <c r="N80" s="7" t="n"/>
+      <c r="Q80" s="7" t="n"/>
+      <c r="U80" s="7" t="n"/>
+      <c r="V80" s="7" t="n"/>
       <c r="Y80" s="7" t="n"/>
+      <c r="AB80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="C81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
-      <c r="L81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
       <c r="M81" s="7" t="n"/>
-      <c r="S81" s="7" t="n"/>
-      <c r="T81" s="7" t="n"/>
+      <c r="N81" s="7" t="n"/>
+      <c r="Q81" s="7" t="n"/>
+      <c r="U81" s="7" t="n"/>
+      <c r="V81" s="7" t="n"/>
       <c r="Y81" s="7" t="n"/>
+      <c r="AB81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="C82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
-      <c r="L82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
       <c r="M82" s="7" t="n"/>
-      <c r="S82" s="7" t="n"/>
-      <c r="T82" s="7" t="n"/>
+      <c r="N82" s="7" t="n"/>
+      <c r="Q82" s="7" t="n"/>
+      <c r="U82" s="7" t="n"/>
+      <c r="V82" s="7" t="n"/>
       <c r="Y82" s="7" t="n"/>
+      <c r="AB82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="C83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
-      <c r="L83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
       <c r="M83" s="7" t="n"/>
-      <c r="S83" s="7" t="n"/>
-      <c r="T83" s="7" t="n"/>
+      <c r="N83" s="7" t="n"/>
+      <c r="Q83" s="7" t="n"/>
+      <c r="U83" s="7" t="n"/>
+      <c r="V83" s="7" t="n"/>
       <c r="Y83" s="7" t="n"/>
+      <c r="AB83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="C84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
-      <c r="L84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
-      <c r="S84" s="7" t="n"/>
-      <c r="T84" s="7" t="n"/>
+      <c r="N84" s="7" t="n"/>
+      <c r="Q84" s="7" t="n"/>
+      <c r="U84" s="7" t="n"/>
+      <c r="V84" s="7" t="n"/>
       <c r="Y84" s="7" t="n"/>
+      <c r="AB84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="C85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
-      <c r="L85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
-      <c r="S85" s="7" t="n"/>
-      <c r="T85" s="7" t="n"/>
+      <c r="N85" s="7" t="n"/>
+      <c r="Q85" s="7" t="n"/>
+      <c r="U85" s="7" t="n"/>
+      <c r="V85" s="7" t="n"/>
       <c r="Y85" s="7" t="n"/>
+      <c r="AB85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="C86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
-      <c r="L86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
       <c r="M86" s="7" t="n"/>
-      <c r="S86" s="7" t="n"/>
-      <c r="T86" s="7" t="n"/>
+      <c r="N86" s="7" t="n"/>
+      <c r="Q86" s="7" t="n"/>
+      <c r="U86" s="7" t="n"/>
+      <c r="V86" s="7" t="n"/>
       <c r="Y86" s="7" t="n"/>
+      <c r="AB86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="C87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
-      <c r="L87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
       <c r="M87" s="7" t="n"/>
-      <c r="S87" s="7" t="n"/>
-      <c r="T87" s="7" t="n"/>
+      <c r="N87" s="7" t="n"/>
+      <c r="Q87" s="7" t="n"/>
+      <c r="U87" s="7" t="n"/>
+      <c r="V87" s="7" t="n"/>
       <c r="Y87" s="7" t="n"/>
+      <c r="AB87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="C88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
-      <c r="L88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
       <c r="M88" s="7" t="n"/>
-      <c r="S88" s="7" t="n"/>
-      <c r="T88" s="7" t="n"/>
+      <c r="N88" s="7" t="n"/>
+      <c r="Q88" s="7" t="n"/>
+      <c r="U88" s="7" t="n"/>
+      <c r="V88" s="7" t="n"/>
       <c r="Y88" s="7" t="n"/>
+      <c r="AB88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="C89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
-      <c r="L89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
       <c r="M89" s="7" t="n"/>
-      <c r="S89" s="7" t="n"/>
-      <c r="T89" s="7" t="n"/>
+      <c r="N89" s="7" t="n"/>
+      <c r="Q89" s="7" t="n"/>
+      <c r="U89" s="7" t="n"/>
+      <c r="V89" s="7" t="n"/>
       <c r="Y89" s="7" t="n"/>
+      <c r="AB89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="C90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
-      <c r="L90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
       <c r="M90" s="7" t="n"/>
-      <c r="S90" s="7" t="n"/>
-      <c r="T90" s="7" t="n"/>
+      <c r="N90" s="7" t="n"/>
+      <c r="Q90" s="7" t="n"/>
+      <c r="U90" s="7" t="n"/>
+      <c r="V90" s="7" t="n"/>
       <c r="Y90" s="7" t="n"/>
+      <c r="AB90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="C91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
-      <c r="L91" s="7" t="n"/>
+      <c r="I91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
-      <c r="S91" s="7" t="n"/>
-      <c r="T91" s="7" t="n"/>
+      <c r="N91" s="7" t="n"/>
+      <c r="Q91" s="7" t="n"/>
+      <c r="U91" s="7" t="n"/>
+      <c r="V91" s="7" t="n"/>
       <c r="Y91" s="7" t="n"/>
+      <c r="AB91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="C92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
-      <c r="L92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
-      <c r="S92" s="7" t="n"/>
-      <c r="T92" s="7" t="n"/>
+      <c r="N92" s="7" t="n"/>
+      <c r="Q92" s="7" t="n"/>
+      <c r="U92" s="7" t="n"/>
+      <c r="V92" s="7" t="n"/>
       <c r="Y92" s="7" t="n"/>
+      <c r="AB92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="C93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
-      <c r="L93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
       <c r="M93" s="7" t="n"/>
-      <c r="S93" s="7" t="n"/>
-      <c r="T93" s="7" t="n"/>
+      <c r="N93" s="7" t="n"/>
+      <c r="Q93" s="7" t="n"/>
+      <c r="U93" s="7" t="n"/>
+      <c r="V93" s="7" t="n"/>
       <c r="Y93" s="7" t="n"/>
+      <c r="AB93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="C94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
-      <c r="L94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
       <c r="M94" s="7" t="n"/>
-      <c r="S94" s="7" t="n"/>
-      <c r="T94" s="7" t="n"/>
+      <c r="N94" s="7" t="n"/>
+      <c r="Q94" s="7" t="n"/>
+      <c r="U94" s="7" t="n"/>
+      <c r="V94" s="7" t="n"/>
       <c r="Y94" s="7" t="n"/>
+      <c r="AB94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="C95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
-      <c r="L95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
       <c r="M95" s="7" t="n"/>
-      <c r="S95" s="7" t="n"/>
-      <c r="T95" s="7" t="n"/>
+      <c r="N95" s="7" t="n"/>
+      <c r="Q95" s="7" t="n"/>
+      <c r="U95" s="7" t="n"/>
+      <c r="V95" s="7" t="n"/>
       <c r="Y95" s="7" t="n"/>
+      <c r="AB95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="C96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
-      <c r="L96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
       <c r="M96" s="7" t="n"/>
-      <c r="S96" s="7" t="n"/>
-      <c r="T96" s="7" t="n"/>
+      <c r="N96" s="7" t="n"/>
+      <c r="Q96" s="7" t="n"/>
+      <c r="U96" s="7" t="n"/>
+      <c r="V96" s="7" t="n"/>
       <c r="Y96" s="7" t="n"/>
+      <c r="AB96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="C97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
-      <c r="L97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
       <c r="M97" s="7" t="n"/>
-      <c r="S97" s="7" t="n"/>
-      <c r="T97" s="7" t="n"/>
+      <c r="N97" s="7" t="n"/>
+      <c r="Q97" s="7" t="n"/>
+      <c r="U97" s="7" t="n"/>
+      <c r="V97" s="7" t="n"/>
       <c r="Y97" s="7" t="n"/>
+      <c r="AB97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="C98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
-      <c r="L98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
-      <c r="S98" s="7" t="n"/>
-      <c r="T98" s="7" t="n"/>
+      <c r="N98" s="7" t="n"/>
+      <c r="Q98" s="7" t="n"/>
+      <c r="U98" s="7" t="n"/>
+      <c r="V98" s="7" t="n"/>
       <c r="Y98" s="7" t="n"/>
+      <c r="AB98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="C99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
-      <c r="L99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
-      <c r="S99" s="7" t="n"/>
-      <c r="T99" s="7" t="n"/>
+      <c r="N99" s="7" t="n"/>
+      <c r="Q99" s="7" t="n"/>
+      <c r="U99" s="7" t="n"/>
+      <c r="V99" s="7" t="n"/>
       <c r="Y99" s="7" t="n"/>
+      <c r="AB99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="C100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
-      <c r="L100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
       <c r="M100" s="7" t="n"/>
-      <c r="S100" s="7" t="n"/>
-      <c r="T100" s="7" t="n"/>
+      <c r="N100" s="7" t="n"/>
+      <c r="Q100" s="7" t="n"/>
+      <c r="U100" s="7" t="n"/>
+      <c r="V100" s="7" t="n"/>
       <c r="Y100" s="7" t="n"/>
+      <c r="AB100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="C101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
-      <c r="L101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
       <c r="M101" s="7" t="n"/>
-      <c r="S101" s="7" t="n"/>
-      <c r="T101" s="7" t="n"/>
+      <c r="N101" s="7" t="n"/>
+      <c r="Q101" s="7" t="n"/>
+      <c r="U101" s="7" t="n"/>
+      <c r="V101" s="7" t="n"/>
       <c r="Y101" s="7" t="n"/>
+      <c r="AB101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="C102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
-      <c r="L102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
       <c r="M102" s="7" t="n"/>
-      <c r="S102" s="7" t="n"/>
-      <c r="T102" s="7" t="n"/>
+      <c r="N102" s="7" t="n"/>
+      <c r="Q102" s="7" t="n"/>
+      <c r="U102" s="7" t="n"/>
+      <c r="V102" s="7" t="n"/>
       <c r="Y102" s="7" t="n"/>
+      <c r="AB102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="C103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
-      <c r="L103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
       <c r="M103" s="7" t="n"/>
-      <c r="S103" s="7" t="n"/>
-      <c r="T103" s="7" t="n"/>
+      <c r="N103" s="7" t="n"/>
+      <c r="Q103" s="7" t="n"/>
+      <c r="U103" s="7" t="n"/>
+      <c r="V103" s="7" t="n"/>
       <c r="Y103" s="7" t="n"/>
+      <c r="AB103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="C104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
-      <c r="L104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
       <c r="M104" s="7" t="n"/>
-      <c r="S104" s="7" t="n"/>
-      <c r="T104" s="7" t="n"/>
+      <c r="N104" s="7" t="n"/>
+      <c r="Q104" s="7" t="n"/>
+      <c r="U104" s="7" t="n"/>
+      <c r="V104" s="7" t="n"/>
       <c r="Y104" s="7" t="n"/>
+      <c r="AB104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="C105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
-      <c r="L105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
-      <c r="S105" s="7" t="n"/>
-      <c r="T105" s="7" t="n"/>
+      <c r="N105" s="7" t="n"/>
+      <c r="Q105" s="7" t="n"/>
+      <c r="U105" s="7" t="n"/>
+      <c r="V105" s="7" t="n"/>
       <c r="Y105" s="7" t="n"/>
+      <c r="AB105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="C106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
-      <c r="L106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
-      <c r="S106" s="7" t="n"/>
-      <c r="T106" s="7" t="n"/>
+      <c r="N106" s="7" t="n"/>
+      <c r="Q106" s="7" t="n"/>
+      <c r="U106" s="7" t="n"/>
+      <c r="V106" s="7" t="n"/>
       <c r="Y106" s="7" t="n"/>
+      <c r="AB106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="C107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
-      <c r="L107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
       <c r="M107" s="7" t="n"/>
-      <c r="S107" s="7" t="n"/>
-      <c r="T107" s="7" t="n"/>
+      <c r="N107" s="7" t="n"/>
+      <c r="Q107" s="7" t="n"/>
+      <c r="U107" s="7" t="n"/>
+      <c r="V107" s="7" t="n"/>
       <c r="Y107" s="7" t="n"/>
+      <c r="AB107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="C108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
-      <c r="L108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
       <c r="M108" s="7" t="n"/>
-      <c r="S108" s="7" t="n"/>
-      <c r="T108" s="7" t="n"/>
+      <c r="N108" s="7" t="n"/>
+      <c r="Q108" s="7" t="n"/>
+      <c r="U108" s="7" t="n"/>
+      <c r="V108" s="7" t="n"/>
       <c r="Y108" s="7" t="n"/>
+      <c r="AB108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="C109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
       <c r="G109" s="7" t="n"/>
-      <c r="L109" s="7" t="n"/>
+      <c r="I109" s="7" t="n"/>
       <c r="M109" s="7" t="n"/>
-      <c r="S109" s="7" t="n"/>
-      <c r="T109" s="7" t="n"/>
+      <c r="N109" s="7" t="n"/>
+      <c r="Q109" s="7" t="n"/>
+      <c r="U109" s="7" t="n"/>
+      <c r="V109" s="7" t="n"/>
       <c r="Y109" s="7" t="n"/>
+      <c r="AB109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="C110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
       <c r="G110" s="7" t="n"/>
-      <c r="L110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
       <c r="M110" s="7" t="n"/>
-      <c r="S110" s="7" t="n"/>
-      <c r="T110" s="7" t="n"/>
+      <c r="N110" s="7" t="n"/>
+      <c r="Q110" s="7" t="n"/>
+      <c r="U110" s="7" t="n"/>
+      <c r="V110" s="7" t="n"/>
       <c r="Y110" s="7" t="n"/>
+      <c r="AB110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="C111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
       <c r="G111" s="7" t="n"/>
-      <c r="L111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
       <c r="M111" s="7" t="n"/>
-      <c r="S111" s="7" t="n"/>
-      <c r="T111" s="7" t="n"/>
+      <c r="N111" s="7" t="n"/>
+      <c r="Q111" s="7" t="n"/>
+      <c r="U111" s="7" t="n"/>
+      <c r="V111" s="7" t="n"/>
       <c r="Y111" s="7" t="n"/>
+      <c r="AB111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="C112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
       <c r="G112" s="7" t="n"/>
-      <c r="L112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
-      <c r="S112" s="7" t="n"/>
-      <c r="T112" s="7" t="n"/>
+      <c r="N112" s="7" t="n"/>
+      <c r="Q112" s="7" t="n"/>
+      <c r="U112" s="7" t="n"/>
+      <c r="V112" s="7" t="n"/>
       <c r="Y112" s="7" t="n"/>
+      <c r="AB112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="C113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
       <c r="G113" s="7" t="n"/>
-      <c r="L113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
-      <c r="S113" s="7" t="n"/>
-      <c r="T113" s="7" t="n"/>
+      <c r="N113" s="7" t="n"/>
+      <c r="Q113" s="7" t="n"/>
+      <c r="U113" s="7" t="n"/>
+      <c r="V113" s="7" t="n"/>
       <c r="Y113" s="7" t="n"/>
+      <c r="AB113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="C114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
       <c r="G114" s="7" t="n"/>
-      <c r="L114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
       <c r="M114" s="7" t="n"/>
-      <c r="S114" s="7" t="n"/>
-      <c r="T114" s="7" t="n"/>
+      <c r="N114" s="7" t="n"/>
+      <c r="Q114" s="7" t="n"/>
+      <c r="U114" s="7" t="n"/>
+      <c r="V114" s="7" t="n"/>
       <c r="Y114" s="7" t="n"/>
+      <c r="AB114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="C115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
       <c r="G115" s="7" t="n"/>
-      <c r="L115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
       <c r="M115" s="7" t="n"/>
-      <c r="S115" s="7" t="n"/>
-      <c r="T115" s="7" t="n"/>
+      <c r="N115" s="7" t="n"/>
+      <c r="Q115" s="7" t="n"/>
+      <c r="U115" s="7" t="n"/>
+      <c r="V115" s="7" t="n"/>
       <c r="Y115" s="7" t="n"/>
+      <c r="AB115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="C116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
       <c r="G116" s="7" t="n"/>
-      <c r="L116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
       <c r="M116" s="7" t="n"/>
-      <c r="S116" s="7" t="n"/>
-      <c r="T116" s="7" t="n"/>
+      <c r="N116" s="7" t="n"/>
+      <c r="Q116" s="7" t="n"/>
+      <c r="U116" s="7" t="n"/>
+      <c r="V116" s="7" t="n"/>
       <c r="Y116" s="7" t="n"/>
+      <c r="AB116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="C117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
       <c r="G117" s="7" t="n"/>
-      <c r="L117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
       <c r="M117" s="7" t="n"/>
-      <c r="S117" s="7" t="n"/>
-      <c r="T117" s="7" t="n"/>
+      <c r="N117" s="7" t="n"/>
+      <c r="Q117" s="7" t="n"/>
+      <c r="U117" s="7" t="n"/>
+      <c r="V117" s="7" t="n"/>
       <c r="Y117" s="7" t="n"/>
+      <c r="AB117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="C118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
       <c r="G118" s="7" t="n"/>
-      <c r="L118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
       <c r="M118" s="7" t="n"/>
-      <c r="S118" s="7" t="n"/>
-      <c r="T118" s="7" t="n"/>
+      <c r="N118" s="7" t="n"/>
+      <c r="Q118" s="7" t="n"/>
+      <c r="U118" s="7" t="n"/>
+      <c r="V118" s="7" t="n"/>
       <c r="Y118" s="7" t="n"/>
+      <c r="AB118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="C119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
       <c r="G119" s="7" t="n"/>
-      <c r="L119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
-      <c r="S119" s="7" t="n"/>
-      <c r="T119" s="7" t="n"/>
+      <c r="N119" s="7" t="n"/>
+      <c r="Q119" s="7" t="n"/>
+      <c r="U119" s="7" t="n"/>
+      <c r="V119" s="7" t="n"/>
       <c r="Y119" s="7" t="n"/>
+      <c r="AB119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="C120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
       <c r="G120" s="7" t="n"/>
-      <c r="L120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
-      <c r="S120" s="7" t="n"/>
-      <c r="T120" s="7" t="n"/>
+      <c r="N120" s="7" t="n"/>
+      <c r="Q120" s="7" t="n"/>
+      <c r="U120" s="7" t="n"/>
+      <c r="V120" s="7" t="n"/>
       <c r="Y120" s="7" t="n"/>
+      <c r="AB120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="C121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
       <c r="G121" s="7" t="n"/>
-      <c r="L121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
       <c r="M121" s="7" t="n"/>
-      <c r="S121" s="7" t="n"/>
-      <c r="T121" s="7" t="n"/>
+      <c r="N121" s="7" t="n"/>
+      <c r="Q121" s="7" t="n"/>
+      <c r="U121" s="7" t="n"/>
+      <c r="V121" s="7" t="n"/>
       <c r="Y121" s="7" t="n"/>
+      <c r="AB121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="C122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
       <c r="G122" s="7" t="n"/>
-      <c r="L122" s="7" t="n"/>
+      <c r="I122" s="7" t="n"/>
       <c r="M122" s="7" t="n"/>
-      <c r="S122" s="7" t="n"/>
-      <c r="T122" s="7" t="n"/>
+      <c r="N122" s="7" t="n"/>
+      <c r="Q122" s="7" t="n"/>
+      <c r="U122" s="7" t="n"/>
+      <c r="V122" s="7" t="n"/>
       <c r="Y122" s="7" t="n"/>
+      <c r="AB122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="C123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
       <c r="G123" s="7" t="n"/>
-      <c r="L123" s="7" t="n"/>
+      <c r="I123" s="7" t="n"/>
       <c r="M123" s="7" t="n"/>
-      <c r="S123" s="7" t="n"/>
-      <c r="T123" s="7" t="n"/>
+      <c r="N123" s="7" t="n"/>
+      <c r="Q123" s="7" t="n"/>
+      <c r="U123" s="7" t="n"/>
+      <c r="V123" s="7" t="n"/>
       <c r="Y123" s="7" t="n"/>
+      <c r="AB123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="C124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
       <c r="G124" s="7" t="n"/>
-      <c r="L124" s="7" t="n"/>
+      <c r="I124" s="7" t="n"/>
       <c r="M124" s="7" t="n"/>
-      <c r="S124" s="7" t="n"/>
-      <c r="T124" s="7" t="n"/>
+      <c r="N124" s="7" t="n"/>
+      <c r="Q124" s="7" t="n"/>
+      <c r="U124" s="7" t="n"/>
+      <c r="V124" s="7" t="n"/>
       <c r="Y124" s="7" t="n"/>
+      <c r="AB124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="C125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
       <c r="G125" s="7" t="n"/>
-      <c r="L125" s="7" t="n"/>
+      <c r="I125" s="7" t="n"/>
       <c r="M125" s="7" t="n"/>
-      <c r="S125" s="7" t="n"/>
-      <c r="T125" s="7" t="n"/>
+      <c r="N125" s="7" t="n"/>
+      <c r="Q125" s="7" t="n"/>
+      <c r="U125" s="7" t="n"/>
+      <c r="V125" s="7" t="n"/>
       <c r="Y125" s="7" t="n"/>
+      <c r="AB125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="C126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
       <c r="G126" s="7" t="n"/>
-      <c r="L126" s="7" t="n"/>
+      <c r="I126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
-      <c r="S126" s="7" t="n"/>
-      <c r="T126" s="7" t="n"/>
+      <c r="N126" s="7" t="n"/>
+      <c r="Q126" s="7" t="n"/>
+      <c r="U126" s="7" t="n"/>
+      <c r="V126" s="7" t="n"/>
       <c r="Y126" s="7" t="n"/>
+      <c r="AB126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="C127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
       <c r="G127" s="7" t="n"/>
-      <c r="L127" s="7" t="n"/>
+      <c r="I127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
-      <c r="S127" s="7" t="n"/>
-      <c r="T127" s="7" t="n"/>
+      <c r="N127" s="7" t="n"/>
+      <c r="Q127" s="7" t="n"/>
+      <c r="U127" s="7" t="n"/>
+      <c r="V127" s="7" t="n"/>
       <c r="Y127" s="7" t="n"/>
+      <c r="AB127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="C128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
       <c r="G128" s="7" t="n"/>
-      <c r="L128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
       <c r="M128" s="7" t="n"/>
-      <c r="S128" s="7" t="n"/>
-      <c r="T128" s="7" t="n"/>
+      <c r="N128" s="7" t="n"/>
+      <c r="Q128" s="7" t="n"/>
+      <c r="U128" s="7" t="n"/>
+      <c r="V128" s="7" t="n"/>
       <c r="Y128" s="7" t="n"/>
+      <c r="AB128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="C129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
       <c r="G129" s="7" t="n"/>
-      <c r="L129" s="7" t="n"/>
+      <c r="I129" s="7" t="n"/>
       <c r="M129" s="7" t="n"/>
-      <c r="S129" s="7" t="n"/>
-      <c r="T129" s="7" t="n"/>
+      <c r="N129" s="7" t="n"/>
+      <c r="Q129" s="7" t="n"/>
+      <c r="U129" s="7" t="n"/>
+      <c r="V129" s="7" t="n"/>
       <c r="Y129" s="7" t="n"/>
+      <c r="AB129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="C130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
       <c r="G130" s="7" t="n"/>
-      <c r="L130" s="7" t="n"/>
+      <c r="I130" s="7" t="n"/>
       <c r="M130" s="7" t="n"/>
-      <c r="S130" s="7" t="n"/>
-      <c r="T130" s="7" t="n"/>
+      <c r="N130" s="7" t="n"/>
+      <c r="Q130" s="7" t="n"/>
+      <c r="U130" s="7" t="n"/>
+      <c r="V130" s="7" t="n"/>
       <c r="Y130" s="7" t="n"/>
+      <c r="AB130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="C131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
       <c r="G131" s="7" t="n"/>
-      <c r="L131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
       <c r="M131" s="7" t="n"/>
-      <c r="S131" s="7" t="n"/>
-      <c r="T131" s="7" t="n"/>
+      <c r="N131" s="7" t="n"/>
+      <c r="Q131" s="7" t="n"/>
+      <c r="U131" s="7" t="n"/>
+      <c r="V131" s="7" t="n"/>
       <c r="Y131" s="7" t="n"/>
+      <c r="AB131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="C132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
       <c r="G132" s="7" t="n"/>
-      <c r="L132" s="7" t="n"/>
+      <c r="I132" s="7" t="n"/>
       <c r="M132" s="7" t="n"/>
-      <c r="S132" s="7" t="n"/>
-      <c r="T132" s="7" t="n"/>
+      <c r="N132" s="7" t="n"/>
+      <c r="Q132" s="7" t="n"/>
+      <c r="U132" s="7" t="n"/>
+      <c r="V132" s="7" t="n"/>
       <c r="Y132" s="7" t="n"/>
+      <c r="AB132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="C133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
       <c r="G133" s="7" t="n"/>
-      <c r="L133" s="7" t="n"/>
+      <c r="I133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
-      <c r="S133" s="7" t="n"/>
-      <c r="T133" s="7" t="n"/>
+      <c r="N133" s="7" t="n"/>
+      <c r="Q133" s="7" t="n"/>
+      <c r="U133" s="7" t="n"/>
+      <c r="V133" s="7" t="n"/>
       <c r="Y133" s="7" t="n"/>
+      <c r="AB133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="C134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
       <c r="G134" s="7" t="n"/>
-      <c r="L134" s="7" t="n"/>
+      <c r="I134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
-      <c r="S134" s="7" t="n"/>
-      <c r="T134" s="7" t="n"/>
+      <c r="N134" s="7" t="n"/>
+      <c r="Q134" s="7" t="n"/>
+      <c r="U134" s="7" t="n"/>
+      <c r="V134" s="7" t="n"/>
       <c r="Y134" s="7" t="n"/>
+      <c r="AB134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="C135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
       <c r="G135" s="7" t="n"/>
-      <c r="L135" s="7" t="n"/>
+      <c r="I135" s="7" t="n"/>
       <c r="M135" s="7" t="n"/>
-      <c r="S135" s="7" t="n"/>
-      <c r="T135" s="7" t="n"/>
+      <c r="N135" s="7" t="n"/>
+      <c r="Q135" s="7" t="n"/>
+      <c r="U135" s="7" t="n"/>
+      <c r="V135" s="7" t="n"/>
       <c r="Y135" s="7" t="n"/>
+      <c r="AB135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="C136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
       <c r="G136" s="7" t="n"/>
-      <c r="L136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
       <c r="M136" s="7" t="n"/>
-      <c r="S136" s="7" t="n"/>
-      <c r="T136" s="7" t="n"/>
+      <c r="N136" s="7" t="n"/>
+      <c r="Q136" s="7" t="n"/>
+      <c r="U136" s="7" t="n"/>
+      <c r="V136" s="7" t="n"/>
       <c r="Y136" s="7" t="n"/>
+      <c r="AB136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="C137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
       <c r="G137" s="7" t="n"/>
-      <c r="L137" s="7" t="n"/>
+      <c r="I137" s="7" t="n"/>
       <c r="M137" s="7" t="n"/>
-      <c r="S137" s="7" t="n"/>
-      <c r="T137" s="7" t="n"/>
+      <c r="N137" s="7" t="n"/>
+      <c r="Q137" s="7" t="n"/>
+      <c r="U137" s="7" t="n"/>
+      <c r="V137" s="7" t="n"/>
       <c r="Y137" s="7" t="n"/>
+      <c r="AB137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="C138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
       <c r="G138" s="7" t="n"/>
-      <c r="L138" s="7" t="n"/>
+      <c r="I138" s="7" t="n"/>
       <c r="M138" s="7" t="n"/>
-      <c r="S138" s="7" t="n"/>
-      <c r="T138" s="7" t="n"/>
+      <c r="N138" s="7" t="n"/>
+      <c r="Q138" s="7" t="n"/>
+      <c r="U138" s="7" t="n"/>
+      <c r="V138" s="7" t="n"/>
       <c r="Y138" s="7" t="n"/>
+      <c r="AB138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="C139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
       <c r="G139" s="7" t="n"/>
-      <c r="L139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
       <c r="M139" s="7" t="n"/>
-      <c r="S139" s="7" t="n"/>
-      <c r="T139" s="7" t="n"/>
+      <c r="N139" s="7" t="n"/>
+      <c r="Q139" s="7" t="n"/>
+      <c r="U139" s="7" t="n"/>
+      <c r="V139" s="7" t="n"/>
       <c r="Y139" s="7" t="n"/>
+      <c r="AB139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="C140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
       <c r="G140" s="7" t="n"/>
-      <c r="L140" s="7" t="n"/>
+      <c r="I140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
-      <c r="S140" s="7" t="n"/>
-      <c r="T140" s="7" t="n"/>
+      <c r="N140" s="7" t="n"/>
+      <c r="Q140" s="7" t="n"/>
+      <c r="U140" s="7" t="n"/>
+      <c r="V140" s="7" t="n"/>
       <c r="Y140" s="7" t="n"/>
+      <c r="AB140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="C141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
       <c r="G141" s="7" t="n"/>
-      <c r="L141" s="7" t="n"/>
+      <c r="I141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
-      <c r="S141" s="7" t="n"/>
-      <c r="T141" s="7" t="n"/>
+      <c r="N141" s="7" t="n"/>
+      <c r="Q141" s="7" t="n"/>
+      <c r="U141" s="7" t="n"/>
+      <c r="V141" s="7" t="n"/>
       <c r="Y141" s="7" t="n"/>
+      <c r="AB141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="C142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
       <c r="G142" s="7" t="n"/>
-      <c r="L142" s="7" t="n"/>
+      <c r="I142" s="7" t="n"/>
       <c r="M142" s="7" t="n"/>
-      <c r="S142" s="7" t="n"/>
-      <c r="T142" s="7" t="n"/>
+      <c r="N142" s="7" t="n"/>
+      <c r="Q142" s="7" t="n"/>
+      <c r="U142" s="7" t="n"/>
+      <c r="V142" s="7" t="n"/>
       <c r="Y142" s="7" t="n"/>
+      <c r="AB142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="C143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
       <c r="G143" s="7" t="n"/>
-      <c r="L143" s="7" t="n"/>
+      <c r="I143" s="7" t="n"/>
       <c r="M143" s="7" t="n"/>
-      <c r="S143" s="7" t="n"/>
-      <c r="T143" s="7" t="n"/>
+      <c r="N143" s="7" t="n"/>
+      <c r="Q143" s="7" t="n"/>
+      <c r="U143" s="7" t="n"/>
+      <c r="V143" s="7" t="n"/>
       <c r="Y143" s="7" t="n"/>
+      <c r="AB143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="C144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
       <c r="G144" s="7" t="n"/>
-      <c r="L144" s="7" t="n"/>
+      <c r="I144" s="7" t="n"/>
       <c r="M144" s="7" t="n"/>
-      <c r="S144" s="7" t="n"/>
-      <c r="T144" s="7" t="n"/>
+      <c r="N144" s="7" t="n"/>
+      <c r="Q144" s="7" t="n"/>
+      <c r="U144" s="7" t="n"/>
+      <c r="V144" s="7" t="n"/>
       <c r="Y144" s="7" t="n"/>
+      <c r="AB144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="C145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
       <c r="G145" s="7" t="n"/>
-      <c r="L145" s="7" t="n"/>
+      <c r="I145" s="7" t="n"/>
       <c r="M145" s="7" t="n"/>
-      <c r="S145" s="7" t="n"/>
-      <c r="T145" s="7" t="n"/>
+      <c r="N145" s="7" t="n"/>
+      <c r="Q145" s="7" t="n"/>
+      <c r="U145" s="7" t="n"/>
+      <c r="V145" s="7" t="n"/>
       <c r="Y145" s="7" t="n"/>
+      <c r="AB145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="C146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
       <c r="G146" s="7" t="n"/>
-      <c r="L146" s="7" t="n"/>
+      <c r="I146" s="7" t="n"/>
       <c r="M146" s="7" t="n"/>
-      <c r="S146" s="7" t="n"/>
-      <c r="T146" s="7" t="n"/>
+      <c r="N146" s="7" t="n"/>
+      <c r="Q146" s="7" t="n"/>
+      <c r="U146" s="7" t="n"/>
+      <c r="V146" s="7" t="n"/>
       <c r="Y146" s="7" t="n"/>
+      <c r="AB146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="C147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
       <c r="G147" s="7" t="n"/>
-      <c r="L147" s="7" t="n"/>
+      <c r="I147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
-      <c r="S147" s="7" t="n"/>
-      <c r="T147" s="7" t="n"/>
+      <c r="N147" s="7" t="n"/>
+      <c r="Q147" s="7" t="n"/>
+      <c r="U147" s="7" t="n"/>
+      <c r="V147" s="7" t="n"/>
       <c r="Y147" s="7" t="n"/>
+      <c r="AB147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="C148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
       <c r="G148" s="7" t="n"/>
-      <c r="L148" s="7" t="n"/>
+      <c r="I148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
-      <c r="S148" s="7" t="n"/>
-      <c r="T148" s="7" t="n"/>
+      <c r="N148" s="7" t="n"/>
+      <c r="Q148" s="7" t="n"/>
+      <c r="U148" s="7" t="n"/>
+      <c r="V148" s="7" t="n"/>
       <c r="Y148" s="7" t="n"/>
+      <c r="AB148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="C149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
       <c r="G149" s="7" t="n"/>
-      <c r="L149" s="7" t="n"/>
+      <c r="I149" s="7" t="n"/>
       <c r="M149" s="7" t="n"/>
-      <c r="S149" s="7" t="n"/>
-      <c r="T149" s="7" t="n"/>
+      <c r="N149" s="7" t="n"/>
+      <c r="Q149" s="7" t="n"/>
+      <c r="U149" s="7" t="n"/>
+      <c r="V149" s="7" t="n"/>
       <c r="Y149" s="7" t="n"/>
+      <c r="AB149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="C150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
       <c r="G150" s="7" t="n"/>
-      <c r="L150" s="7" t="n"/>
+      <c r="I150" s="7" t="n"/>
       <c r="M150" s="7" t="n"/>
-      <c r="S150" s="7" t="n"/>
-      <c r="T150" s="7" t="n"/>
+      <c r="N150" s="7" t="n"/>
+      <c r="Q150" s="7" t="n"/>
+      <c r="U150" s="7" t="n"/>
+      <c r="V150" s="7" t="n"/>
       <c r="Y150" s="7" t="n"/>
+      <c r="AB150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="C151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
       <c r="G151" s="7" t="n"/>
-      <c r="L151" s="7" t="n"/>
+      <c r="I151" s="7" t="n"/>
       <c r="M151" s="7" t="n"/>
-      <c r="S151" s="7" t="n"/>
-      <c r="T151" s="7" t="n"/>
+      <c r="N151" s="7" t="n"/>
+      <c r="Q151" s="7" t="n"/>
+      <c r="U151" s="7" t="n"/>
+      <c r="V151" s="7" t="n"/>
       <c r="Y151" s="7" t="n"/>
+      <c r="AB151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="C152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
       <c r="G152" s="7" t="n"/>
-      <c r="L152" s="7" t="n"/>
+      <c r="I152" s="7" t="n"/>
       <c r="M152" s="7" t="n"/>
-      <c r="S152" s="7" t="n"/>
-      <c r="T152" s="7" t="n"/>
+      <c r="N152" s="7" t="n"/>
+      <c r="Q152" s="7" t="n"/>
+      <c r="U152" s="7" t="n"/>
+      <c r="V152" s="7" t="n"/>
       <c r="Y152" s="7" t="n"/>
+      <c r="AB152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="C153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
       <c r="G153" s="7" t="n"/>
-      <c r="L153" s="7" t="n"/>
+      <c r="I153" s="7" t="n"/>
       <c r="M153" s="7" t="n"/>
-      <c r="S153" s="7" t="n"/>
-      <c r="T153" s="7" t="n"/>
+      <c r="N153" s="7" t="n"/>
+      <c r="Q153" s="7" t="n"/>
+      <c r="U153" s="7" t="n"/>
+      <c r="V153" s="7" t="n"/>
       <c r="Y153" s="7" t="n"/>
+      <c r="AB153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="C154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
       <c r="G154" s="7" t="n"/>
-      <c r="L154" s="7" t="n"/>
+      <c r="I154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
-      <c r="S154" s="7" t="n"/>
-      <c r="T154" s="7" t="n"/>
+      <c r="N154" s="7" t="n"/>
+      <c r="Q154" s="7" t="n"/>
+      <c r="U154" s="7" t="n"/>
+      <c r="V154" s="7" t="n"/>
       <c r="Y154" s="7" t="n"/>
+      <c r="AB154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="C155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
       <c r="G155" s="7" t="n"/>
-      <c r="L155" s="7" t="n"/>
+      <c r="I155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
-      <c r="S155" s="7" t="n"/>
-      <c r="T155" s="7" t="n"/>
+      <c r="N155" s="7" t="n"/>
+      <c r="Q155" s="7" t="n"/>
+      <c r="U155" s="7" t="n"/>
+      <c r="V155" s="7" t="n"/>
       <c r="Y155" s="7" t="n"/>
+      <c r="AB155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="C156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
       <c r="G156" s="7" t="n"/>
-      <c r="L156" s="7" t="n"/>
+      <c r="I156" s="7" t="n"/>
       <c r="M156" s="7" t="n"/>
-      <c r="S156" s="7" t="n"/>
-      <c r="T156" s="7" t="n"/>
+      <c r="N156" s="7" t="n"/>
+      <c r="Q156" s="7" t="n"/>
+      <c r="U156" s="7" t="n"/>
+      <c r="V156" s="7" t="n"/>
       <c r="Y156" s="7" t="n"/>
+      <c r="AB156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="C157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
       <c r="G157" s="7" t="n"/>
-      <c r="L157" s="7" t="n"/>
+      <c r="I157" s="7" t="n"/>
       <c r="M157" s="7" t="n"/>
-      <c r="S157" s="7" t="n"/>
-      <c r="T157" s="7" t="n"/>
+      <c r="N157" s="7" t="n"/>
+      <c r="Q157" s="7" t="n"/>
+      <c r="U157" s="7" t="n"/>
+      <c r="V157" s="7" t="n"/>
       <c r="Y157" s="7" t="n"/>
+      <c r="AB157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="C158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
       <c r="G158" s="7" t="n"/>
-      <c r="L158" s="7" t="n"/>
+      <c r="I158" s="7" t="n"/>
       <c r="M158" s="7" t="n"/>
-      <c r="S158" s="7" t="n"/>
-      <c r="T158" s="7" t="n"/>
+      <c r="N158" s="7" t="n"/>
+      <c r="Q158" s="7" t="n"/>
+      <c r="U158" s="7" t="n"/>
+      <c r="V158" s="7" t="n"/>
       <c r="Y158" s="7" t="n"/>
+      <c r="AB158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="C159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
       <c r="G159" s="7" t="n"/>
-      <c r="L159" s="7" t="n"/>
+      <c r="I159" s="7" t="n"/>
       <c r="M159" s="7" t="n"/>
-      <c r="S159" s="7" t="n"/>
-      <c r="T159" s="7" t="n"/>
+      <c r="N159" s="7" t="n"/>
+      <c r="Q159" s="7" t="n"/>
+      <c r="U159" s="7" t="n"/>
+      <c r="V159" s="7" t="n"/>
       <c r="Y159" s="7" t="n"/>
+      <c r="AB159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="C160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
       <c r="G160" s="7" t="n"/>
-      <c r="L160" s="7" t="n"/>
+      <c r="I160" s="7" t="n"/>
       <c r="M160" s="7" t="n"/>
-      <c r="S160" s="7" t="n"/>
-      <c r="T160" s="7" t="n"/>
+      <c r="N160" s="7" t="n"/>
+      <c r="Q160" s="7" t="n"/>
+      <c r="U160" s="7" t="n"/>
+      <c r="V160" s="7" t="n"/>
       <c r="Y160" s="7" t="n"/>
+      <c r="AB160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="C161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
       <c r="G161" s="7" t="n"/>
-      <c r="L161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
-      <c r="S161" s="7" t="n"/>
-      <c r="T161" s="7" t="n"/>
+      <c r="N161" s="7" t="n"/>
+      <c r="Q161" s="7" t="n"/>
+      <c r="U161" s="7" t="n"/>
+      <c r="V161" s="7" t="n"/>
       <c r="Y161" s="7" t="n"/>
+      <c r="AB161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="C162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
       <c r="G162" s="7" t="n"/>
-      <c r="L162" s="7" t="n"/>
+      <c r="I162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
-      <c r="S162" s="7" t="n"/>
-      <c r="T162" s="7" t="n"/>
+      <c r="N162" s="7" t="n"/>
+      <c r="Q162" s="7" t="n"/>
+      <c r="U162" s="7" t="n"/>
+      <c r="V162" s="7" t="n"/>
       <c r="Y162" s="7" t="n"/>
+      <c r="AB162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="C163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
       <c r="G163" s="7" t="n"/>
-      <c r="L163" s="7" t="n"/>
+      <c r="I163" s="7" t="n"/>
       <c r="M163" s="7" t="n"/>
-      <c r="S163" s="7" t="n"/>
-      <c r="T163" s="7" t="n"/>
+      <c r="N163" s="7" t="n"/>
+      <c r="Q163" s="7" t="n"/>
+      <c r="U163" s="7" t="n"/>
+      <c r="V163" s="7" t="n"/>
       <c r="Y163" s="7" t="n"/>
+      <c r="AB163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="C164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
       <c r="G164" s="7" t="n"/>
-      <c r="L164" s="7" t="n"/>
+      <c r="I164" s="7" t="n"/>
       <c r="M164" s="7" t="n"/>
-      <c r="S164" s="7" t="n"/>
-      <c r="T164" s="7" t="n"/>
+      <c r="N164" s="7" t="n"/>
+      <c r="Q164" s="7" t="n"/>
+      <c r="U164" s="7" t="n"/>
+      <c r="V164" s="7" t="n"/>
       <c r="Y164" s="7" t="n"/>
+      <c r="AB164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="C165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
       <c r="G165" s="7" t="n"/>
-      <c r="L165" s="7" t="n"/>
+      <c r="I165" s="7" t="n"/>
       <c r="M165" s="7" t="n"/>
-      <c r="S165" s="7" t="n"/>
-      <c r="T165" s="7" t="n"/>
+      <c r="N165" s="7" t="n"/>
+      <c r="Q165" s="7" t="n"/>
+      <c r="U165" s="7" t="n"/>
+      <c r="V165" s="7" t="n"/>
       <c r="Y165" s="7" t="n"/>
+      <c r="AB165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="C166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
       <c r="G166" s="7" t="n"/>
-      <c r="L166" s="7" t="n"/>
+      <c r="I166" s="7" t="n"/>
       <c r="M166" s="7" t="n"/>
-      <c r="S166" s="7" t="n"/>
-      <c r="T166" s="7" t="n"/>
+      <c r="N166" s="7" t="n"/>
+      <c r="Q166" s="7" t="n"/>
+      <c r="U166" s="7" t="n"/>
+      <c r="V166" s="7" t="n"/>
       <c r="Y166" s="7" t="n"/>
+      <c r="AB166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="C167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
       <c r="G167" s="7" t="n"/>
-      <c r="L167" s="7" t="n"/>
+      <c r="I167" s="7" t="n"/>
       <c r="M167" s="7" t="n"/>
-      <c r="S167" s="7" t="n"/>
-      <c r="T167" s="7" t="n"/>
+      <c r="N167" s="7" t="n"/>
+      <c r="Q167" s="7" t="n"/>
+      <c r="U167" s="7" t="n"/>
+      <c r="V167" s="7" t="n"/>
       <c r="Y167" s="7" t="n"/>
+      <c r="AB167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="C168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
       <c r="G168" s="7" t="n"/>
-      <c r="L168" s="7" t="n"/>
+      <c r="I168" s="7" t="n"/>
       <c r="M168" s="7" t="n"/>
-      <c r="S168" s="7" t="n"/>
-      <c r="T168" s="7" t="n"/>
+      <c r="N168" s="7" t="n"/>
+      <c r="Q168" s="7" t="n"/>
+      <c r="U168" s="7" t="n"/>
+      <c r="V168" s="7" t="n"/>
       <c r="Y168" s="7" t="n"/>
+      <c r="AB168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="C169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
       <c r="G169" s="7" t="n"/>
-      <c r="L169" s="7" t="n"/>
+      <c r="I169" s="7" t="n"/>
       <c r="M169" s="7" t="n"/>
-      <c r="S169" s="7" t="n"/>
-      <c r="T169" s="7" t="n"/>
+      <c r="N169" s="7" t="n"/>
+      <c r="Q169" s="7" t="n"/>
+      <c r="U169" s="7" t="n"/>
+      <c r="V169" s="7" t="n"/>
       <c r="Y169" s="7" t="n"/>
+      <c r="AB169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="C170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
       <c r="G170" s="7" t="n"/>
-      <c r="L170" s="7" t="n"/>
+      <c r="I170" s="7" t="n"/>
       <c r="M170" s="7" t="n"/>
-      <c r="S170" s="7" t="n"/>
-      <c r="T170" s="7" t="n"/>
+      <c r="N170" s="7" t="n"/>
+      <c r="Q170" s="7" t="n"/>
+      <c r="U170" s="7" t="n"/>
+      <c r="V170" s="7" t="n"/>
       <c r="Y170" s="7" t="n"/>
+      <c r="AB170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="C171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
       <c r="G171" s="7" t="n"/>
-      <c r="L171" s="7" t="n"/>
+      <c r="I171" s="7" t="n"/>
       <c r="M171" s="7" t="n"/>
-      <c r="S171" s="7" t="n"/>
-      <c r="T171" s="7" t="n"/>
+      <c r="N171" s="7" t="n"/>
+      <c r="Q171" s="7" t="n"/>
+      <c r="U171" s="7" t="n"/>
+      <c r="V171" s="7" t="n"/>
       <c r="Y171" s="7" t="n"/>
+      <c r="AB171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="C172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
       <c r="G172" s="7" t="n"/>
-      <c r="L172" s="7" t="n"/>
+      <c r="I172" s="7" t="n"/>
       <c r="M172" s="7" t="n"/>
-      <c r="S172" s="7" t="n"/>
-      <c r="T172" s="7" t="n"/>
+      <c r="N172" s="7" t="n"/>
+      <c r="Q172" s="7" t="n"/>
+      <c r="U172" s="7" t="n"/>
+      <c r="V172" s="7" t="n"/>
       <c r="Y172" s="7" t="n"/>
+      <c r="AB172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="C173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
       <c r="G173" s="7" t="n"/>
-      <c r="L173" s="7" t="n"/>
+      <c r="I173" s="7" t="n"/>
       <c r="M173" s="7" t="n"/>
-      <c r="S173" s="7" t="n"/>
-      <c r="T173" s="7" t="n"/>
+      <c r="N173" s="7" t="n"/>
+      <c r="Q173" s="7" t="n"/>
+      <c r="U173" s="7" t="n"/>
+      <c r="V173" s="7" t="n"/>
       <c r="Y173" s="7" t="n"/>
+      <c r="AB173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="C174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
       <c r="G174" s="7" t="n"/>
-      <c r="L174" s="7" t="n"/>
+      <c r="I174" s="7" t="n"/>
       <c r="M174" s="7" t="n"/>
-      <c r="S174" s="7" t="n"/>
-      <c r="T174" s="7" t="n"/>
+      <c r="N174" s="7" t="n"/>
+      <c r="Q174" s="7" t="n"/>
+      <c r="U174" s="7" t="n"/>
+      <c r="V174" s="7" t="n"/>
       <c r="Y174" s="7" t="n"/>
+      <c r="AB174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="C175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
       <c r="G175" s="7" t="n"/>
-      <c r="L175" s="7" t="n"/>
+      <c r="I175" s="7" t="n"/>
       <c r="M175" s="7" t="n"/>
-      <c r="S175" s="7" t="n"/>
-      <c r="T175" s="7" t="n"/>
+      <c r="N175" s="7" t="n"/>
+      <c r="Q175" s="7" t="n"/>
+      <c r="U175" s="7" t="n"/>
+      <c r="V175" s="7" t="n"/>
       <c r="Y175" s="7" t="n"/>
+      <c r="AB175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="C176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
       <c r="G176" s="7" t="n"/>
-      <c r="L176" s="7" t="n"/>
+      <c r="I176" s="7" t="n"/>
       <c r="M176" s="7" t="n"/>
-      <c r="S176" s="7" t="n"/>
-      <c r="T176" s="7" t="n"/>
+      <c r="N176" s="7" t="n"/>
+      <c r="Q176" s="7" t="n"/>
+      <c r="U176" s="7" t="n"/>
+      <c r="V176" s="7" t="n"/>
       <c r="Y176" s="7" t="n"/>
+      <c r="AB176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="C177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
       <c r="G177" s="7" t="n"/>
-      <c r="L177" s="7" t="n"/>
+      <c r="I177" s="7" t="n"/>
       <c r="M177" s="7" t="n"/>
-      <c r="S177" s="7" t="n"/>
-      <c r="T177" s="7" t="n"/>
+      <c r="N177" s="7" t="n"/>
+      <c r="Q177" s="7" t="n"/>
+      <c r="U177" s="7" t="n"/>
+      <c r="V177" s="7" t="n"/>
       <c r="Y177" s="7" t="n"/>
+      <c r="AB177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="C178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
       <c r="G178" s="7" t="n"/>
-      <c r="L178" s="7" t="n"/>
+      <c r="I178" s="7" t="n"/>
       <c r="M178" s="7" t="n"/>
-      <c r="S178" s="7" t="n"/>
-      <c r="T178" s="7" t="n"/>
+      <c r="N178" s="7" t="n"/>
+      <c r="Q178" s="7" t="n"/>
+      <c r="U178" s="7" t="n"/>
+      <c r="V178" s="7" t="n"/>
       <c r="Y178" s="7" t="n"/>
+      <c r="AB178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="C179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
       <c r="G179" s="7" t="n"/>
-      <c r="L179" s="7" t="n"/>
+      <c r="I179" s="7" t="n"/>
       <c r="M179" s="7" t="n"/>
-      <c r="S179" s="7" t="n"/>
-      <c r="T179" s="7" t="n"/>
+      <c r="N179" s="7" t="n"/>
+      <c r="Q179" s="7" t="n"/>
+      <c r="U179" s="7" t="n"/>
+      <c r="V179" s="7" t="n"/>
       <c r="Y179" s="7" t="n"/>
+      <c r="AB179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="C180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
       <c r="G180" s="7" t="n"/>
-      <c r="L180" s="7" t="n"/>
+      <c r="I180" s="7" t="n"/>
       <c r="M180" s="7" t="n"/>
-      <c r="S180" s="7" t="n"/>
-      <c r="T180" s="7" t="n"/>
+      <c r="N180" s="7" t="n"/>
+      <c r="Q180" s="7" t="n"/>
+      <c r="U180" s="7" t="n"/>
+      <c r="V180" s="7" t="n"/>
       <c r="Y180" s="7" t="n"/>
+      <c r="AB180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="C181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
       <c r="G181" s="7" t="n"/>
-      <c r="L181" s="7" t="n"/>
+      <c r="I181" s="7" t="n"/>
       <c r="M181" s="7" t="n"/>
-      <c r="S181" s="7" t="n"/>
-      <c r="T181" s="7" t="n"/>
+      <c r="N181" s="7" t="n"/>
+      <c r="Q181" s="7" t="n"/>
+      <c r="U181" s="7" t="n"/>
+      <c r="V181" s="7" t="n"/>
       <c r="Y181" s="7" t="n"/>
+      <c r="AB181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="C182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
       <c r="G182" s="7" t="n"/>
-      <c r="L182" s="7" t="n"/>
+      <c r="I182" s="7" t="n"/>
       <c r="M182" s="7" t="n"/>
-      <c r="S182" s="7" t="n"/>
-      <c r="T182" s="7" t="n"/>
+      <c r="N182" s="7" t="n"/>
+      <c r="Q182" s="7" t="n"/>
+      <c r="U182" s="7" t="n"/>
+      <c r="V182" s="7" t="n"/>
       <c r="Y182" s="7" t="n"/>
+      <c r="AB182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="C183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
       <c r="G183" s="7" t="n"/>
-      <c r="L183" s="7" t="n"/>
+      <c r="I183" s="7" t="n"/>
       <c r="M183" s="7" t="n"/>
-      <c r="S183" s="7" t="n"/>
-      <c r="T183" s="7" t="n"/>
+      <c r="N183" s="7" t="n"/>
+      <c r="Q183" s="7" t="n"/>
+      <c r="U183" s="7" t="n"/>
+      <c r="V183" s="7" t="n"/>
       <c r="Y183" s="7" t="n"/>
+      <c r="AB183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="C184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
       <c r="G184" s="7" t="n"/>
-      <c r="L184" s="7" t="n"/>
+      <c r="I184" s="7" t="n"/>
       <c r="M184" s="7" t="n"/>
-      <c r="S184" s="7" t="n"/>
-      <c r="T184" s="7" t="n"/>
+      <c r="N184" s="7" t="n"/>
+      <c r="Q184" s="7" t="n"/>
+      <c r="U184" s="7" t="n"/>
+      <c r="V184" s="7" t="n"/>
       <c r="Y184" s="7" t="n"/>
+      <c r="AB184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="C185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
       <c r="G185" s="7" t="n"/>
-      <c r="L185" s="7" t="n"/>
+      <c r="I185" s="7" t="n"/>
       <c r="M185" s="7" t="n"/>
-      <c r="S185" s="7" t="n"/>
-      <c r="T185" s="7" t="n"/>
+      <c r="N185" s="7" t="n"/>
+      <c r="Q185" s="7" t="n"/>
+      <c r="U185" s="7" t="n"/>
+      <c r="V185" s="7" t="n"/>
       <c r="Y185" s="7" t="n"/>
+      <c r="AB185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="C186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
       <c r="G186" s="7" t="n"/>
-      <c r="L186" s="7" t="n"/>
+      <c r="I186" s="7" t="n"/>
       <c r="M186" s="7" t="n"/>
-      <c r="S186" s="7" t="n"/>
-      <c r="T186" s="7" t="n"/>
+      <c r="N186" s="7" t="n"/>
+      <c r="Q186" s="7" t="n"/>
+      <c r="U186" s="7" t="n"/>
+      <c r="V186" s="7" t="n"/>
       <c r="Y186" s="7" t="n"/>
+      <c r="AB186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="C187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
       <c r="G187" s="7" t="n"/>
-      <c r="L187" s="7" t="n"/>
+      <c r="I187" s="7" t="n"/>
       <c r="M187" s="7" t="n"/>
-      <c r="S187" s="7" t="n"/>
-      <c r="T187" s="7" t="n"/>
+      <c r="N187" s="7" t="n"/>
+      <c r="Q187" s="7" t="n"/>
+      <c r="U187" s="7" t="n"/>
+      <c r="V187" s="7" t="n"/>
       <c r="Y187" s="7" t="n"/>
+      <c r="AB187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="C188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
       <c r="G188" s="7" t="n"/>
-      <c r="L188" s="7" t="n"/>
+      <c r="I188" s="7" t="n"/>
       <c r="M188" s="7" t="n"/>
-      <c r="S188" s="7" t="n"/>
-      <c r="T188" s="7" t="n"/>
+      <c r="N188" s="7" t="n"/>
+      <c r="Q188" s="7" t="n"/>
+      <c r="U188" s="7" t="n"/>
+      <c r="V188" s="7" t="n"/>
       <c r="Y188" s="7" t="n"/>
+      <c r="AB188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="C189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
       <c r="G189" s="7" t="n"/>
-      <c r="L189" s="7" t="n"/>
+      <c r="I189" s="7" t="n"/>
       <c r="M189" s="7" t="n"/>
-      <c r="S189" s="7" t="n"/>
-      <c r="T189" s="7" t="n"/>
+      <c r="N189" s="7" t="n"/>
+      <c r="Q189" s="7" t="n"/>
+      <c r="U189" s="7" t="n"/>
+      <c r="V189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
+      <c r="AB189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="C190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
       <c r="G190" s="7" t="n"/>
-      <c r="L190" s="7" t="n"/>
+      <c r="I190" s="7" t="n"/>
       <c r="M190" s="7" t="n"/>
-      <c r="S190" s="7" t="n"/>
-      <c r="T190" s="7" t="n"/>
+      <c r="N190" s="7" t="n"/>
+      <c r="Q190" s="7" t="n"/>
+      <c r="U190" s="7" t="n"/>
+      <c r="V190" s="7" t="n"/>
       <c r="Y190" s="7" t="n"/>
+      <c r="AB190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="C191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
       <c r="G191" s="7" t="n"/>
-      <c r="L191" s="7" t="n"/>
+      <c r="I191" s="7" t="n"/>
       <c r="M191" s="7" t="n"/>
-      <c r="S191" s="7" t="n"/>
-      <c r="T191" s="7" t="n"/>
+      <c r="N191" s="7" t="n"/>
+      <c r="Q191" s="7" t="n"/>
+      <c r="U191" s="7" t="n"/>
+      <c r="V191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
+      <c r="AB191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="C192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
       <c r="G192" s="7" t="n"/>
-      <c r="L192" s="7" t="n"/>
+      <c r="I192" s="7" t="n"/>
       <c r="M192" s="7" t="n"/>
-      <c r="S192" s="7" t="n"/>
-      <c r="T192" s="7" t="n"/>
+      <c r="N192" s="7" t="n"/>
+      <c r="Q192" s="7" t="n"/>
+      <c r="U192" s="7" t="n"/>
+      <c r="V192" s="7" t="n"/>
       <c r="Y192" s="7" t="n"/>
+      <c r="AB192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="C193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
       <c r="G193" s="7" t="n"/>
-      <c r="L193" s="7" t="n"/>
+      <c r="I193" s="7" t="n"/>
       <c r="M193" s="7" t="n"/>
-      <c r="S193" s="7" t="n"/>
-      <c r="T193" s="7" t="n"/>
+      <c r="N193" s="7" t="n"/>
+      <c r="Q193" s="7" t="n"/>
+      <c r="U193" s="7" t="n"/>
+      <c r="V193" s="7" t="n"/>
       <c r="Y193" s="7" t="n"/>
+      <c r="AB193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="C194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
       <c r="G194" s="7" t="n"/>
-      <c r="L194" s="7" t="n"/>
+      <c r="I194" s="7" t="n"/>
       <c r="M194" s="7" t="n"/>
-      <c r="S194" s="7" t="n"/>
-      <c r="T194" s="7" t="n"/>
+      <c r="N194" s="7" t="n"/>
+      <c r="Q194" s="7" t="n"/>
+      <c r="U194" s="7" t="n"/>
+      <c r="V194" s="7" t="n"/>
       <c r="Y194" s="7" t="n"/>
+      <c r="AB194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="C195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
       <c r="G195" s="7" t="n"/>
-      <c r="L195" s="7" t="n"/>
+      <c r="I195" s="7" t="n"/>
       <c r="M195" s="7" t="n"/>
-      <c r="S195" s="7" t="n"/>
-      <c r="T195" s="7" t="n"/>
+      <c r="N195" s="7" t="n"/>
+      <c r="Q195" s="7" t="n"/>
+      <c r="U195" s="7" t="n"/>
+      <c r="V195" s="7" t="n"/>
       <c r="Y195" s="7" t="n"/>
+      <c r="AB195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="C196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
       <c r="G196" s="7" t="n"/>
-      <c r="L196" s="7" t="n"/>
+      <c r="I196" s="7" t="n"/>
       <c r="M196" s="7" t="n"/>
-      <c r="S196" s="7" t="n"/>
-      <c r="T196" s="7" t="n"/>
+      <c r="N196" s="7" t="n"/>
+      <c r="Q196" s="7" t="n"/>
+      <c r="U196" s="7" t="n"/>
+      <c r="V196" s="7" t="n"/>
       <c r="Y196" s="7" t="n"/>
+      <c r="AB196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="C197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
       <c r="G197" s="7" t="n"/>
-      <c r="L197" s="7" t="n"/>
+      <c r="I197" s="7" t="n"/>
       <c r="M197" s="7" t="n"/>
-      <c r="S197" s="7" t="n"/>
-      <c r="T197" s="7" t="n"/>
+      <c r="N197" s="7" t="n"/>
+      <c r="Q197" s="7" t="n"/>
+      <c r="U197" s="7" t="n"/>
+      <c r="V197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
+      <c r="AB197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="C198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
       <c r="G198" s="7" t="n"/>
-      <c r="L198" s="7" t="n"/>
+      <c r="I198" s="7" t="n"/>
       <c r="M198" s="7" t="n"/>
-      <c r="S198" s="7" t="n"/>
-      <c r="T198" s="7" t="n"/>
+      <c r="N198" s="7" t="n"/>
+      <c r="Q198" s="7" t="n"/>
+      <c r="U198" s="7" t="n"/>
+      <c r="V198" s="7" t="n"/>
       <c r="Y198" s="7" t="n"/>
+      <c r="AB198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="C199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
       <c r="G199" s="7" t="n"/>
-      <c r="L199" s="7" t="n"/>
+      <c r="I199" s="7" t="n"/>
       <c r="M199" s="7" t="n"/>
-      <c r="S199" s="7" t="n"/>
-      <c r="T199" s="7" t="n"/>
+      <c r="N199" s="7" t="n"/>
+      <c r="Q199" s="7" t="n"/>
+      <c r="U199" s="7" t="n"/>
+      <c r="V199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
+      <c r="AB199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="C200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
       <c r="G200" s="7" t="n"/>
-      <c r="L200" s="7" t="n"/>
+      <c r="I200" s="7" t="n"/>
       <c r="M200" s="7" t="n"/>
-      <c r="S200" s="7" t="n"/>
-      <c r="T200" s="7" t="n"/>
+      <c r="N200" s="7" t="n"/>
+      <c r="Q200" s="7" t="n"/>
+      <c r="U200" s="7" t="n"/>
+      <c r="V200" s="7" t="n"/>
       <c r="Y200" s="7" t="n"/>
+      <c r="AB200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="C201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
       <c r="G201" s="7" t="n"/>
-      <c r="L201" s="7" t="n"/>
+      <c r="I201" s="7" t="n"/>
       <c r="M201" s="7" t="n"/>
-      <c r="S201" s="7" t="n"/>
-      <c r="T201" s="7" t="n"/>
+      <c r="N201" s="7" t="n"/>
+      <c r="Q201" s="7" t="n"/>
+      <c r="U201" s="7" t="n"/>
+      <c r="V201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
+      <c r="AB201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="C202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
       <c r="G202" s="7" t="n"/>
-      <c r="L202" s="7" t="n"/>
+      <c r="I202" s="7" t="n"/>
       <c r="M202" s="7" t="n"/>
-      <c r="S202" s="7" t="n"/>
-      <c r="T202" s="7" t="n"/>
+      <c r="N202" s="7" t="n"/>
+      <c r="Q202" s="7" t="n"/>
+      <c r="U202" s="7" t="n"/>
+      <c r="V202" s="7" t="n"/>
       <c r="Y202" s="7" t="n"/>
+      <c r="AB202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="C203" s="7" t="n"/>
       <c r="E203" s="7" t="n"/>
       <c r="G203" s="7" t="n"/>
-      <c r="L203" s="7" t="n"/>
+      <c r="I203" s="7" t="n"/>
       <c r="M203" s="7" t="n"/>
-      <c r="S203" s="7" t="n"/>
-      <c r="T203" s="7" t="n"/>
+      <c r="N203" s="7" t="n"/>
+      <c r="Q203" s="7" t="n"/>
+      <c r="U203" s="7" t="n"/>
+      <c r="V203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
+      <c r="AB203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="C204" s="7" t="n"/>
       <c r="E204" s="7" t="n"/>
       <c r="G204" s="7" t="n"/>
-      <c r="L204" s="7" t="n"/>
+      <c r="I204" s="7" t="n"/>
       <c r="M204" s="7" t="n"/>
-      <c r="S204" s="7" t="n"/>
-      <c r="T204" s="7" t="n"/>
+      <c r="N204" s="7" t="n"/>
+      <c r="Q204" s="7" t="n"/>
+      <c r="U204" s="7" t="n"/>
+      <c r="V204" s="7" t="n"/>
       <c r="Y204" s="7" t="n"/>
+      <c r="AB204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="C205" s="7" t="n"/>
       <c r="E205" s="7" t="n"/>
       <c r="G205" s="7" t="n"/>
-      <c r="L205" s="7" t="n"/>
+      <c r="I205" s="7" t="n"/>
       <c r="M205" s="7" t="n"/>
-      <c r="S205" s="7" t="n"/>
-      <c r="T205" s="7" t="n"/>
+      <c r="N205" s="7" t="n"/>
+      <c r="Q205" s="7" t="n"/>
+      <c r="U205" s="7" t="n"/>
+      <c r="V205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
+      <c r="AB205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="C206" s="7" t="n"/>
       <c r="E206" s="7" t="n"/>
       <c r="G206" s="7" t="n"/>
-      <c r="L206" s="7" t="n"/>
+      <c r="I206" s="7" t="n"/>
       <c r="M206" s="7" t="n"/>
-      <c r="S206" s="7" t="n"/>
-      <c r="T206" s="7" t="n"/>
+      <c r="N206" s="7" t="n"/>
+      <c r="Q206" s="7" t="n"/>
+      <c r="U206" s="7" t="n"/>
+      <c r="V206" s="7" t="n"/>
       <c r="Y206" s="7" t="n"/>
+      <c r="AB206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="C207" s="7" t="n"/>
       <c r="E207" s="7" t="n"/>
       <c r="G207" s="7" t="n"/>
-      <c r="L207" s="7" t="n"/>
+      <c r="I207" s="7" t="n"/>
       <c r="M207" s="7" t="n"/>
-      <c r="S207" s="7" t="n"/>
-      <c r="T207" s="7" t="n"/>
+      <c r="N207" s="7" t="n"/>
+      <c r="Q207" s="7" t="n"/>
+      <c r="U207" s="7" t="n"/>
+      <c r="V207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
+      <c r="AB207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="C208" s="7" t="n"/>
       <c r="E208" s="7" t="n"/>
       <c r="G208" s="7" t="n"/>
-      <c r="L208" s="7" t="n"/>
+      <c r="I208" s="7" t="n"/>
       <c r="M208" s="7" t="n"/>
-      <c r="S208" s="7" t="n"/>
-      <c r="T208" s="7" t="n"/>
+      <c r="N208" s="7" t="n"/>
+      <c r="Q208" s="7" t="n"/>
+      <c r="U208" s="7" t="n"/>
+      <c r="V208" s="7" t="n"/>
       <c r="Y208" s="7" t="n"/>
+      <c r="AB208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="C209" s="7" t="n"/>
       <c r="E209" s="7" t="n"/>
       <c r="G209" s="7" t="n"/>
-      <c r="L209" s="7" t="n"/>
+      <c r="I209" s="7" t="n"/>
       <c r="M209" s="7" t="n"/>
-      <c r="S209" s="7" t="n"/>
-      <c r="T209" s="7" t="n"/>
+      <c r="N209" s="7" t="n"/>
+      <c r="Q209" s="7" t="n"/>
+      <c r="U209" s="7" t="n"/>
+      <c r="V209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
+      <c r="AB209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="C210" s="7" t="n"/>
       <c r="E210" s="7" t="n"/>
       <c r="G210" s="7" t="n"/>
-      <c r="L210" s="7" t="n"/>
+      <c r="I210" s="7" t="n"/>
       <c r="M210" s="7" t="n"/>
-      <c r="S210" s="7" t="n"/>
-      <c r="T210" s="7" t="n"/>
+      <c r="N210" s="7" t="n"/>
+      <c r="Q210" s="7" t="n"/>
+      <c r="U210" s="7" t="n"/>
+      <c r="V210" s="7" t="n"/>
       <c r="Y210" s="7" t="n"/>
+      <c r="AB210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="C211" s="7" t="n"/>
       <c r="E211" s="7" t="n"/>
       <c r="G211" s="7" t="n"/>
-      <c r="L211" s="7" t="n"/>
+      <c r="I211" s="7" t="n"/>
       <c r="M211" s="7" t="n"/>
-      <c r="S211" s="7" t="n"/>
-      <c r="T211" s="7" t="n"/>
+      <c r="N211" s="7" t="n"/>
+      <c r="Q211" s="7" t="n"/>
+      <c r="U211" s="7" t="n"/>
+      <c r="V211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
+      <c r="AB211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="C212" s="7" t="n"/>
       <c r="E212" s="7" t="n"/>
       <c r="G212" s="7" t="n"/>
-      <c r="L212" s="7" t="n"/>
+      <c r="I212" s="7" t="n"/>
       <c r="M212" s="7" t="n"/>
-      <c r="S212" s="7" t="n"/>
-      <c r="T212" s="7" t="n"/>
+      <c r="N212" s="7" t="n"/>
+      <c r="Q212" s="7" t="n"/>
+      <c r="U212" s="7" t="n"/>
+      <c r="V212" s="7" t="n"/>
       <c r="Y212" s="7" t="n"/>
+      <c r="AB212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="C213" s="7" t="n"/>
       <c r="E213" s="7" t="n"/>
       <c r="G213" s="7" t="n"/>
-      <c r="L213" s="7" t="n"/>
+      <c r="I213" s="7" t="n"/>
       <c r="M213" s="7" t="n"/>
-      <c r="S213" s="7" t="n"/>
-      <c r="T213" s="7" t="n"/>
+      <c r="N213" s="7" t="n"/>
+      <c r="Q213" s="7" t="n"/>
+      <c r="U213" s="7" t="n"/>
+      <c r="V213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
+      <c r="AB213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="C214" s="7" t="n"/>
       <c r="E214" s="7" t="n"/>
       <c r="G214" s="7" t="n"/>
-      <c r="L214" s="7" t="n"/>
+      <c r="I214" s="7" t="n"/>
       <c r="M214" s="7" t="n"/>
-      <c r="S214" s="7" t="n"/>
-      <c r="T214" s="7" t="n"/>
+      <c r="N214" s="7" t="n"/>
+      <c r="Q214" s="7" t="n"/>
+      <c r="U214" s="7" t="n"/>
+      <c r="V214" s="7" t="n"/>
       <c r="Y214" s="7" t="n"/>
+      <c r="AB214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="C215" s="7" t="n"/>
       <c r="E215" s="7" t="n"/>
       <c r="G215" s="7" t="n"/>
-      <c r="L215" s="7" t="n"/>
+      <c r="I215" s="7" t="n"/>
       <c r="M215" s="7" t="n"/>
-      <c r="S215" s="7" t="n"/>
-      <c r="T215" s="7" t="n"/>
+      <c r="N215" s="7" t="n"/>
+      <c r="Q215" s="7" t="n"/>
+      <c r="U215" s="7" t="n"/>
+      <c r="V215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
+      <c r="AB215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="C216" s="7" t="n"/>
       <c r="E216" s="7" t="n"/>
       <c r="G216" s="7" t="n"/>
-      <c r="L216" s="7" t="n"/>
+      <c r="I216" s="7" t="n"/>
       <c r="M216" s="7" t="n"/>
-      <c r="S216" s="7" t="n"/>
-      <c r="T216" s="7" t="n"/>
+      <c r="N216" s="7" t="n"/>
+      <c r="Q216" s="7" t="n"/>
+      <c r="U216" s="7" t="n"/>
+      <c r="V216" s="7" t="n"/>
       <c r="Y216" s="7" t="n"/>
+      <c r="AB216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="C217" s="7" t="n"/>
       <c r="E217" s="7" t="n"/>
       <c r="G217" s="7" t="n"/>
-      <c r="L217" s="7" t="n"/>
+      <c r="I217" s="7" t="n"/>
       <c r="M217" s="7" t="n"/>
-      <c r="S217" s="7" t="n"/>
-      <c r="T217" s="7" t="n"/>
+      <c r="N217" s="7" t="n"/>
+      <c r="Q217" s="7" t="n"/>
+      <c r="U217" s="7" t="n"/>
+      <c r="V217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
+      <c r="AB217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="C218" s="7" t="n"/>
       <c r="E218" s="7" t="n"/>
       <c r="G218" s="7" t="n"/>
-      <c r="L218" s="7" t="n"/>
+      <c r="I218" s="7" t="n"/>
       <c r="M218" s="7" t="n"/>
-      <c r="S218" s="7" t="n"/>
-      <c r="T218" s="7" t="n"/>
+      <c r="N218" s="7" t="n"/>
+      <c r="Q218" s="7" t="n"/>
+      <c r="U218" s="7" t="n"/>
+      <c r="V218" s="7" t="n"/>
       <c r="Y218" s="7" t="n"/>
+      <c r="AB218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="C219" s="7" t="n"/>
       <c r="E219" s="7" t="n"/>
       <c r="G219" s="7" t="n"/>
-      <c r="L219" s="7" t="n"/>
+      <c r="I219" s="7" t="n"/>
       <c r="M219" s="7" t="n"/>
-      <c r="S219" s="7" t="n"/>
-      <c r="T219" s="7" t="n"/>
+      <c r="N219" s="7" t="n"/>
+      <c r="Q219" s="7" t="n"/>
+      <c r="U219" s="7" t="n"/>
+      <c r="V219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
+      <c r="AB219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="C220" s="7" t="n"/>
       <c r="E220" s="7" t="n"/>
       <c r="G220" s="7" t="n"/>
-      <c r="L220" s="7" t="n"/>
+      <c r="I220" s="7" t="n"/>
       <c r="M220" s="7" t="n"/>
-      <c r="S220" s="7" t="n"/>
-      <c r="T220" s="7" t="n"/>
+      <c r="N220" s="7" t="n"/>
+      <c r="Q220" s="7" t="n"/>
+      <c r="U220" s="7" t="n"/>
+      <c r="V220" s="7" t="n"/>
       <c r="Y220" s="7" t="n"/>
+      <c r="AB220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="C221" s="7" t="n"/>
       <c r="E221" s="7" t="n"/>
       <c r="G221" s="7" t="n"/>
-      <c r="L221" s="7" t="n"/>
+      <c r="I221" s="7" t="n"/>
       <c r="M221" s="7" t="n"/>
-      <c r="S221" s="7" t="n"/>
-      <c r="T221" s="7" t="n"/>
+      <c r="N221" s="7" t="n"/>
+      <c r="Q221" s="7" t="n"/>
+      <c r="U221" s="7" t="n"/>
+      <c r="V221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
+      <c r="AB221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="C222" s="7" t="n"/>
       <c r="E222" s="7" t="n"/>
       <c r="G222" s="7" t="n"/>
-      <c r="L222" s="7" t="n"/>
+      <c r="I222" s="7" t="n"/>
       <c r="M222" s="7" t="n"/>
-      <c r="S222" s="7" t="n"/>
-      <c r="T222" s="7" t="n"/>
+      <c r="N222" s="7" t="n"/>
+      <c r="Q222" s="7" t="n"/>
+      <c r="U222" s="7" t="n"/>
+      <c r="V222" s="7" t="n"/>
       <c r="Y222" s="7" t="n"/>
+      <c r="AB222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="C223" s="7" t="n"/>
       <c r="E223" s="7" t="n"/>
       <c r="G223" s="7" t="n"/>
-      <c r="L223" s="7" t="n"/>
+      <c r="I223" s="7" t="n"/>
       <c r="M223" s="7" t="n"/>
-      <c r="S223" s="7" t="n"/>
-      <c r="T223" s="7" t="n"/>
+      <c r="N223" s="7" t="n"/>
+      <c r="Q223" s="7" t="n"/>
+      <c r="U223" s="7" t="n"/>
+      <c r="V223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
+      <c r="AB223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="C224" s="7" t="n"/>
       <c r="E224" s="7" t="n"/>
       <c r="G224" s="7" t="n"/>
-      <c r="L224" s="7" t="n"/>
+      <c r="I224" s="7" t="n"/>
       <c r="M224" s="7" t="n"/>
-      <c r="S224" s="7" t="n"/>
-      <c r="T224" s="7" t="n"/>
+      <c r="N224" s="7" t="n"/>
+      <c r="Q224" s="7" t="n"/>
+      <c r="U224" s="7" t="n"/>
+      <c r="V224" s="7" t="n"/>
       <c r="Y224" s="7" t="n"/>
+      <c r="AB224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="C225" s="7" t="n"/>
       <c r="E225" s="7" t="n"/>
       <c r="G225" s="7" t="n"/>
-      <c r="L225" s="7" t="n"/>
+      <c r="I225" s="7" t="n"/>
       <c r="M225" s="7" t="n"/>
-      <c r="S225" s="7" t="n"/>
-      <c r="T225" s="7" t="n"/>
+      <c r="N225" s="7" t="n"/>
+      <c r="Q225" s="7" t="n"/>
+      <c r="U225" s="7" t="n"/>
+      <c r="V225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
+      <c r="AB225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="C226" s="7" t="n"/>
       <c r="E226" s="7" t="n"/>
       <c r="G226" s="7" t="n"/>
-      <c r="L226" s="7" t="n"/>
+      <c r="I226" s="7" t="n"/>
       <c r="M226" s="7" t="n"/>
-      <c r="S226" s="7" t="n"/>
-      <c r="T226" s="7" t="n"/>
+      <c r="N226" s="7" t="n"/>
+      <c r="Q226" s="7" t="n"/>
+      <c r="U226" s="7" t="n"/>
+      <c r="V226" s="7" t="n"/>
       <c r="Y226" s="7" t="n"/>
+      <c r="AB226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="C227" s="7" t="n"/>
       <c r="E227" s="7" t="n"/>
       <c r="G227" s="7" t="n"/>
-      <c r="L227" s="7" t="n"/>
+      <c r="I227" s="7" t="n"/>
       <c r="M227" s="7" t="n"/>
-      <c r="S227" s="7" t="n"/>
-      <c r="T227" s="7" t="n"/>
+      <c r="N227" s="7" t="n"/>
+      <c r="Q227" s="7" t="n"/>
+      <c r="U227" s="7" t="n"/>
+      <c r="V227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
+      <c r="AB227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="C228" s="7" t="n"/>
       <c r="E228" s="7" t="n"/>
       <c r="G228" s="7" t="n"/>
-      <c r="L228" s="7" t="n"/>
+      <c r="I228" s="7" t="n"/>
       <c r="M228" s="7" t="n"/>
-      <c r="S228" s="7" t="n"/>
-      <c r="T228" s="7" t="n"/>
+      <c r="N228" s="7" t="n"/>
+      <c r="Q228" s="7" t="n"/>
+      <c r="U228" s="7" t="n"/>
+      <c r="V228" s="7" t="n"/>
       <c r="Y228" s="7" t="n"/>
+      <c r="AB228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="C229" s="7" t="n"/>
       <c r="E229" s="7" t="n"/>
       <c r="G229" s="7" t="n"/>
-      <c r="L229" s="7" t="n"/>
+      <c r="I229" s="7" t="n"/>
       <c r="M229" s="7" t="n"/>
-      <c r="S229" s="7" t="n"/>
-      <c r="T229" s="7" t="n"/>
+      <c r="N229" s="7" t="n"/>
+      <c r="Q229" s="7" t="n"/>
+      <c r="U229" s="7" t="n"/>
+      <c r="V229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
+      <c r="AB229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="C230" s="7" t="n"/>
       <c r="E230" s="7" t="n"/>
       <c r="G230" s="7" t="n"/>
-      <c r="L230" s="7" t="n"/>
+      <c r="I230" s="7" t="n"/>
       <c r="M230" s="7" t="n"/>
-      <c r="S230" s="7" t="n"/>
-      <c r="T230" s="7" t="n"/>
+      <c r="N230" s="7" t="n"/>
+      <c r="Q230" s="7" t="n"/>
+      <c r="U230" s="7" t="n"/>
+      <c r="V230" s="7" t="n"/>
       <c r="Y230" s="7" t="n"/>
+      <c r="AB230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="C231" s="7" t="n"/>
       <c r="E231" s="7" t="n"/>
       <c r="G231" s="7" t="n"/>
-      <c r="L231" s="7" t="n"/>
+      <c r="I231" s="7" t="n"/>
       <c r="M231" s="7" t="n"/>
-      <c r="S231" s="7" t="n"/>
-      <c r="T231" s="7" t="n"/>
+      <c r="N231" s="7" t="n"/>
+      <c r="Q231" s="7" t="n"/>
+      <c r="U231" s="7" t="n"/>
+      <c r="V231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
+      <c r="AB231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="C232" s="7" t="n"/>
       <c r="E232" s="7" t="n"/>
       <c r="G232" s="7" t="n"/>
-      <c r="L232" s="7" t="n"/>
+      <c r="I232" s="7" t="n"/>
       <c r="M232" s="7" t="n"/>
-      <c r="S232" s="7" t="n"/>
-      <c r="T232" s="7" t="n"/>
+      <c r="N232" s="7" t="n"/>
+      <c r="Q232" s="7" t="n"/>
+      <c r="U232" s="7" t="n"/>
+      <c r="V232" s="7" t="n"/>
       <c r="Y232" s="7" t="n"/>
+      <c r="AB232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="C233" s="7" t="n"/>
       <c r="E233" s="7" t="n"/>
       <c r="G233" s="7" t="n"/>
-      <c r="L233" s="7" t="n"/>
+      <c r="I233" s="7" t="n"/>
       <c r="M233" s="7" t="n"/>
-      <c r="S233" s="7" t="n"/>
-      <c r="T233" s="7" t="n"/>
+      <c r="N233" s="7" t="n"/>
+      <c r="Q233" s="7" t="n"/>
+      <c r="U233" s="7" t="n"/>
+      <c r="V233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
+      <c r="AB233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="C234" s="7" t="n"/>
       <c r="E234" s="7" t="n"/>
       <c r="G234" s="7" t="n"/>
-      <c r="L234" s="7" t="n"/>
+      <c r="I234" s="7" t="n"/>
       <c r="M234" s="7" t="n"/>
-      <c r="S234" s="7" t="n"/>
-      <c r="T234" s="7" t="n"/>
+      <c r="N234" s="7" t="n"/>
+      <c r="Q234" s="7" t="n"/>
+      <c r="U234" s="7" t="n"/>
+      <c r="V234" s="7" t="n"/>
       <c r="Y234" s="7" t="n"/>
+      <c r="AB234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="C235" s="7" t="n"/>
       <c r="E235" s="7" t="n"/>
       <c r="G235" s="7" t="n"/>
-      <c r="L235" s="7" t="n"/>
+      <c r="I235" s="7" t="n"/>
       <c r="M235" s="7" t="n"/>
-      <c r="S235" s="7" t="n"/>
-      <c r="T235" s="7" t="n"/>
+      <c r="N235" s="7" t="n"/>
+      <c r="Q235" s="7" t="n"/>
+      <c r="U235" s="7" t="n"/>
+      <c r="V235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
+      <c r="AB235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="C236" s="7" t="n"/>
       <c r="E236" s="7" t="n"/>
       <c r="G236" s="7" t="n"/>
-      <c r="L236" s="7" t="n"/>
+      <c r="I236" s="7" t="n"/>
       <c r="M236" s="7" t="n"/>
-      <c r="S236" s="7" t="n"/>
-      <c r="T236" s="7" t="n"/>
+      <c r="N236" s="7" t="n"/>
+      <c r="Q236" s="7" t="n"/>
+      <c r="U236" s="7" t="n"/>
+      <c r="V236" s="7" t="n"/>
       <c r="Y236" s="7" t="n"/>
+      <c r="AB236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="C237" s="7" t="n"/>
       <c r="E237" s="7" t="n"/>
       <c r="G237" s="7" t="n"/>
-      <c r="L237" s="7" t="n"/>
+      <c r="I237" s="7" t="n"/>
       <c r="M237" s="7" t="n"/>
-      <c r="S237" s="7" t="n"/>
-      <c r="T237" s="7" t="n"/>
+      <c r="N237" s="7" t="n"/>
+      <c r="Q237" s="7" t="n"/>
+      <c r="U237" s="7" t="n"/>
+      <c r="V237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
+      <c r="AB237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="C238" s="7" t="n"/>
       <c r="E238" s="7" t="n"/>
       <c r="G238" s="7" t="n"/>
-      <c r="L238" s="7" t="n"/>
+      <c r="I238" s="7" t="n"/>
       <c r="M238" s="7" t="n"/>
-      <c r="S238" s="7" t="n"/>
-      <c r="T238" s="7" t="n"/>
+      <c r="N238" s="7" t="n"/>
+      <c r="Q238" s="7" t="n"/>
+      <c r="U238" s="7" t="n"/>
+      <c r="V238" s="7" t="n"/>
       <c r="Y238" s="7" t="n"/>
+      <c r="AB238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="C239" s="7" t="n"/>
       <c r="E239" s="7" t="n"/>
       <c r="G239" s="7" t="n"/>
-      <c r="L239" s="7" t="n"/>
+      <c r="I239" s="7" t="n"/>
       <c r="M239" s="7" t="n"/>
-      <c r="S239" s="7" t="n"/>
-      <c r="T239" s="7" t="n"/>
+      <c r="N239" s="7" t="n"/>
+      <c r="Q239" s="7" t="n"/>
+      <c r="U239" s="7" t="n"/>
+      <c r="V239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
+      <c r="AB239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="C240" s="7" t="n"/>
       <c r="E240" s="7" t="n"/>
       <c r="G240" s="7" t="n"/>
-      <c r="L240" s="7" t="n"/>
+      <c r="I240" s="7" t="n"/>
       <c r="M240" s="7" t="n"/>
-      <c r="S240" s="7" t="n"/>
-      <c r="T240" s="7" t="n"/>
+      <c r="N240" s="7" t="n"/>
+      <c r="Q240" s="7" t="n"/>
+      <c r="U240" s="7" t="n"/>
+      <c r="V240" s="7" t="n"/>
       <c r="Y240" s="7" t="n"/>
+      <c r="AB240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="C241" s="7" t="n"/>
       <c r="E241" s="7" t="n"/>
       <c r="G241" s="7" t="n"/>
-      <c r="L241" s="7" t="n"/>
+      <c r="I241" s="7" t="n"/>
       <c r="M241" s="7" t="n"/>
-      <c r="S241" s="7" t="n"/>
-      <c r="T241" s="7" t="n"/>
+      <c r="N241" s="7" t="n"/>
+      <c r="Q241" s="7" t="n"/>
+      <c r="U241" s="7" t="n"/>
+      <c r="V241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
+      <c r="AB241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="C242" s="7" t="n"/>
       <c r="E242" s="7" t="n"/>
       <c r="G242" s="7" t="n"/>
-      <c r="L242" s="7" t="n"/>
+      <c r="I242" s="7" t="n"/>
       <c r="M242" s="7" t="n"/>
-      <c r="S242" s="7" t="n"/>
-      <c r="T242" s="7" t="n"/>
+      <c r="N242" s="7" t="n"/>
+      <c r="Q242" s="7" t="n"/>
+      <c r="U242" s="7" t="n"/>
+      <c r="V242" s="7" t="n"/>
       <c r="Y242" s="7" t="n"/>
+      <c r="AB242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="C243" s="7" t="n"/>
       <c r="E243" s="7" t="n"/>
       <c r="G243" s="7" t="n"/>
-      <c r="L243" s="7" t="n"/>
+      <c r="I243" s="7" t="n"/>
       <c r="M243" s="7" t="n"/>
-      <c r="S243" s="7" t="n"/>
-      <c r="T243" s="7" t="n"/>
+      <c r="N243" s="7" t="n"/>
+      <c r="Q243" s="7" t="n"/>
+      <c r="U243" s="7" t="n"/>
+      <c r="V243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
+      <c r="AB243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="C244" s="7" t="n"/>
       <c r="E244" s="7" t="n"/>
       <c r="G244" s="7" t="n"/>
-      <c r="L244" s="7" t="n"/>
+      <c r="I244" s="7" t="n"/>
       <c r="M244" s="7" t="n"/>
-      <c r="S244" s="7" t="n"/>
-      <c r="T244" s="7" t="n"/>
+      <c r="N244" s="7" t="n"/>
+      <c r="Q244" s="7" t="n"/>
+      <c r="U244" s="7" t="n"/>
+      <c r="V244" s="7" t="n"/>
       <c r="Y244" s="7" t="n"/>
+      <c r="AB244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="C245" s="7" t="n"/>
       <c r="E245" s="7" t="n"/>
       <c r="G245" s="7" t="n"/>
-      <c r="L245" s="7" t="n"/>
+      <c r="I245" s="7" t="n"/>
       <c r="M245" s="7" t="n"/>
-      <c r="S245" s="7" t="n"/>
-      <c r="T245" s="7" t="n"/>
+      <c r="N245" s="7" t="n"/>
+      <c r="Q245" s="7" t="n"/>
+      <c r="U245" s="7" t="n"/>
+      <c r="V245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
+      <c r="AB245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="C246" s="7" t="n"/>
       <c r="E246" s="7" t="n"/>
       <c r="G246" s="7" t="n"/>
-      <c r="L246" s="7" t="n"/>
+      <c r="I246" s="7" t="n"/>
       <c r="M246" s="7" t="n"/>
-      <c r="S246" s="7" t="n"/>
-      <c r="T246" s="7" t="n"/>
+      <c r="N246" s="7" t="n"/>
+      <c r="Q246" s="7" t="n"/>
+      <c r="U246" s="7" t="n"/>
+      <c r="V246" s="7" t="n"/>
       <c r="Y246" s="7" t="n"/>
+      <c r="AB246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="C247" s="7" t="n"/>
       <c r="E247" s="7" t="n"/>
       <c r="G247" s="7" t="n"/>
-      <c r="L247" s="7" t="n"/>
+      <c r="I247" s="7" t="n"/>
       <c r="M247" s="7" t="n"/>
-      <c r="S247" s="7" t="n"/>
-      <c r="T247" s="7" t="n"/>
+      <c r="N247" s="7" t="n"/>
+      <c r="Q247" s="7" t="n"/>
+      <c r="U247" s="7" t="n"/>
+      <c r="V247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
+      <c r="AB247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="C248" s="7" t="n"/>
       <c r="E248" s="7" t="n"/>
       <c r="G248" s="7" t="n"/>
-      <c r="L248" s="7" t="n"/>
+      <c r="I248" s="7" t="n"/>
       <c r="M248" s="7" t="n"/>
-      <c r="S248" s="7" t="n"/>
-      <c r="T248" s="7" t="n"/>
+      <c r="N248" s="7" t="n"/>
+      <c r="Q248" s="7" t="n"/>
+      <c r="U248" s="7" t="n"/>
+      <c r="V248" s="7" t="n"/>
       <c r="Y248" s="7" t="n"/>
+      <c r="AB248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="C249" s="7" t="n"/>
       <c r="E249" s="7" t="n"/>
       <c r="G249" s="7" t="n"/>
-      <c r="L249" s="7" t="n"/>
+      <c r="I249" s="7" t="n"/>
       <c r="M249" s="7" t="n"/>
-      <c r="S249" s="7" t="n"/>
-      <c r="T249" s="7" t="n"/>
+      <c r="N249" s="7" t="n"/>
+      <c r="Q249" s="7" t="n"/>
+      <c r="U249" s="7" t="n"/>
+      <c r="V249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
+      <c r="AB249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="C250" s="7" t="n"/>
       <c r="E250" s="7" t="n"/>
       <c r="G250" s="7" t="n"/>
-      <c r="L250" s="7" t="n"/>
+      <c r="I250" s="7" t="n"/>
       <c r="M250" s="7" t="n"/>
-      <c r="S250" s="7" t="n"/>
-      <c r="T250" s="7" t="n"/>
+      <c r="N250" s="7" t="n"/>
+      <c r="Q250" s="7" t="n"/>
+      <c r="U250" s="7" t="n"/>
+      <c r="V250" s="7" t="n"/>
       <c r="Y250" s="7" t="n"/>
+      <c r="AB250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="C251" s="7" t="n"/>
       <c r="E251" s="7" t="n"/>
       <c r="G251" s="7" t="n"/>
-      <c r="L251" s="7" t="n"/>
+      <c r="I251" s="7" t="n"/>
       <c r="M251" s="7" t="n"/>
-      <c r="S251" s="7" t="n"/>
-      <c r="T251" s="7" t="n"/>
+      <c r="N251" s="7" t="n"/>
+      <c r="Q251" s="7" t="n"/>
+      <c r="U251" s="7" t="n"/>
+      <c r="V251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
+      <c r="AB251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="C252" s="7" t="n"/>
       <c r="E252" s="7" t="n"/>
       <c r="G252" s="7" t="n"/>
-      <c r="L252" s="7" t="n"/>
+      <c r="I252" s="7" t="n"/>
       <c r="M252" s="7" t="n"/>
-      <c r="S252" s="7" t="n"/>
-      <c r="T252" s="7" t="n"/>
+      <c r="N252" s="7" t="n"/>
+      <c r="Q252" s="7" t="n"/>
+      <c r="U252" s="7" t="n"/>
+      <c r="V252" s="7" t="n"/>
       <c r="Y252" s="7" t="n"/>
+      <c r="AB252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="C253" s="7" t="n"/>
       <c r="E253" s="7" t="n"/>
       <c r="G253" s="7" t="n"/>
-      <c r="L253" s="7" t="n"/>
+      <c r="I253" s="7" t="n"/>
       <c r="M253" s="7" t="n"/>
-      <c r="S253" s="7" t="n"/>
-      <c r="T253" s="7" t="n"/>
+      <c r="N253" s="7" t="n"/>
+      <c r="Q253" s="7" t="n"/>
+      <c r="U253" s="7" t="n"/>
+      <c r="V253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
+      <c r="AB253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="C254" s="7" t="n"/>
       <c r="E254" s="7" t="n"/>
       <c r="G254" s="7" t="n"/>
-      <c r="L254" s="7" t="n"/>
+      <c r="I254" s="7" t="n"/>
       <c r="M254" s="7" t="n"/>
-      <c r="S254" s="7" t="n"/>
-      <c r="T254" s="7" t="n"/>
+      <c r="N254" s="7" t="n"/>
+      <c r="Q254" s="7" t="n"/>
+      <c r="U254" s="7" t="n"/>
+      <c r="V254" s="7" t="n"/>
       <c r="Y254" s="7" t="n"/>
+      <c r="AB254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="C255" s="7" t="n"/>
       <c r="E255" s="7" t="n"/>
       <c r="G255" s="7" t="n"/>
-      <c r="L255" s="7" t="n"/>
+      <c r="I255" s="7" t="n"/>
       <c r="M255" s="7" t="n"/>
-      <c r="S255" s="7" t="n"/>
-      <c r="T255" s="7" t="n"/>
+      <c r="N255" s="7" t="n"/>
+      <c r="Q255" s="7" t="n"/>
+      <c r="U255" s="7" t="n"/>
+      <c r="V255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
+      <c r="AB255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="C256" s="7" t="n"/>
       <c r="E256" s="7" t="n"/>
       <c r="G256" s="7" t="n"/>
-      <c r="L256" s="7" t="n"/>
+      <c r="I256" s="7" t="n"/>
       <c r="M256" s="7" t="n"/>
-      <c r="S256" s="7" t="n"/>
-      <c r="T256" s="7" t="n"/>
+      <c r="N256" s="7" t="n"/>
+      <c r="Q256" s="7" t="n"/>
+      <c r="U256" s="7" t="n"/>
+      <c r="V256" s="7" t="n"/>
       <c r="Y256" s="7" t="n"/>
+      <c r="AB256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="C257" s="7" t="n"/>
       <c r="E257" s="7" t="n"/>
       <c r="G257" s="7" t="n"/>
-      <c r="L257" s="7" t="n"/>
+      <c r="I257" s="7" t="n"/>
       <c r="M257" s="7" t="n"/>
-      <c r="S257" s="7" t="n"/>
-      <c r="T257" s="7" t="n"/>
+      <c r="N257" s="7" t="n"/>
+      <c r="Q257" s="7" t="n"/>
+      <c r="U257" s="7" t="n"/>
+      <c r="V257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
+      <c r="AB257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="C258" s="7" t="n"/>
       <c r="E258" s="7" t="n"/>
       <c r="G258" s="7" t="n"/>
-      <c r="L258" s="7" t="n"/>
+      <c r="I258" s="7" t="n"/>
       <c r="M258" s="7" t="n"/>
-      <c r="S258" s="7" t="n"/>
-      <c r="T258" s="7" t="n"/>
+      <c r="N258" s="7" t="n"/>
+      <c r="Q258" s="7" t="n"/>
+      <c r="U258" s="7" t="n"/>
+      <c r="V258" s="7" t="n"/>
       <c r="Y258" s="7" t="n"/>
+      <c r="AB258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="C259" s="7" t="n"/>
       <c r="E259" s="7" t="n"/>
       <c r="G259" s="7" t="n"/>
-      <c r="L259" s="7" t="n"/>
+      <c r="I259" s="7" t="n"/>
       <c r="M259" s="7" t="n"/>
-      <c r="S259" s="7" t="n"/>
-      <c r="T259" s="7" t="n"/>
+      <c r="N259" s="7" t="n"/>
+      <c r="Q259" s="7" t="n"/>
+      <c r="U259" s="7" t="n"/>
+      <c r="V259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
+      <c r="AB259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="C260" s="7" t="n"/>
       <c r="E260" s="7" t="n"/>
       <c r="G260" s="7" t="n"/>
-      <c r="L260" s="7" t="n"/>
+      <c r="I260" s="7" t="n"/>
       <c r="M260" s="7" t="n"/>
-      <c r="S260" s="7" t="n"/>
-      <c r="T260" s="7" t="n"/>
+      <c r="N260" s="7" t="n"/>
+      <c r="Q260" s="7" t="n"/>
+      <c r="U260" s="7" t="n"/>
+      <c r="V260" s="7" t="n"/>
       <c r="Y260" s="7" t="n"/>
+      <c r="AB260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="C261" s="7" t="n"/>
       <c r="E261" s="7" t="n"/>
       <c r="G261" s="7" t="n"/>
-      <c r="L261" s="7" t="n"/>
+      <c r="I261" s="7" t="n"/>
       <c r="M261" s="7" t="n"/>
-      <c r="S261" s="7" t="n"/>
-      <c r="T261" s="7" t="n"/>
+      <c r="N261" s="7" t="n"/>
+      <c r="Q261" s="7" t="n"/>
+      <c r="U261" s="7" t="n"/>
+      <c r="V261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
+      <c r="AB261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="C262" s="7" t="n"/>
       <c r="E262" s="7" t="n"/>
       <c r="G262" s="7" t="n"/>
-      <c r="L262" s="7" t="n"/>
+      <c r="I262" s="7" t="n"/>
       <c r="M262" s="7" t="n"/>
-      <c r="S262" s="7" t="n"/>
-      <c r="T262" s="7" t="n"/>
+      <c r="N262" s="7" t="n"/>
+      <c r="Q262" s="7" t="n"/>
+      <c r="U262" s="7" t="n"/>
+      <c r="V262" s="7" t="n"/>
       <c r="Y262" s="7" t="n"/>
+      <c r="AB262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="C263" s="7" t="n"/>
       <c r="E263" s="7" t="n"/>
       <c r="G263" s="7" t="n"/>
-      <c r="L263" s="7" t="n"/>
+      <c r="I263" s="7" t="n"/>
       <c r="M263" s="7" t="n"/>
-      <c r="S263" s="7" t="n"/>
-      <c r="T263" s="7" t="n"/>
+      <c r="N263" s="7" t="n"/>
+      <c r="Q263" s="7" t="n"/>
+      <c r="U263" s="7" t="n"/>
+      <c r="V263" s="7" t="n"/>
       <c r="Y263" s="7" t="n"/>
+      <c r="AB263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="C264" s="7" t="n"/>
       <c r="E264" s="7" t="n"/>
       <c r="G264" s="7" t="n"/>
-      <c r="L264" s="7" t="n"/>
+      <c r="I264" s="7" t="n"/>
       <c r="M264" s="7" t="n"/>
-      <c r="S264" s="7" t="n"/>
-      <c r="T264" s="7" t="n"/>
+      <c r="N264" s="7" t="n"/>
+      <c r="Q264" s="7" t="n"/>
+      <c r="U264" s="7" t="n"/>
+      <c r="V264" s="7" t="n"/>
       <c r="Y264" s="7" t="n"/>
+      <c r="AB264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="C265" s="7" t="n"/>
       <c r="E265" s="7" t="n"/>
       <c r="G265" s="7" t="n"/>
-      <c r="L265" s="7" t="n"/>
+      <c r="I265" s="7" t="n"/>
       <c r="M265" s="7" t="n"/>
-      <c r="S265" s="7" t="n"/>
-      <c r="T265" s="7" t="n"/>
+      <c r="N265" s="7" t="n"/>
+      <c r="Q265" s="7" t="n"/>
+      <c r="U265" s="7" t="n"/>
+      <c r="V265" s="7" t="n"/>
       <c r="Y265" s="7" t="n"/>
+      <c r="AB265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="C266" s="7" t="n"/>
       <c r="E266" s="7" t="n"/>
       <c r="G266" s="7" t="n"/>
-      <c r="L266" s="7" t="n"/>
+      <c r="I266" s="7" t="n"/>
       <c r="M266" s="7" t="n"/>
-      <c r="S266" s="7" t="n"/>
-      <c r="T266" s="7" t="n"/>
+      <c r="N266" s="7" t="n"/>
+      <c r="Q266" s="7" t="n"/>
+      <c r="U266" s="7" t="n"/>
+      <c r="V266" s="7" t="n"/>
       <c r="Y266" s="7" t="n"/>
+      <c r="AB266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="C267" s="7" t="n"/>
       <c r="E267" s="7" t="n"/>
       <c r="G267" s="7" t="n"/>
-      <c r="L267" s="7" t="n"/>
+      <c r="I267" s="7" t="n"/>
       <c r="M267" s="7" t="n"/>
-      <c r="S267" s="7" t="n"/>
-      <c r="T267" s="7" t="n"/>
+      <c r="N267" s="7" t="n"/>
+      <c r="Q267" s="7" t="n"/>
+      <c r="U267" s="7" t="n"/>
+      <c r="V267" s="7" t="n"/>
       <c r="Y267" s="7" t="n"/>
+      <c r="AB267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="C268" s="7" t="n"/>
       <c r="E268" s="7" t="n"/>
       <c r="G268" s="7" t="n"/>
-      <c r="L268" s="7" t="n"/>
+      <c r="I268" s="7" t="n"/>
       <c r="M268" s="7" t="n"/>
-      <c r="S268" s="7" t="n"/>
-      <c r="T268" s="7" t="n"/>
+      <c r="N268" s="7" t="n"/>
+      <c r="Q268" s="7" t="n"/>
+      <c r="U268" s="7" t="n"/>
+      <c r="V268" s="7" t="n"/>
       <c r="Y268" s="7" t="n"/>
+      <c r="AB268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="C269" s="7" t="n"/>
       <c r="E269" s="7" t="n"/>
       <c r="G269" s="7" t="n"/>
-      <c r="L269" s="7" t="n"/>
+      <c r="I269" s="7" t="n"/>
       <c r="M269" s="7" t="n"/>
-      <c r="S269" s="7" t="n"/>
-      <c r="T269" s="7" t="n"/>
+      <c r="N269" s="7" t="n"/>
+      <c r="Q269" s="7" t="n"/>
+      <c r="U269" s="7" t="n"/>
+      <c r="V269" s="7" t="n"/>
       <c r="Y269" s="7" t="n"/>
+      <c r="AB269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="C270" s="7" t="n"/>
       <c r="E270" s="7" t="n"/>
       <c r="G270" s="7" t="n"/>
-      <c r="L270" s="7" t="n"/>
+      <c r="I270" s="7" t="n"/>
       <c r="M270" s="7" t="n"/>
-      <c r="S270" s="7" t="n"/>
-      <c r="T270" s="7" t="n"/>
+      <c r="N270" s="7" t="n"/>
+      <c r="Q270" s="7" t="n"/>
+      <c r="U270" s="7" t="n"/>
+      <c r="V270" s="7" t="n"/>
       <c r="Y270" s="7" t="n"/>
+      <c r="AB270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="C271" s="7" t="n"/>
       <c r="E271" s="7" t="n"/>
       <c r="G271" s="7" t="n"/>
-      <c r="L271" s="7" t="n"/>
+      <c r="I271" s="7" t="n"/>
       <c r="M271" s="7" t="n"/>
-      <c r="S271" s="7" t="n"/>
-      <c r="T271" s="7" t="n"/>
+      <c r="N271" s="7" t="n"/>
+      <c r="Q271" s="7" t="n"/>
+      <c r="U271" s="7" t="n"/>
+      <c r="V271" s="7" t="n"/>
       <c r="Y271" s="7" t="n"/>
+      <c r="AB271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="C272" s="7" t="n"/>
       <c r="E272" s="7" t="n"/>
       <c r="G272" s="7" t="n"/>
-      <c r="L272" s="7" t="n"/>
+      <c r="I272" s="7" t="n"/>
       <c r="M272" s="7" t="n"/>
-      <c r="S272" s="7" t="n"/>
-      <c r="T272" s="7" t="n"/>
+      <c r="N272" s="7" t="n"/>
+      <c r="Q272" s="7" t="n"/>
+      <c r="U272" s="7" t="n"/>
+      <c r="V272" s="7" t="n"/>
       <c r="Y272" s="7" t="n"/>
+      <c r="AB272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="C273" s="7" t="n"/>
       <c r="E273" s="7" t="n"/>
       <c r="G273" s="7" t="n"/>
-      <c r="L273" s="7" t="n"/>
+      <c r="I273" s="7" t="n"/>
       <c r="M273" s="7" t="n"/>
-      <c r="S273" s="7" t="n"/>
-      <c r="T273" s="7" t="n"/>
+      <c r="N273" s="7" t="n"/>
+      <c r="Q273" s="7" t="n"/>
+      <c r="U273" s="7" t="n"/>
+      <c r="V273" s="7" t="n"/>
       <c r="Y273" s="7" t="n"/>
+      <c r="AB273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="C274" s="7" t="n"/>
       <c r="E274" s="7" t="n"/>
       <c r="G274" s="7" t="n"/>
-      <c r="L274" s="7" t="n"/>
+      <c r="I274" s="7" t="n"/>
       <c r="M274" s="7" t="n"/>
-      <c r="S274" s="7" t="n"/>
-      <c r="T274" s="7" t="n"/>
+      <c r="N274" s="7" t="n"/>
+      <c r="Q274" s="7" t="n"/>
+      <c r="U274" s="7" t="n"/>
+      <c r="V274" s="7" t="n"/>
       <c r="Y274" s="7" t="n"/>
+      <c r="AB274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="C275" s="7" t="n"/>
       <c r="E275" s="7" t="n"/>
       <c r="G275" s="7" t="n"/>
-      <c r="L275" s="7" t="n"/>
+      <c r="I275" s="7" t="n"/>
       <c r="M275" s="7" t="n"/>
-      <c r="S275" s="7" t="n"/>
-      <c r="T275" s="7" t="n"/>
+      <c r="N275" s="7" t="n"/>
+      <c r="Q275" s="7" t="n"/>
+      <c r="U275" s="7" t="n"/>
+      <c r="V275" s="7" t="n"/>
       <c r="Y275" s="7" t="n"/>
+      <c r="AB275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="C276" s="7" t="n"/>
       <c r="E276" s="7" t="n"/>
       <c r="G276" s="7" t="n"/>
-      <c r="L276" s="7" t="n"/>
+      <c r="I276" s="7" t="n"/>
       <c r="M276" s="7" t="n"/>
-      <c r="S276" s="7" t="n"/>
-      <c r="T276" s="7" t="n"/>
+      <c r="N276" s="7" t="n"/>
+      <c r="Q276" s="7" t="n"/>
+      <c r="U276" s="7" t="n"/>
+      <c r="V276" s="7" t="n"/>
       <c r="Y276" s="7" t="n"/>
+      <c r="AB276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="C277" s="7" t="n"/>
       <c r="E277" s="7" t="n"/>
       <c r="G277" s="7" t="n"/>
-      <c r="L277" s="7" t="n"/>
+      <c r="I277" s="7" t="n"/>
       <c r="M277" s="7" t="n"/>
-      <c r="S277" s="7" t="n"/>
-      <c r="T277" s="7" t="n"/>
+      <c r="N277" s="7" t="n"/>
+      <c r="Q277" s="7" t="n"/>
+      <c r="U277" s="7" t="n"/>
+      <c r="V277" s="7" t="n"/>
       <c r="Y277" s="7" t="n"/>
+      <c r="AB277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="C278" s="7" t="n"/>
       <c r="E278" s="7" t="n"/>
       <c r="G278" s="7" t="n"/>
-      <c r="L278" s="7" t="n"/>
+      <c r="I278" s="7" t="n"/>
       <c r="M278" s="7" t="n"/>
-      <c r="S278" s="7" t="n"/>
-      <c r="T278" s="7" t="n"/>
+      <c r="N278" s="7" t="n"/>
+      <c r="Q278" s="7" t="n"/>
+      <c r="U278" s="7" t="n"/>
+      <c r="V278" s="7" t="n"/>
       <c r="Y278" s="7" t="n"/>
+      <c r="AB278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="C279" s="7" t="n"/>
       <c r="E279" s="7" t="n"/>
       <c r="G279" s="7" t="n"/>
-      <c r="L279" s="7" t="n"/>
+      <c r="I279" s="7" t="n"/>
       <c r="M279" s="7" t="n"/>
-      <c r="S279" s="7" t="n"/>
-      <c r="T279" s="7" t="n"/>
+      <c r="N279" s="7" t="n"/>
+      <c r="Q279" s="7" t="n"/>
+      <c r="U279" s="7" t="n"/>
+      <c r="V279" s="7" t="n"/>
       <c r="Y279" s="7" t="n"/>
+      <c r="AB279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="C280" s="7" t="n"/>
       <c r="E280" s="7" t="n"/>
       <c r="G280" s="7" t="n"/>
-      <c r="L280" s="7" t="n"/>
+      <c r="I280" s="7" t="n"/>
       <c r="M280" s="7" t="n"/>
-      <c r="S280" s="7" t="n"/>
-      <c r="T280" s="7" t="n"/>
+      <c r="N280" s="7" t="n"/>
+      <c r="Q280" s="7" t="n"/>
+      <c r="U280" s="7" t="n"/>
+      <c r="V280" s="7" t="n"/>
       <c r="Y280" s="7" t="n"/>
+      <c r="AB280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="C281" s="7" t="n"/>
       <c r="E281" s="7" t="n"/>
       <c r="G281" s="7" t="n"/>
-      <c r="L281" s="7" t="n"/>
+      <c r="I281" s="7" t="n"/>
       <c r="M281" s="7" t="n"/>
-      <c r="S281" s="7" t="n"/>
-      <c r="T281" s="7" t="n"/>
+      <c r="N281" s="7" t="n"/>
+      <c r="Q281" s="7" t="n"/>
+      <c r="U281" s="7" t="n"/>
+      <c r="V281" s="7" t="n"/>
       <c r="Y281" s="7" t="n"/>
+      <c r="AB281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="C282" s="7" t="n"/>
       <c r="E282" s="7" t="n"/>
       <c r="G282" s="7" t="n"/>
-      <c r="L282" s="7" t="n"/>
+      <c r="I282" s="7" t="n"/>
       <c r="M282" s="7" t="n"/>
-      <c r="S282" s="7" t="n"/>
-      <c r="T282" s="7" t="n"/>
+      <c r="N282" s="7" t="n"/>
+      <c r="Q282" s="7" t="n"/>
+      <c r="U282" s="7" t="n"/>
+      <c r="V282" s="7" t="n"/>
       <c r="Y282" s="7" t="n"/>
+      <c r="AB282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="C283" s="7" t="n"/>
       <c r="E283" s="7" t="n"/>
       <c r="G283" s="7" t="n"/>
-      <c r="L283" s="7" t="n"/>
+      <c r="I283" s="7" t="n"/>
       <c r="M283" s="7" t="n"/>
-      <c r="S283" s="7" t="n"/>
-      <c r="T283" s="7" t="n"/>
+      <c r="N283" s="7" t="n"/>
+      <c r="Q283" s="7" t="n"/>
+      <c r="U283" s="7" t="n"/>
+      <c r="V283" s="7" t="n"/>
       <c r="Y283" s="7" t="n"/>
+      <c r="AB283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="C284" s="7" t="n"/>
       <c r="E284" s="7" t="n"/>
       <c r="G284" s="7" t="n"/>
-      <c r="L284" s="7" t="n"/>
+      <c r="I284" s="7" t="n"/>
       <c r="M284" s="7" t="n"/>
-      <c r="S284" s="7" t="n"/>
-      <c r="T284" s="7" t="n"/>
+      <c r="N284" s="7" t="n"/>
+      <c r="Q284" s="7" t="n"/>
+      <c r="U284" s="7" t="n"/>
+      <c r="V284" s="7" t="n"/>
       <c r="Y284" s="7" t="n"/>
+      <c r="AB284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="C285" s="7" t="n"/>
       <c r="E285" s="7" t="n"/>
       <c r="G285" s="7" t="n"/>
-      <c r="L285" s="7" t="n"/>
+      <c r="I285" s="7" t="n"/>
       <c r="M285" s="7" t="n"/>
-      <c r="S285" s="7" t="n"/>
-      <c r="T285" s="7" t="n"/>
+      <c r="N285" s="7" t="n"/>
+      <c r="Q285" s="7" t="n"/>
+      <c r="U285" s="7" t="n"/>
+      <c r="V285" s="7" t="n"/>
       <c r="Y285" s="7" t="n"/>
+      <c r="AB285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="C286" s="7" t="n"/>
       <c r="E286" s="7" t="n"/>
       <c r="G286" s="7" t="n"/>
-      <c r="L286" s="7" t="n"/>
+      <c r="I286" s="7" t="n"/>
       <c r="M286" s="7" t="n"/>
-      <c r="S286" s="7" t="n"/>
-      <c r="T286" s="7" t="n"/>
+      <c r="N286" s="7" t="n"/>
+      <c r="Q286" s="7" t="n"/>
+      <c r="U286" s="7" t="n"/>
+      <c r="V286" s="7" t="n"/>
       <c r="Y286" s="7" t="n"/>
+      <c r="AB286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="C287" s="7" t="n"/>
       <c r="E287" s="7" t="n"/>
       <c r="G287" s="7" t="n"/>
-      <c r="L287" s="7" t="n"/>
+      <c r="I287" s="7" t="n"/>
       <c r="M287" s="7" t="n"/>
-      <c r="S287" s="7" t="n"/>
-      <c r="T287" s="7" t="n"/>
+      <c r="N287" s="7" t="n"/>
+      <c r="Q287" s="7" t="n"/>
+      <c r="U287" s="7" t="n"/>
+      <c r="V287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
+      <c r="AB287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="C288" s="7" t="n"/>
       <c r="E288" s="7" t="n"/>
       <c r="G288" s="7" t="n"/>
-      <c r="L288" s="7" t="n"/>
+      <c r="I288" s="7" t="n"/>
       <c r="M288" s="7" t="n"/>
-      <c r="S288" s="7" t="n"/>
-      <c r="T288" s="7" t="n"/>
+      <c r="N288" s="7" t="n"/>
+      <c r="Q288" s="7" t="n"/>
+      <c r="U288" s="7" t="n"/>
+      <c r="V288" s="7" t="n"/>
       <c r="Y288" s="7" t="n"/>
+      <c r="AB288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="C289" s="7" t="n"/>
       <c r="E289" s="7" t="n"/>
       <c r="G289" s="7" t="n"/>
-      <c r="L289" s="7" t="n"/>
+      <c r="I289" s="7" t="n"/>
       <c r="M289" s="7" t="n"/>
-      <c r="S289" s="7" t="n"/>
-      <c r="T289" s="7" t="n"/>
+      <c r="N289" s="7" t="n"/>
+      <c r="Q289" s="7" t="n"/>
+      <c r="U289" s="7" t="n"/>
+      <c r="V289" s="7" t="n"/>
       <c r="Y289" s="7" t="n"/>
+      <c r="AB289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="C290" s="7" t="n"/>
       <c r="E290" s="7" t="n"/>
       <c r="G290" s="7" t="n"/>
-      <c r="L290" s="7" t="n"/>
+      <c r="I290" s="7" t="n"/>
       <c r="M290" s="7" t="n"/>
-      <c r="S290" s="7" t="n"/>
-      <c r="T290" s="7" t="n"/>
+      <c r="N290" s="7" t="n"/>
+      <c r="Q290" s="7" t="n"/>
+      <c r="U290" s="7" t="n"/>
+      <c r="V290" s="7" t="n"/>
       <c r="Y290" s="7" t="n"/>
+      <c r="AB290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="C291" s="7" t="n"/>
       <c r="E291" s="7" t="n"/>
       <c r="G291" s="7" t="n"/>
-      <c r="L291" s="7" t="n"/>
+      <c r="I291" s="7" t="n"/>
       <c r="M291" s="7" t="n"/>
-      <c r="S291" s="7" t="n"/>
-      <c r="T291" s="7" t="n"/>
+      <c r="N291" s="7" t="n"/>
+      <c r="Q291" s="7" t="n"/>
+      <c r="U291" s="7" t="n"/>
+      <c r="V291" s="7" t="n"/>
       <c r="Y291" s="7" t="n"/>
+      <c r="AB291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="C292" s="7" t="n"/>
       <c r="E292" s="7" t="n"/>
       <c r="G292" s="7" t="n"/>
-      <c r="L292" s="7" t="n"/>
+      <c r="I292" s="7" t="n"/>
       <c r="M292" s="7" t="n"/>
-      <c r="S292" s="7" t="n"/>
-      <c r="T292" s="7" t="n"/>
+      <c r="N292" s="7" t="n"/>
+      <c r="Q292" s="7" t="n"/>
+      <c r="U292" s="7" t="n"/>
+      <c r="V292" s="7" t="n"/>
       <c r="Y292" s="7" t="n"/>
+      <c r="AB292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="C293" s="7" t="n"/>
       <c r="E293" s="7" t="n"/>
       <c r="G293" s="7" t="n"/>
-      <c r="L293" s="7" t="n"/>
+      <c r="I293" s="7" t="n"/>
       <c r="M293" s="7" t="n"/>
-      <c r="S293" s="7" t="n"/>
-      <c r="T293" s="7" t="n"/>
+      <c r="N293" s="7" t="n"/>
+      <c r="Q293" s="7" t="n"/>
+      <c r="U293" s="7" t="n"/>
+      <c r="V293" s="7" t="n"/>
       <c r="Y293" s="7" t="n"/>
+      <c r="AB293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="C294" s="7" t="n"/>
       <c r="E294" s="7" t="n"/>
       <c r="G294" s="7" t="n"/>
-      <c r="L294" s="7" t="n"/>
+      <c r="I294" s="7" t="n"/>
       <c r="M294" s="7" t="n"/>
-      <c r="S294" s="7" t="n"/>
-      <c r="T294" s="7" t="n"/>
+      <c r="N294" s="7" t="n"/>
+      <c r="Q294" s="7" t="n"/>
+      <c r="U294" s="7" t="n"/>
+      <c r="V294" s="7" t="n"/>
       <c r="Y294" s="7" t="n"/>
+      <c r="AB294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="C295" s="7" t="n"/>
       <c r="E295" s="7" t="n"/>
       <c r="G295" s="7" t="n"/>
-      <c r="L295" s="7" t="n"/>
+      <c r="I295" s="7" t="n"/>
       <c r="M295" s="7" t="n"/>
-      <c r="S295" s="7" t="n"/>
-      <c r="T295" s="7" t="n"/>
+      <c r="N295" s="7" t="n"/>
+      <c r="Q295" s="7" t="n"/>
+      <c r="U295" s="7" t="n"/>
+      <c r="V295" s="7" t="n"/>
       <c r="Y295" s="7" t="n"/>
+      <c r="AB295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="C296" s="7" t="n"/>
       <c r="E296" s="7" t="n"/>
       <c r="G296" s="7" t="n"/>
-      <c r="L296" s="7" t="n"/>
+      <c r="I296" s="7" t="n"/>
       <c r="M296" s="7" t="n"/>
-      <c r="S296" s="7" t="n"/>
-      <c r="T296" s="7" t="n"/>
+      <c r="N296" s="7" t="n"/>
+      <c r="Q296" s="7" t="n"/>
+      <c r="U296" s="7" t="n"/>
+      <c r="V296" s="7" t="n"/>
       <c r="Y296" s="7" t="n"/>
+      <c r="AB296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="C297" s="7" t="n"/>
       <c r="E297" s="7" t="n"/>
       <c r="G297" s="7" t="n"/>
-      <c r="L297" s="7" t="n"/>
+      <c r="I297" s="7" t="n"/>
       <c r="M297" s="7" t="n"/>
-      <c r="S297" s="7" t="n"/>
-      <c r="T297" s="7" t="n"/>
+      <c r="N297" s="7" t="n"/>
+      <c r="Q297" s="7" t="n"/>
+      <c r="U297" s="7" t="n"/>
+      <c r="V297" s="7" t="n"/>
       <c r="Y297" s="7" t="n"/>
+      <c r="AB297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="C298" s="7" t="n"/>
       <c r="E298" s="7" t="n"/>
       <c r="G298" s="7" t="n"/>
-      <c r="L298" s="7" t="n"/>
+      <c r="I298" s="7" t="n"/>
       <c r="M298" s="7" t="n"/>
-      <c r="S298" s="7" t="n"/>
-      <c r="T298" s="7" t="n"/>
+      <c r="N298" s="7" t="n"/>
+      <c r="Q298" s="7" t="n"/>
+      <c r="U298" s="7" t="n"/>
+      <c r="V298" s="7" t="n"/>
       <c r="Y298" s="7" t="n"/>
+      <c r="AB298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="C299" s="7" t="n"/>
       <c r="E299" s="7" t="n"/>
       <c r="G299" s="7" t="n"/>
-      <c r="L299" s="7" t="n"/>
+      <c r="I299" s="7" t="n"/>
       <c r="M299" s="7" t="n"/>
-      <c r="S299" s="7" t="n"/>
-      <c r="T299" s="7" t="n"/>
+      <c r="N299" s="7" t="n"/>
+      <c r="Q299" s="7" t="n"/>
+      <c r="U299" s="7" t="n"/>
+      <c r="V299" s="7" t="n"/>
       <c r="Y299" s="7" t="n"/>
+      <c r="AB299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="C300" s="7" t="n"/>
       <c r="E300" s="7" t="n"/>
       <c r="G300" s="7" t="n"/>
-      <c r="L300" s="7" t="n"/>
+      <c r="I300" s="7" t="n"/>
       <c r="M300" s="7" t="n"/>
-      <c r="S300" s="7" t="n"/>
-      <c r="T300" s="7" t="n"/>
+      <c r="N300" s="7" t="n"/>
+      <c r="Q300" s="7" t="n"/>
+      <c r="U300" s="7" t="n"/>
+      <c r="V300" s="7" t="n"/>
       <c r="Y300" s="7" t="n"/>
+      <c r="AB300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="C301" s="7" t="n"/>
       <c r="E301" s="7" t="n"/>
       <c r="G301" s="7" t="n"/>
-      <c r="L301" s="7" t="n"/>
+      <c r="I301" s="7" t="n"/>
       <c r="M301" s="7" t="n"/>
-      <c r="S301" s="7" t="n"/>
-      <c r="T301" s="7" t="n"/>
+      <c r="N301" s="7" t="n"/>
+      <c r="Q301" s="7" t="n"/>
+      <c r="U301" s="7" t="n"/>
+      <c r="V301" s="7" t="n"/>
       <c r="Y301" s="7" t="n"/>
+      <c r="AB301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="C302" s="7" t="n"/>
       <c r="E302" s="7" t="n"/>
       <c r="G302" s="7" t="n"/>
-      <c r="L302" s="7" t="n"/>
+      <c r="I302" s="7" t="n"/>
       <c r="M302" s="7" t="n"/>
-      <c r="S302" s="7" t="n"/>
-      <c r="T302" s="7" t="n"/>
+      <c r="N302" s="7" t="n"/>
+      <c r="Q302" s="7" t="n"/>
+      <c r="U302" s="7" t="n"/>
+      <c r="V302" s="7" t="n"/>
       <c r="Y302" s="7" t="n"/>
+      <c r="AB302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="C303" s="7" t="n"/>
       <c r="E303" s="7" t="n"/>
       <c r="G303" s="7" t="n"/>
-      <c r="L303" s="7" t="n"/>
+      <c r="I303" s="7" t="n"/>
       <c r="M303" s="7" t="n"/>
-      <c r="S303" s="7" t="n"/>
-      <c r="T303" s="7" t="n"/>
+      <c r="N303" s="7" t="n"/>
+      <c r="Q303" s="7" t="n"/>
+      <c r="U303" s="7" t="n"/>
+      <c r="V303" s="7" t="n"/>
       <c r="Y303" s="7" t="n"/>
+      <c r="AB303" s="7" t="n"/>
     </row>
     <row r="304">
       <c r="C304" s="7" t="n"/>
       <c r="E304" s="7" t="n"/>
       <c r="G304" s="7" t="n"/>
-      <c r="L304" s="7" t="n"/>
+      <c r="I304" s="7" t="n"/>
       <c r="M304" s="7" t="n"/>
-      <c r="S304" s="7" t="n"/>
-      <c r="T304" s="7" t="n"/>
+      <c r="N304" s="7" t="n"/>
+      <c r="Q304" s="7" t="n"/>
+      <c r="U304" s="7" t="n"/>
+      <c r="V304" s="7" t="n"/>
       <c r="Y304" s="7" t="n"/>
+      <c r="AB304" s="7" t="n"/>
     </row>
     <row r="305">
       <c r="C305" s="7" t="n"/>
       <c r="E305" s="7" t="n"/>
       <c r="G305" s="7" t="n"/>
-      <c r="L305" s="7" t="n"/>
+      <c r="I305" s="7" t="n"/>
       <c r="M305" s="7" t="n"/>
-      <c r="S305" s="7" t="n"/>
-      <c r="T305" s="7" t="n"/>
+      <c r="N305" s="7" t="n"/>
+      <c r="Q305" s="7" t="n"/>
+      <c r="U305" s="7" t="n"/>
+      <c r="V305" s="7" t="n"/>
       <c r="Y305" s="7" t="n"/>
+      <c r="AB305" s="7" t="n"/>
     </row>
     <row r="306">
       <c r="C306" s="7" t="n"/>
       <c r="E306" s="7" t="n"/>
       <c r="G306" s="7" t="n"/>
-      <c r="L306" s="7" t="n"/>
+      <c r="I306" s="7" t="n"/>
       <c r="M306" s="7" t="n"/>
-      <c r="S306" s="7" t="n"/>
-      <c r="T306" s="7" t="n"/>
+      <c r="N306" s="7" t="n"/>
+      <c r="Q306" s="7" t="n"/>
+      <c r="U306" s="7" t="n"/>
+      <c r="V306" s="7" t="n"/>
       <c r="Y306" s="7" t="n"/>
+      <c r="AB306" s="7" t="n"/>
     </row>
     <row r="307">
       <c r="C307" s="7" t="n"/>
       <c r="E307" s="7" t="n"/>
       <c r="G307" s="7" t="n"/>
-      <c r="L307" s="7" t="n"/>
+      <c r="I307" s="7" t="n"/>
       <c r="M307" s="7" t="n"/>
-      <c r="S307" s="7" t="n"/>
-      <c r="T307" s="7" t="n"/>
+      <c r="N307" s="7" t="n"/>
+      <c r="Q307" s="7" t="n"/>
+      <c r="U307" s="7" t="n"/>
+      <c r="V307" s="7" t="n"/>
       <c r="Y307" s="7" t="n"/>
+      <c r="AB307" s="7" t="n"/>
     </row>
     <row r="308">
       <c r="C308" s="7" t="n"/>
       <c r="E308" s="7" t="n"/>
       <c r="G308" s="7" t="n"/>
-      <c r="L308" s="7" t="n"/>
+      <c r="I308" s="7" t="n"/>
       <c r="M308" s="7" t="n"/>
-      <c r="S308" s="7" t="n"/>
-      <c r="T308" s="7" t="n"/>
+      <c r="N308" s="7" t="n"/>
+      <c r="Q308" s="7" t="n"/>
+      <c r="U308" s="7" t="n"/>
+      <c r="V308" s="7" t="n"/>
       <c r="Y308" s="7" t="n"/>
+      <c r="AB308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="C309" s="7" t="n"/>
       <c r="E309" s="7" t="n"/>
       <c r="G309" s="7" t="n"/>
-      <c r="L309" s="7" t="n"/>
+      <c r="I309" s="7" t="n"/>
       <c r="M309" s="7" t="n"/>
-      <c r="S309" s="7" t="n"/>
-      <c r="T309" s="7" t="n"/>
+      <c r="N309" s="7" t="n"/>
+      <c r="Q309" s="7" t="n"/>
+      <c r="U309" s="7" t="n"/>
+      <c r="V309" s="7" t="n"/>
       <c r="Y309" s="7" t="n"/>
+      <c r="AB309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="C310" s="7" t="n"/>
       <c r="E310" s="7" t="n"/>
       <c r="G310" s="7" t="n"/>
-      <c r="L310" s="7" t="n"/>
+      <c r="I310" s="7" t="n"/>
       <c r="M310" s="7" t="n"/>
-      <c r="S310" s="7" t="n"/>
-      <c r="T310" s="7" t="n"/>
+      <c r="N310" s="7" t="n"/>
+      <c r="Q310" s="7" t="n"/>
+      <c r="U310" s="7" t="n"/>
+      <c r="V310" s="7" t="n"/>
       <c r="Y310" s="7" t="n"/>
+      <c r="AB310" s="7" t="n"/>
     </row>
     <row r="311">
       <c r="C311" s="7" t="n"/>
       <c r="E311" s="7" t="n"/>
       <c r="G311" s="7" t="n"/>
-      <c r="L311" s="7" t="n"/>
+      <c r="I311" s="7" t="n"/>
       <c r="M311" s="7" t="n"/>
-      <c r="S311" s="7" t="n"/>
-      <c r="T311" s="7" t="n"/>
+      <c r="N311" s="7" t="n"/>
+      <c r="Q311" s="7" t="n"/>
+      <c r="U311" s="7" t="n"/>
+      <c r="V311" s="7" t="n"/>
       <c r="Y311" s="7" t="n"/>
+      <c r="AB311" s="7" t="n"/>
     </row>
     <row r="312">
       <c r="C312" s="7" t="n"/>
       <c r="E312" s="7" t="n"/>
       <c r="G312" s="7" t="n"/>
-      <c r="L312" s="7" t="n"/>
+      <c r="I312" s="7" t="n"/>
       <c r="M312" s="7" t="n"/>
-      <c r="S312" s="7" t="n"/>
-      <c r="T312" s="7" t="n"/>
+      <c r="N312" s="7" t="n"/>
+      <c r="Q312" s="7" t="n"/>
+      <c r="U312" s="7" t="n"/>
+      <c r="V312" s="7" t="n"/>
       <c r="Y312" s="7" t="n"/>
+      <c r="AB312" s="7" t="n"/>
     </row>
     <row r="313">
       <c r="C313" s="7" t="n"/>
       <c r="E313" s="7" t="n"/>
       <c r="G313" s="7" t="n"/>
-      <c r="L313" s="7" t="n"/>
+      <c r="I313" s="7" t="n"/>
       <c r="M313" s="7" t="n"/>
-      <c r="S313" s="7" t="n"/>
-      <c r="T313" s="7" t="n"/>
+      <c r="N313" s="7" t="n"/>
+      <c r="Q313" s="7" t="n"/>
+      <c r="U313" s="7" t="n"/>
+      <c r="V313" s="7" t="n"/>
       <c r="Y313" s="7" t="n"/>
+      <c r="AB313" s="7" t="n"/>
     </row>
     <row r="314">
       <c r="C314" s="7" t="n"/>
       <c r="E314" s="7" t="n"/>
       <c r="G314" s="7" t="n"/>
-      <c r="L314" s="7" t="n"/>
+      <c r="I314" s="7" t="n"/>
       <c r="M314" s="7" t="n"/>
-      <c r="S314" s="7" t="n"/>
-      <c r="T314" s="7" t="n"/>
+      <c r="N314" s="7" t="n"/>
+      <c r="Q314" s="7" t="n"/>
+      <c r="U314" s="7" t="n"/>
+      <c r="V314" s="7" t="n"/>
       <c r="Y314" s="7" t="n"/>
+      <c r="AB314" s="7" t="n"/>
     </row>
     <row r="315">
       <c r="C315" s="7" t="n"/>
       <c r="E315" s="7" t="n"/>
       <c r="G315" s="7" t="n"/>
-      <c r="L315" s="7" t="n"/>
+      <c r="I315" s="7" t="n"/>
       <c r="M315" s="7" t="n"/>
-      <c r="S315" s="7" t="n"/>
-      <c r="T315" s="7" t="n"/>
+      <c r="N315" s="7" t="n"/>
+      <c r="Q315" s="7" t="n"/>
+      <c r="U315" s="7" t="n"/>
+      <c r="V315" s="7" t="n"/>
       <c r="Y315" s="7" t="n"/>
+      <c r="AB315" s="7" t="n"/>
     </row>
     <row r="316">
       <c r="C316" s="7" t="n"/>
       <c r="E316" s="7" t="n"/>
       <c r="G316" s="7" t="n"/>
-      <c r="L316" s="7" t="n"/>
+      <c r="I316" s="7" t="n"/>
       <c r="M316" s="7" t="n"/>
-      <c r="S316" s="7" t="n"/>
-      <c r="T316" s="7" t="n"/>
+      <c r="N316" s="7" t="n"/>
+      <c r="Q316" s="7" t="n"/>
+      <c r="U316" s="7" t="n"/>
+      <c r="V316" s="7" t="n"/>
       <c r="Y316" s="7" t="n"/>
+      <c r="AB316" s="7" t="n"/>
     </row>
     <row r="317">
       <c r="C317" s="7" t="n"/>
       <c r="E317" s="7" t="n"/>
       <c r="G317" s="7" t="n"/>
-      <c r="L317" s="7" t="n"/>
+      <c r="I317" s="7" t="n"/>
       <c r="M317" s="7" t="n"/>
-      <c r="S317" s="7" t="n"/>
-      <c r="T317" s="7" t="n"/>
+      <c r="N317" s="7" t="n"/>
+      <c r="Q317" s="7" t="n"/>
+      <c r="U317" s="7" t="n"/>
+      <c r="V317" s="7" t="n"/>
       <c r="Y317" s="7" t="n"/>
+      <c r="AB317" s="7" t="n"/>
     </row>
     <row r="318">
       <c r="C318" s="7" t="n"/>
       <c r="E318" s="7" t="n"/>
       <c r="G318" s="7" t="n"/>
-      <c r="L318" s="7" t="n"/>
+      <c r="I318" s="7" t="n"/>
       <c r="M318" s="7" t="n"/>
-      <c r="S318" s="7" t="n"/>
-      <c r="T318" s="7" t="n"/>
+      <c r="N318" s="7" t="n"/>
+      <c r="Q318" s="7" t="n"/>
+      <c r="U318" s="7" t="n"/>
+      <c r="V318" s="7" t="n"/>
       <c r="Y318" s="7" t="n"/>
+      <c r="AB318" s="7" t="n"/>
     </row>
     <row r="319">
       <c r="C319" s="7" t="n"/>
       <c r="E319" s="7" t="n"/>
       <c r="G319" s="7" t="n"/>
-      <c r="L319" s="7" t="n"/>
+      <c r="I319" s="7" t="n"/>
       <c r="M319" s="7" t="n"/>
-      <c r="S319" s="7" t="n"/>
-      <c r="T319" s="7" t="n"/>
+      <c r="N319" s="7" t="n"/>
+      <c r="Q319" s="7" t="n"/>
+      <c r="U319" s="7" t="n"/>
+      <c r="V319" s="7" t="n"/>
       <c r="Y319" s="7" t="n"/>
+      <c r="AB319" s="7" t="n"/>
     </row>
     <row r="320">
       <c r="C320" s="7" t="n"/>
       <c r="E320" s="7" t="n"/>
       <c r="G320" s="7" t="n"/>
-      <c r="L320" s="7" t="n"/>
+      <c r="I320" s="7" t="n"/>
       <c r="M320" s="7" t="n"/>
-      <c r="S320" s="7" t="n"/>
-      <c r="T320" s="7" t="n"/>
+      <c r="N320" s="7" t="n"/>
+      <c r="Q320" s="7" t="n"/>
+      <c r="U320" s="7" t="n"/>
+      <c r="V320" s="7" t="n"/>
       <c r="Y320" s="7" t="n"/>
+      <c r="AB320" s="7" t="n"/>
     </row>
     <row r="321">
       <c r="C321" s="7" t="n"/>
       <c r="E321" s="7" t="n"/>
       <c r="G321" s="7" t="n"/>
-      <c r="L321" s="7" t="n"/>
+      <c r="I321" s="7" t="n"/>
       <c r="M321" s="7" t="n"/>
-      <c r="S321" s="7" t="n"/>
-      <c r="T321" s="7" t="n"/>
+      <c r="N321" s="7" t="n"/>
+      <c r="Q321" s="7" t="n"/>
+      <c r="U321" s="7" t="n"/>
+      <c r="V321" s="7" t="n"/>
       <c r="Y321" s="7" t="n"/>
+      <c r="AB321" s="7" t="n"/>
     </row>
     <row r="322">
       <c r="C322" s="7" t="n"/>
       <c r="E322" s="7" t="n"/>
       <c r="G322" s="7" t="n"/>
-      <c r="L322" s="7" t="n"/>
+      <c r="I322" s="7" t="n"/>
       <c r="M322" s="7" t="n"/>
-      <c r="S322" s="7" t="n"/>
-      <c r="T322" s="7" t="n"/>
+      <c r="N322" s="7" t="n"/>
+      <c r="Q322" s="7" t="n"/>
+      <c r="U322" s="7" t="n"/>
+      <c r="V322" s="7" t="n"/>
       <c r="Y322" s="7" t="n"/>
+      <c r="AB322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="C323" s="7" t="n"/>
       <c r="E323" s="7" t="n"/>
       <c r="G323" s="7" t="n"/>
-      <c r="L323" s="7" t="n"/>
+      <c r="I323" s="7" t="n"/>
       <c r="M323" s="7" t="n"/>
-      <c r="S323" s="7" t="n"/>
-      <c r="T323" s="7" t="n"/>
+      <c r="N323" s="7" t="n"/>
+      <c r="Q323" s="7" t="n"/>
+      <c r="U323" s="7" t="n"/>
+      <c r="V323" s="7" t="n"/>
       <c r="Y323" s="7" t="n"/>
+      <c r="AB323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="C324" s="7" t="n"/>
       <c r="E324" s="7" t="n"/>
       <c r="G324" s="7" t="n"/>
-      <c r="L324" s="7" t="n"/>
+      <c r="I324" s="7" t="n"/>
       <c r="M324" s="7" t="n"/>
-      <c r="S324" s="7" t="n"/>
-      <c r="T324" s="7" t="n"/>
+      <c r="N324" s="7" t="n"/>
+      <c r="Q324" s="7" t="n"/>
+      <c r="U324" s="7" t="n"/>
+      <c r="V324" s="7" t="n"/>
       <c r="Y324" s="7" t="n"/>
+      <c r="AB324" s="7" t="n"/>
     </row>
     <row r="325">
       <c r="C325" s="7" t="n"/>
       <c r="E325" s="7" t="n"/>
       <c r="G325" s="7" t="n"/>
-      <c r="L325" s="7" t="n"/>
+      <c r="I325" s="7" t="n"/>
       <c r="M325" s="7" t="n"/>
-      <c r="S325" s="7" t="n"/>
-      <c r="T325" s="7" t="n"/>
+      <c r="N325" s="7" t="n"/>
+      <c r="Q325" s="7" t="n"/>
+      <c r="U325" s="7" t="n"/>
+      <c r="V325" s="7" t="n"/>
       <c r="Y325" s="7" t="n"/>
+      <c r="AB325" s="7" t="n"/>
     </row>
     <row r="326">
       <c r="C326" s="7" t="n"/>
       <c r="E326" s="7" t="n"/>
       <c r="G326" s="7" t="n"/>
-      <c r="L326" s="7" t="n"/>
+      <c r="I326" s="7" t="n"/>
       <c r="M326" s="7" t="n"/>
-      <c r="S326" s="7" t="n"/>
-      <c r="T326" s="7" t="n"/>
+      <c r="N326" s="7" t="n"/>
+      <c r="Q326" s="7" t="n"/>
+      <c r="U326" s="7" t="n"/>
+      <c r="V326" s="7" t="n"/>
       <c r="Y326" s="7" t="n"/>
+      <c r="AB326" s="7" t="n"/>
     </row>
     <row r="327">
       <c r="C327" s="7" t="n"/>
       <c r="E327" s="7" t="n"/>
       <c r="G327" s="7" t="n"/>
-      <c r="L327" s="7" t="n"/>
+      <c r="I327" s="7" t="n"/>
       <c r="M327" s="7" t="n"/>
-      <c r="S327" s="7" t="n"/>
-      <c r="T327" s="7" t="n"/>
+      <c r="N327" s="7" t="n"/>
+      <c r="Q327" s="7" t="n"/>
+      <c r="U327" s="7" t="n"/>
+      <c r="V327" s="7" t="n"/>
       <c r="Y327" s="7" t="n"/>
+      <c r="AB327" s="7" t="n"/>
     </row>
     <row r="328">
       <c r="C328" s="7" t="n"/>
       <c r="E328" s="7" t="n"/>
       <c r="G328" s="7" t="n"/>
-      <c r="L328" s="7" t="n"/>
+      <c r="I328" s="7" t="n"/>
       <c r="M328" s="7" t="n"/>
-      <c r="S328" s="7" t="n"/>
-      <c r="T328" s="7" t="n"/>
+      <c r="N328" s="7" t="n"/>
+      <c r="Q328" s="7" t="n"/>
+      <c r="U328" s="7" t="n"/>
+      <c r="V328" s="7" t="n"/>
       <c r="Y328" s="7" t="n"/>
+      <c r="AB328" s="7" t="n"/>
     </row>
     <row r="329">
       <c r="C329" s="7" t="n"/>
       <c r="E329" s="7" t="n"/>
       <c r="G329" s="7" t="n"/>
-      <c r="L329" s="7" t="n"/>
+      <c r="I329" s="7" t="n"/>
       <c r="M329" s="7" t="n"/>
-      <c r="S329" s="7" t="n"/>
-      <c r="T329" s="7" t="n"/>
+      <c r="N329" s="7" t="n"/>
+      <c r="Q329" s="7" t="n"/>
+      <c r="U329" s="7" t="n"/>
+      <c r="V329" s="7" t="n"/>
       <c r="Y329" s="7" t="n"/>
+      <c r="AB329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="C330" s="7" t="n"/>
       <c r="E330" s="7" t="n"/>
       <c r="G330" s="7" t="n"/>
-      <c r="L330" s="7" t="n"/>
+      <c r="I330" s="7" t="n"/>
       <c r="M330" s="7" t="n"/>
-      <c r="S330" s="7" t="n"/>
-      <c r="T330" s="7" t="n"/>
+      <c r="N330" s="7" t="n"/>
+      <c r="Q330" s="7" t="n"/>
+      <c r="U330" s="7" t="n"/>
+      <c r="V330" s="7" t="n"/>
       <c r="Y330" s="7" t="n"/>
+      <c r="AB330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="C331" s="7" t="n"/>
       <c r="E331" s="7" t="n"/>
       <c r="G331" s="7" t="n"/>
-      <c r="L331" s="7" t="n"/>
+      <c r="I331" s="7" t="n"/>
       <c r="M331" s="7" t="n"/>
-      <c r="S331" s="7" t="n"/>
-      <c r="T331" s="7" t="n"/>
+      <c r="N331" s="7" t="n"/>
+      <c r="Q331" s="7" t="n"/>
+      <c r="U331" s="7" t="n"/>
+      <c r="V331" s="7" t="n"/>
       <c r="Y331" s="7" t="n"/>
+      <c r="AB331" s="7" t="n"/>
     </row>
     <row r="332">
       <c r="C332" s="7" t="n"/>
       <c r="E332" s="7" t="n"/>
       <c r="G332" s="7" t="n"/>
-      <c r="L332" s="7" t="n"/>
+      <c r="I332" s="7" t="n"/>
       <c r="M332" s="7" t="n"/>
-      <c r="S332" s="7" t="n"/>
-      <c r="T332" s="7" t="n"/>
+      <c r="N332" s="7" t="n"/>
+      <c r="Q332" s="7" t="n"/>
+      <c r="U332" s="7" t="n"/>
+      <c r="V332" s="7" t="n"/>
       <c r="Y332" s="7" t="n"/>
+      <c r="AB332" s="7" t="n"/>
     </row>
     <row r="333">
       <c r="C333" s="7" t="n"/>
       <c r="E333" s="7" t="n"/>
       <c r="G333" s="7" t="n"/>
-      <c r="L333" s="7" t="n"/>
+      <c r="I333" s="7" t="n"/>
       <c r="M333" s="7" t="n"/>
-      <c r="S333" s="7" t="n"/>
-      <c r="T333" s="7" t="n"/>
+      <c r="N333" s="7" t="n"/>
+      <c r="Q333" s="7" t="n"/>
+      <c r="U333" s="7" t="n"/>
+      <c r="V333" s="7" t="n"/>
       <c r="Y333" s="7" t="n"/>
+      <c r="AB333" s="7" t="n"/>
     </row>
     <row r="334">
       <c r="C334" s="7" t="n"/>
       <c r="E334" s="7" t="n"/>
       <c r="G334" s="7" t="n"/>
-      <c r="L334" s="7" t="n"/>
+      <c r="I334" s="7" t="n"/>
       <c r="M334" s="7" t="n"/>
-      <c r="S334" s="7" t="n"/>
-      <c r="T334" s="7" t="n"/>
+      <c r="N334" s="7" t="n"/>
+      <c r="Q334" s="7" t="n"/>
+      <c r="U334" s="7" t="n"/>
+      <c r="V334" s="7" t="n"/>
       <c r="Y334" s="7" t="n"/>
+      <c r="AB334" s="7" t="n"/>
     </row>
     <row r="335">
       <c r="C335" s="7" t="n"/>
       <c r="E335" s="7" t="n"/>
       <c r="G335" s="7" t="n"/>
-      <c r="L335" s="7" t="n"/>
+      <c r="I335" s="7" t="n"/>
       <c r="M335" s="7" t="n"/>
-      <c r="S335" s="7" t="n"/>
-      <c r="T335" s="7" t="n"/>
+      <c r="N335" s="7" t="n"/>
+      <c r="Q335" s="7" t="n"/>
+      <c r="U335" s="7" t="n"/>
+      <c r="V335" s="7" t="n"/>
       <c r="Y335" s="7" t="n"/>
+      <c r="AB335" s="7" t="n"/>
     </row>
     <row r="336">
       <c r="C336" s="7" t="n"/>
       <c r="E336" s="7" t="n"/>
       <c r="G336" s="7" t="n"/>
-      <c r="L336" s="7" t="n"/>
+      <c r="I336" s="7" t="n"/>
       <c r="M336" s="7" t="n"/>
-      <c r="S336" s="7" t="n"/>
-      <c r="T336" s="7" t="n"/>
+      <c r="N336" s="7" t="n"/>
+      <c r="Q336" s="7" t="n"/>
+      <c r="U336" s="7" t="n"/>
+      <c r="V336" s="7" t="n"/>
       <c r="Y336" s="7" t="n"/>
+      <c r="AB336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="C337" s="7" t="n"/>
       <c r="E337" s="7" t="n"/>
       <c r="G337" s="7" t="n"/>
-      <c r="L337" s="7" t="n"/>
+      <c r="I337" s="7" t="n"/>
       <c r="M337" s="7" t="n"/>
-      <c r="S337" s="7" t="n"/>
-      <c r="T337" s="7" t="n"/>
+      <c r="N337" s="7" t="n"/>
+      <c r="Q337" s="7" t="n"/>
+      <c r="U337" s="7" t="n"/>
+      <c r="V337" s="7" t="n"/>
       <c r="Y337" s="7" t="n"/>
+      <c r="AB337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="C338" s="7" t="n"/>
       <c r="E338" s="7" t="n"/>
       <c r="G338" s="7" t="n"/>
-      <c r="L338" s="7" t="n"/>
+      <c r="I338" s="7" t="n"/>
       <c r="M338" s="7" t="n"/>
-      <c r="S338" s="7" t="n"/>
-      <c r="T338" s="7" t="n"/>
+      <c r="N338" s="7" t="n"/>
+      <c r="Q338" s="7" t="n"/>
+      <c r="U338" s="7" t="n"/>
+      <c r="V338" s="7" t="n"/>
       <c r="Y338" s="7" t="n"/>
+      <c r="AB338" s="7" t="n"/>
     </row>
     <row r="339">
       <c r="C339" s="7" t="n"/>
       <c r="E339" s="7" t="n"/>
       <c r="G339" s="7" t="n"/>
-      <c r="L339" s="7" t="n"/>
+      <c r="I339" s="7" t="n"/>
       <c r="M339" s="7" t="n"/>
-      <c r="S339" s="7" t="n"/>
-      <c r="T339" s="7" t="n"/>
+      <c r="N339" s="7" t="n"/>
+      <c r="Q339" s="7" t="n"/>
+      <c r="U339" s="7" t="n"/>
+      <c r="V339" s="7" t="n"/>
       <c r="Y339" s="7" t="n"/>
+      <c r="AB339" s="7" t="n"/>
     </row>
     <row r="340">
       <c r="C340" s="7" t="n"/>
       <c r="E340" s="7" t="n"/>
       <c r="G340" s="7" t="n"/>
-      <c r="L340" s="7" t="n"/>
+      <c r="I340" s="7" t="n"/>
       <c r="M340" s="7" t="n"/>
-      <c r="S340" s="7" t="n"/>
-      <c r="T340" s="7" t="n"/>
+      <c r="N340" s="7" t="n"/>
+      <c r="Q340" s="7" t="n"/>
+      <c r="U340" s="7" t="n"/>
+      <c r="V340" s="7" t="n"/>
       <c r="Y340" s="7" t="n"/>
+      <c r="AB340" s="7" t="n"/>
     </row>
     <row r="341">
       <c r="C341" s="7" t="n"/>
       <c r="E341" s="7" t="n"/>
       <c r="G341" s="7" t="n"/>
-      <c r="L341" s="7" t="n"/>
+      <c r="I341" s="7" t="n"/>
       <c r="M341" s="7" t="n"/>
-      <c r="S341" s="7" t="n"/>
-      <c r="T341" s="7" t="n"/>
+      <c r="N341" s="7" t="n"/>
+      <c r="Q341" s="7" t="n"/>
+      <c r="U341" s="7" t="n"/>
+      <c r="V341" s="7" t="n"/>
       <c r="Y341" s="7" t="n"/>
+      <c r="AB341" s="7" t="n"/>
     </row>
     <row r="342">
       <c r="C342" s="7" t="n"/>
       <c r="E342" s="7" t="n"/>
       <c r="G342" s="7" t="n"/>
-      <c r="L342" s="7" t="n"/>
+      <c r="I342" s="7" t="n"/>
       <c r="M342" s="7" t="n"/>
-      <c r="S342" s="7" t="n"/>
-      <c r="T342" s="7" t="n"/>
+      <c r="N342" s="7" t="n"/>
+      <c r="Q342" s="7" t="n"/>
+      <c r="U342" s="7" t="n"/>
+      <c r="V342" s="7" t="n"/>
       <c r="Y342" s="7" t="n"/>
+      <c r="AB342" s="7" t="n"/>
     </row>
     <row r="343">
       <c r="C343" s="7" t="n"/>
       <c r="E343" s="7" t="n"/>
       <c r="G343" s="7" t="n"/>
-      <c r="L343" s="7" t="n"/>
+      <c r="I343" s="7" t="n"/>
       <c r="M343" s="7" t="n"/>
-      <c r="S343" s="7" t="n"/>
-      <c r="T343" s="7" t="n"/>
+      <c r="N343" s="7" t="n"/>
+      <c r="Q343" s="7" t="n"/>
+      <c r="U343" s="7" t="n"/>
+      <c r="V343" s="7" t="n"/>
       <c r="Y343" s="7" t="n"/>
+      <c r="AB343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="C344" s="7" t="n"/>
       <c r="E344" s="7" t="n"/>
       <c r="G344" s="7" t="n"/>
-      <c r="L344" s="7" t="n"/>
+      <c r="I344" s="7" t="n"/>
       <c r="M344" s="7" t="n"/>
-      <c r="S344" s="7" t="n"/>
-      <c r="T344" s="7" t="n"/>
+      <c r="N344" s="7" t="n"/>
+      <c r="Q344" s="7" t="n"/>
+      <c r="U344" s="7" t="n"/>
+      <c r="V344" s="7" t="n"/>
       <c r="Y344" s="7" t="n"/>
+      <c r="AB344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="C345" s="7" t="n"/>
       <c r="E345" s="7" t="n"/>
       <c r="G345" s="7" t="n"/>
-      <c r="L345" s="7" t="n"/>
+      <c r="I345" s="7" t="n"/>
       <c r="M345" s="7" t="n"/>
-      <c r="S345" s="7" t="n"/>
-      <c r="T345" s="7" t="n"/>
+      <c r="N345" s="7" t="n"/>
+      <c r="Q345" s="7" t="n"/>
+      <c r="U345" s="7" t="n"/>
+      <c r="V345" s="7" t="n"/>
       <c r="Y345" s="7" t="n"/>
+      <c r="AB345" s="7" t="n"/>
     </row>
     <row r="346">
       <c r="C346" s="7" t="n"/>
       <c r="E346" s="7" t="n"/>
       <c r="G346" s="7" t="n"/>
-      <c r="L346" s="7" t="n"/>
+      <c r="I346" s="7" t="n"/>
       <c r="M346" s="7" t="n"/>
-      <c r="S346" s="7" t="n"/>
-      <c r="T346" s="7" t="n"/>
+      <c r="N346" s="7" t="n"/>
+      <c r="Q346" s="7" t="n"/>
+      <c r="U346" s="7" t="n"/>
+      <c r="V346" s="7" t="n"/>
       <c r="Y346" s="7" t="n"/>
+      <c r="AB346" s="7" t="n"/>
     </row>
     <row r="347">
       <c r="C347" s="7" t="n"/>
       <c r="E347" s="7" t="n"/>
       <c r="G347" s="7" t="n"/>
-      <c r="L347" s="7" t="n"/>
+      <c r="I347" s="7" t="n"/>
       <c r="M347" s="7" t="n"/>
-      <c r="S347" s="7" t="n"/>
-      <c r="T347" s="7" t="n"/>
+      <c r="N347" s="7" t="n"/>
+      <c r="Q347" s="7" t="n"/>
+      <c r="U347" s="7" t="n"/>
+      <c r="V347" s="7" t="n"/>
       <c r="Y347" s="7" t="n"/>
+      <c r="AB347" s="7" t="n"/>
     </row>
     <row r="348">
       <c r="C348" s="7" t="n"/>
       <c r="E348" s="7" t="n"/>
       <c r="G348" s="7" t="n"/>
-      <c r="L348" s="7" t="n"/>
+      <c r="I348" s="7" t="n"/>
       <c r="M348" s="7" t="n"/>
-      <c r="S348" s="7" t="n"/>
-      <c r="T348" s="7" t="n"/>
+      <c r="N348" s="7" t="n"/>
+      <c r="Q348" s="7" t="n"/>
+      <c r="U348" s="7" t="n"/>
+      <c r="V348" s="7" t="n"/>
       <c r="Y348" s="7" t="n"/>
+      <c r="AB348" s="7" t="n"/>
     </row>
     <row r="349">
       <c r="C349" s="7" t="n"/>
       <c r="E349" s="7" t="n"/>
       <c r="G349" s="7" t="n"/>
-      <c r="L349" s="7" t="n"/>
+      <c r="I349" s="7" t="n"/>
       <c r="M349" s="7" t="n"/>
-      <c r="S349" s="7" t="n"/>
-      <c r="T349" s="7" t="n"/>
+      <c r="N349" s="7" t="n"/>
+      <c r="Q349" s="7" t="n"/>
+      <c r="U349" s="7" t="n"/>
+      <c r="V349" s="7" t="n"/>
       <c r="Y349" s="7" t="n"/>
+      <c r="AB349" s="7" t="n"/>
     </row>
     <row r="350">
       <c r="C350" s="7" t="n"/>
       <c r="E350" s="7" t="n"/>
       <c r="G350" s="7" t="n"/>
-      <c r="L350" s="7" t="n"/>
+      <c r="I350" s="7" t="n"/>
       <c r="M350" s="7" t="n"/>
-      <c r="S350" s="7" t="n"/>
-      <c r="T350" s="7" t="n"/>
+      <c r="N350" s="7" t="n"/>
+      <c r="Q350" s="7" t="n"/>
+      <c r="U350" s="7" t="n"/>
+      <c r="V350" s="7" t="n"/>
       <c r="Y350" s="7" t="n"/>
+      <c r="AB350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="C351" s="7" t="n"/>
       <c r="E351" s="7" t="n"/>
       <c r="G351" s="7" t="n"/>
-      <c r="L351" s="7" t="n"/>
+      <c r="I351" s="7" t="n"/>
       <c r="M351" s="7" t="n"/>
-      <c r="S351" s="7" t="n"/>
-      <c r="T351" s="7" t="n"/>
+      <c r="N351" s="7" t="n"/>
+      <c r="Q351" s="7" t="n"/>
+      <c r="U351" s="7" t="n"/>
+      <c r="V351" s="7" t="n"/>
       <c r="Y351" s="7" t="n"/>
+      <c r="AB351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="C352" s="7" t="n"/>
       <c r="E352" s="7" t="n"/>
       <c r="G352" s="7" t="n"/>
-      <c r="L352" s="7" t="n"/>
+      <c r="I352" s="7" t="n"/>
       <c r="M352" s="7" t="n"/>
-      <c r="S352" s="7" t="n"/>
-      <c r="T352" s="7" t="n"/>
+      <c r="N352" s="7" t="n"/>
+      <c r="Q352" s="7" t="n"/>
+      <c r="U352" s="7" t="n"/>
+      <c r="V352" s="7" t="n"/>
       <c r="Y352" s="7" t="n"/>
+      <c r="AB352" s="7" t="n"/>
     </row>
     <row r="353">
       <c r="C353" s="7" t="n"/>
       <c r="E353" s="7" t="n"/>
       <c r="G353" s="7" t="n"/>
-      <c r="L353" s="7" t="n"/>
+      <c r="I353" s="7" t="n"/>
       <c r="M353" s="7" t="n"/>
-      <c r="S353" s="7" t="n"/>
-      <c r="T353" s="7" t="n"/>
+      <c r="N353" s="7" t="n"/>
+      <c r="Q353" s="7" t="n"/>
+      <c r="U353" s="7" t="n"/>
+      <c r="V353" s="7" t="n"/>
       <c r="Y353" s="7" t="n"/>
+      <c r="AB353" s="7" t="n"/>
     </row>
     <row r="354">
       <c r="C354" s="7" t="n"/>
       <c r="E354" s="7" t="n"/>
       <c r="G354" s="7" t="n"/>
-      <c r="L354" s="7" t="n"/>
+      <c r="I354" s="7" t="n"/>
       <c r="M354" s="7" t="n"/>
-      <c r="S354" s="7" t="n"/>
-      <c r="T354" s="7" t="n"/>
+      <c r="N354" s="7" t="n"/>
+      <c r="Q354" s="7" t="n"/>
+      <c r="U354" s="7" t="n"/>
+      <c r="V354" s="7" t="n"/>
       <c r="Y354" s="7" t="n"/>
+      <c r="AB354" s="7" t="n"/>
     </row>
     <row r="355">
       <c r="C355" s="7" t="n"/>
       <c r="E355" s="7" t="n"/>
       <c r="G355" s="7" t="n"/>
-      <c r="L355" s="7" t="n"/>
+      <c r="I355" s="7" t="n"/>
       <c r="M355" s="7" t="n"/>
-      <c r="S355" s="7" t="n"/>
-      <c r="T355" s="7" t="n"/>
+      <c r="N355" s="7" t="n"/>
+      <c r="Q355" s="7" t="n"/>
+      <c r="U355" s="7" t="n"/>
+      <c r="V355" s="7" t="n"/>
       <c r="Y355" s="7" t="n"/>
+      <c r="AB355" s="7" t="n"/>
     </row>
     <row r="356">
       <c r="C356" s="7" t="n"/>
       <c r="E356" s="7" t="n"/>
       <c r="G356" s="7" t="n"/>
-      <c r="L356" s="7" t="n"/>
+      <c r="I356" s="7" t="n"/>
       <c r="M356" s="7" t="n"/>
-      <c r="S356" s="7" t="n"/>
-      <c r="T356" s="7" t="n"/>
+      <c r="N356" s="7" t="n"/>
+      <c r="Q356" s="7" t="n"/>
+      <c r="U356" s="7" t="n"/>
+      <c r="V356" s="7" t="n"/>
       <c r="Y356" s="7" t="n"/>
+      <c r="AB356" s="7" t="n"/>
     </row>
     <row r="357">
       <c r="C357" s="7" t="n"/>
       <c r="E357" s="7" t="n"/>
       <c r="G357" s="7" t="n"/>
-      <c r="L357" s="7" t="n"/>
+      <c r="I357" s="7" t="n"/>
       <c r="M357" s="7" t="n"/>
-      <c r="S357" s="7" t="n"/>
-      <c r="T357" s="7" t="n"/>
+      <c r="N357" s="7" t="n"/>
+      <c r="Q357" s="7" t="n"/>
+      <c r="U357" s="7" t="n"/>
+      <c r="V357" s="7" t="n"/>
       <c r="Y357" s="7" t="n"/>
+      <c r="AB357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="C358" s="7" t="n"/>
       <c r="E358" s="7" t="n"/>
       <c r="G358" s="7" t="n"/>
-      <c r="L358" s="7" t="n"/>
+      <c r="I358" s="7" t="n"/>
       <c r="M358" s="7" t="n"/>
-      <c r="S358" s="7" t="n"/>
-      <c r="T358" s="7" t="n"/>
+      <c r="N358" s="7" t="n"/>
+      <c r="Q358" s="7" t="n"/>
+      <c r="U358" s="7" t="n"/>
+      <c r="V358" s="7" t="n"/>
       <c r="Y358" s="7" t="n"/>
+      <c r="AB358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="C359" s="7" t="n"/>
       <c r="E359" s="7" t="n"/>
       <c r="G359" s="7" t="n"/>
-      <c r="L359" s="7" t="n"/>
+      <c r="I359" s="7" t="n"/>
       <c r="M359" s="7" t="n"/>
-      <c r="S359" s="7" t="n"/>
-      <c r="T359" s="7" t="n"/>
+      <c r="N359" s="7" t="n"/>
+      <c r="Q359" s="7" t="n"/>
+      <c r="U359" s="7" t="n"/>
+      <c r="V359" s="7" t="n"/>
       <c r="Y359" s="7" t="n"/>
+      <c r="AB359" s="7" t="n"/>
     </row>
     <row r="360">
       <c r="C360" s="7" t="n"/>
       <c r="E360" s="7" t="n"/>
       <c r="G360" s="7" t="n"/>
-      <c r="L360" s="7" t="n"/>
+      <c r="I360" s="7" t="n"/>
       <c r="M360" s="7" t="n"/>
-      <c r="S360" s="7" t="n"/>
-      <c r="T360" s="7" t="n"/>
+      <c r="N360" s="7" t="n"/>
+      <c r="Q360" s="7" t="n"/>
+      <c r="U360" s="7" t="n"/>
+      <c r="V360" s="7" t="n"/>
       <c r="Y360" s="7" t="n"/>
+      <c r="AB360" s="7" t="n"/>
     </row>
     <row r="361">
       <c r="C361" s="7" t="n"/>
       <c r="E361" s="7" t="n"/>
       <c r="G361" s="7" t="n"/>
-      <c r="L361" s="7" t="n"/>
+      <c r="I361" s="7" t="n"/>
       <c r="M361" s="7" t="n"/>
-      <c r="S361" s="7" t="n"/>
-      <c r="T361" s="7" t="n"/>
+      <c r="N361" s="7" t="n"/>
+      <c r="Q361" s="7" t="n"/>
+      <c r="U361" s="7" t="n"/>
+      <c r="V361" s="7" t="n"/>
       <c r="Y361" s="7" t="n"/>
+      <c r="AB361" s="7" t="n"/>
     </row>
     <row r="362">
       <c r="C362" s="7" t="n"/>
       <c r="E362" s="7" t="n"/>
       <c r="G362" s="7" t="n"/>
-      <c r="L362" s="7" t="n"/>
+      <c r="I362" s="7" t="n"/>
       <c r="M362" s="7" t="n"/>
-      <c r="S362" s="7" t="n"/>
-      <c r="T362" s="7" t="n"/>
+      <c r="N362" s="7" t="n"/>
+      <c r="Q362" s="7" t="n"/>
+      <c r="U362" s="7" t="n"/>
+      <c r="V362" s="7" t="n"/>
       <c r="Y362" s="7" t="n"/>
+      <c r="AB362" s="7" t="n"/>
     </row>
     <row r="363">
       <c r="C363" s="7" t="n"/>
       <c r="E363" s="7" t="n"/>
       <c r="G363" s="7" t="n"/>
-      <c r="L363" s="7" t="n"/>
+      <c r="I363" s="7" t="n"/>
       <c r="M363" s="7" t="n"/>
-      <c r="S363" s="7" t="n"/>
-      <c r="T363" s="7" t="n"/>
+      <c r="N363" s="7" t="n"/>
+      <c r="Q363" s="7" t="n"/>
+      <c r="U363" s="7" t="n"/>
+      <c r="V363" s="7" t="n"/>
       <c r="Y363" s="7" t="n"/>
+      <c r="AB363" s="7" t="n"/>
     </row>
     <row r="364">
       <c r="C364" s="7" t="n"/>
       <c r="E364" s="7" t="n"/>
       <c r="G364" s="7" t="n"/>
-      <c r="L364" s="7" t="n"/>
+      <c r="I364" s="7" t="n"/>
       <c r="M364" s="7" t="n"/>
-      <c r="S364" s="7" t="n"/>
-      <c r="T364" s="7" t="n"/>
+      <c r="N364" s="7" t="n"/>
+      <c r="Q364" s="7" t="n"/>
+      <c r="U364" s="7" t="n"/>
+      <c r="V364" s="7" t="n"/>
       <c r="Y364" s="7" t="n"/>
+      <c r="AB364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="C365" s="7" t="n"/>
       <c r="E365" s="7" t="n"/>
       <c r="G365" s="7" t="n"/>
-      <c r="L365" s="7" t="n"/>
+      <c r="I365" s="7" t="n"/>
       <c r="M365" s="7" t="n"/>
-      <c r="S365" s="7" t="n"/>
-      <c r="T365" s="7" t="n"/>
+      <c r="N365" s="7" t="n"/>
+      <c r="Q365" s="7" t="n"/>
+      <c r="U365" s="7" t="n"/>
+      <c r="V365" s="7" t="n"/>
       <c r="Y365" s="7" t="n"/>
+      <c r="AB365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="C366" s="7" t="n"/>
       <c r="E366" s="7" t="n"/>
       <c r="G366" s="7" t="n"/>
-      <c r="L366" s="7" t="n"/>
+      <c r="I366" s="7" t="n"/>
       <c r="M366" s="7" t="n"/>
-      <c r="S366" s="7" t="n"/>
-      <c r="T366" s="7" t="n"/>
+      <c r="N366" s="7" t="n"/>
+      <c r="Q366" s="7" t="n"/>
+      <c r="U366" s="7" t="n"/>
+      <c r="V366" s="7" t="n"/>
       <c r="Y366" s="7" t="n"/>
+      <c r="AB366" s="7" t="n"/>
     </row>
     <row r="367">
       <c r="C367" s="7" t="n"/>
       <c r="E367" s="7" t="n"/>
       <c r="G367" s="7" t="n"/>
-      <c r="L367" s="7" t="n"/>
+      <c r="I367" s="7" t="n"/>
       <c r="M367" s="7" t="n"/>
-      <c r="S367" s="7" t="n"/>
-      <c r="T367" s="7" t="n"/>
+      <c r="N367" s="7" t="n"/>
+      <c r="Q367" s="7" t="n"/>
+      <c r="U367" s="7" t="n"/>
+      <c r="V367" s="7" t="n"/>
       <c r="Y367" s="7" t="n"/>
+      <c r="AB367" s="7" t="n"/>
     </row>
     <row r="368">
       <c r="C368" s="7" t="n"/>
       <c r="E368" s="7" t="n"/>
       <c r="G368" s="7" t="n"/>
-      <c r="L368" s="7" t="n"/>
+      <c r="I368" s="7" t="n"/>
       <c r="M368" s="7" t="n"/>
-      <c r="S368" s="7" t="n"/>
-      <c r="T368" s="7" t="n"/>
+      <c r="N368" s="7" t="n"/>
+      <c r="Q368" s="7" t="n"/>
+      <c r="U368" s="7" t="n"/>
+      <c r="V368" s="7" t="n"/>
       <c r="Y368" s="7" t="n"/>
+      <c r="AB368" s="7" t="n"/>
     </row>
     <row r="369">
       <c r="C369" s="7" t="n"/>
       <c r="E369" s="7" t="n"/>
       <c r="G369" s="7" t="n"/>
-      <c r="L369" s="7" t="n"/>
+      <c r="I369" s="7" t="n"/>
       <c r="M369" s="7" t="n"/>
-      <c r="S369" s="7" t="n"/>
-      <c r="T369" s="7" t="n"/>
+      <c r="N369" s="7" t="n"/>
+      <c r="Q369" s="7" t="n"/>
+      <c r="U369" s="7" t="n"/>
+      <c r="V369" s="7" t="n"/>
       <c r="Y369" s="7" t="n"/>
+      <c r="AB369" s="7" t="n"/>
     </row>
     <row r="370">
       <c r="C370" s="7" t="n"/>
       <c r="E370" s="7" t="n"/>
       <c r="G370" s="7" t="n"/>
-      <c r="L370" s="7" t="n"/>
+      <c r="I370" s="7" t="n"/>
       <c r="M370" s="7" t="n"/>
-      <c r="S370" s="7" t="n"/>
-      <c r="T370" s="7" t="n"/>
+      <c r="N370" s="7" t="n"/>
+      <c r="Q370" s="7" t="n"/>
+      <c r="U370" s="7" t="n"/>
+      <c r="V370" s="7" t="n"/>
       <c r="Y370" s="7" t="n"/>
+      <c r="AB370" s="7" t="n"/>
     </row>
     <row r="371">
       <c r="C371" s="7" t="n"/>
       <c r="E371" s="7" t="n"/>
       <c r="G371" s="7" t="n"/>
-      <c r="L371" s="7" t="n"/>
+      <c r="I371" s="7" t="n"/>
       <c r="M371" s="7" t="n"/>
-      <c r="S371" s="7" t="n"/>
-      <c r="T371" s="7" t="n"/>
+      <c r="N371" s="7" t="n"/>
+      <c r="Q371" s="7" t="n"/>
+      <c r="U371" s="7" t="n"/>
+      <c r="V371" s="7" t="n"/>
       <c r="Y371" s="7" t="n"/>
+      <c r="AB371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="C372" s="7" t="n"/>
       <c r="E372" s="7" t="n"/>
       <c r="G372" s="7" t="n"/>
-      <c r="L372" s="7" t="n"/>
+      <c r="I372" s="7" t="n"/>
       <c r="M372" s="7" t="n"/>
-      <c r="S372" s="7" t="n"/>
-      <c r="T372" s="7" t="n"/>
+      <c r="N372" s="7" t="n"/>
+      <c r="Q372" s="7" t="n"/>
+      <c r="U372" s="7" t="n"/>
+      <c r="V372" s="7" t="n"/>
       <c r="Y372" s="7" t="n"/>
+      <c r="AB372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="C373" s="7" t="n"/>
       <c r="E373" s="7" t="n"/>
       <c r="G373" s="7" t="n"/>
-      <c r="L373" s="7" t="n"/>
+      <c r="I373" s="7" t="n"/>
       <c r="M373" s="7" t="n"/>
-      <c r="S373" s="7" t="n"/>
-      <c r="T373" s="7" t="n"/>
+      <c r="N373" s="7" t="n"/>
+      <c r="Q373" s="7" t="n"/>
+      <c r="U373" s="7" t="n"/>
+      <c r="V373" s="7" t="n"/>
       <c r="Y373" s="7" t="n"/>
+      <c r="AB373" s="7" t="n"/>
     </row>
     <row r="374">
       <c r="C374" s="7" t="n"/>
       <c r="E374" s="7" t="n"/>
       <c r="G374" s="7" t="n"/>
-      <c r="L374" s="7" t="n"/>
+      <c r="I374" s="7" t="n"/>
       <c r="M374" s="7" t="n"/>
-      <c r="S374" s="7" t="n"/>
-      <c r="T374" s="7" t="n"/>
+      <c r="N374" s="7" t="n"/>
+      <c r="Q374" s="7" t="n"/>
+      <c r="U374" s="7" t="n"/>
+      <c r="V374" s="7" t="n"/>
       <c r="Y374" s="7" t="n"/>
+      <c r="AB374" s="7" t="n"/>
     </row>
     <row r="375">
       <c r="C375" s="7" t="n"/>
       <c r="E375" s="7" t="n"/>
       <c r="G375" s="7" t="n"/>
-      <c r="L375" s="7" t="n"/>
+      <c r="I375" s="7" t="n"/>
       <c r="M375" s="7" t="n"/>
-      <c r="S375" s="7" t="n"/>
-      <c r="T375" s="7" t="n"/>
+      <c r="N375" s="7" t="n"/>
+      <c r="Q375" s="7" t="n"/>
+      <c r="U375" s="7" t="n"/>
+      <c r="V375" s="7" t="n"/>
       <c r="Y375" s="7" t="n"/>
+      <c r="AB375" s="7" t="n"/>
     </row>
     <row r="376">
       <c r="C376" s="7" t="n"/>
       <c r="E376" s="7" t="n"/>
       <c r="G376" s="7" t="n"/>
-      <c r="L376" s="7" t="n"/>
+      <c r="I376" s="7" t="n"/>
       <c r="M376" s="7" t="n"/>
-      <c r="S376" s="7" t="n"/>
-      <c r="T376" s="7" t="n"/>
+      <c r="N376" s="7" t="n"/>
+      <c r="Q376" s="7" t="n"/>
+      <c r="U376" s="7" t="n"/>
+      <c r="V376" s="7" t="n"/>
       <c r="Y376" s="7" t="n"/>
+      <c r="AB376" s="7" t="n"/>
     </row>
     <row r="377">
       <c r="C377" s="7" t="n"/>
       <c r="E377" s="7" t="n"/>
       <c r="G377" s="7" t="n"/>
-      <c r="L377" s="7" t="n"/>
+      <c r="I377" s="7" t="n"/>
       <c r="M377" s="7" t="n"/>
-      <c r="S377" s="7" t="n"/>
-      <c r="T377" s="7" t="n"/>
+      <c r="N377" s="7" t="n"/>
+      <c r="Q377" s="7" t="n"/>
+      <c r="U377" s="7" t="n"/>
+      <c r="V377" s="7" t="n"/>
       <c r="Y377" s="7" t="n"/>
+      <c r="AB377" s="7" t="n"/>
     </row>
     <row r="378">
       <c r="C378" s="7" t="n"/>
       <c r="E378" s="7" t="n"/>
       <c r="G378" s="7" t="n"/>
-      <c r="L378" s="7" t="n"/>
+      <c r="I378" s="7" t="n"/>
       <c r="M378" s="7" t="n"/>
-      <c r="S378" s="7" t="n"/>
-      <c r="T378" s="7" t="n"/>
+      <c r="N378" s="7" t="n"/>
+      <c r="Q378" s="7" t="n"/>
+      <c r="U378" s="7" t="n"/>
+      <c r="V378" s="7" t="n"/>
       <c r="Y378" s="7" t="n"/>
+      <c r="AB378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="C379" s="7" t="n"/>
       <c r="E379" s="7" t="n"/>
       <c r="G379" s="7" t="n"/>
-      <c r="L379" s="7" t="n"/>
+      <c r="I379" s="7" t="n"/>
       <c r="M379" s="7" t="n"/>
-      <c r="S379" s="7" t="n"/>
-      <c r="T379" s="7" t="n"/>
+      <c r="N379" s="7" t="n"/>
+      <c r="Q379" s="7" t="n"/>
+      <c r="U379" s="7" t="n"/>
+      <c r="V379" s="7" t="n"/>
       <c r="Y379" s="7" t="n"/>
+      <c r="AB379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="C380" s="7" t="n"/>
       <c r="E380" s="7" t="n"/>
       <c r="G380" s="7" t="n"/>
-      <c r="L380" s="7" t="n"/>
+      <c r="I380" s="7" t="n"/>
       <c r="M380" s="7" t="n"/>
-      <c r="S380" s="7" t="n"/>
-      <c r="T380" s="7" t="n"/>
+      <c r="N380" s="7" t="n"/>
+      <c r="Q380" s="7" t="n"/>
+      <c r="U380" s="7" t="n"/>
+      <c r="V380" s="7" t="n"/>
       <c r="Y380" s="7" t="n"/>
+      <c r="AB380" s="7" t="n"/>
     </row>
     <row r="381">
       <c r="C381" s="7" t="n"/>
       <c r="E381" s="7" t="n"/>
       <c r="G381" s="7" t="n"/>
-      <c r="L381" s="7" t="n"/>
+      <c r="I381" s="7" t="n"/>
       <c r="M381" s="7" t="n"/>
-      <c r="S381" s="7" t="n"/>
-      <c r="T381" s="7" t="n"/>
+      <c r="N381" s="7" t="n"/>
+      <c r="Q381" s="7" t="n"/>
+      <c r="U381" s="7" t="n"/>
+      <c r="V381" s="7" t="n"/>
       <c r="Y381" s="7" t="n"/>
+      <c r="AB381" s="7" t="n"/>
     </row>
     <row r="382">
       <c r="C382" s="7" t="n"/>
       <c r="E382" s="7" t="n"/>
       <c r="G382" s="7" t="n"/>
-      <c r="L382" s="7" t="n"/>
+      <c r="I382" s="7" t="n"/>
       <c r="M382" s="7" t="n"/>
-      <c r="S382" s="7" t="n"/>
-      <c r="T382" s="7" t="n"/>
+      <c r="N382" s="7" t="n"/>
+      <c r="Q382" s="7" t="n"/>
+      <c r="U382" s="7" t="n"/>
+      <c r="V382" s="7" t="n"/>
       <c r="Y382" s="7" t="n"/>
+      <c r="AB382" s="7" t="n"/>
     </row>
     <row r="383">
       <c r="C383" s="7" t="n"/>
       <c r="E383" s="7" t="n"/>
       <c r="G383" s="7" t="n"/>
-      <c r="L383" s="7" t="n"/>
+      <c r="I383" s="7" t="n"/>
       <c r="M383" s="7" t="n"/>
-      <c r="S383" s="7" t="n"/>
-      <c r="T383" s="7" t="n"/>
+      <c r="N383" s="7" t="n"/>
+      <c r="Q383" s="7" t="n"/>
+      <c r="U383" s="7" t="n"/>
+      <c r="V383" s="7" t="n"/>
       <c r="Y383" s="7" t="n"/>
+      <c r="AB383" s="7" t="n"/>
     </row>
     <row r="384">
       <c r="C384" s="7" t="n"/>
       <c r="E384" s="7" t="n"/>
       <c r="G384" s="7" t="n"/>
-      <c r="L384" s="7" t="n"/>
+      <c r="I384" s="7" t="n"/>
       <c r="M384" s="7" t="n"/>
-      <c r="S384" s="7" t="n"/>
-      <c r="T384" s="7" t="n"/>
+      <c r="N384" s="7" t="n"/>
+      <c r="Q384" s="7" t="n"/>
+      <c r="U384" s="7" t="n"/>
+      <c r="V384" s="7" t="n"/>
       <c r="Y384" s="7" t="n"/>
+      <c r="AB384" s="7" t="n"/>
     </row>
     <row r="385">
       <c r="C385" s="7" t="n"/>
       <c r="E385" s="7" t="n"/>
       <c r="G385" s="7" t="n"/>
-      <c r="L385" s="7" t="n"/>
+      <c r="I385" s="7" t="n"/>
       <c r="M385" s="7" t="n"/>
-      <c r="S385" s="7" t="n"/>
-      <c r="T385" s="7" t="n"/>
+      <c r="N385" s="7" t="n"/>
+      <c r="Q385" s="7" t="n"/>
+      <c r="U385" s="7" t="n"/>
+      <c r="V385" s="7" t="n"/>
       <c r="Y385" s="7" t="n"/>
+      <c r="AB385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="C386" s="7" t="n"/>
       <c r="E386" s="7" t="n"/>
       <c r="G386" s="7" t="n"/>
-      <c r="L386" s="7" t="n"/>
+      <c r="I386" s="7" t="n"/>
       <c r="M386" s="7" t="n"/>
-      <c r="S386" s="7" t="n"/>
-      <c r="T386" s="7" t="n"/>
+      <c r="N386" s="7" t="n"/>
+      <c r="Q386" s="7" t="n"/>
+      <c r="U386" s="7" t="n"/>
+      <c r="V386" s="7" t="n"/>
       <c r="Y386" s="7" t="n"/>
+      <c r="AB386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="C387" s="7" t="n"/>
       <c r="E387" s="7" t="n"/>
       <c r="G387" s="7" t="n"/>
-      <c r="L387" s="7" t="n"/>
+      <c r="I387" s="7" t="n"/>
       <c r="M387" s="7" t="n"/>
-      <c r="S387" s="7" t="n"/>
-      <c r="T387" s="7" t="n"/>
+      <c r="N387" s="7" t="n"/>
+      <c r="Q387" s="7" t="n"/>
+      <c r="U387" s="7" t="n"/>
+      <c r="V387" s="7" t="n"/>
       <c r="Y387" s="7" t="n"/>
+      <c r="AB387" s="7" t="n"/>
     </row>
     <row r="388">
       <c r="C388" s="7" t="n"/>
       <c r="E388" s="7" t="n"/>
       <c r="G388" s="7" t="n"/>
-      <c r="L388" s="7" t="n"/>
+      <c r="I388" s="7" t="n"/>
       <c r="M388" s="7" t="n"/>
-      <c r="S388" s="7" t="n"/>
-      <c r="T388" s="7" t="n"/>
+      <c r="N388" s="7" t="n"/>
+      <c r="Q388" s="7" t="n"/>
+      <c r="U388" s="7" t="n"/>
+      <c r="V388" s="7" t="n"/>
       <c r="Y388" s="7" t="n"/>
+      <c r="AB388" s="7" t="n"/>
     </row>
     <row r="389">
       <c r="C389" s="7" t="n"/>
       <c r="E389" s="7" t="n"/>
       <c r="G389" s="7" t="n"/>
-      <c r="L389" s="7" t="n"/>
+      <c r="I389" s="7" t="n"/>
       <c r="M389" s="7" t="n"/>
-      <c r="S389" s="7" t="n"/>
-      <c r="T389" s="7" t="n"/>
+      <c r="N389" s="7" t="n"/>
+      <c r="Q389" s="7" t="n"/>
+      <c r="U389" s="7" t="n"/>
+      <c r="V389" s="7" t="n"/>
       <c r="Y389" s="7" t="n"/>
+      <c r="AB389" s="7" t="n"/>
     </row>
     <row r="390">
       <c r="C390" s="7" t="n"/>
       <c r="E390" s="7" t="n"/>
       <c r="G390" s="7" t="n"/>
-      <c r="L390" s="7" t="n"/>
+      <c r="I390" s="7" t="n"/>
       <c r="M390" s="7" t="n"/>
-      <c r="S390" s="7" t="n"/>
-      <c r="T390" s="7" t="n"/>
+      <c r="N390" s="7" t="n"/>
+      <c r="Q390" s="7" t="n"/>
+      <c r="U390" s="7" t="n"/>
+      <c r="V390" s="7" t="n"/>
       <c r="Y390" s="7" t="n"/>
+      <c r="AB390" s="7" t="n"/>
     </row>
     <row r="391">
       <c r="C391" s="7" t="n"/>
       <c r="E391" s="7" t="n"/>
       <c r="G391" s="7" t="n"/>
-      <c r="L391" s="7" t="n"/>
+      <c r="I391" s="7" t="n"/>
       <c r="M391" s="7" t="n"/>
-      <c r="S391" s="7" t="n"/>
-      <c r="T391" s="7" t="n"/>
+      <c r="N391" s="7" t="n"/>
+      <c r="Q391" s="7" t="n"/>
+      <c r="U391" s="7" t="n"/>
+      <c r="V391" s="7" t="n"/>
       <c r="Y391" s="7" t="n"/>
+      <c r="AB391" s="7" t="n"/>
     </row>
     <row r="392">
       <c r="C392" s="7" t="n"/>
       <c r="E392" s="7" t="n"/>
       <c r="G392" s="7" t="n"/>
-      <c r="L392" s="7" t="n"/>
+      <c r="I392" s="7" t="n"/>
       <c r="M392" s="7" t="n"/>
-      <c r="S392" s="7" t="n"/>
-      <c r="T392" s="7" t="n"/>
+      <c r="N392" s="7" t="n"/>
+      <c r="Q392" s="7" t="n"/>
+      <c r="U392" s="7" t="n"/>
+      <c r="V392" s="7" t="n"/>
       <c r="Y392" s="7" t="n"/>
+      <c r="AB392" s="7" t="n"/>
     </row>
     <row r="393">
       <c r="C393" s="7" t="n"/>
       <c r="E393" s="7" t="n"/>
       <c r="G393" s="7" t="n"/>
-      <c r="L393" s="7" t="n"/>
+      <c r="I393" s="7" t="n"/>
       <c r="M393" s="7" t="n"/>
-      <c r="S393" s="7" t="n"/>
-      <c r="T393" s="7" t="n"/>
+      <c r="N393" s="7" t="n"/>
+      <c r="Q393" s="7" t="n"/>
+      <c r="U393" s="7" t="n"/>
+      <c r="V393" s="7" t="n"/>
       <c r="Y393" s="7" t="n"/>
+      <c r="AB393" s="7" t="n"/>
     </row>
     <row r="394">
       <c r="C394" s="7" t="n"/>
       <c r="E394" s="7" t="n"/>
       <c r="G394" s="7" t="n"/>
-      <c r="L394" s="7" t="n"/>
+      <c r="I394" s="7" t="n"/>
       <c r="M394" s="7" t="n"/>
-      <c r="S394" s="7" t="n"/>
-      <c r="T394" s="7" t="n"/>
+      <c r="N394" s="7" t="n"/>
+      <c r="Q394" s="7" t="n"/>
+      <c r="U394" s="7" t="n"/>
+      <c r="V394" s="7" t="n"/>
       <c r="Y394" s="7" t="n"/>
+      <c r="AB394" s="7" t="n"/>
     </row>
     <row r="395">
       <c r="C395" s="7" t="n"/>
       <c r="E395" s="7" t="n"/>
       <c r="G395" s="7" t="n"/>
-      <c r="L395" s="7" t="n"/>
+      <c r="I395" s="7" t="n"/>
       <c r="M395" s="7" t="n"/>
-      <c r="S395" s="7" t="n"/>
-      <c r="T395" s="7" t="n"/>
+      <c r="N395" s="7" t="n"/>
+      <c r="Q395" s="7" t="n"/>
+      <c r="U395" s="7" t="n"/>
+      <c r="V395" s="7" t="n"/>
       <c r="Y395" s="7" t="n"/>
+      <c r="AB395" s="7" t="n"/>
     </row>
     <row r="396">
       <c r="C396" s="7" t="n"/>
       <c r="E396" s="7" t="n"/>
       <c r="G396" s="7" t="n"/>
-      <c r="L396" s="7" t="n"/>
+      <c r="I396" s="7" t="n"/>
       <c r="M396" s="7" t="n"/>
-      <c r="S396" s="7" t="n"/>
-      <c r="T396" s="7" t="n"/>
+      <c r="N396" s="7" t="n"/>
+      <c r="Q396" s="7" t="n"/>
+      <c r="U396" s="7" t="n"/>
+      <c r="V396" s="7" t="n"/>
       <c r="Y396" s="7" t="n"/>
+      <c r="AB396" s="7" t="n"/>
     </row>
     <row r="397">
       <c r="C397" s="7" t="n"/>
       <c r="E397" s="7" t="n"/>
       <c r="G397" s="7" t="n"/>
-      <c r="L397" s="7" t="n"/>
+      <c r="I397" s="7" t="n"/>
       <c r="M397" s="7" t="n"/>
-      <c r="S397" s="7" t="n"/>
-      <c r="T397" s="7" t="n"/>
+      <c r="N397" s="7" t="n"/>
+      <c r="Q397" s="7" t="n"/>
+      <c r="U397" s="7" t="n"/>
+      <c r="V397" s="7" t="n"/>
       <c r="Y397" s="7" t="n"/>
+      <c r="AB397" s="7" t="n"/>
     </row>
     <row r="398">
       <c r="C398" s="7" t="n"/>
       <c r="E398" s="7" t="n"/>
       <c r="G398" s="7" t="n"/>
-      <c r="L398" s="7" t="n"/>
+      <c r="I398" s="7" t="n"/>
       <c r="M398" s="7" t="n"/>
-      <c r="S398" s="7" t="n"/>
-      <c r="T398" s="7" t="n"/>
+      <c r="N398" s="7" t="n"/>
+      <c r="Q398" s="7" t="n"/>
+      <c r="U398" s="7" t="n"/>
+      <c r="V398" s="7" t="n"/>
       <c r="Y398" s="7" t="n"/>
+      <c r="AB398" s="7" t="n"/>
     </row>
     <row r="399">
       <c r="C399" s="7" t="n"/>
       <c r="E399" s="7" t="n"/>
       <c r="G399" s="7" t="n"/>
-      <c r="L399" s="7" t="n"/>
+      <c r="I399" s="7" t="n"/>
       <c r="M399" s="7" t="n"/>
-      <c r="S399" s="7" t="n"/>
-      <c r="T399" s="7" t="n"/>
+      <c r="N399" s="7" t="n"/>
+      <c r="Q399" s="7" t="n"/>
+      <c r="U399" s="7" t="n"/>
+      <c r="V399" s="7" t="n"/>
       <c r="Y399" s="7" t="n"/>
+      <c r="AB399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="C400" s="7" t="n"/>
       <c r="E400" s="7" t="n"/>
       <c r="G400" s="7" t="n"/>
-      <c r="L400" s="7" t="n"/>
+      <c r="I400" s="7" t="n"/>
       <c r="M400" s="7" t="n"/>
-      <c r="S400" s="7" t="n"/>
-      <c r="T400" s="7" t="n"/>
+      <c r="N400" s="7" t="n"/>
+      <c r="Q400" s="7" t="n"/>
+      <c r="U400" s="7" t="n"/>
+      <c r="V400" s="7" t="n"/>
       <c r="Y400" s="7" t="n"/>
+      <c r="AB400" s="7" t="n"/>
     </row>
     <row r="401">
       <c r="C401" s="7" t="n"/>
       <c r="E401" s="7" t="n"/>
       <c r="G401" s="7" t="n"/>
-      <c r="L401" s="7" t="n"/>
+      <c r="I401" s="7" t="n"/>
       <c r="M401" s="7" t="n"/>
-      <c r="S401" s="7" t="n"/>
-      <c r="T401" s="7" t="n"/>
+      <c r="N401" s="7" t="n"/>
+      <c r="Q401" s="7" t="n"/>
+      <c r="U401" s="7" t="n"/>
+      <c r="V401" s="7" t="n"/>
       <c r="Y401" s="7" t="n"/>
+      <c r="AB401" s="7" t="n"/>
     </row>
     <row r="402">
       <c r="C402" s="7" t="n"/>
       <c r="E402" s="7" t="n"/>
       <c r="G402" s="7" t="n"/>
-      <c r="L402" s="7" t="n"/>
+      <c r="I402" s="7" t="n"/>
       <c r="M402" s="7" t="n"/>
-      <c r="S402" s="7" t="n"/>
-      <c r="T402" s="7" t="n"/>
+      <c r="N402" s="7" t="n"/>
+      <c r="Q402" s="7" t="n"/>
+      <c r="U402" s="7" t="n"/>
+      <c r="V402" s="7" t="n"/>
       <c r="Y402" s="7" t="n"/>
+      <c r="AB402" s="7" t="n"/>
     </row>
     <row r="403">
       <c r="C403" s="7" t="n"/>
       <c r="E403" s="7" t="n"/>
       <c r="G403" s="7" t="n"/>
-      <c r="L403" s="7" t="n"/>
+      <c r="I403" s="7" t="n"/>
       <c r="M403" s="7" t="n"/>
-      <c r="S403" s="7" t="n"/>
-      <c r="T403" s="7" t="n"/>
+      <c r="N403" s="7" t="n"/>
+      <c r="Q403" s="7" t="n"/>
+      <c r="U403" s="7" t="n"/>
+      <c r="V403" s="7" t="n"/>
       <c r="Y403" s="7" t="n"/>
+      <c r="AB403" s="7" t="n"/>
     </row>
     <row r="404">
       <c r="C404" s="7" t="n"/>
       <c r="E404" s="7" t="n"/>
       <c r="G404" s="7" t="n"/>
-      <c r="L404" s="7" t="n"/>
+      <c r="I404" s="7" t="n"/>
       <c r="M404" s="7" t="n"/>
-      <c r="S404" s="7" t="n"/>
-      <c r="T404" s="7" t="n"/>
+      <c r="N404" s="7" t="n"/>
+      <c r="Q404" s="7" t="n"/>
+      <c r="U404" s="7" t="n"/>
+      <c r="V404" s="7" t="n"/>
       <c r="Y404" s="7" t="n"/>
+      <c r="AB404" s="7" t="n"/>
     </row>
     <row r="405">
       <c r="C405" s="7" t="n"/>
       <c r="E405" s="7" t="n"/>
       <c r="G405" s="7" t="n"/>
-      <c r="L405" s="7" t="n"/>
+      <c r="I405" s="7" t="n"/>
       <c r="M405" s="7" t="n"/>
-      <c r="S405" s="7" t="n"/>
-      <c r="T405" s="7" t="n"/>
+      <c r="N405" s="7" t="n"/>
+      <c r="Q405" s="7" t="n"/>
+      <c r="U405" s="7" t="n"/>
+      <c r="V405" s="7" t="n"/>
       <c r="Y405" s="7" t="n"/>
+      <c r="AB405" s="7" t="n"/>
     </row>
     <row r="406">
       <c r="C406" s="7" t="n"/>
       <c r="E406" s="7" t="n"/>
       <c r="G406" s="7" t="n"/>
-      <c r="L406" s="7" t="n"/>
+      <c r="I406" s="7" t="n"/>
       <c r="M406" s="7" t="n"/>
-      <c r="S406" s="7" t="n"/>
-      <c r="T406" s="7" t="n"/>
+      <c r="N406" s="7" t="n"/>
+      <c r="Q406" s="7" t="n"/>
+      <c r="U406" s="7" t="n"/>
+      <c r="V406" s="7" t="n"/>
       <c r="Y406" s="7" t="n"/>
+      <c r="AB406" s="7" t="n"/>
     </row>
     <row r="407">
       <c r="C407" s="7" t="n"/>
       <c r="E407" s="7" t="n"/>
       <c r="G407" s="7" t="n"/>
-      <c r="L407" s="7" t="n"/>
+      <c r="I407" s="7" t="n"/>
       <c r="M407" s="7" t="n"/>
-      <c r="S407" s="7" t="n"/>
-      <c r="T407" s="7" t="n"/>
+      <c r="N407" s="7" t="n"/>
+      <c r="Q407" s="7" t="n"/>
+      <c r="U407" s="7" t="n"/>
+      <c r="V407" s="7" t="n"/>
       <c r="Y407" s="7" t="n"/>
+      <c r="AB407" s="7" t="n"/>
     </row>
     <row r="408">
       <c r="C408" s="7" t="n"/>
       <c r="E408" s="7" t="n"/>
       <c r="G408" s="7" t="n"/>
-      <c r="L408" s="7" t="n"/>
+      <c r="I408" s="7" t="n"/>
       <c r="M408" s="7" t="n"/>
-      <c r="S408" s="7" t="n"/>
-      <c r="T408" s="7" t="n"/>
+      <c r="N408" s="7" t="n"/>
+      <c r="Q408" s="7" t="n"/>
+      <c r="U408" s="7" t="n"/>
+      <c r="V408" s="7" t="n"/>
       <c r="Y408" s="7" t="n"/>
+      <c r="AB408" s="7" t="n"/>
     </row>
     <row r="409">
       <c r="C409" s="7" t="n"/>
       <c r="E409" s="7" t="n"/>
       <c r="G409" s="7" t="n"/>
-      <c r="L409" s="7" t="n"/>
+      <c r="I409" s="7" t="n"/>
       <c r="M409" s="7" t="n"/>
-      <c r="S409" s="7" t="n"/>
-      <c r="T409" s="7" t="n"/>
+      <c r="N409" s="7" t="n"/>
+      <c r="Q409" s="7" t="n"/>
+      <c r="U409" s="7" t="n"/>
+      <c r="V409" s="7" t="n"/>
       <c r="Y409" s="7" t="n"/>
+      <c r="AB409" s="7" t="n"/>
     </row>
     <row r="410">
       <c r="C410" s="7" t="n"/>
       <c r="E410" s="7" t="n"/>
       <c r="G410" s="7" t="n"/>
-      <c r="L410" s="7" t="n"/>
+      <c r="I410" s="7" t="n"/>
       <c r="M410" s="7" t="n"/>
-      <c r="S410" s="7" t="n"/>
-      <c r="T410" s="7" t="n"/>
+      <c r="N410" s="7" t="n"/>
+      <c r="Q410" s="7" t="n"/>
+      <c r="U410" s="7" t="n"/>
+      <c r="V410" s="7" t="n"/>
       <c r="Y410" s="7" t="n"/>
+      <c r="AB410" s="7" t="n"/>
     </row>
     <row r="411">
       <c r="C411" s="7" t="n"/>
       <c r="E411" s="7" t="n"/>
       <c r="G411" s="7" t="n"/>
-      <c r="L411" s="7" t="n"/>
+      <c r="I411" s="7" t="n"/>
       <c r="M411" s="7" t="n"/>
-      <c r="S411" s="7" t="n"/>
-      <c r="T411" s="7" t="n"/>
+      <c r="N411" s="7" t="n"/>
+      <c r="Q411" s="7" t="n"/>
+      <c r="U411" s="7" t="n"/>
+      <c r="V411" s="7" t="n"/>
       <c r="Y411" s="7" t="n"/>
+      <c r="AB411" s="7" t="n"/>
     </row>
     <row r="412">
       <c r="C412" s="7" t="n"/>
       <c r="E412" s="7" t="n"/>
       <c r="G412" s="7" t="n"/>
-      <c r="L412" s="7" t="n"/>
+      <c r="I412" s="7" t="n"/>
       <c r="M412" s="7" t="n"/>
-      <c r="S412" s="7" t="n"/>
-      <c r="T412" s="7" t="n"/>
+      <c r="N412" s="7" t="n"/>
+      <c r="Q412" s="7" t="n"/>
+      <c r="U412" s="7" t="n"/>
+      <c r="V412" s="7" t="n"/>
       <c r="Y412" s="7" t="n"/>
+      <c r="AB412" s="7" t="n"/>
     </row>
     <row r="413">
       <c r="C413" s="7" t="n"/>
       <c r="E413" s="7" t="n"/>
       <c r="G413" s="7" t="n"/>
-      <c r="L413" s="7" t="n"/>
+      <c r="I413" s="7" t="n"/>
       <c r="M413" s="7" t="n"/>
-      <c r="S413" s="7" t="n"/>
-      <c r="T413" s="7" t="n"/>
+      <c r="N413" s="7" t="n"/>
+      <c r="Q413" s="7" t="n"/>
+      <c r="U413" s="7" t="n"/>
+      <c r="V413" s="7" t="n"/>
       <c r="Y413" s="7" t="n"/>
+      <c r="AB413" s="7" t="n"/>
     </row>
     <row r="414">
       <c r="C414" s="7" t="n"/>
       <c r="E414" s="7" t="n"/>
       <c r="G414" s="7" t="n"/>
-      <c r="L414" s="7" t="n"/>
+      <c r="I414" s="7" t="n"/>
       <c r="M414" s="7" t="n"/>
-      <c r="S414" s="7" t="n"/>
-      <c r="T414" s="7" t="n"/>
+      <c r="N414" s="7" t="n"/>
+      <c r="Q414" s="7" t="n"/>
+      <c r="U414" s="7" t="n"/>
+      <c r="V414" s="7" t="n"/>
       <c r="Y414" s="7" t="n"/>
+      <c r="AB414" s="7" t="n"/>
     </row>
     <row r="415">
       <c r="C415" s="7" t="n"/>
       <c r="E415" s="7" t="n"/>
       <c r="G415" s="7" t="n"/>
-      <c r="L415" s="7" t="n"/>
+      <c r="I415" s="7" t="n"/>
       <c r="M415" s="7" t="n"/>
-      <c r="S415" s="7" t="n"/>
-      <c r="T415" s="7" t="n"/>
+      <c r="N415" s="7" t="n"/>
+      <c r="Q415" s="7" t="n"/>
+      <c r="U415" s="7" t="n"/>
+      <c r="V415" s="7" t="n"/>
       <c r="Y415" s="7" t="n"/>
+      <c r="AB415" s="7" t="n"/>
     </row>
     <row r="416">
       <c r="C416" s="7" t="n"/>
       <c r="E416" s="7" t="n"/>
       <c r="G416" s="7" t="n"/>
-      <c r="L416" s="7" t="n"/>
+      <c r="I416" s="7" t="n"/>
       <c r="M416" s="7" t="n"/>
-      <c r="S416" s="7" t="n"/>
-      <c r="T416" s="7" t="n"/>
+      <c r="N416" s="7" t="n"/>
+      <c r="Q416" s="7" t="n"/>
+      <c r="U416" s="7" t="n"/>
+      <c r="V416" s="7" t="n"/>
       <c r="Y416" s="7" t="n"/>
+      <c r="AB416" s="7" t="n"/>
     </row>
     <row r="417">
       <c r="C417" s="7" t="n"/>
       <c r="E417" s="7" t="n"/>
       <c r="G417" s="7" t="n"/>
-      <c r="L417" s="7" t="n"/>
+      <c r="I417" s="7" t="n"/>
       <c r="M417" s="7" t="n"/>
-      <c r="S417" s="7" t="n"/>
-      <c r="T417" s="7" t="n"/>
+      <c r="N417" s="7" t="n"/>
+      <c r="Q417" s="7" t="n"/>
+      <c r="U417" s="7" t="n"/>
+      <c r="V417" s="7" t="n"/>
       <c r="Y417" s="7" t="n"/>
+      <c r="AB417" s="7" t="n"/>
     </row>
     <row r="418">
       <c r="C418" s="7" t="n"/>
       <c r="E418" s="7" t="n"/>
       <c r="G418" s="7" t="n"/>
-      <c r="L418" s="7" t="n"/>
+      <c r="I418" s="7" t="n"/>
       <c r="M418" s="7" t="n"/>
-      <c r="S418" s="7" t="n"/>
-      <c r="T418" s="7" t="n"/>
+      <c r="N418" s="7" t="n"/>
+      <c r="Q418" s="7" t="n"/>
+      <c r="U418" s="7" t="n"/>
+      <c r="V418" s="7" t="n"/>
       <c r="Y418" s="7" t="n"/>
+      <c r="AB418" s="7" t="n"/>
     </row>
     <row r="419">
       <c r="C419" s="7" t="n"/>
       <c r="E419" s="7" t="n"/>
       <c r="G419" s="7" t="n"/>
-      <c r="L419" s="7" t="n"/>
+      <c r="I419" s="7" t="n"/>
       <c r="M419" s="7" t="n"/>
-      <c r="S419" s="7" t="n"/>
-      <c r="T419" s="7" t="n"/>
+      <c r="N419" s="7" t="n"/>
+      <c r="Q419" s="7" t="n"/>
+      <c r="U419" s="7" t="n"/>
+      <c r="V419" s="7" t="n"/>
       <c r="Y419" s="7" t="n"/>
+      <c r="AB419" s="7" t="n"/>
     </row>
     <row r="420">
       <c r="C420" s="7" t="n"/>
       <c r="E420" s="7" t="n"/>
       <c r="G420" s="7" t="n"/>
-      <c r="L420" s="7" t="n"/>
+      <c r="I420" s="7" t="n"/>
       <c r="M420" s="7" t="n"/>
-      <c r="S420" s="7" t="n"/>
-      <c r="T420" s="7" t="n"/>
+      <c r="N420" s="7" t="n"/>
+      <c r="Q420" s="7" t="n"/>
+      <c r="U420" s="7" t="n"/>
+      <c r="V420" s="7" t="n"/>
       <c r="Y420" s="7" t="n"/>
+      <c r="AB420" s="7" t="n"/>
     </row>
     <row r="421">
       <c r="C421" s="7" t="n"/>
       <c r="E421" s="7" t="n"/>
       <c r="G421" s="7" t="n"/>
-      <c r="L421" s="7" t="n"/>
+      <c r="I421" s="7" t="n"/>
       <c r="M421" s="7" t="n"/>
-      <c r="S421" s="7" t="n"/>
-      <c r="T421" s="7" t="n"/>
+      <c r="N421" s="7" t="n"/>
+      <c r="Q421" s="7" t="n"/>
+      <c r="U421" s="7" t="n"/>
+      <c r="V421" s="7" t="n"/>
       <c r="Y421" s="7" t="n"/>
+      <c r="AB421" s="7" t="n"/>
     </row>
     <row r="422">
       <c r="C422" s="7" t="n"/>
       <c r="E422" s="7" t="n"/>
       <c r="G422" s="7" t="n"/>
-      <c r="L422" s="7" t="n"/>
+      <c r="I422" s="7" t="n"/>
       <c r="M422" s="7" t="n"/>
-      <c r="S422" s="7" t="n"/>
-      <c r="T422" s="7" t="n"/>
+      <c r="N422" s="7" t="n"/>
+      <c r="Q422" s="7" t="n"/>
+      <c r="U422" s="7" t="n"/>
+      <c r="V422" s="7" t="n"/>
       <c r="Y422" s="7" t="n"/>
+      <c r="AB422" s="7" t="n"/>
     </row>
     <row r="423">
       <c r="C423" s="7" t="n"/>
       <c r="E423" s="7" t="n"/>
       <c r="G423" s="7" t="n"/>
-      <c r="L423" s="7" t="n"/>
+      <c r="I423" s="7" t="n"/>
       <c r="M423" s="7" t="n"/>
-      <c r="S423" s="7" t="n"/>
-      <c r="T423" s="7" t="n"/>
+      <c r="N423" s="7" t="n"/>
+      <c r="Q423" s="7" t="n"/>
+      <c r="U423" s="7" t="n"/>
+      <c r="V423" s="7" t="n"/>
       <c r="Y423" s="7" t="n"/>
+      <c r="AB423" s="7" t="n"/>
     </row>
     <row r="424">
       <c r="C424" s="7" t="n"/>
       <c r="E424" s="7" t="n"/>
       <c r="G424" s="7" t="n"/>
-      <c r="L424" s="7" t="n"/>
+      <c r="I424" s="7" t="n"/>
       <c r="M424" s="7" t="n"/>
-      <c r="S424" s="7" t="n"/>
-      <c r="T424" s="7" t="n"/>
+      <c r="N424" s="7" t="n"/>
+      <c r="Q424" s="7" t="n"/>
+      <c r="U424" s="7" t="n"/>
+      <c r="V424" s="7" t="n"/>
       <c r="Y424" s="7" t="n"/>
+      <c r="AB424" s="7" t="n"/>
     </row>
     <row r="425">
       <c r="C425" s="7" t="n"/>
       <c r="E425" s="7" t="n"/>
       <c r="G425" s="7" t="n"/>
-      <c r="L425" s="7" t="n"/>
+      <c r="I425" s="7" t="n"/>
       <c r="M425" s="7" t="n"/>
-      <c r="S425" s="7" t="n"/>
-      <c r="T425" s="7" t="n"/>
+      <c r="N425" s="7" t="n"/>
+      <c r="Q425" s="7" t="n"/>
+      <c r="U425" s="7" t="n"/>
+      <c r="V425" s="7" t="n"/>
       <c r="Y425" s="7" t="n"/>
+      <c r="AB425" s="7" t="n"/>
     </row>
     <row r="426">
       <c r="C426" s="7" t="n"/>
       <c r="E426" s="7" t="n"/>
       <c r="G426" s="7" t="n"/>
-      <c r="L426" s="7" t="n"/>
+      <c r="I426" s="7" t="n"/>
       <c r="M426" s="7" t="n"/>
-      <c r="S426" s="7" t="n"/>
-      <c r="T426" s="7" t="n"/>
+      <c r="N426" s="7" t="n"/>
+      <c r="Q426" s="7" t="n"/>
+      <c r="U426" s="7" t="n"/>
+      <c r="V426" s="7" t="n"/>
       <c r="Y426" s="7" t="n"/>
+      <c r="AB426" s="7" t="n"/>
     </row>
     <row r="427">
       <c r="C427" s="7" t="n"/>
       <c r="E427" s="7" t="n"/>
       <c r="G427" s="7" t="n"/>
-      <c r="L427" s="7" t="n"/>
+      <c r="I427" s="7" t="n"/>
       <c r="M427" s="7" t="n"/>
-      <c r="S427" s="7" t="n"/>
-      <c r="T427" s="7" t="n"/>
+      <c r="N427" s="7" t="n"/>
+      <c r="Q427" s="7" t="n"/>
+      <c r="U427" s="7" t="n"/>
+      <c r="V427" s="7" t="n"/>
       <c r="Y427" s="7" t="n"/>
+      <c r="AB427" s="7" t="n"/>
     </row>
     <row r="428">
       <c r="C428" s="7" t="n"/>
       <c r="E428" s="7" t="n"/>
       <c r="G428" s="7" t="n"/>
-      <c r="L428" s="7" t="n"/>
+      <c r="I428" s="7" t="n"/>
       <c r="M428" s="7" t="n"/>
-      <c r="S428" s="7" t="n"/>
-      <c r="T428" s="7" t="n"/>
+      <c r="N428" s="7" t="n"/>
+      <c r="Q428" s="7" t="n"/>
+      <c r="U428" s="7" t="n"/>
+      <c r="V428" s="7" t="n"/>
       <c r="Y428" s="7" t="n"/>
+      <c r="AB428" s="7" t="n"/>
     </row>
     <row r="429">
       <c r="C429" s="7" t="n"/>
       <c r="E429" s="7" t="n"/>
       <c r="G429" s="7" t="n"/>
-      <c r="L429" s="7" t="n"/>
+      <c r="I429" s="7" t="n"/>
       <c r="M429" s="7" t="n"/>
-      <c r="S429" s="7" t="n"/>
-      <c r="T429" s="7" t="n"/>
+      <c r="N429" s="7" t="n"/>
+      <c r="Q429" s="7" t="n"/>
+      <c r="U429" s="7" t="n"/>
+      <c r="V429" s="7" t="n"/>
       <c r="Y429" s="7" t="n"/>
+      <c r="AB429" s="7" t="n"/>
     </row>
     <row r="430">
       <c r="C430" s="7" t="n"/>
       <c r="E430" s="7" t="n"/>
       <c r="G430" s="7" t="n"/>
-      <c r="L430" s="7" t="n"/>
+      <c r="I430" s="7" t="n"/>
       <c r="M430" s="7" t="n"/>
-      <c r="S430" s="7" t="n"/>
-      <c r="T430" s="7" t="n"/>
+      <c r="N430" s="7" t="n"/>
+      <c r="Q430" s="7" t="n"/>
+      <c r="U430" s="7" t="n"/>
+      <c r="V430" s="7" t="n"/>
       <c r="Y430" s="7" t="n"/>
+      <c r="AB430" s="7" t="n"/>
     </row>
     <row r="431">
       <c r="C431" s="7" t="n"/>
       <c r="E431" s="7" t="n"/>
       <c r="G431" s="7" t="n"/>
-      <c r="L431" s="7" t="n"/>
+      <c r="I431" s="7" t="n"/>
       <c r="M431" s="7" t="n"/>
-      <c r="S431" s="7" t="n"/>
-      <c r="T431" s="7" t="n"/>
+      <c r="N431" s="7" t="n"/>
+      <c r="Q431" s="7" t="n"/>
+      <c r="U431" s="7" t="n"/>
+      <c r="V431" s="7" t="n"/>
       <c r="Y431" s="7" t="n"/>
+      <c r="AB431" s="7" t="n"/>
     </row>
     <row r="432">
       <c r="C432" s="7" t="n"/>
       <c r="E432" s="7" t="n"/>
       <c r="G432" s="7" t="n"/>
-      <c r="L432" s="7" t="n"/>
+      <c r="I432" s="7" t="n"/>
       <c r="M432" s="7" t="n"/>
-      <c r="S432" s="7" t="n"/>
-      <c r="T432" s="7" t="n"/>
+      <c r="N432" s="7" t="n"/>
+      <c r="Q432" s="7" t="n"/>
+      <c r="U432" s="7" t="n"/>
+      <c r="V432" s="7" t="n"/>
       <c r="Y432" s="7" t="n"/>
+      <c r="AB432" s="7" t="n"/>
     </row>
     <row r="433">
       <c r="C433" s="7" t="n"/>
       <c r="E433" s="7" t="n"/>
       <c r="G433" s="7" t="n"/>
-      <c r="L433" s="7" t="n"/>
+      <c r="I433" s="7" t="n"/>
       <c r="M433" s="7" t="n"/>
-      <c r="S433" s="7" t="n"/>
-      <c r="T433" s="7" t="n"/>
+      <c r="N433" s="7" t="n"/>
+      <c r="Q433" s="7" t="n"/>
+      <c r="U433" s="7" t="n"/>
+      <c r="V433" s="7" t="n"/>
       <c r="Y433" s="7" t="n"/>
+      <c r="AB433" s="7" t="n"/>
     </row>
     <row r="434">
       <c r="C434" s="7" t="n"/>
       <c r="E434" s="7" t="n"/>
       <c r="G434" s="7" t="n"/>
-      <c r="L434" s="7" t="n"/>
+      <c r="I434" s="7" t="n"/>
       <c r="M434" s="7" t="n"/>
-      <c r="S434" s="7" t="n"/>
-      <c r="T434" s="7" t="n"/>
+      <c r="N434" s="7" t="n"/>
+      <c r="Q434" s="7" t="n"/>
+      <c r="U434" s="7" t="n"/>
+      <c r="V434" s="7" t="n"/>
       <c r="Y434" s="7" t="n"/>
+      <c r="AB434" s="7" t="n"/>
     </row>
     <row r="435">
       <c r="C435" s="7" t="n"/>
       <c r="E435" s="7" t="n"/>
       <c r="G435" s="7" t="n"/>
-      <c r="L435" s="7" t="n"/>
+      <c r="I435" s="7" t="n"/>
       <c r="M435" s="7" t="n"/>
-      <c r="S435" s="7" t="n"/>
-      <c r="T435" s="7" t="n"/>
+      <c r="N435" s="7" t="n"/>
+      <c r="Q435" s="7" t="n"/>
+      <c r="U435" s="7" t="n"/>
+      <c r="V435" s="7" t="n"/>
       <c r="Y435" s="7" t="n"/>
+      <c r="AB435" s="7" t="n"/>
     </row>
     <row r="436">
       <c r="C436" s="7" t="n"/>
       <c r="E436" s="7" t="n"/>
       <c r="G436" s="7" t="n"/>
-      <c r="L436" s="7" t="n"/>
+      <c r="I436" s="7" t="n"/>
       <c r="M436" s="7" t="n"/>
-      <c r="S436" s="7" t="n"/>
-      <c r="T436" s="7" t="n"/>
+      <c r="N436" s="7" t="n"/>
+      <c r="Q436" s="7" t="n"/>
+      <c r="U436" s="7" t="n"/>
+      <c r="V436" s="7" t="n"/>
       <c r="Y436" s="7" t="n"/>
+      <c r="AB436" s="7" t="n"/>
     </row>
     <row r="437">
       <c r="C437" s="7" t="n"/>
       <c r="E437" s="7" t="n"/>
       <c r="G437" s="7" t="n"/>
-      <c r="L437" s="7" t="n"/>
+      <c r="I437" s="7" t="n"/>
       <c r="M437" s="7" t="n"/>
-      <c r="S437" s="7" t="n"/>
-      <c r="T437" s="7" t="n"/>
+      <c r="N437" s="7" t="n"/>
+      <c r="Q437" s="7" t="n"/>
+      <c r="U437" s="7" t="n"/>
+      <c r="V437" s="7" t="n"/>
       <c r="Y437" s="7" t="n"/>
+      <c r="AB437" s="7" t="n"/>
     </row>
     <row r="438">
       <c r="C438" s="7" t="n"/>
       <c r="E438" s="7" t="n"/>
       <c r="G438" s="7" t="n"/>
-      <c r="L438" s="7" t="n"/>
+      <c r="I438" s="7" t="n"/>
       <c r="M438" s="7" t="n"/>
-      <c r="S438" s="7" t="n"/>
-      <c r="T438" s="7" t="n"/>
+      <c r="N438" s="7" t="n"/>
+      <c r="Q438" s="7" t="n"/>
+      <c r="U438" s="7" t="n"/>
+      <c r="V438" s="7" t="n"/>
       <c r="Y438" s="7" t="n"/>
+      <c r="AB438" s="7" t="n"/>
     </row>
     <row r="439">
       <c r="C439" s="7" t="n"/>
       <c r="E439" s="7" t="n"/>
       <c r="G439" s="7" t="n"/>
-      <c r="L439" s="7" t="n"/>
+      <c r="I439" s="7" t="n"/>
       <c r="M439" s="7" t="n"/>
-      <c r="S439" s="7" t="n"/>
-      <c r="T439" s="7" t="n"/>
+      <c r="N439" s="7" t="n"/>
+      <c r="Q439" s="7" t="n"/>
+      <c r="U439" s="7" t="n"/>
+      <c r="V439" s="7" t="n"/>
       <c r="Y439" s="7" t="n"/>
+      <c r="AB439" s="7" t="n"/>
     </row>
     <row r="440">
       <c r="C440" s="7" t="n"/>
       <c r="E440" s="7" t="n"/>
       <c r="G440" s="7" t="n"/>
-      <c r="L440" s="7" t="n"/>
+      <c r="I440" s="7" t="n"/>
       <c r="M440" s="7" t="n"/>
-      <c r="S440" s="7" t="n"/>
-      <c r="T440" s="7" t="n"/>
+      <c r="N440" s="7" t="n"/>
+      <c r="Q440" s="7" t="n"/>
+      <c r="U440" s="7" t="n"/>
+      <c r="V440" s="7" t="n"/>
       <c r="Y440" s="7" t="n"/>
+      <c r="AB440" s="7" t="n"/>
     </row>
     <row r="441">
       <c r="C441" s="7" t="n"/>
       <c r="E441" s="7" t="n"/>
       <c r="G441" s="7" t="n"/>
-      <c r="L441" s="7" t="n"/>
+      <c r="I441" s="7" t="n"/>
       <c r="M441" s="7" t="n"/>
-      <c r="S441" s="7" t="n"/>
-      <c r="T441" s="7" t="n"/>
+      <c r="N441" s="7" t="n"/>
+      <c r="Q441" s="7" t="n"/>
+      <c r="U441" s="7" t="n"/>
+      <c r="V441" s="7" t="n"/>
       <c r="Y441" s="7" t="n"/>
+      <c r="AB441" s="7" t="n"/>
     </row>
     <row r="442">
       <c r="C442" s="7" t="n"/>
       <c r="E442" s="7" t="n"/>
       <c r="G442" s="7" t="n"/>
-      <c r="L442" s="7" t="n"/>
+      <c r="I442" s="7" t="n"/>
       <c r="M442" s="7" t="n"/>
-      <c r="S442" s="7" t="n"/>
-      <c r="T442" s="7" t="n"/>
+      <c r="N442" s="7" t="n"/>
+      <c r="Q442" s="7" t="n"/>
+      <c r="U442" s="7" t="n"/>
+      <c r="V442" s="7" t="n"/>
       <c r="Y442" s="7" t="n"/>
+      <c r="AB442" s="7" t="n"/>
     </row>
     <row r="443">
       <c r="C443" s="7" t="n"/>
       <c r="E443" s="7" t="n"/>
       <c r="G443" s="7" t="n"/>
-      <c r="L443" s="7" t="n"/>
+      <c r="I443" s="7" t="n"/>
       <c r="M443" s="7" t="n"/>
-      <c r="S443" s="7" t="n"/>
-      <c r="T443" s="7" t="n"/>
+      <c r="N443" s="7" t="n"/>
+      <c r="Q443" s="7" t="n"/>
+      <c r="U443" s="7" t="n"/>
+      <c r="V443" s="7" t="n"/>
       <c r="Y443" s="7" t="n"/>
+      <c r="AB443" s="7" t="n"/>
     </row>
     <row r="444">
       <c r="C444" s="7" t="n"/>
       <c r="E444" s="7" t="n"/>
       <c r="G444" s="7" t="n"/>
-      <c r="L444" s="7" t="n"/>
+      <c r="I444" s="7" t="n"/>
       <c r="M444" s="7" t="n"/>
-      <c r="S444" s="7" t="n"/>
-      <c r="T444" s="7" t="n"/>
+      <c r="N444" s="7" t="n"/>
+      <c r="Q444" s="7" t="n"/>
+      <c r="U444" s="7" t="n"/>
+      <c r="V444" s="7" t="n"/>
       <c r="Y444" s="7" t="n"/>
+      <c r="AB444" s="7" t="n"/>
     </row>
     <row r="445">
       <c r="C445" s="7" t="n"/>
       <c r="E445" s="7" t="n"/>
       <c r="G445" s="7" t="n"/>
-      <c r="L445" s="7" t="n"/>
+      <c r="I445" s="7" t="n"/>
       <c r="M445" s="7" t="n"/>
-      <c r="S445" s="7" t="n"/>
-      <c r="T445" s="7" t="n"/>
+      <c r="N445" s="7" t="n"/>
+      <c r="Q445" s="7" t="n"/>
+      <c r="U445" s="7" t="n"/>
+      <c r="V445" s="7" t="n"/>
       <c r="Y445" s="7" t="n"/>
+      <c r="AB445" s="7" t="n"/>
     </row>
     <row r="446">
       <c r="C446" s="7" t="n"/>
       <c r="E446" s="7" t="n"/>
       <c r="G446" s="7" t="n"/>
-      <c r="L446" s="7" t="n"/>
+      <c r="I446" s="7" t="n"/>
       <c r="M446" s="7" t="n"/>
-      <c r="S446" s="7" t="n"/>
-      <c r="T446" s="7" t="n"/>
+      <c r="N446" s="7" t="n"/>
+      <c r="Q446" s="7" t="n"/>
+      <c r="U446" s="7" t="n"/>
+      <c r="V446" s="7" t="n"/>
       <c r="Y446" s="7" t="n"/>
+      <c r="AB446" s="7" t="n"/>
     </row>
     <row r="447">
       <c r="C447" s="7" t="n"/>
       <c r="E447" s="7" t="n"/>
       <c r="G447" s="7" t="n"/>
-      <c r="L447" s="7" t="n"/>
+      <c r="I447" s="7" t="n"/>
       <c r="M447" s="7" t="n"/>
-      <c r="S447" s="7" t="n"/>
-      <c r="T447" s="7" t="n"/>
+      <c r="N447" s="7" t="n"/>
+      <c r="Q447" s="7" t="n"/>
+      <c r="U447" s="7" t="n"/>
+      <c r="V447" s="7" t="n"/>
       <c r="Y447" s="7" t="n"/>
+      <c r="AB447" s="7" t="n"/>
     </row>
     <row r="448">
       <c r="C448" s="7" t="n"/>
       <c r="E448" s="7" t="n"/>
       <c r="G448" s="7" t="n"/>
-      <c r="L448" s="7" t="n"/>
+      <c r="I448" s="7" t="n"/>
       <c r="M448" s="7" t="n"/>
-      <c r="S448" s="7" t="n"/>
-      <c r="T448" s="7" t="n"/>
+      <c r="N448" s="7" t="n"/>
+      <c r="Q448" s="7" t="n"/>
+      <c r="U448" s="7" t="n"/>
+      <c r="V448" s="7" t="n"/>
       <c r="Y448" s="7" t="n"/>
+      <c r="AB448" s="7" t="n"/>
     </row>
     <row r="449">
       <c r="C449" s="7" t="n"/>
       <c r="E449" s="7" t="n"/>
       <c r="G449" s="7" t="n"/>
-      <c r="L449" s="7" t="n"/>
+      <c r="I449" s="7" t="n"/>
       <c r="M449" s="7" t="n"/>
-      <c r="S449" s="7" t="n"/>
-      <c r="T449" s="7" t="n"/>
+      <c r="N449" s="7" t="n"/>
+      <c r="Q449" s="7" t="n"/>
+      <c r="U449" s="7" t="n"/>
+      <c r="V449" s="7" t="n"/>
       <c r="Y449" s="7" t="n"/>
+      <c r="AB449" s="7" t="n"/>
     </row>
     <row r="450">
       <c r="C450" s="7" t="n"/>
       <c r="E450" s="7" t="n"/>
       <c r="G450" s="7" t="n"/>
-      <c r="L450" s="7" t="n"/>
+      <c r="I450" s="7" t="n"/>
       <c r="M450" s="7" t="n"/>
-      <c r="S450" s="7" t="n"/>
-      <c r="T450" s="7" t="n"/>
+      <c r="N450" s="7" t="n"/>
+      <c r="Q450" s="7" t="n"/>
+      <c r="U450" s="7" t="n"/>
+      <c r="V450" s="7" t="n"/>
       <c r="Y450" s="7" t="n"/>
+      <c r="AB450" s="7" t="n"/>
     </row>
     <row r="451">
       <c r="C451" s="7" t="n"/>
       <c r="E451" s="7" t="n"/>
       <c r="G451" s="7" t="n"/>
-      <c r="L451" s="7" t="n"/>
+      <c r="I451" s="7" t="n"/>
       <c r="M451" s="7" t="n"/>
-      <c r="S451" s="7" t="n"/>
-      <c r="T451" s="7" t="n"/>
+      <c r="N451" s="7" t="n"/>
+      <c r="Q451" s="7" t="n"/>
+      <c r="U451" s="7" t="n"/>
+      <c r="V451" s="7" t="n"/>
       <c r="Y451" s="7" t="n"/>
+      <c r="AB451" s="7" t="n"/>
     </row>
     <row r="452">
       <c r="C452" s="7" t="n"/>
       <c r="E452" s="7" t="n"/>
       <c r="G452" s="7" t="n"/>
-      <c r="L452" s="7" t="n"/>
+      <c r="I452" s="7" t="n"/>
       <c r="M452" s="7" t="n"/>
-      <c r="S452" s="7" t="n"/>
-      <c r="T452" s="7" t="n"/>
+      <c r="N452" s="7" t="n"/>
+      <c r="Q452" s="7" t="n"/>
+      <c r="U452" s="7" t="n"/>
+      <c r="V452" s="7" t="n"/>
       <c r="Y452" s="7" t="n"/>
+      <c r="AB452" s="7" t="n"/>
     </row>
     <row r="453">
       <c r="C453" s="7" t="n"/>
       <c r="E453" s="7" t="n"/>
       <c r="G453" s="7" t="n"/>
-      <c r="L453" s="7" t="n"/>
+      <c r="I453" s="7" t="n"/>
       <c r="M453" s="7" t="n"/>
-      <c r="S453" s="7" t="n"/>
-      <c r="T453" s="7" t="n"/>
+      <c r="N453" s="7" t="n"/>
+      <c r="Q453" s="7" t="n"/>
+      <c r="U453" s="7" t="n"/>
+      <c r="V453" s="7" t="n"/>
       <c r="Y453" s="7" t="n"/>
+      <c r="AB453" s="7" t="n"/>
     </row>
     <row r="454">
       <c r="C454" s="7" t="n"/>
       <c r="E454" s="7" t="n"/>
       <c r="G454" s="7" t="n"/>
-      <c r="L454" s="7" t="n"/>
+      <c r="I454" s="7" t="n"/>
       <c r="M454" s="7" t="n"/>
-      <c r="S454" s="7" t="n"/>
-      <c r="T454" s="7" t="n"/>
+      <c r="N454" s="7" t="n"/>
+      <c r="Q454" s="7" t="n"/>
+      <c r="U454" s="7" t="n"/>
+      <c r="V454" s="7" t="n"/>
       <c r="Y454" s="7" t="n"/>
+      <c r="AB454" s="7" t="n"/>
     </row>
     <row r="455">
       <c r="C455" s="7" t="n"/>
       <c r="E455" s="7" t="n"/>
       <c r="G455" s="7" t="n"/>
-      <c r="L455" s="7" t="n"/>
+      <c r="I455" s="7" t="n"/>
       <c r="M455" s="7" t="n"/>
-      <c r="S455" s="7" t="n"/>
-      <c r="T455" s="7" t="n"/>
+      <c r="N455" s="7" t="n"/>
+      <c r="Q455" s="7" t="n"/>
+      <c r="U455" s="7" t="n"/>
+      <c r="V455" s="7" t="n"/>
       <c r="Y455" s="7" t="n"/>
+      <c r="AB455" s="7" t="n"/>
     </row>
     <row r="456">
       <c r="C456" s="7" t="n"/>
       <c r="E456" s="7" t="n"/>
       <c r="G456" s="7" t="n"/>
-      <c r="L456" s="7" t="n"/>
+      <c r="I456" s="7" t="n"/>
       <c r="M456" s="7" t="n"/>
-      <c r="S456" s="7" t="n"/>
-      <c r="T456" s="7" t="n"/>
+      <c r="N456" s="7" t="n"/>
+      <c r="Q456" s="7" t="n"/>
+      <c r="U456" s="7" t="n"/>
+      <c r="V456" s="7" t="n"/>
       <c r="Y456" s="7" t="n"/>
+      <c r="AB456" s="7" t="n"/>
     </row>
     <row r="457">
       <c r="C457" s="7" t="n"/>
       <c r="E457" s="7" t="n"/>
       <c r="G457" s="7" t="n"/>
-      <c r="L457" s="7" t="n"/>
+      <c r="I457" s="7" t="n"/>
       <c r="M457" s="7" t="n"/>
-      <c r="S457" s="7" t="n"/>
-      <c r="T457" s="7" t="n"/>
+      <c r="N457" s="7" t="n"/>
+      <c r="Q457" s="7" t="n"/>
+      <c r="U457" s="7" t="n"/>
+      <c r="V457" s="7" t="n"/>
       <c r="Y457" s="7" t="n"/>
+      <c r="AB457" s="7" t="n"/>
     </row>
     <row r="458">
       <c r="C458" s="7" t="n"/>
       <c r="E458" s="7" t="n"/>
       <c r="G458" s="7" t="n"/>
-      <c r="L458" s="7" t="n"/>
+      <c r="I458" s="7" t="n"/>
       <c r="M458" s="7" t="n"/>
-      <c r="S458" s="7" t="n"/>
-      <c r="T458" s="7" t="n"/>
+      <c r="N458" s="7" t="n"/>
+      <c r="Q458" s="7" t="n"/>
+      <c r="U458" s="7" t="n"/>
+      <c r="V458" s="7" t="n"/>
       <c r="Y458" s="7" t="n"/>
+      <c r="AB458" s="7" t="n"/>
     </row>
     <row r="459">
       <c r="C459" s="7" t="n"/>
       <c r="E459" s="7" t="n"/>
       <c r="G459" s="7" t="n"/>
-      <c r="L459" s="7" t="n"/>
+      <c r="I459" s="7" t="n"/>
       <c r="M459" s="7" t="n"/>
-      <c r="S459" s="7" t="n"/>
-      <c r="T459" s="7" t="n"/>
+      <c r="N459" s="7" t="n"/>
+      <c r="Q459" s="7" t="n"/>
+      <c r="U459" s="7" t="n"/>
+      <c r="V459" s="7" t="n"/>
       <c r="Y459" s="7" t="n"/>
+      <c r="AB459" s="7" t="n"/>
     </row>
     <row r="460">
       <c r="C460" s="7" t="n"/>
       <c r="E460" s="7" t="n"/>
       <c r="G460" s="7" t="n"/>
-      <c r="L460" s="7" t="n"/>
+      <c r="I460" s="7" t="n"/>
       <c r="M460" s="7" t="n"/>
-      <c r="S460" s="7" t="n"/>
-      <c r="T460" s="7" t="n"/>
+      <c r="N460" s="7" t="n"/>
+      <c r="Q460" s="7" t="n"/>
+      <c r="U460" s="7" t="n"/>
+      <c r="V460" s="7" t="n"/>
       <c r="Y460" s="7" t="n"/>
+      <c r="AB460" s="7" t="n"/>
     </row>
     <row r="461">
       <c r="C461" s="7" t="n"/>
       <c r="E461" s="7" t="n"/>
       <c r="G461" s="7" t="n"/>
-      <c r="L461" s="7" t="n"/>
+      <c r="I461" s="7" t="n"/>
       <c r="M461" s="7" t="n"/>
-      <c r="S461" s="7" t="n"/>
-      <c r="T461" s="7" t="n"/>
+      <c r="N461" s="7" t="n"/>
+      <c r="Q461" s="7" t="n"/>
+      <c r="U461" s="7" t="n"/>
+      <c r="V461" s="7" t="n"/>
       <c r="Y461" s="7" t="n"/>
+      <c r="AB461" s="7" t="n"/>
     </row>
     <row r="462">
       <c r="C462" s="7" t="n"/>
       <c r="E462" s="7" t="n"/>
       <c r="G462" s="7" t="n"/>
-      <c r="L462" s="7" t="n"/>
+      <c r="I462" s="7" t="n"/>
       <c r="M462" s="7" t="n"/>
-      <c r="S462" s="7" t="n"/>
-      <c r="T462" s="7" t="n"/>
+      <c r="N462" s="7" t="n"/>
+      <c r="Q462" s="7" t="n"/>
+      <c r="U462" s="7" t="n"/>
+      <c r="V462" s="7" t="n"/>
       <c r="Y462" s="7" t="n"/>
+      <c r="AB462" s="7" t="n"/>
     </row>
     <row r="463">
       <c r="C463" s="7" t="n"/>
       <c r="E463" s="7" t="n"/>
       <c r="G463" s="7" t="n"/>
-      <c r="L463" s="7" t="n"/>
+      <c r="I463" s="7" t="n"/>
       <c r="M463" s="7" t="n"/>
-      <c r="S463" s="7" t="n"/>
-      <c r="T463" s="7" t="n"/>
+      <c r="N463" s="7" t="n"/>
+      <c r="Q463" s="7" t="n"/>
+      <c r="U463" s="7" t="n"/>
+      <c r="V463" s="7" t="n"/>
       <c r="Y463" s="7" t="n"/>
+      <c r="AB463" s="7" t="n"/>
     </row>
     <row r="464">
       <c r="C464" s="7" t="n"/>
       <c r="E464" s="7" t="n"/>
       <c r="G464" s="7" t="n"/>
-      <c r="L464" s="7" t="n"/>
+      <c r="I464" s="7" t="n"/>
       <c r="M464" s="7" t="n"/>
-      <c r="S464" s="7" t="n"/>
-      <c r="T464" s="7" t="n"/>
+      <c r="N464" s="7" t="n"/>
+      <c r="Q464" s="7" t="n"/>
+      <c r="U464" s="7" t="n"/>
+      <c r="V464" s="7" t="n"/>
       <c r="Y464" s="7" t="n"/>
+      <c r="AB464" s="7" t="n"/>
     </row>
     <row r="465">
       <c r="C465" s="7" t="n"/>
       <c r="E465" s="7" t="n"/>
       <c r="G465" s="7" t="n"/>
-      <c r="L465" s="7" t="n"/>
+      <c r="I465" s="7" t="n"/>
       <c r="M465" s="7" t="n"/>
-      <c r="S465" s="7" t="n"/>
-      <c r="T465" s="7" t="n"/>
+      <c r="N465" s="7" t="n"/>
+      <c r="Q465" s="7" t="n"/>
+      <c r="U465" s="7" t="n"/>
+      <c r="V465" s="7" t="n"/>
       <c r="Y465" s="7" t="n"/>
+      <c r="AB465" s="7" t="n"/>
     </row>
     <row r="466">
       <c r="C466" s="7" t="n"/>
       <c r="E466" s="7" t="n"/>
       <c r="G466" s="7" t="n"/>
-      <c r="L466" s="7" t="n"/>
+      <c r="I466" s="7" t="n"/>
       <c r="M466" s="7" t="n"/>
-      <c r="S466" s="7" t="n"/>
-      <c r="T466" s="7" t="n"/>
+      <c r="N466" s="7" t="n"/>
+      <c r="Q466" s="7" t="n"/>
+      <c r="U466" s="7" t="n"/>
+      <c r="V466" s="7" t="n"/>
       <c r="Y466" s="7" t="n"/>
+      <c r="AB466" s="7" t="n"/>
     </row>
     <row r="467">
       <c r="C467" s="7" t="n"/>
       <c r="E467" s="7" t="n"/>
       <c r="G467" s="7" t="n"/>
-      <c r="L467" s="7" t="n"/>
+      <c r="I467" s="7" t="n"/>
       <c r="M467" s="7" t="n"/>
-      <c r="S467" s="7" t="n"/>
-      <c r="T467" s="7" t="n"/>
+      <c r="N467" s="7" t="n"/>
+      <c r="Q467" s="7" t="n"/>
+      <c r="U467" s="7" t="n"/>
+      <c r="V467" s="7" t="n"/>
       <c r="Y467" s="7" t="n"/>
+      <c r="AB467" s="7" t="n"/>
     </row>
     <row r="468">
       <c r="C468" s="7" t="n"/>
       <c r="E468" s="7" t="n"/>
       <c r="G468" s="7" t="n"/>
-      <c r="L468" s="7" t="n"/>
+      <c r="I468" s="7" t="n"/>
       <c r="M468" s="7" t="n"/>
-      <c r="S468" s="7" t="n"/>
-      <c r="T468" s="7" t="n"/>
+      <c r="N468" s="7" t="n"/>
+      <c r="Q468" s="7" t="n"/>
+      <c r="U468" s="7" t="n"/>
+      <c r="V468" s="7" t="n"/>
       <c r="Y468" s="7" t="n"/>
+      <c r="AB468" s="7" t="n"/>
     </row>
     <row r="469">
       <c r="C469" s="7" t="n"/>
       <c r="E469" s="7" t="n"/>
       <c r="G469" s="7" t="n"/>
-      <c r="L469" s="7" t="n"/>
+      <c r="I469" s="7" t="n"/>
       <c r="M469" s="7" t="n"/>
-      <c r="S469" s="7" t="n"/>
-      <c r="T469" s="7" t="n"/>
+      <c r="N469" s="7" t="n"/>
+      <c r="Q469" s="7" t="n"/>
+      <c r="U469" s="7" t="n"/>
+      <c r="V469" s="7" t="n"/>
       <c r="Y469" s="7" t="n"/>
+      <c r="AB469" s="7" t="n"/>
     </row>
     <row r="470">
       <c r="C470" s="7" t="n"/>
       <c r="E470" s="7" t="n"/>
       <c r="G470" s="7" t="n"/>
-      <c r="L470" s="7" t="n"/>
+      <c r="I470" s="7" t="n"/>
       <c r="M470" s="7" t="n"/>
-      <c r="S470" s="7" t="n"/>
-      <c r="T470" s="7" t="n"/>
+      <c r="N470" s="7" t="n"/>
+      <c r="Q470" s="7" t="n"/>
+      <c r="U470" s="7" t="n"/>
+      <c r="V470" s="7" t="n"/>
       <c r="Y470" s="7" t="n"/>
+      <c r="AB470" s="7" t="n"/>
     </row>
     <row r="471">
       <c r="C471" s="7" t="n"/>
       <c r="E471" s="7" t="n"/>
       <c r="G471" s="7" t="n"/>
-      <c r="L471" s="7" t="n"/>
+      <c r="I471" s="7" t="n"/>
       <c r="M471" s="7" t="n"/>
-      <c r="S471" s="7" t="n"/>
-      <c r="T471" s="7" t="n"/>
+      <c r="N471" s="7" t="n"/>
+      <c r="Q471" s="7" t="n"/>
+      <c r="U471" s="7" t="n"/>
+      <c r="V471" s="7" t="n"/>
       <c r="Y471" s="7" t="n"/>
+      <c r="AB471" s="7" t="n"/>
     </row>
     <row r="472">
       <c r="C472" s="7" t="n"/>
       <c r="E472" s="7" t="n"/>
       <c r="G472" s="7" t="n"/>
-      <c r="L472" s="7" t="n"/>
+      <c r="I472" s="7" t="n"/>
       <c r="M472" s="7" t="n"/>
-      <c r="S472" s="7" t="n"/>
-      <c r="T472" s="7" t="n"/>
+      <c r="N472" s="7" t="n"/>
+      <c r="Q472" s="7" t="n"/>
+      <c r="U472" s="7" t="n"/>
+      <c r="V472" s="7" t="n"/>
       <c r="Y472" s="7" t="n"/>
+      <c r="AB472" s="7" t="n"/>
     </row>
     <row r="473">
       <c r="C473" s="7" t="n"/>
       <c r="E473" s="7" t="n"/>
       <c r="G473" s="7" t="n"/>
-      <c r="L473" s="7" t="n"/>
+      <c r="I473" s="7" t="n"/>
       <c r="M473" s="7" t="n"/>
-      <c r="S473" s="7" t="n"/>
-      <c r="T473" s="7" t="n"/>
+      <c r="N473" s="7" t="n"/>
+      <c r="Q473" s="7" t="n"/>
+      <c r="U473" s="7" t="n"/>
+      <c r="V473" s="7" t="n"/>
       <c r="Y473" s="7" t="n"/>
+      <c r="AB473" s="7" t="n"/>
     </row>
     <row r="474">
       <c r="C474" s="7" t="n"/>
       <c r="E474" s="7" t="n"/>
       <c r="G474" s="7" t="n"/>
-      <c r="L474" s="7" t="n"/>
+      <c r="I474" s="7" t="n"/>
       <c r="M474" s="7" t="n"/>
-      <c r="S474" s="7" t="n"/>
-      <c r="T474" s="7" t="n"/>
+      <c r="N474" s="7" t="n"/>
+      <c r="Q474" s="7" t="n"/>
+      <c r="U474" s="7" t="n"/>
+      <c r="V474" s="7" t="n"/>
       <c r="Y474" s="7" t="n"/>
+      <c r="AB474" s="7" t="n"/>
     </row>
     <row r="475">
       <c r="C475" s="7" t="n"/>
       <c r="E475" s="7" t="n"/>
       <c r="G475" s="7" t="n"/>
-      <c r="L475" s="7" t="n"/>
+      <c r="I475" s="7" t="n"/>
       <c r="M475" s="7" t="n"/>
-      <c r="S475" s="7" t="n"/>
-      <c r="T475" s="7" t="n"/>
+      <c r="N475" s="7" t="n"/>
+      <c r="Q475" s="7" t="n"/>
+      <c r="U475" s="7" t="n"/>
+      <c r="V475" s="7" t="n"/>
       <c r="Y475" s="7" t="n"/>
+      <c r="AB475" s="7" t="n"/>
     </row>
     <row r="476">
       <c r="C476" s="7" t="n"/>
       <c r="E476" s="7" t="n"/>
       <c r="G476" s="7" t="n"/>
-      <c r="L476" s="7" t="n"/>
+      <c r="I476" s="7" t="n"/>
       <c r="M476" s="7" t="n"/>
-      <c r="S476" s="7" t="n"/>
-      <c r="T476" s="7" t="n"/>
+      <c r="N476" s="7" t="n"/>
+      <c r="Q476" s="7" t="n"/>
+      <c r="U476" s="7" t="n"/>
+      <c r="V476" s="7" t="n"/>
       <c r="Y476" s="7" t="n"/>
+      <c r="AB476" s="7" t="n"/>
     </row>
     <row r="477">
       <c r="C477" s="7" t="n"/>
       <c r="E477" s="7" t="n"/>
       <c r="G477" s="7" t="n"/>
-      <c r="L477" s="7" t="n"/>
+      <c r="I477" s="7" t="n"/>
       <c r="M477" s="7" t="n"/>
-      <c r="S477" s="7" t="n"/>
-      <c r="T477" s="7" t="n"/>
+      <c r="N477" s="7" t="n"/>
+      <c r="Q477" s="7" t="n"/>
+      <c r="U477" s="7" t="n"/>
+      <c r="V477" s="7" t="n"/>
       <c r="Y477" s="7" t="n"/>
+      <c r="AB477" s="7" t="n"/>
     </row>
     <row r="478">
       <c r="C478" s="7" t="n"/>
       <c r="E478" s="7" t="n"/>
       <c r="G478" s="7" t="n"/>
-      <c r="L478" s="7" t="n"/>
+      <c r="I478" s="7" t="n"/>
       <c r="M478" s="7" t="n"/>
-      <c r="S478" s="7" t="n"/>
-      <c r="T478" s="7" t="n"/>
+      <c r="N478" s="7" t="n"/>
+      <c r="Q478" s="7" t="n"/>
+      <c r="U478" s="7" t="n"/>
+      <c r="V478" s="7" t="n"/>
       <c r="Y478" s="7" t="n"/>
+      <c r="AB478" s="7" t="n"/>
     </row>
     <row r="479">
       <c r="C479" s="7" t="n"/>
       <c r="E479" s="7" t="n"/>
       <c r="G479" s="7" t="n"/>
-      <c r="L479" s="7" t="n"/>
+      <c r="I479" s="7" t="n"/>
       <c r="M479" s="7" t="n"/>
-      <c r="S479" s="7" t="n"/>
-      <c r="T479" s="7" t="n"/>
+      <c r="N479" s="7" t="n"/>
+      <c r="Q479" s="7" t="n"/>
+      <c r="U479" s="7" t="n"/>
+      <c r="V479" s="7" t="n"/>
       <c r="Y479" s="7" t="n"/>
+      <c r="AB479" s="7" t="n"/>
     </row>
     <row r="480">
       <c r="C480" s="7" t="n"/>
       <c r="E480" s="7" t="n"/>
       <c r="G480" s="7" t="n"/>
-      <c r="L480" s="7" t="n"/>
+      <c r="I480" s="7" t="n"/>
       <c r="M480" s="7" t="n"/>
-      <c r="S480" s="7" t="n"/>
-      <c r="T480" s="7" t="n"/>
+      <c r="N480" s="7" t="n"/>
+      <c r="Q480" s="7" t="n"/>
+      <c r="U480" s="7" t="n"/>
+      <c r="V480" s="7" t="n"/>
       <c r="Y480" s="7" t="n"/>
+      <c r="AB480" s="7" t="n"/>
     </row>
     <row r="481">
       <c r="C481" s="7" t="n"/>
       <c r="E481" s="7" t="n"/>
       <c r="G481" s="7" t="n"/>
-      <c r="L481" s="7" t="n"/>
+      <c r="I481" s="7" t="n"/>
       <c r="M481" s="7" t="n"/>
-      <c r="S481" s="7" t="n"/>
-      <c r="T481" s="7" t="n"/>
+      <c r="N481" s="7" t="n"/>
+      <c r="Q481" s="7" t="n"/>
+      <c r="U481" s="7" t="n"/>
+      <c r="V481" s="7" t="n"/>
       <c r="Y481" s="7" t="n"/>
+      <c r="AB481" s="7" t="n"/>
     </row>
     <row r="482">
       <c r="C482" s="7" t="n"/>
       <c r="E482" s="7" t="n"/>
       <c r="G482" s="7" t="n"/>
-      <c r="L482" s="7" t="n"/>
+      <c r="I482" s="7" t="n"/>
       <c r="M482" s="7" t="n"/>
-      <c r="S482" s="7" t="n"/>
-      <c r="T482" s="7" t="n"/>
+      <c r="N482" s="7" t="n"/>
+      <c r="Q482" s="7" t="n"/>
+      <c r="U482" s="7" t="n"/>
+      <c r="V482" s="7" t="n"/>
       <c r="Y482" s="7" t="n"/>
+      <c r="AB482" s="7" t="n"/>
     </row>
     <row r="483">
       <c r="C483" s="7" t="n"/>
       <c r="E483" s="7" t="n"/>
       <c r="G483" s="7" t="n"/>
-      <c r="L483" s="7" t="n"/>
+      <c r="I483" s="7" t="n"/>
       <c r="M483" s="7" t="n"/>
-      <c r="S483" s="7" t="n"/>
-      <c r="T483" s="7" t="n"/>
+      <c r="N483" s="7" t="n"/>
+      <c r="Q483" s="7" t="n"/>
+      <c r="U483" s="7" t="n"/>
+      <c r="V483" s="7" t="n"/>
       <c r="Y483" s="7" t="n"/>
+      <c r="AB483" s="7" t="n"/>
     </row>
     <row r="484">
       <c r="C484" s="7" t="n"/>
       <c r="E484" s="7" t="n"/>
       <c r="G484" s="7" t="n"/>
-      <c r="L484" s="7" t="n"/>
+      <c r="I484" s="7" t="n"/>
       <c r="M484" s="7" t="n"/>
-      <c r="S484" s="7" t="n"/>
-      <c r="T484" s="7" t="n"/>
+      <c r="N484" s="7" t="n"/>
+      <c r="Q484" s="7" t="n"/>
+      <c r="U484" s="7" t="n"/>
+      <c r="V484" s="7" t="n"/>
       <c r="Y484" s="7" t="n"/>
+      <c r="AB484" s="7" t="n"/>
     </row>
     <row r="485">
       <c r="C485" s="7" t="n"/>
       <c r="E485" s="7" t="n"/>
       <c r="G485" s="7" t="n"/>
-      <c r="L485" s="7" t="n"/>
+      <c r="I485" s="7" t="n"/>
       <c r="M485" s="7" t="n"/>
-      <c r="S485" s="7" t="n"/>
-      <c r="T485" s="7" t="n"/>
+      <c r="N485" s="7" t="n"/>
+      <c r="Q485" s="7" t="n"/>
+      <c r="U485" s="7" t="n"/>
+      <c r="V485" s="7" t="n"/>
       <c r="Y485" s="7" t="n"/>
+      <c r="AB485" s="7" t="n"/>
     </row>
     <row r="486">
       <c r="C486" s="7" t="n"/>
       <c r="E486" s="7" t="n"/>
       <c r="G486" s="7" t="n"/>
-      <c r="L486" s="7" t="n"/>
+      <c r="I486" s="7" t="n"/>
       <c r="M486" s="7" t="n"/>
-      <c r="S486" s="7" t="n"/>
-      <c r="T486" s="7" t="n"/>
+      <c r="N486" s="7" t="n"/>
+      <c r="Q486" s="7" t="n"/>
+      <c r="U486" s="7" t="n"/>
+      <c r="V486" s="7" t="n"/>
       <c r="Y486" s="7" t="n"/>
+      <c r="AB486" s="7" t="n"/>
     </row>
     <row r="487">
       <c r="C487" s="7" t="n"/>
       <c r="E487" s="7" t="n"/>
       <c r="G487" s="7" t="n"/>
-      <c r="L487" s="7" t="n"/>
+      <c r="I487" s="7" t="n"/>
       <c r="M487" s="7" t="n"/>
-      <c r="S487" s="7" t="n"/>
-      <c r="T487" s="7" t="n"/>
+      <c r="N487" s="7" t="n"/>
+      <c r="Q487" s="7" t="n"/>
+      <c r="U487" s="7" t="n"/>
+      <c r="V487" s="7" t="n"/>
       <c r="Y487" s="7" t="n"/>
+      <c r="AB487" s="7" t="n"/>
     </row>
     <row r="488">
       <c r="C488" s="7" t="n"/>
       <c r="E488" s="7" t="n"/>
       <c r="G488" s="7" t="n"/>
-      <c r="L488" s="7" t="n"/>
+      <c r="I488" s="7" t="n"/>
       <c r="M488" s="7" t="n"/>
-      <c r="S488" s="7" t="n"/>
-      <c r="T488" s="7" t="n"/>
+      <c r="N488" s="7" t="n"/>
+      <c r="Q488" s="7" t="n"/>
+      <c r="U488" s="7" t="n"/>
+      <c r="V488" s="7" t="n"/>
       <c r="Y488" s="7" t="n"/>
+      <c r="AB488" s="7" t="n"/>
     </row>
     <row r="489">
       <c r="C489" s="7" t="n"/>
       <c r="E489" s="7" t="n"/>
       <c r="G489" s="7" t="n"/>
-      <c r="L489" s="7" t="n"/>
+      <c r="I489" s="7" t="n"/>
       <c r="M489" s="7" t="n"/>
-      <c r="S489" s="7" t="n"/>
-      <c r="T489" s="7" t="n"/>
+      <c r="N489" s="7" t="n"/>
+      <c r="Q489" s="7" t="n"/>
+      <c r="U489" s="7" t="n"/>
+      <c r="V489" s="7" t="n"/>
       <c r="Y489" s="7" t="n"/>
+      <c r="AB489" s="7" t="n"/>
     </row>
     <row r="490">
       <c r="C490" s="7" t="n"/>
       <c r="E490" s="7" t="n"/>
       <c r="G490" s="7" t="n"/>
-      <c r="L490" s="7" t="n"/>
+      <c r="I490" s="7" t="n"/>
       <c r="M490" s="7" t="n"/>
-      <c r="S490" s="7" t="n"/>
-      <c r="T490" s="7" t="n"/>
+      <c r="N490" s="7" t="n"/>
+      <c r="Q490" s="7" t="n"/>
+      <c r="U490" s="7" t="n"/>
+      <c r="V490" s="7" t="n"/>
       <c r="Y490" s="7" t="n"/>
+      <c r="AB490" s="7" t="n"/>
     </row>
     <row r="491">
       <c r="C491" s="7" t="n"/>
       <c r="E491" s="7" t="n"/>
       <c r="G491" s="7" t="n"/>
-      <c r="L491" s="7" t="n"/>
+      <c r="I491" s="7" t="n"/>
       <c r="M491" s="7" t="n"/>
-      <c r="S491" s="7" t="n"/>
-      <c r="T491" s="7" t="n"/>
+      <c r="N491" s="7" t="n"/>
+      <c r="Q491" s="7" t="n"/>
+      <c r="U491" s="7" t="n"/>
+      <c r="V491" s="7" t="n"/>
       <c r="Y491" s="7" t="n"/>
+      <c r="AB491" s="7" t="n"/>
     </row>
     <row r="492">
       <c r="C492" s="7" t="n"/>
       <c r="E492" s="7" t="n"/>
       <c r="G492" s="7" t="n"/>
-      <c r="L492" s="7" t="n"/>
+      <c r="I492" s="7" t="n"/>
       <c r="M492" s="7" t="n"/>
-      <c r="S492" s="7" t="n"/>
-      <c r="T492" s="7" t="n"/>
+      <c r="N492" s="7" t="n"/>
+      <c r="Q492" s="7" t="n"/>
+      <c r="U492" s="7" t="n"/>
+      <c r="V492" s="7" t="n"/>
       <c r="Y492" s="7" t="n"/>
+      <c r="AB492" s="7" t="n"/>
     </row>
     <row r="493">
       <c r="C493" s="7" t="n"/>
       <c r="E493" s="7" t="n"/>
       <c r="G493" s="7" t="n"/>
-      <c r="L493" s="7" t="n"/>
+      <c r="I493" s="7" t="n"/>
       <c r="M493" s="7" t="n"/>
-      <c r="S493" s="7" t="n"/>
-      <c r="T493" s="7" t="n"/>
+      <c r="N493" s="7" t="n"/>
+      <c r="Q493" s="7" t="n"/>
+      <c r="U493" s="7" t="n"/>
+      <c r="V493" s="7" t="n"/>
       <c r="Y493" s="7" t="n"/>
+      <c r="AB493" s="7" t="n"/>
     </row>
     <row r="494">
       <c r="C494" s="7" t="n"/>
       <c r="E494" s="7" t="n"/>
       <c r="G494" s="7" t="n"/>
-      <c r="L494" s="7" t="n"/>
+      <c r="I494" s="7" t="n"/>
       <c r="M494" s="7" t="n"/>
-      <c r="S494" s="7" t="n"/>
-      <c r="T494" s="7" t="n"/>
+      <c r="N494" s="7" t="n"/>
+      <c r="Q494" s="7" t="n"/>
+      <c r="U494" s="7" t="n"/>
+      <c r="V494" s="7" t="n"/>
       <c r="Y494" s="7" t="n"/>
+      <c r="AB494" s="7" t="n"/>
     </row>
     <row r="495">
       <c r="C495" s="7" t="n"/>
       <c r="E495" s="7" t="n"/>
       <c r="G495" s="7" t="n"/>
-      <c r="L495" s="7" t="n"/>
+      <c r="I495" s="7" t="n"/>
       <c r="M495" s="7" t="n"/>
-      <c r="S495" s="7" t="n"/>
-      <c r="T495" s="7" t="n"/>
+      <c r="N495" s="7" t="n"/>
+      <c r="Q495" s="7" t="n"/>
+      <c r="U495" s="7" t="n"/>
+      <c r="V495" s="7" t="n"/>
       <c r="Y495" s="7" t="n"/>
+      <c r="AB495" s="7" t="n"/>
     </row>
     <row r="496">
       <c r="C496" s="7" t="n"/>
       <c r="E496" s="7" t="n"/>
       <c r="G496" s="7" t="n"/>
-      <c r="L496" s="7" t="n"/>
+      <c r="I496" s="7" t="n"/>
       <c r="M496" s="7" t="n"/>
-      <c r="S496" s="7" t="n"/>
-      <c r="T496" s="7" t="n"/>
+      <c r="N496" s="7" t="n"/>
+      <c r="Q496" s="7" t="n"/>
+      <c r="U496" s="7" t="n"/>
+      <c r="V496" s="7" t="n"/>
       <c r="Y496" s="7" t="n"/>
+      <c r="AB496" s="7" t="n"/>
     </row>
     <row r="497">
       <c r="C497" s="7" t="n"/>
       <c r="E497" s="7" t="n"/>
       <c r="G497" s="7" t="n"/>
-      <c r="L497" s="7" t="n"/>
+      <c r="I497" s="7" t="n"/>
       <c r="M497" s="7" t="n"/>
-      <c r="S497" s="7" t="n"/>
-      <c r="T497" s="7" t="n"/>
+      <c r="N497" s="7" t="n"/>
+      <c r="Q497" s="7" t="n"/>
+      <c r="U497" s="7" t="n"/>
+      <c r="V497" s="7" t="n"/>
       <c r="Y497" s="7" t="n"/>
+      <c r="AB497" s="7" t="n"/>
     </row>
     <row r="498">
       <c r="C498" s="7" t="n"/>
       <c r="E498" s="7" t="n"/>
       <c r="G498" s="7" t="n"/>
-      <c r="L498" s="7" t="n"/>
+      <c r="I498" s="7" t="n"/>
       <c r="M498" s="7" t="n"/>
-      <c r="S498" s="7" t="n"/>
-      <c r="T498" s="7" t="n"/>
+      <c r="N498" s="7" t="n"/>
+      <c r="Q498" s="7" t="n"/>
+      <c r="U498" s="7" t="n"/>
+      <c r="V498" s="7" t="n"/>
       <c r="Y498" s="7" t="n"/>
+      <c r="AB498" s="7" t="n"/>
     </row>
     <row r="499">
       <c r="C499" s="7" t="n"/>
       <c r="E499" s="7" t="n"/>
       <c r="G499" s="7" t="n"/>
-      <c r="L499" s="7" t="n"/>
+      <c r="I499" s="7" t="n"/>
       <c r="M499" s="7" t="n"/>
-      <c r="S499" s="7" t="n"/>
-      <c r="T499" s="7" t="n"/>
+      <c r="N499" s="7" t="n"/>
+      <c r="Q499" s="7" t="n"/>
+      <c r="U499" s="7" t="n"/>
+      <c r="V499" s="7" t="n"/>
       <c r="Y499" s="7" t="n"/>
+      <c r="AB499" s="7" t="n"/>
     </row>
     <row r="500">
       <c r="C500" s="7" t="n"/>
       <c r="E500" s="7" t="n"/>
       <c r="G500" s="7" t="n"/>
-      <c r="L500" s="7" t="n"/>
+      <c r="I500" s="7" t="n"/>
       <c r="M500" s="7" t="n"/>
-      <c r="S500" s="7" t="n"/>
-      <c r="T500" s="7" t="n"/>
+      <c r="N500" s="7" t="n"/>
+      <c r="Q500" s="7" t="n"/>
+      <c r="U500" s="7" t="n"/>
+      <c r="V500" s="7" t="n"/>
       <c r="Y500" s="7" t="n"/>
+      <c r="AB500" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5736,7 +7255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -5783,54 +7302,61 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
+          <t>Home Address: where the child lives. Parent 1 Address and Parent 2 Address: only if that parent lives somewhere else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
           <t>Emergency contact: someone OTHER than Parent 1 and Parent 2, with their own phone number. Rows where the emergency contact is one of the parents, or shares a parent's number, are not imported.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Dates: day/month/year, for example 21/03/2022.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Gender: Male or Female (M / F also work).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Class: must match a class name already set up in Crechely. Leave it blank to use the class you choose when uploading.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Enrolment Date: leave blank to use the date you choose when uploading.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>ID numbers and phone numbers: type them as normal, including the leading 0. These columns are set to text so Excel keeps the 0.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Your own spreadsheet also works: headings like 'Childs Name', 'Surname', 'ID No.', 'DOB', 'Cell', 'Parent 1 Name' and 'Emergency Contact' are recognised.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Save as Excel Workbook (.xlsx) or CSV, then upload it in Crechely under Enrolled &gt; Import from Excel / CSV.</t>
         </is>

--- a/public/templates/crechely-children-template.xlsx
+++ b/public/templates/crechely-children-template.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB500"/>
+  <dimension ref="A1:AC500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -504,6 +504,7 @@
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -647,6 +648,11 @@
           <t>Emergency Contact Phone</t>
         </is>
       </c>
+      <c r="AC1" s="4" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -769,6 +775,7 @@
           <t>084 000 0000</t>
         </is>
       </c>
+      <c r="AC2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="C3" s="7" t="n"/>
@@ -782,6 +789,7 @@
       <c r="V3" s="7" t="n"/>
       <c r="Y3" s="7" t="n"/>
       <c r="AB3" s="7" t="n"/>
+      <c r="AC3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="C4" s="7" t="n"/>
@@ -795,6 +803,7 @@
       <c r="V4" s="7" t="n"/>
       <c r="Y4" s="7" t="n"/>
       <c r="AB4" s="7" t="n"/>
+      <c r="AC4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="7" t="n"/>
@@ -808,6 +817,7 @@
       <c r="V5" s="7" t="n"/>
       <c r="Y5" s="7" t="n"/>
       <c r="AB5" s="7" t="n"/>
+      <c r="AC5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="7" t="n"/>
@@ -821,6 +831,7 @@
       <c r="V6" s="7" t="n"/>
       <c r="Y6" s="7" t="n"/>
       <c r="AB6" s="7" t="n"/>
+      <c r="AC6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="7" t="n"/>
@@ -834,6 +845,7 @@
       <c r="V7" s="7" t="n"/>
       <c r="Y7" s="7" t="n"/>
       <c r="AB7" s="7" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="7" t="n"/>
@@ -847,6 +859,7 @@
       <c r="V8" s="7" t="n"/>
       <c r="Y8" s="7" t="n"/>
       <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="7" t="n"/>
@@ -860,6 +873,7 @@
       <c r="V9" s="7" t="n"/>
       <c r="Y9" s="7" t="n"/>
       <c r="AB9" s="7" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="7" t="n"/>
@@ -873,6 +887,7 @@
       <c r="V10" s="7" t="n"/>
       <c r="Y10" s="7" t="n"/>
       <c r="AB10" s="7" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="7" t="n"/>
@@ -886,6 +901,7 @@
       <c r="V11" s="7" t="n"/>
       <c r="Y11" s="7" t="n"/>
       <c r="AB11" s="7" t="n"/>
+      <c r="AC11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="7" t="n"/>
@@ -899,6 +915,7 @@
       <c r="V12" s="7" t="n"/>
       <c r="Y12" s="7" t="n"/>
       <c r="AB12" s="7" t="n"/>
+      <c r="AC12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="7" t="n"/>
@@ -912,6 +929,7 @@
       <c r="V13" s="7" t="n"/>
       <c r="Y13" s="7" t="n"/>
       <c r="AB13" s="7" t="n"/>
+      <c r="AC13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="7" t="n"/>
@@ -925,6 +943,7 @@
       <c r="V14" s="7" t="n"/>
       <c r="Y14" s="7" t="n"/>
       <c r="AB14" s="7" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="7" t="n"/>
@@ -938,6 +957,7 @@
       <c r="V15" s="7" t="n"/>
       <c r="Y15" s="7" t="n"/>
       <c r="AB15" s="7" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="7" t="n"/>
@@ -951,6 +971,7 @@
       <c r="V16" s="7" t="n"/>
       <c r="Y16" s="7" t="n"/>
       <c r="AB16" s="7" t="n"/>
+      <c r="AC16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="7" t="n"/>
@@ -964,6 +985,7 @@
       <c r="V17" s="7" t="n"/>
       <c r="Y17" s="7" t="n"/>
       <c r="AB17" s="7" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="7" t="n"/>
@@ -977,6 +999,7 @@
       <c r="V18" s="7" t="n"/>
       <c r="Y18" s="7" t="n"/>
       <c r="AB18" s="7" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="C19" s="7" t="n"/>
@@ -990,6 +1013,7 @@
       <c r="V19" s="7" t="n"/>
       <c r="Y19" s="7" t="n"/>
       <c r="AB19" s="7" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="7" t="n"/>
@@ -1003,6 +1027,7 @@
       <c r="V20" s="7" t="n"/>
       <c r="Y20" s="7" t="n"/>
       <c r="AB20" s="7" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="7" t="n"/>
@@ -1016,6 +1041,7 @@
       <c r="V21" s="7" t="n"/>
       <c r="Y21" s="7" t="n"/>
       <c r="AB21" s="7" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="7" t="n"/>
@@ -1029,6 +1055,7 @@
       <c r="V22" s="7" t="n"/>
       <c r="Y22" s="7" t="n"/>
       <c r="AB22" s="7" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="C23" s="7" t="n"/>
@@ -1042,6 +1069,7 @@
       <c r="V23" s="7" t="n"/>
       <c r="Y23" s="7" t="n"/>
       <c r="AB23" s="7" t="n"/>
+      <c r="AC23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="C24" s="7" t="n"/>
@@ -1055,6 +1083,7 @@
       <c r="V24" s="7" t="n"/>
       <c r="Y24" s="7" t="n"/>
       <c r="AB24" s="7" t="n"/>
+      <c r="AC24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="C25" s="7" t="n"/>
@@ -1068,6 +1097,7 @@
       <c r="V25" s="7" t="n"/>
       <c r="Y25" s="7" t="n"/>
       <c r="AB25" s="7" t="n"/>
+      <c r="AC25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="C26" s="7" t="n"/>
@@ -1081,6 +1111,7 @@
       <c r="V26" s="7" t="n"/>
       <c r="Y26" s="7" t="n"/>
       <c r="AB26" s="7" t="n"/>
+      <c r="AC26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="C27" s="7" t="n"/>
@@ -1094,6 +1125,7 @@
       <c r="V27" s="7" t="n"/>
       <c r="Y27" s="7" t="n"/>
       <c r="AB27" s="7" t="n"/>
+      <c r="AC27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="C28" s="7" t="n"/>
@@ -1107,6 +1139,7 @@
       <c r="V28" s="7" t="n"/>
       <c r="Y28" s="7" t="n"/>
       <c r="AB28" s="7" t="n"/>
+      <c r="AC28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="C29" s="7" t="n"/>
@@ -1120,6 +1153,7 @@
       <c r="V29" s="7" t="n"/>
       <c r="Y29" s="7" t="n"/>
       <c r="AB29" s="7" t="n"/>
+      <c r="AC29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="C30" s="7" t="n"/>
@@ -1133,6 +1167,7 @@
       <c r="V30" s="7" t="n"/>
       <c r="Y30" s="7" t="n"/>
       <c r="AB30" s="7" t="n"/>
+      <c r="AC30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="C31" s="7" t="n"/>
@@ -1146,6 +1181,7 @@
       <c r="V31" s="7" t="n"/>
       <c r="Y31" s="7" t="n"/>
       <c r="AB31" s="7" t="n"/>
+      <c r="AC31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="C32" s="7" t="n"/>
@@ -1159,6 +1195,7 @@
       <c r="V32" s="7" t="n"/>
       <c r="Y32" s="7" t="n"/>
       <c r="AB32" s="7" t="n"/>
+      <c r="AC32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="C33" s="7" t="n"/>
@@ -1172,6 +1209,7 @@
       <c r="V33" s="7" t="n"/>
       <c r="Y33" s="7" t="n"/>
       <c r="AB33" s="7" t="n"/>
+      <c r="AC33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="C34" s="7" t="n"/>
@@ -1185,6 +1223,7 @@
       <c r="V34" s="7" t="n"/>
       <c r="Y34" s="7" t="n"/>
       <c r="AB34" s="7" t="n"/>
+      <c r="AC34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="C35" s="7" t="n"/>
@@ -1198,6 +1237,7 @@
       <c r="V35" s="7" t="n"/>
       <c r="Y35" s="7" t="n"/>
       <c r="AB35" s="7" t="n"/>
+      <c r="AC35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="C36" s="7" t="n"/>
@@ -1211,6 +1251,7 @@
       <c r="V36" s="7" t="n"/>
       <c r="Y36" s="7" t="n"/>
       <c r="AB36" s="7" t="n"/>
+      <c r="AC36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="C37" s="7" t="n"/>
@@ -1224,6 +1265,7 @@
       <c r="V37" s="7" t="n"/>
       <c r="Y37" s="7" t="n"/>
       <c r="AB37" s="7" t="n"/>
+      <c r="AC37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="C38" s="7" t="n"/>
@@ -1237,6 +1279,7 @@
       <c r="V38" s="7" t="n"/>
       <c r="Y38" s="7" t="n"/>
       <c r="AB38" s="7" t="n"/>
+      <c r="AC38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="C39" s="7" t="n"/>
@@ -1250,6 +1293,7 @@
       <c r="V39" s="7" t="n"/>
       <c r="Y39" s="7" t="n"/>
       <c r="AB39" s="7" t="n"/>
+      <c r="AC39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="C40" s="7" t="n"/>
@@ -1263,6 +1307,7 @@
       <c r="V40" s="7" t="n"/>
       <c r="Y40" s="7" t="n"/>
       <c r="AB40" s="7" t="n"/>
+      <c r="AC40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="C41" s="7" t="n"/>
@@ -1276,6 +1321,7 @@
       <c r="V41" s="7" t="n"/>
       <c r="Y41" s="7" t="n"/>
       <c r="AB41" s="7" t="n"/>
+      <c r="AC41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="C42" s="7" t="n"/>
@@ -1289,6 +1335,7 @@
       <c r="V42" s="7" t="n"/>
       <c r="Y42" s="7" t="n"/>
       <c r="AB42" s="7" t="n"/>
+      <c r="AC42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="C43" s="7" t="n"/>
@@ -1302,6 +1349,7 @@
       <c r="V43" s="7" t="n"/>
       <c r="Y43" s="7" t="n"/>
       <c r="AB43" s="7" t="n"/>
+      <c r="AC43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="C44" s="7" t="n"/>
@@ -1315,6 +1363,7 @@
       <c r="V44" s="7" t="n"/>
       <c r="Y44" s="7" t="n"/>
       <c r="AB44" s="7" t="n"/>
+      <c r="AC44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="C45" s="7" t="n"/>
@@ -1328,6 +1377,7 @@
       <c r="V45" s="7" t="n"/>
       <c r="Y45" s="7" t="n"/>
       <c r="AB45" s="7" t="n"/>
+      <c r="AC45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="C46" s="7" t="n"/>
@@ -1341,6 +1391,7 @@
       <c r="V46" s="7" t="n"/>
       <c r="Y46" s="7" t="n"/>
       <c r="AB46" s="7" t="n"/>
+      <c r="AC46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="C47" s="7" t="n"/>
@@ -1354,6 +1405,7 @@
       <c r="V47" s="7" t="n"/>
       <c r="Y47" s="7" t="n"/>
       <c r="AB47" s="7" t="n"/>
+      <c r="AC47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="C48" s="7" t="n"/>
@@ -1367,6 +1419,7 @@
       <c r="V48" s="7" t="n"/>
       <c r="Y48" s="7" t="n"/>
       <c r="AB48" s="7" t="n"/>
+      <c r="AC48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="C49" s="7" t="n"/>
@@ -1380,6 +1433,7 @@
       <c r="V49" s="7" t="n"/>
       <c r="Y49" s="7" t="n"/>
       <c r="AB49" s="7" t="n"/>
+      <c r="AC49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="C50" s="7" t="n"/>
@@ -1393,6 +1447,7 @@
       <c r="V50" s="7" t="n"/>
       <c r="Y50" s="7" t="n"/>
       <c r="AB50" s="7" t="n"/>
+      <c r="AC50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="C51" s="7" t="n"/>
@@ -1406,6 +1461,7 @@
       <c r="V51" s="7" t="n"/>
       <c r="Y51" s="7" t="n"/>
       <c r="AB51" s="7" t="n"/>
+      <c r="AC51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="C52" s="7" t="n"/>
@@ -1419,6 +1475,7 @@
       <c r="V52" s="7" t="n"/>
       <c r="Y52" s="7" t="n"/>
       <c r="AB52" s="7" t="n"/>
+      <c r="AC52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="C53" s="7" t="n"/>
@@ -1432,6 +1489,7 @@
       <c r="V53" s="7" t="n"/>
       <c r="Y53" s="7" t="n"/>
       <c r="AB53" s="7" t="n"/>
+      <c r="AC53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="C54" s="7" t="n"/>
@@ -1445,6 +1503,7 @@
       <c r="V54" s="7" t="n"/>
       <c r="Y54" s="7" t="n"/>
       <c r="AB54" s="7" t="n"/>
+      <c r="AC54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="C55" s="7" t="n"/>
@@ -1458,6 +1517,7 @@
       <c r="V55" s="7" t="n"/>
       <c r="Y55" s="7" t="n"/>
       <c r="AB55" s="7" t="n"/>
+      <c r="AC55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="C56" s="7" t="n"/>
@@ -1471,6 +1531,7 @@
       <c r="V56" s="7" t="n"/>
       <c r="Y56" s="7" t="n"/>
       <c r="AB56" s="7" t="n"/>
+      <c r="AC56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="C57" s="7" t="n"/>
@@ -1484,6 +1545,7 @@
       <c r="V57" s="7" t="n"/>
       <c r="Y57" s="7" t="n"/>
       <c r="AB57" s="7" t="n"/>
+      <c r="AC57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="C58" s="7" t="n"/>
@@ -1497,6 +1559,7 @@
       <c r="V58" s="7" t="n"/>
       <c r="Y58" s="7" t="n"/>
       <c r="AB58" s="7" t="n"/>
+      <c r="AC58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="C59" s="7" t="n"/>
@@ -1510,6 +1573,7 @@
       <c r="V59" s="7" t="n"/>
       <c r="Y59" s="7" t="n"/>
       <c r="AB59" s="7" t="n"/>
+      <c r="AC59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="7" t="n"/>
@@ -1523,6 +1587,7 @@
       <c r="V60" s="7" t="n"/>
       <c r="Y60" s="7" t="n"/>
       <c r="AB60" s="7" t="n"/>
+      <c r="AC60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="C61" s="7" t="n"/>
@@ -1536,6 +1601,7 @@
       <c r="V61" s="7" t="n"/>
       <c r="Y61" s="7" t="n"/>
       <c r="AB61" s="7" t="n"/>
+      <c r="AC61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="C62" s="7" t="n"/>
@@ -1549,6 +1615,7 @@
       <c r="V62" s="7" t="n"/>
       <c r="Y62" s="7" t="n"/>
       <c r="AB62" s="7" t="n"/>
+      <c r="AC62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="C63" s="7" t="n"/>
@@ -1562,6 +1629,7 @@
       <c r="V63" s="7" t="n"/>
       <c r="Y63" s="7" t="n"/>
       <c r="AB63" s="7" t="n"/>
+      <c r="AC63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="C64" s="7" t="n"/>
@@ -1575,6 +1643,7 @@
       <c r="V64" s="7" t="n"/>
       <c r="Y64" s="7" t="n"/>
       <c r="AB64" s="7" t="n"/>
+      <c r="AC64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="C65" s="7" t="n"/>
@@ -1588,6 +1657,7 @@
       <c r="V65" s="7" t="n"/>
       <c r="Y65" s="7" t="n"/>
       <c r="AB65" s="7" t="n"/>
+      <c r="AC65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="C66" s="7" t="n"/>
@@ -1601,6 +1671,7 @@
       <c r="V66" s="7" t="n"/>
       <c r="Y66" s="7" t="n"/>
       <c r="AB66" s="7" t="n"/>
+      <c r="AC66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="C67" s="7" t="n"/>
@@ -1614,6 +1685,7 @@
       <c r="V67" s="7" t="n"/>
       <c r="Y67" s="7" t="n"/>
       <c r="AB67" s="7" t="n"/>
+      <c r="AC67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="C68" s="7" t="n"/>
@@ -1627,6 +1699,7 @@
       <c r="V68" s="7" t="n"/>
       <c r="Y68" s="7" t="n"/>
       <c r="AB68" s="7" t="n"/>
+      <c r="AC68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="C69" s="7" t="n"/>
@@ -1640,6 +1713,7 @@
       <c r="V69" s="7" t="n"/>
       <c r="Y69" s="7" t="n"/>
       <c r="AB69" s="7" t="n"/>
+      <c r="AC69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="C70" s="7" t="n"/>
@@ -1653,6 +1727,7 @@
       <c r="V70" s="7" t="n"/>
       <c r="Y70" s="7" t="n"/>
       <c r="AB70" s="7" t="n"/>
+      <c r="AC70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="C71" s="7" t="n"/>
@@ -1666,6 +1741,7 @@
       <c r="V71" s="7" t="n"/>
       <c r="Y71" s="7" t="n"/>
       <c r="AB71" s="7" t="n"/>
+      <c r="AC71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="C72" s="7" t="n"/>
@@ -1679,6 +1755,7 @@
       <c r="V72" s="7" t="n"/>
       <c r="Y72" s="7" t="n"/>
       <c r="AB72" s="7" t="n"/>
+      <c r="AC72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="C73" s="7" t="n"/>
@@ -1692,6 +1769,7 @@
       <c r="V73" s="7" t="n"/>
       <c r="Y73" s="7" t="n"/>
       <c r="AB73" s="7" t="n"/>
+      <c r="AC73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="C74" s="7" t="n"/>
@@ -1705,6 +1783,7 @@
       <c r="V74" s="7" t="n"/>
       <c r="Y74" s="7" t="n"/>
       <c r="AB74" s="7" t="n"/>
+      <c r="AC74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="C75" s="7" t="n"/>
@@ -1718,6 +1797,7 @@
       <c r="V75" s="7" t="n"/>
       <c r="Y75" s="7" t="n"/>
       <c r="AB75" s="7" t="n"/>
+      <c r="AC75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="C76" s="7" t="n"/>
@@ -1731,6 +1811,7 @@
       <c r="V76" s="7" t="n"/>
       <c r="Y76" s="7" t="n"/>
       <c r="AB76" s="7" t="n"/>
+      <c r="AC76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="C77" s="7" t="n"/>
@@ -1744,6 +1825,7 @@
       <c r="V77" s="7" t="n"/>
       <c r="Y77" s="7" t="n"/>
       <c r="AB77" s="7" t="n"/>
+      <c r="AC77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="C78" s="7" t="n"/>
@@ -1757,6 +1839,7 @@
       <c r="V78" s="7" t="n"/>
       <c r="Y78" s="7" t="n"/>
       <c r="AB78" s="7" t="n"/>
+      <c r="AC78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="C79" s="7" t="n"/>
@@ -1770,6 +1853,7 @@
       <c r="V79" s="7" t="n"/>
       <c r="Y79" s="7" t="n"/>
       <c r="AB79" s="7" t="n"/>
+      <c r="AC79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="C80" s="7" t="n"/>
@@ -1783,6 +1867,7 @@
       <c r="V80" s="7" t="n"/>
       <c r="Y80" s="7" t="n"/>
       <c r="AB80" s="7" t="n"/>
+      <c r="AC80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="C81" s="7" t="n"/>
@@ -1796,6 +1881,7 @@
       <c r="V81" s="7" t="n"/>
       <c r="Y81" s="7" t="n"/>
       <c r="AB81" s="7" t="n"/>
+      <c r="AC81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="C82" s="7" t="n"/>
@@ -1809,6 +1895,7 @@
       <c r="V82" s="7" t="n"/>
       <c r="Y82" s="7" t="n"/>
       <c r="AB82" s="7" t="n"/>
+      <c r="AC82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="C83" s="7" t="n"/>
@@ -1822,6 +1909,7 @@
       <c r="V83" s="7" t="n"/>
       <c r="Y83" s="7" t="n"/>
       <c r="AB83" s="7" t="n"/>
+      <c r="AC83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="C84" s="7" t="n"/>
@@ -1835,6 +1923,7 @@
       <c r="V84" s="7" t="n"/>
       <c r="Y84" s="7" t="n"/>
       <c r="AB84" s="7" t="n"/>
+      <c r="AC84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="C85" s="7" t="n"/>
@@ -1848,6 +1937,7 @@
       <c r="V85" s="7" t="n"/>
       <c r="Y85" s="7" t="n"/>
       <c r="AB85" s="7" t="n"/>
+      <c r="AC85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="C86" s="7" t="n"/>
@@ -1861,6 +1951,7 @@
       <c r="V86" s="7" t="n"/>
       <c r="Y86" s="7" t="n"/>
       <c r="AB86" s="7" t="n"/>
+      <c r="AC86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="C87" s="7" t="n"/>
@@ -1874,6 +1965,7 @@
       <c r="V87" s="7" t="n"/>
       <c r="Y87" s="7" t="n"/>
       <c r="AB87" s="7" t="n"/>
+      <c r="AC87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="C88" s="7" t="n"/>
@@ -1887,6 +1979,7 @@
       <c r="V88" s="7" t="n"/>
       <c r="Y88" s="7" t="n"/>
       <c r="AB88" s="7" t="n"/>
+      <c r="AC88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="C89" s="7" t="n"/>
@@ -1900,6 +1993,7 @@
       <c r="V89" s="7" t="n"/>
       <c r="Y89" s="7" t="n"/>
       <c r="AB89" s="7" t="n"/>
+      <c r="AC89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="C90" s="7" t="n"/>
@@ -1913,6 +2007,7 @@
       <c r="V90" s="7" t="n"/>
       <c r="Y90" s="7" t="n"/>
       <c r="AB90" s="7" t="n"/>
+      <c r="AC90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="C91" s="7" t="n"/>
@@ -1926,6 +2021,7 @@
       <c r="V91" s="7" t="n"/>
       <c r="Y91" s="7" t="n"/>
       <c r="AB91" s="7" t="n"/>
+      <c r="AC91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="C92" s="7" t="n"/>
@@ -1939,6 +2035,7 @@
       <c r="V92" s="7" t="n"/>
       <c r="Y92" s="7" t="n"/>
       <c r="AB92" s="7" t="n"/>
+      <c r="AC92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="C93" s="7" t="n"/>
@@ -1952,6 +2049,7 @@
       <c r="V93" s="7" t="n"/>
       <c r="Y93" s="7" t="n"/>
       <c r="AB93" s="7" t="n"/>
+      <c r="AC93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="C94" s="7" t="n"/>
@@ -1965,6 +2063,7 @@
       <c r="V94" s="7" t="n"/>
       <c r="Y94" s="7" t="n"/>
       <c r="AB94" s="7" t="n"/>
+      <c r="AC94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="C95" s="7" t="n"/>
@@ -1978,6 +2077,7 @@
       <c r="V95" s="7" t="n"/>
       <c r="Y95" s="7" t="n"/>
       <c r="AB95" s="7" t="n"/>
+      <c r="AC95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="C96" s="7" t="n"/>
@@ -1991,6 +2091,7 @@
       <c r="V96" s="7" t="n"/>
       <c r="Y96" s="7" t="n"/>
       <c r="AB96" s="7" t="n"/>
+      <c r="AC96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="C97" s="7" t="n"/>
@@ -2004,6 +2105,7 @@
       <c r="V97" s="7" t="n"/>
       <c r="Y97" s="7" t="n"/>
       <c r="AB97" s="7" t="n"/>
+      <c r="AC97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="C98" s="7" t="n"/>
@@ -2017,6 +2119,7 @@
       <c r="V98" s="7" t="n"/>
       <c r="Y98" s="7" t="n"/>
       <c r="AB98" s="7" t="n"/>
+      <c r="AC98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="C99" s="7" t="n"/>
@@ -2030,6 +2133,7 @@
       <c r="V99" s="7" t="n"/>
       <c r="Y99" s="7" t="n"/>
       <c r="AB99" s="7" t="n"/>
+      <c r="AC99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="C100" s="7" t="n"/>
@@ -2043,6 +2147,7 @@
       <c r="V100" s="7" t="n"/>
       <c r="Y100" s="7" t="n"/>
       <c r="AB100" s="7" t="n"/>
+      <c r="AC100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="C101" s="7" t="n"/>
@@ -2056,6 +2161,7 @@
       <c r="V101" s="7" t="n"/>
       <c r="Y101" s="7" t="n"/>
       <c r="AB101" s="7" t="n"/>
+      <c r="AC101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="C102" s="7" t="n"/>
@@ -2069,6 +2175,7 @@
       <c r="V102" s="7" t="n"/>
       <c r="Y102" s="7" t="n"/>
       <c r="AB102" s="7" t="n"/>
+      <c r="AC102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="C103" s="7" t="n"/>
@@ -2082,6 +2189,7 @@
       <c r="V103" s="7" t="n"/>
       <c r="Y103" s="7" t="n"/>
       <c r="AB103" s="7" t="n"/>
+      <c r="AC103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="C104" s="7" t="n"/>
@@ -2095,6 +2203,7 @@
       <c r="V104" s="7" t="n"/>
       <c r="Y104" s="7" t="n"/>
       <c r="AB104" s="7" t="n"/>
+      <c r="AC104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="C105" s="7" t="n"/>
@@ -2108,6 +2217,7 @@
       <c r="V105" s="7" t="n"/>
       <c r="Y105" s="7" t="n"/>
       <c r="AB105" s="7" t="n"/>
+      <c r="AC105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="C106" s="7" t="n"/>
@@ -2121,6 +2231,7 @@
       <c r="V106" s="7" t="n"/>
       <c r="Y106" s="7" t="n"/>
       <c r="AB106" s="7" t="n"/>
+      <c r="AC106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="C107" s="7" t="n"/>
@@ -2134,6 +2245,7 @@
       <c r="V107" s="7" t="n"/>
       <c r="Y107" s="7" t="n"/>
       <c r="AB107" s="7" t="n"/>
+      <c r="AC107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="C108" s="7" t="n"/>
@@ -2147,6 +2259,7 @@
       <c r="V108" s="7" t="n"/>
       <c r="Y108" s="7" t="n"/>
       <c r="AB108" s="7" t="n"/>
+      <c r="AC108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="C109" s="7" t="n"/>
@@ -2160,6 +2273,7 @@
       <c r="V109" s="7" t="n"/>
       <c r="Y109" s="7" t="n"/>
       <c r="AB109" s="7" t="n"/>
+      <c r="AC109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="C110" s="7" t="n"/>
@@ -2173,6 +2287,7 @@
       <c r="V110" s="7" t="n"/>
       <c r="Y110" s="7" t="n"/>
       <c r="AB110" s="7" t="n"/>
+      <c r="AC110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="C111" s="7" t="n"/>
@@ -2186,6 +2301,7 @@
       <c r="V111" s="7" t="n"/>
       <c r="Y111" s="7" t="n"/>
       <c r="AB111" s="7" t="n"/>
+      <c r="AC111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="C112" s="7" t="n"/>
@@ -2199,6 +2315,7 @@
       <c r="V112" s="7" t="n"/>
       <c r="Y112" s="7" t="n"/>
       <c r="AB112" s="7" t="n"/>
+      <c r="AC112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="C113" s="7" t="n"/>
@@ -2212,6 +2329,7 @@
       <c r="V113" s="7" t="n"/>
       <c r="Y113" s="7" t="n"/>
       <c r="AB113" s="7" t="n"/>
+      <c r="AC113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="C114" s="7" t="n"/>
@@ -2225,6 +2343,7 @@
       <c r="V114" s="7" t="n"/>
       <c r="Y114" s="7" t="n"/>
       <c r="AB114" s="7" t="n"/>
+      <c r="AC114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="C115" s="7" t="n"/>
@@ -2238,6 +2357,7 @@
       <c r="V115" s="7" t="n"/>
       <c r="Y115" s="7" t="n"/>
       <c r="AB115" s="7" t="n"/>
+      <c r="AC115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="C116" s="7" t="n"/>
@@ -2251,6 +2371,7 @@
       <c r="V116" s="7" t="n"/>
       <c r="Y116" s="7" t="n"/>
       <c r="AB116" s="7" t="n"/>
+      <c r="AC116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="C117" s="7" t="n"/>
@@ -2264,6 +2385,7 @@
       <c r="V117" s="7" t="n"/>
       <c r="Y117" s="7" t="n"/>
       <c r="AB117" s="7" t="n"/>
+      <c r="AC117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="C118" s="7" t="n"/>
@@ -2277,6 +2399,7 @@
       <c r="V118" s="7" t="n"/>
       <c r="Y118" s="7" t="n"/>
       <c r="AB118" s="7" t="n"/>
+      <c r="AC118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="C119" s="7" t="n"/>
@@ -2290,6 +2413,7 @@
       <c r="V119" s="7" t="n"/>
       <c r="Y119" s="7" t="n"/>
       <c r="AB119" s="7" t="n"/>
+      <c r="AC119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="C120" s="7" t="n"/>
@@ -2303,6 +2427,7 @@
       <c r="V120" s="7" t="n"/>
       <c r="Y120" s="7" t="n"/>
       <c r="AB120" s="7" t="n"/>
+      <c r="AC120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="C121" s="7" t="n"/>
@@ -2316,6 +2441,7 @@
       <c r="V121" s="7" t="n"/>
       <c r="Y121" s="7" t="n"/>
       <c r="AB121" s="7" t="n"/>
+      <c r="AC121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="C122" s="7" t="n"/>
@@ -2329,6 +2455,7 @@
       <c r="V122" s="7" t="n"/>
       <c r="Y122" s="7" t="n"/>
       <c r="AB122" s="7" t="n"/>
+      <c r="AC122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="C123" s="7" t="n"/>
@@ -2342,6 +2469,7 @@
       <c r="V123" s="7" t="n"/>
       <c r="Y123" s="7" t="n"/>
       <c r="AB123" s="7" t="n"/>
+      <c r="AC123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="C124" s="7" t="n"/>
@@ -2355,6 +2483,7 @@
       <c r="V124" s="7" t="n"/>
       <c r="Y124" s="7" t="n"/>
       <c r="AB124" s="7" t="n"/>
+      <c r="AC124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="C125" s="7" t="n"/>
@@ -2368,6 +2497,7 @@
       <c r="V125" s="7" t="n"/>
       <c r="Y125" s="7" t="n"/>
       <c r="AB125" s="7" t="n"/>
+      <c r="AC125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="C126" s="7" t="n"/>
@@ -2381,6 +2511,7 @@
       <c r="V126" s="7" t="n"/>
       <c r="Y126" s="7" t="n"/>
       <c r="AB126" s="7" t="n"/>
+      <c r="AC126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="C127" s="7" t="n"/>
@@ -2394,6 +2525,7 @@
       <c r="V127" s="7" t="n"/>
       <c r="Y127" s="7" t="n"/>
       <c r="AB127" s="7" t="n"/>
+      <c r="AC127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="C128" s="7" t="n"/>
@@ -2407,6 +2539,7 @@
       <c r="V128" s="7" t="n"/>
       <c r="Y128" s="7" t="n"/>
       <c r="AB128" s="7" t="n"/>
+      <c r="AC128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="C129" s="7" t="n"/>
@@ -2420,6 +2553,7 @@
       <c r="V129" s="7" t="n"/>
       <c r="Y129" s="7" t="n"/>
       <c r="AB129" s="7" t="n"/>
+      <c r="AC129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="C130" s="7" t="n"/>
@@ -2433,6 +2567,7 @@
       <c r="V130" s="7" t="n"/>
       <c r="Y130" s="7" t="n"/>
       <c r="AB130" s="7" t="n"/>
+      <c r="AC130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="C131" s="7" t="n"/>
@@ -2446,6 +2581,7 @@
       <c r="V131" s="7" t="n"/>
       <c r="Y131" s="7" t="n"/>
       <c r="AB131" s="7" t="n"/>
+      <c r="AC131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="C132" s="7" t="n"/>
@@ -2459,6 +2595,7 @@
       <c r="V132" s="7" t="n"/>
       <c r="Y132" s="7" t="n"/>
       <c r="AB132" s="7" t="n"/>
+      <c r="AC132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="C133" s="7" t="n"/>
@@ -2472,6 +2609,7 @@
       <c r="V133" s="7" t="n"/>
       <c r="Y133" s="7" t="n"/>
       <c r="AB133" s="7" t="n"/>
+      <c r="AC133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="C134" s="7" t="n"/>
@@ -2485,6 +2623,7 @@
       <c r="V134" s="7" t="n"/>
       <c r="Y134" s="7" t="n"/>
       <c r="AB134" s="7" t="n"/>
+      <c r="AC134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="C135" s="7" t="n"/>
@@ -2498,6 +2637,7 @@
       <c r="V135" s="7" t="n"/>
       <c r="Y135" s="7" t="n"/>
       <c r="AB135" s="7" t="n"/>
+      <c r="AC135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="C136" s="7" t="n"/>
@@ -2511,6 +2651,7 @@
       <c r="V136" s="7" t="n"/>
       <c r="Y136" s="7" t="n"/>
       <c r="AB136" s="7" t="n"/>
+      <c r="AC136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="C137" s="7" t="n"/>
@@ -2524,6 +2665,7 @@
       <c r="V137" s="7" t="n"/>
       <c r="Y137" s="7" t="n"/>
       <c r="AB137" s="7" t="n"/>
+      <c r="AC137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="C138" s="7" t="n"/>
@@ -2537,6 +2679,7 @@
       <c r="V138" s="7" t="n"/>
       <c r="Y138" s="7" t="n"/>
       <c r="AB138" s="7" t="n"/>
+      <c r="AC138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="C139" s="7" t="n"/>
@@ -2550,6 +2693,7 @@
       <c r="V139" s="7" t="n"/>
       <c r="Y139" s="7" t="n"/>
       <c r="AB139" s="7" t="n"/>
+      <c r="AC139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="C140" s="7" t="n"/>
@@ -2563,6 +2707,7 @@
       <c r="V140" s="7" t="n"/>
       <c r="Y140" s="7" t="n"/>
       <c r="AB140" s="7" t="n"/>
+      <c r="AC140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="C141" s="7" t="n"/>
@@ -2576,6 +2721,7 @@
       <c r="V141" s="7" t="n"/>
       <c r="Y141" s="7" t="n"/>
       <c r="AB141" s="7" t="n"/>
+      <c r="AC141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="C142" s="7" t="n"/>
@@ -2589,6 +2735,7 @@
       <c r="V142" s="7" t="n"/>
       <c r="Y142" s="7" t="n"/>
       <c r="AB142" s="7" t="n"/>
+      <c r="AC142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="C143" s="7" t="n"/>
@@ -2602,6 +2749,7 @@
       <c r="V143" s="7" t="n"/>
       <c r="Y143" s="7" t="n"/>
       <c r="AB143" s="7" t="n"/>
+      <c r="AC143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="C144" s="7" t="n"/>
@@ -2615,6 +2763,7 @@
       <c r="V144" s="7" t="n"/>
       <c r="Y144" s="7" t="n"/>
       <c r="AB144" s="7" t="n"/>
+      <c r="AC144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="C145" s="7" t="n"/>
@@ -2628,6 +2777,7 @@
       <c r="V145" s="7" t="n"/>
       <c r="Y145" s="7" t="n"/>
       <c r="AB145" s="7" t="n"/>
+      <c r="AC145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="C146" s="7" t="n"/>
@@ -2641,6 +2791,7 @@
       <c r="V146" s="7" t="n"/>
       <c r="Y146" s="7" t="n"/>
       <c r="AB146" s="7" t="n"/>
+      <c r="AC146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="C147" s="7" t="n"/>
@@ -2654,6 +2805,7 @@
       <c r="V147" s="7" t="n"/>
       <c r="Y147" s="7" t="n"/>
       <c r="AB147" s="7" t="n"/>
+      <c r="AC147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="C148" s="7" t="n"/>
@@ -2667,6 +2819,7 @@
       <c r="V148" s="7" t="n"/>
       <c r="Y148" s="7" t="n"/>
       <c r="AB148" s="7" t="n"/>
+      <c r="AC148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="C149" s="7" t="n"/>
@@ -2680,6 +2833,7 @@
       <c r="V149" s="7" t="n"/>
       <c r="Y149" s="7" t="n"/>
       <c r="AB149" s="7" t="n"/>
+      <c r="AC149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="C150" s="7" t="n"/>
@@ -2693,6 +2847,7 @@
       <c r="V150" s="7" t="n"/>
       <c r="Y150" s="7" t="n"/>
       <c r="AB150" s="7" t="n"/>
+      <c r="AC150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="C151" s="7" t="n"/>
@@ -2706,6 +2861,7 @@
       <c r="V151" s="7" t="n"/>
       <c r="Y151" s="7" t="n"/>
       <c r="AB151" s="7" t="n"/>
+      <c r="AC151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="C152" s="7" t="n"/>
@@ -2719,6 +2875,7 @@
       <c r="V152" s="7" t="n"/>
       <c r="Y152" s="7" t="n"/>
       <c r="AB152" s="7" t="n"/>
+      <c r="AC152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="C153" s="7" t="n"/>
@@ -2732,6 +2889,7 @@
       <c r="V153" s="7" t="n"/>
       <c r="Y153" s="7" t="n"/>
       <c r="AB153" s="7" t="n"/>
+      <c r="AC153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="C154" s="7" t="n"/>
@@ -2745,6 +2903,7 @@
       <c r="V154" s="7" t="n"/>
       <c r="Y154" s="7" t="n"/>
       <c r="AB154" s="7" t="n"/>
+      <c r="AC154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="C155" s="7" t="n"/>
@@ -2758,6 +2917,7 @@
       <c r="V155" s="7" t="n"/>
       <c r="Y155" s="7" t="n"/>
       <c r="AB155" s="7" t="n"/>
+      <c r="AC155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="C156" s="7" t="n"/>
@@ -2771,6 +2931,7 @@
       <c r="V156" s="7" t="n"/>
       <c r="Y156" s="7" t="n"/>
       <c r="AB156" s="7" t="n"/>
+      <c r="AC156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="C157" s="7" t="n"/>
@@ -2784,6 +2945,7 @@
       <c r="V157" s="7" t="n"/>
       <c r="Y157" s="7" t="n"/>
       <c r="AB157" s="7" t="n"/>
+      <c r="AC157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="C158" s="7" t="n"/>
@@ -2797,6 +2959,7 @@
       <c r="V158" s="7" t="n"/>
       <c r="Y158" s="7" t="n"/>
       <c r="AB158" s="7" t="n"/>
+      <c r="AC158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="C159" s="7" t="n"/>
@@ -2810,6 +2973,7 @@
       <c r="V159" s="7" t="n"/>
       <c r="Y159" s="7" t="n"/>
       <c r="AB159" s="7" t="n"/>
+      <c r="AC159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="C160" s="7" t="n"/>
@@ -2823,6 +2987,7 @@
       <c r="V160" s="7" t="n"/>
       <c r="Y160" s="7" t="n"/>
       <c r="AB160" s="7" t="n"/>
+      <c r="AC160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="C161" s="7" t="n"/>
@@ -2836,6 +3001,7 @@
       <c r="V161" s="7" t="n"/>
       <c r="Y161" s="7" t="n"/>
       <c r="AB161" s="7" t="n"/>
+      <c r="AC161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="C162" s="7" t="n"/>
@@ -2849,6 +3015,7 @@
       <c r="V162" s="7" t="n"/>
       <c r="Y162" s="7" t="n"/>
       <c r="AB162" s="7" t="n"/>
+      <c r="AC162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="C163" s="7" t="n"/>
@@ -2862,6 +3029,7 @@
       <c r="V163" s="7" t="n"/>
       <c r="Y163" s="7" t="n"/>
       <c r="AB163" s="7" t="n"/>
+      <c r="AC163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="C164" s="7" t="n"/>
@@ -2875,6 +3043,7 @@
       <c r="V164" s="7" t="n"/>
       <c r="Y164" s="7" t="n"/>
       <c r="AB164" s="7" t="n"/>
+      <c r="AC164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="C165" s="7" t="n"/>
@@ -2888,6 +3057,7 @@
       <c r="V165" s="7" t="n"/>
       <c r="Y165" s="7" t="n"/>
       <c r="AB165" s="7" t="n"/>
+      <c r="AC165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="C166" s="7" t="n"/>
@@ -2901,6 +3071,7 @@
       <c r="V166" s="7" t="n"/>
       <c r="Y166" s="7" t="n"/>
       <c r="AB166" s="7" t="n"/>
+      <c r="AC166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="C167" s="7" t="n"/>
@@ -2914,6 +3085,7 @@
       <c r="V167" s="7" t="n"/>
       <c r="Y167" s="7" t="n"/>
       <c r="AB167" s="7" t="n"/>
+      <c r="AC167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="C168" s="7" t="n"/>
@@ -2927,6 +3099,7 @@
       <c r="V168" s="7" t="n"/>
       <c r="Y168" s="7" t="n"/>
       <c r="AB168" s="7" t="n"/>
+      <c r="AC168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="C169" s="7" t="n"/>
@@ -2940,6 +3113,7 @@
       <c r="V169" s="7" t="n"/>
       <c r="Y169" s="7" t="n"/>
       <c r="AB169" s="7" t="n"/>
+      <c r="AC169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="C170" s="7" t="n"/>
@@ -2953,6 +3127,7 @@
       <c r="V170" s="7" t="n"/>
       <c r="Y170" s="7" t="n"/>
       <c r="AB170" s="7" t="n"/>
+      <c r="AC170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="C171" s="7" t="n"/>
@@ -2966,6 +3141,7 @@
       <c r="V171" s="7" t="n"/>
       <c r="Y171" s="7" t="n"/>
       <c r="AB171" s="7" t="n"/>
+      <c r="AC171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="C172" s="7" t="n"/>
@@ -2979,6 +3155,7 @@
       <c r="V172" s="7" t="n"/>
       <c r="Y172" s="7" t="n"/>
       <c r="AB172" s="7" t="n"/>
+      <c r="AC172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="C173" s="7" t="n"/>
@@ -2992,6 +3169,7 @@
       <c r="V173" s="7" t="n"/>
       <c r="Y173" s="7" t="n"/>
       <c r="AB173" s="7" t="n"/>
+      <c r="AC173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="C174" s="7" t="n"/>
@@ -3005,6 +3183,7 @@
       <c r="V174" s="7" t="n"/>
       <c r="Y174" s="7" t="n"/>
       <c r="AB174" s="7" t="n"/>
+      <c r="AC174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="C175" s="7" t="n"/>
@@ -3018,6 +3197,7 @@
       <c r="V175" s="7" t="n"/>
       <c r="Y175" s="7" t="n"/>
       <c r="AB175" s="7" t="n"/>
+      <c r="AC175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="C176" s="7" t="n"/>
@@ -3031,6 +3211,7 @@
       <c r="V176" s="7" t="n"/>
       <c r="Y176" s="7" t="n"/>
       <c r="AB176" s="7" t="n"/>
+      <c r="AC176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="C177" s="7" t="n"/>
@@ -3044,6 +3225,7 @@
       <c r="V177" s="7" t="n"/>
       <c r="Y177" s="7" t="n"/>
       <c r="AB177" s="7" t="n"/>
+      <c r="AC177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="C178" s="7" t="n"/>
@@ -3057,6 +3239,7 @@
       <c r="V178" s="7" t="n"/>
       <c r="Y178" s="7" t="n"/>
       <c r="AB178" s="7" t="n"/>
+      <c r="AC178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="C179" s="7" t="n"/>
@@ -3070,6 +3253,7 @@
       <c r="V179" s="7" t="n"/>
       <c r="Y179" s="7" t="n"/>
       <c r="AB179" s="7" t="n"/>
+      <c r="AC179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="C180" s="7" t="n"/>
@@ -3083,6 +3267,7 @@
       <c r="V180" s="7" t="n"/>
       <c r="Y180" s="7" t="n"/>
       <c r="AB180" s="7" t="n"/>
+      <c r="AC180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="C181" s="7" t="n"/>
@@ -3096,6 +3281,7 @@
       <c r="V181" s="7" t="n"/>
       <c r="Y181" s="7" t="n"/>
       <c r="AB181" s="7" t="n"/>
+      <c r="AC181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="C182" s="7" t="n"/>
@@ -3109,6 +3295,7 @@
       <c r="V182" s="7" t="n"/>
       <c r="Y182" s="7" t="n"/>
       <c r="AB182" s="7" t="n"/>
+      <c r="AC182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="C183" s="7" t="n"/>
@@ -3122,6 +3309,7 @@
       <c r="V183" s="7" t="n"/>
       <c r="Y183" s="7" t="n"/>
       <c r="AB183" s="7" t="n"/>
+      <c r="AC183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="C184" s="7" t="n"/>
@@ -3135,6 +3323,7 @@
       <c r="V184" s="7" t="n"/>
       <c r="Y184" s="7" t="n"/>
       <c r="AB184" s="7" t="n"/>
+      <c r="AC184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="C185" s="7" t="n"/>
@@ -3148,6 +3337,7 @@
       <c r="V185" s="7" t="n"/>
       <c r="Y185" s="7" t="n"/>
       <c r="AB185" s="7" t="n"/>
+      <c r="AC185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="C186" s="7" t="n"/>
@@ -3161,6 +3351,7 @@
       <c r="V186" s="7" t="n"/>
       <c r="Y186" s="7" t="n"/>
       <c r="AB186" s="7" t="n"/>
+      <c r="AC186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="C187" s="7" t="n"/>
@@ -3174,6 +3365,7 @@
       <c r="V187" s="7" t="n"/>
       <c r="Y187" s="7" t="n"/>
       <c r="AB187" s="7" t="n"/>
+      <c r="AC187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="C188" s="7" t="n"/>
@@ -3187,6 +3379,7 @@
       <c r="V188" s="7" t="n"/>
       <c r="Y188" s="7" t="n"/>
       <c r="AB188" s="7" t="n"/>
+      <c r="AC188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="C189" s="7" t="n"/>
@@ -3200,6 +3393,7 @@
       <c r="V189" s="7" t="n"/>
       <c r="Y189" s="7" t="n"/>
       <c r="AB189" s="7" t="n"/>
+      <c r="AC189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="C190" s="7" t="n"/>
@@ -3213,6 +3407,7 @@
       <c r="V190" s="7" t="n"/>
       <c r="Y190" s="7" t="n"/>
       <c r="AB190" s="7" t="n"/>
+      <c r="AC190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="C191" s="7" t="n"/>
@@ -3226,6 +3421,7 @@
       <c r="V191" s="7" t="n"/>
       <c r="Y191" s="7" t="n"/>
       <c r="AB191" s="7" t="n"/>
+      <c r="AC191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="C192" s="7" t="n"/>
@@ -3239,6 +3435,7 @@
       <c r="V192" s="7" t="n"/>
       <c r="Y192" s="7" t="n"/>
       <c r="AB192" s="7" t="n"/>
+      <c r="AC192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="C193" s="7" t="n"/>
@@ -3252,6 +3449,7 @@
       <c r="V193" s="7" t="n"/>
       <c r="Y193" s="7" t="n"/>
       <c r="AB193" s="7" t="n"/>
+      <c r="AC193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="C194" s="7" t="n"/>
@@ -3265,6 +3463,7 @@
       <c r="V194" s="7" t="n"/>
       <c r="Y194" s="7" t="n"/>
       <c r="AB194" s="7" t="n"/>
+      <c r="AC194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="C195" s="7" t="n"/>
@@ -3278,6 +3477,7 @@
       <c r="V195" s="7" t="n"/>
       <c r="Y195" s="7" t="n"/>
       <c r="AB195" s="7" t="n"/>
+      <c r="AC195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="C196" s="7" t="n"/>
@@ -3291,6 +3491,7 @@
       <c r="V196" s="7" t="n"/>
       <c r="Y196" s="7" t="n"/>
       <c r="AB196" s="7" t="n"/>
+      <c r="AC196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="C197" s="7" t="n"/>
@@ -3304,6 +3505,7 @@
       <c r="V197" s="7" t="n"/>
       <c r="Y197" s="7" t="n"/>
       <c r="AB197" s="7" t="n"/>
+      <c r="AC197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="C198" s="7" t="n"/>
@@ -3317,6 +3519,7 @@
       <c r="V198" s="7" t="n"/>
       <c r="Y198" s="7" t="n"/>
       <c r="AB198" s="7" t="n"/>
+      <c r="AC198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="C199" s="7" t="n"/>
@@ -3330,6 +3533,7 @@
       <c r="V199" s="7" t="n"/>
       <c r="Y199" s="7" t="n"/>
       <c r="AB199" s="7" t="n"/>
+      <c r="AC199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="C200" s="7" t="n"/>
@@ -3343,6 +3547,7 @@
       <c r="V200" s="7" t="n"/>
       <c r="Y200" s="7" t="n"/>
       <c r="AB200" s="7" t="n"/>
+      <c r="AC200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="C201" s="7" t="n"/>
@@ -3356,6 +3561,7 @@
       <c r="V201" s="7" t="n"/>
       <c r="Y201" s="7" t="n"/>
       <c r="AB201" s="7" t="n"/>
+      <c r="AC201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="C202" s="7" t="n"/>
@@ -3369,6 +3575,7 @@
       <c r="V202" s="7" t="n"/>
       <c r="Y202" s="7" t="n"/>
       <c r="AB202" s="7" t="n"/>
+      <c r="AC202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="C203" s="7" t="n"/>
@@ -3382,6 +3589,7 @@
       <c r="V203" s="7" t="n"/>
       <c r="Y203" s="7" t="n"/>
       <c r="AB203" s="7" t="n"/>
+      <c r="AC203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="C204" s="7" t="n"/>
@@ -3395,6 +3603,7 @@
       <c r="V204" s="7" t="n"/>
       <c r="Y204" s="7" t="n"/>
       <c r="AB204" s="7" t="n"/>
+      <c r="AC204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="C205" s="7" t="n"/>
@@ -3408,6 +3617,7 @@
       <c r="V205" s="7" t="n"/>
       <c r="Y205" s="7" t="n"/>
       <c r="AB205" s="7" t="n"/>
+      <c r="AC205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="C206" s="7" t="n"/>
@@ -3421,6 +3631,7 @@
       <c r="V206" s="7" t="n"/>
       <c r="Y206" s="7" t="n"/>
       <c r="AB206" s="7" t="n"/>
+      <c r="AC206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="C207" s="7" t="n"/>
@@ -3434,6 +3645,7 @@
       <c r="V207" s="7" t="n"/>
       <c r="Y207" s="7" t="n"/>
       <c r="AB207" s="7" t="n"/>
+      <c r="AC207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="C208" s="7" t="n"/>
@@ -3447,6 +3659,7 @@
       <c r="V208" s="7" t="n"/>
       <c r="Y208" s="7" t="n"/>
       <c r="AB208" s="7" t="n"/>
+      <c r="AC208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="C209" s="7" t="n"/>
@@ -3460,6 +3673,7 @@
       <c r="V209" s="7" t="n"/>
       <c r="Y209" s="7" t="n"/>
       <c r="AB209" s="7" t="n"/>
+      <c r="AC209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="C210" s="7" t="n"/>
@@ -3473,6 +3687,7 @@
       <c r="V210" s="7" t="n"/>
       <c r="Y210" s="7" t="n"/>
       <c r="AB210" s="7" t="n"/>
+      <c r="AC210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="C211" s="7" t="n"/>
@@ -3486,6 +3701,7 @@
       <c r="V211" s="7" t="n"/>
       <c r="Y211" s="7" t="n"/>
       <c r="AB211" s="7" t="n"/>
+      <c r="AC211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="C212" s="7" t="n"/>
@@ -3499,6 +3715,7 @@
       <c r="V212" s="7" t="n"/>
       <c r="Y212" s="7" t="n"/>
       <c r="AB212" s="7" t="n"/>
+      <c r="AC212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="C213" s="7" t="n"/>
@@ -3512,6 +3729,7 @@
       <c r="V213" s="7" t="n"/>
       <c r="Y213" s="7" t="n"/>
       <c r="AB213" s="7" t="n"/>
+      <c r="AC213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="C214" s="7" t="n"/>
@@ -3525,6 +3743,7 @@
       <c r="V214" s="7" t="n"/>
       <c r="Y214" s="7" t="n"/>
       <c r="AB214" s="7" t="n"/>
+      <c r="AC214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="C215" s="7" t="n"/>
@@ -3538,6 +3757,7 @@
       <c r="V215" s="7" t="n"/>
       <c r="Y215" s="7" t="n"/>
       <c r="AB215" s="7" t="n"/>
+      <c r="AC215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="C216" s="7" t="n"/>
@@ -3551,6 +3771,7 @@
       <c r="V216" s="7" t="n"/>
       <c r="Y216" s="7" t="n"/>
       <c r="AB216" s="7" t="n"/>
+      <c r="AC216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="C217" s="7" t="n"/>
@@ -3564,6 +3785,7 @@
       <c r="V217" s="7" t="n"/>
       <c r="Y217" s="7" t="n"/>
       <c r="AB217" s="7" t="n"/>
+      <c r="AC217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="C218" s="7" t="n"/>
@@ -3577,6 +3799,7 @@
       <c r="V218" s="7" t="n"/>
       <c r="Y218" s="7" t="n"/>
       <c r="AB218" s="7" t="n"/>
+      <c r="AC218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="C219" s="7" t="n"/>
@@ -3590,6 +3813,7 @@
       <c r="V219" s="7" t="n"/>
       <c r="Y219" s="7" t="n"/>
       <c r="AB219" s="7" t="n"/>
+      <c r="AC219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="C220" s="7" t="n"/>
@@ -3603,6 +3827,7 @@
       <c r="V220" s="7" t="n"/>
       <c r="Y220" s="7" t="n"/>
       <c r="AB220" s="7" t="n"/>
+      <c r="AC220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="C221" s="7" t="n"/>
@@ -3616,6 +3841,7 @@
       <c r="V221" s="7" t="n"/>
       <c r="Y221" s="7" t="n"/>
       <c r="AB221" s="7" t="n"/>
+      <c r="AC221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="C222" s="7" t="n"/>
@@ -3629,6 +3855,7 @@
       <c r="V222" s="7" t="n"/>
       <c r="Y222" s="7" t="n"/>
       <c r="AB222" s="7" t="n"/>
+      <c r="AC222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="C223" s="7" t="n"/>
@@ -3642,6 +3869,7 @@
       <c r="V223" s="7" t="n"/>
       <c r="Y223" s="7" t="n"/>
       <c r="AB223" s="7" t="n"/>
+      <c r="AC223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="C224" s="7" t="n"/>
@@ -3655,6 +3883,7 @@
       <c r="V224" s="7" t="n"/>
       <c r="Y224" s="7" t="n"/>
       <c r="AB224" s="7" t="n"/>
+      <c r="AC224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="C225" s="7" t="n"/>
@@ -3668,6 +3897,7 @@
       <c r="V225" s="7" t="n"/>
       <c r="Y225" s="7" t="n"/>
       <c r="AB225" s="7" t="n"/>
+      <c r="AC225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="C226" s="7" t="n"/>
@@ -3681,6 +3911,7 @@
       <c r="V226" s="7" t="n"/>
       <c r="Y226" s="7" t="n"/>
       <c r="AB226" s="7" t="n"/>
+      <c r="AC226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="C227" s="7" t="n"/>
@@ -3694,6 +3925,7 @@
       <c r="V227" s="7" t="n"/>
       <c r="Y227" s="7" t="n"/>
       <c r="AB227" s="7" t="n"/>
+      <c r="AC227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="C228" s="7" t="n"/>
@@ -3707,6 +3939,7 @@
       <c r="V228" s="7" t="n"/>
       <c r="Y228" s="7" t="n"/>
       <c r="AB228" s="7" t="n"/>
+      <c r="AC228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="C229" s="7" t="n"/>
@@ -3720,6 +3953,7 @@
       <c r="V229" s="7" t="n"/>
       <c r="Y229" s="7" t="n"/>
       <c r="AB229" s="7" t="n"/>
+      <c r="AC229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="C230" s="7" t="n"/>
@@ -3733,6 +3967,7 @@
       <c r="V230" s="7" t="n"/>
       <c r="Y230" s="7" t="n"/>
       <c r="AB230" s="7" t="n"/>
+      <c r="AC230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="C231" s="7" t="n"/>
@@ -3746,6 +3981,7 @@
       <c r="V231" s="7" t="n"/>
       <c r="Y231" s="7" t="n"/>
       <c r="AB231" s="7" t="n"/>
+      <c r="AC231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="C232" s="7" t="n"/>
@@ -3759,6 +3995,7 @@
       <c r="V232" s="7" t="n"/>
       <c r="Y232" s="7" t="n"/>
       <c r="AB232" s="7" t="n"/>
+      <c r="AC232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="C233" s="7" t="n"/>
@@ -3772,6 +4009,7 @@
       <c r="V233" s="7" t="n"/>
       <c r="Y233" s="7" t="n"/>
       <c r="AB233" s="7" t="n"/>
+      <c r="AC233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="C234" s="7" t="n"/>
@@ -3785,6 +4023,7 @@
       <c r="V234" s="7" t="n"/>
       <c r="Y234" s="7" t="n"/>
       <c r="AB234" s="7" t="n"/>
+      <c r="AC234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="C235" s="7" t="n"/>
@@ -3798,6 +4037,7 @@
       <c r="V235" s="7" t="n"/>
       <c r="Y235" s="7" t="n"/>
       <c r="AB235" s="7" t="n"/>
+      <c r="AC235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="C236" s="7" t="n"/>
@@ -3811,6 +4051,7 @@
       <c r="V236" s="7" t="n"/>
       <c r="Y236" s="7" t="n"/>
       <c r="AB236" s="7" t="n"/>
+      <c r="AC236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="C237" s="7" t="n"/>
@@ -3824,6 +4065,7 @@
       <c r="V237" s="7" t="n"/>
       <c r="Y237" s="7" t="n"/>
       <c r="AB237" s="7" t="n"/>
+      <c r="AC237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="C238" s="7" t="n"/>
@@ -3837,6 +4079,7 @@
       <c r="V238" s="7" t="n"/>
       <c r="Y238" s="7" t="n"/>
       <c r="AB238" s="7" t="n"/>
+      <c r="AC238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="C239" s="7" t="n"/>
@@ -3850,6 +4093,7 @@
       <c r="V239" s="7" t="n"/>
       <c r="Y239" s="7" t="n"/>
       <c r="AB239" s="7" t="n"/>
+      <c r="AC239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="C240" s="7" t="n"/>
@@ -3863,6 +4107,7 @@
       <c r="V240" s="7" t="n"/>
       <c r="Y240" s="7" t="n"/>
       <c r="AB240" s="7" t="n"/>
+      <c r="AC240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="C241" s="7" t="n"/>
@@ -3876,6 +4121,7 @@
       <c r="V241" s="7" t="n"/>
       <c r="Y241" s="7" t="n"/>
       <c r="AB241" s="7" t="n"/>
+      <c r="AC241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="C242" s="7" t="n"/>
@@ -3889,6 +4135,7 @@
       <c r="V242" s="7" t="n"/>
       <c r="Y242" s="7" t="n"/>
       <c r="AB242" s="7" t="n"/>
+      <c r="AC242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="C243" s="7" t="n"/>
@@ -3902,6 +4149,7 @@
       <c r="V243" s="7" t="n"/>
       <c r="Y243" s="7" t="n"/>
       <c r="AB243" s="7" t="n"/>
+      <c r="AC243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="C244" s="7" t="n"/>
@@ -3915,6 +4163,7 @@
       <c r="V244" s="7" t="n"/>
       <c r="Y244" s="7" t="n"/>
       <c r="AB244" s="7" t="n"/>
+      <c r="AC244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="C245" s="7" t="n"/>
@@ -3928,6 +4177,7 @@
       <c r="V245" s="7" t="n"/>
       <c r="Y245" s="7" t="n"/>
       <c r="AB245" s="7" t="n"/>
+      <c r="AC245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="C246" s="7" t="n"/>
@@ -3941,6 +4191,7 @@
       <c r="V246" s="7" t="n"/>
       <c r="Y246" s="7" t="n"/>
       <c r="AB246" s="7" t="n"/>
+      <c r="AC246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="C247" s="7" t="n"/>
@@ -3954,6 +4205,7 @@
       <c r="V247" s="7" t="n"/>
       <c r="Y247" s="7" t="n"/>
       <c r="AB247" s="7" t="n"/>
+      <c r="AC247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="C248" s="7" t="n"/>
@@ -3967,6 +4219,7 @@
       <c r="V248" s="7" t="n"/>
       <c r="Y248" s="7" t="n"/>
       <c r="AB248" s="7" t="n"/>
+      <c r="AC248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="C249" s="7" t="n"/>
@@ -3980,6 +4233,7 @@
       <c r="V249" s="7" t="n"/>
       <c r="Y249" s="7" t="n"/>
       <c r="AB249" s="7" t="n"/>
+      <c r="AC249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="C250" s="7" t="n"/>
@@ -3993,6 +4247,7 @@
       <c r="V250" s="7" t="n"/>
       <c r="Y250" s="7" t="n"/>
       <c r="AB250" s="7" t="n"/>
+      <c r="AC250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="C251" s="7" t="n"/>
@@ -4006,6 +4261,7 @@
       <c r="V251" s="7" t="n"/>
       <c r="Y251" s="7" t="n"/>
       <c r="AB251" s="7" t="n"/>
+      <c r="AC251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="C252" s="7" t="n"/>
@@ -4019,6 +4275,7 @@
       <c r="V252" s="7" t="n"/>
       <c r="Y252" s="7" t="n"/>
       <c r="AB252" s="7" t="n"/>
+      <c r="AC252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="C253" s="7" t="n"/>
@@ -4032,6 +4289,7 @@
       <c r="V253" s="7" t="n"/>
       <c r="Y253" s="7" t="n"/>
       <c r="AB253" s="7" t="n"/>
+      <c r="AC253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="C254" s="7" t="n"/>
@@ -4045,6 +4303,7 @@
       <c r="V254" s="7" t="n"/>
       <c r="Y254" s="7" t="n"/>
       <c r="AB254" s="7" t="n"/>
+      <c r="AC254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="C255" s="7" t="n"/>
@@ -4058,6 +4317,7 @@
       <c r="V255" s="7" t="n"/>
       <c r="Y255" s="7" t="n"/>
       <c r="AB255" s="7" t="n"/>
+      <c r="AC255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="C256" s="7" t="n"/>
@@ -4071,6 +4331,7 @@
       <c r="V256" s="7" t="n"/>
       <c r="Y256" s="7" t="n"/>
       <c r="AB256" s="7" t="n"/>
+      <c r="AC256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="C257" s="7" t="n"/>
@@ -4084,6 +4345,7 @@
       <c r="V257" s="7" t="n"/>
       <c r="Y257" s="7" t="n"/>
       <c r="AB257" s="7" t="n"/>
+      <c r="AC257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="C258" s="7" t="n"/>
@@ -4097,6 +4359,7 @@
       <c r="V258" s="7" t="n"/>
       <c r="Y258" s="7" t="n"/>
       <c r="AB258" s="7" t="n"/>
+      <c r="AC258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="C259" s="7" t="n"/>
@@ -4110,6 +4373,7 @@
       <c r="V259" s="7" t="n"/>
       <c r="Y259" s="7" t="n"/>
       <c r="AB259" s="7" t="n"/>
+      <c r="AC259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="C260" s="7" t="n"/>
@@ -4123,6 +4387,7 @@
       <c r="V260" s="7" t="n"/>
       <c r="Y260" s="7" t="n"/>
       <c r="AB260" s="7" t="n"/>
+      <c r="AC260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="C261" s="7" t="n"/>
@@ -4136,6 +4401,7 @@
       <c r="V261" s="7" t="n"/>
       <c r="Y261" s="7" t="n"/>
       <c r="AB261" s="7" t="n"/>
+      <c r="AC261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="C262" s="7" t="n"/>
@@ -4149,6 +4415,7 @@
       <c r="V262" s="7" t="n"/>
       <c r="Y262" s="7" t="n"/>
       <c r="AB262" s="7" t="n"/>
+      <c r="AC262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="C263" s="7" t="n"/>
@@ -4162,6 +4429,7 @@
       <c r="V263" s="7" t="n"/>
       <c r="Y263" s="7" t="n"/>
       <c r="AB263" s="7" t="n"/>
+      <c r="AC263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="C264" s="7" t="n"/>
@@ -4175,6 +4443,7 @@
       <c r="V264" s="7" t="n"/>
       <c r="Y264" s="7" t="n"/>
       <c r="AB264" s="7" t="n"/>
+      <c r="AC264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="C265" s="7" t="n"/>
@@ -4188,6 +4457,7 @@
       <c r="V265" s="7" t="n"/>
       <c r="Y265" s="7" t="n"/>
       <c r="AB265" s="7" t="n"/>
+      <c r="AC265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="C266" s="7" t="n"/>
@@ -4201,6 +4471,7 @@
       <c r="V266" s="7" t="n"/>
       <c r="Y266" s="7" t="n"/>
       <c r="AB266" s="7" t="n"/>
+      <c r="AC266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="C267" s="7" t="n"/>
@@ -4214,6 +4485,7 @@
       <c r="V267" s="7" t="n"/>
       <c r="Y267" s="7" t="n"/>
       <c r="AB267" s="7" t="n"/>
+      <c r="AC267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="C268" s="7" t="n"/>
@@ -4227,6 +4499,7 @@
       <c r="V268" s="7" t="n"/>
       <c r="Y268" s="7" t="n"/>
       <c r="AB268" s="7" t="n"/>
+      <c r="AC268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="C269" s="7" t="n"/>
@@ -4240,6 +4513,7 @@
       <c r="V269" s="7" t="n"/>
       <c r="Y269" s="7" t="n"/>
       <c r="AB269" s="7" t="n"/>
+      <c r="AC269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="C270" s="7" t="n"/>
@@ -4253,6 +4527,7 @@
       <c r="V270" s="7" t="n"/>
       <c r="Y270" s="7" t="n"/>
       <c r="AB270" s="7" t="n"/>
+      <c r="AC270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="C271" s="7" t="n"/>
@@ -4266,6 +4541,7 @@
       <c r="V271" s="7" t="n"/>
       <c r="Y271" s="7" t="n"/>
       <c r="AB271" s="7" t="n"/>
+      <c r="AC271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="C272" s="7" t="n"/>
@@ -4279,6 +4555,7 @@
       <c r="V272" s="7" t="n"/>
       <c r="Y272" s="7" t="n"/>
       <c r="AB272" s="7" t="n"/>
+      <c r="AC272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="C273" s="7" t="n"/>
@@ -4292,6 +4569,7 @@
       <c r="V273" s="7" t="n"/>
       <c r="Y273" s="7" t="n"/>
       <c r="AB273" s="7" t="n"/>
+      <c r="AC273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="C274" s="7" t="n"/>
@@ -4305,6 +4583,7 @@
       <c r="V274" s="7" t="n"/>
       <c r="Y274" s="7" t="n"/>
       <c r="AB274" s="7" t="n"/>
+      <c r="AC274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="C275" s="7" t="n"/>
@@ -4318,6 +4597,7 @@
       <c r="V275" s="7" t="n"/>
       <c r="Y275" s="7" t="n"/>
       <c r="AB275" s="7" t="n"/>
+      <c r="AC275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="C276" s="7" t="n"/>
@@ -4331,6 +4611,7 @@
       <c r="V276" s="7" t="n"/>
       <c r="Y276" s="7" t="n"/>
       <c r="AB276" s="7" t="n"/>
+      <c r="AC276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="C277" s="7" t="n"/>
@@ -4344,6 +4625,7 @@
       <c r="V277" s="7" t="n"/>
       <c r="Y277" s="7" t="n"/>
       <c r="AB277" s="7" t="n"/>
+      <c r="AC277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="C278" s="7" t="n"/>
@@ -4357,6 +4639,7 @@
       <c r="V278" s="7" t="n"/>
       <c r="Y278" s="7" t="n"/>
       <c r="AB278" s="7" t="n"/>
+      <c r="AC278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="C279" s="7" t="n"/>
@@ -4370,6 +4653,7 @@
       <c r="V279" s="7" t="n"/>
       <c r="Y279" s="7" t="n"/>
       <c r="AB279" s="7" t="n"/>
+      <c r="AC279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="C280" s="7" t="n"/>
@@ -4383,6 +4667,7 @@
       <c r="V280" s="7" t="n"/>
       <c r="Y280" s="7" t="n"/>
       <c r="AB280" s="7" t="n"/>
+      <c r="AC280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="C281" s="7" t="n"/>
@@ -4396,6 +4681,7 @@
       <c r="V281" s="7" t="n"/>
       <c r="Y281" s="7" t="n"/>
       <c r="AB281" s="7" t="n"/>
+      <c r="AC281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="C282" s="7" t="n"/>
@@ -4409,6 +4695,7 @@
       <c r="V282" s="7" t="n"/>
       <c r="Y282" s="7" t="n"/>
       <c r="AB282" s="7" t="n"/>
+      <c r="AC282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="C283" s="7" t="n"/>
@@ -4422,6 +4709,7 @@
       <c r="V283" s="7" t="n"/>
       <c r="Y283" s="7" t="n"/>
       <c r="AB283" s="7" t="n"/>
+      <c r="AC283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="C284" s="7" t="n"/>
@@ -4435,6 +4723,7 @@
       <c r="V284" s="7" t="n"/>
       <c r="Y284" s="7" t="n"/>
       <c r="AB284" s="7" t="n"/>
+      <c r="AC284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="C285" s="7" t="n"/>
@@ -4448,6 +4737,7 @@
       <c r="V285" s="7" t="n"/>
       <c r="Y285" s="7" t="n"/>
       <c r="AB285" s="7" t="n"/>
+      <c r="AC285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="C286" s="7" t="n"/>
@@ -4461,6 +4751,7 @@
       <c r="V286" s="7" t="n"/>
       <c r="Y286" s="7" t="n"/>
       <c r="AB286" s="7" t="n"/>
+      <c r="AC286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="C287" s="7" t="n"/>
@@ -4474,6 +4765,7 @@
       <c r="V287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
       <c r="AB287" s="7" t="n"/>
+      <c r="AC287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="C288" s="7" t="n"/>
@@ -4487,6 +4779,7 @@
       <c r="V288" s="7" t="n"/>
       <c r="Y288" s="7" t="n"/>
       <c r="AB288" s="7" t="n"/>
+      <c r="AC288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="C289" s="7" t="n"/>
@@ -4500,6 +4793,7 @@
       <c r="V289" s="7" t="n"/>
       <c r="Y289" s="7" t="n"/>
       <c r="AB289" s="7" t="n"/>
+      <c r="AC289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="C290" s="7" t="n"/>
@@ -4513,6 +4807,7 @@
       <c r="V290" s="7" t="n"/>
       <c r="Y290" s="7" t="n"/>
       <c r="AB290" s="7" t="n"/>
+      <c r="AC290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="C291" s="7" t="n"/>
@@ -4526,6 +4821,7 @@
       <c r="V291" s="7" t="n"/>
       <c r="Y291" s="7" t="n"/>
       <c r="AB291" s="7" t="n"/>
+      <c r="AC291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="C292" s="7" t="n"/>
@@ -4539,6 +4835,7 @@
       <c r="V292" s="7" t="n"/>
       <c r="Y292" s="7" t="n"/>
       <c r="AB292" s="7" t="n"/>
+      <c r="AC292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="C293" s="7" t="n"/>
@@ -4552,6 +4849,7 @@
       <c r="V293" s="7" t="n"/>
       <c r="Y293" s="7" t="n"/>
       <c r="AB293" s="7" t="n"/>
+      <c r="AC293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="C294" s="7" t="n"/>
@@ -4565,6 +4863,7 @@
       <c r="V294" s="7" t="n"/>
       <c r="Y294" s="7" t="n"/>
       <c r="AB294" s="7" t="n"/>
+      <c r="AC294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="C295" s="7" t="n"/>
@@ -4578,6 +4877,7 @@
       <c r="V295" s="7" t="n"/>
       <c r="Y295" s="7" t="n"/>
       <c r="AB295" s="7" t="n"/>
+      <c r="AC295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="C296" s="7" t="n"/>
@@ -4591,6 +4891,7 @@
       <c r="V296" s="7" t="n"/>
       <c r="Y296" s="7" t="n"/>
       <c r="AB296" s="7" t="n"/>
+      <c r="AC296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="C297" s="7" t="n"/>
@@ -4604,6 +4905,7 @@
       <c r="V297" s="7" t="n"/>
       <c r="Y297" s="7" t="n"/>
       <c r="AB297" s="7" t="n"/>
+      <c r="AC297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="C298" s="7" t="n"/>
@@ -4617,6 +4919,7 @@
       <c r="V298" s="7" t="n"/>
       <c r="Y298" s="7" t="n"/>
       <c r="AB298" s="7" t="n"/>
+      <c r="AC298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="C299" s="7" t="n"/>
@@ -4630,6 +4933,7 @@
       <c r="V299" s="7" t="n"/>
       <c r="Y299" s="7" t="n"/>
       <c r="AB299" s="7" t="n"/>
+      <c r="AC299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="C300" s="7" t="n"/>
@@ -4643,6 +4947,7 @@
       <c r="V300" s="7" t="n"/>
       <c r="Y300" s="7" t="n"/>
       <c r="AB300" s="7" t="n"/>
+      <c r="AC300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="C301" s="7" t="n"/>
@@ -4656,6 +4961,7 @@
       <c r="V301" s="7" t="n"/>
       <c r="Y301" s="7" t="n"/>
       <c r="AB301" s="7" t="n"/>
+      <c r="AC301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="C302" s="7" t="n"/>
@@ -4669,6 +4975,7 @@
       <c r="V302" s="7" t="n"/>
       <c r="Y302" s="7" t="n"/>
       <c r="AB302" s="7" t="n"/>
+      <c r="AC302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="C303" s="7" t="n"/>
@@ -4682,6 +4989,7 @@
       <c r="V303" s="7" t="n"/>
       <c r="Y303" s="7" t="n"/>
       <c r="AB303" s="7" t="n"/>
+      <c r="AC303" s="7" t="n"/>
     </row>
     <row r="304">
       <c r="C304" s="7" t="n"/>
@@ -4695,6 +5003,7 @@
       <c r="V304" s="7" t="n"/>
       <c r="Y304" s="7" t="n"/>
       <c r="AB304" s="7" t="n"/>
+      <c r="AC304" s="7" t="n"/>
     </row>
     <row r="305">
       <c r="C305" s="7" t="n"/>
@@ -4708,6 +5017,7 @@
       <c r="V305" s="7" t="n"/>
       <c r="Y305" s="7" t="n"/>
       <c r="AB305" s="7" t="n"/>
+      <c r="AC305" s="7" t="n"/>
     </row>
     <row r="306">
       <c r="C306" s="7" t="n"/>
@@ -4721,6 +5031,7 @@
       <c r="V306" s="7" t="n"/>
       <c r="Y306" s="7" t="n"/>
       <c r="AB306" s="7" t="n"/>
+      <c r="AC306" s="7" t="n"/>
     </row>
     <row r="307">
       <c r="C307" s="7" t="n"/>
@@ -4734,6 +5045,7 @@
       <c r="V307" s="7" t="n"/>
       <c r="Y307" s="7" t="n"/>
       <c r="AB307" s="7" t="n"/>
+      <c r="AC307" s="7" t="n"/>
     </row>
     <row r="308">
       <c r="C308" s="7" t="n"/>
@@ -4747,6 +5059,7 @@
       <c r="V308" s="7" t="n"/>
       <c r="Y308" s="7" t="n"/>
       <c r="AB308" s="7" t="n"/>
+      <c r="AC308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="C309" s="7" t="n"/>
@@ -4760,6 +5073,7 @@
       <c r="V309" s="7" t="n"/>
       <c r="Y309" s="7" t="n"/>
       <c r="AB309" s="7" t="n"/>
+      <c r="AC309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="C310" s="7" t="n"/>
@@ -4773,6 +5087,7 @@
       <c r="V310" s="7" t="n"/>
       <c r="Y310" s="7" t="n"/>
       <c r="AB310" s="7" t="n"/>
+      <c r="AC310" s="7" t="n"/>
     </row>
     <row r="311">
       <c r="C311" s="7" t="n"/>
@@ -4786,6 +5101,7 @@
       <c r="V311" s="7" t="n"/>
       <c r="Y311" s="7" t="n"/>
       <c r="AB311" s="7" t="n"/>
+      <c r="AC311" s="7" t="n"/>
     </row>
     <row r="312">
       <c r="C312" s="7" t="n"/>
@@ -4799,6 +5115,7 @@
       <c r="V312" s="7" t="n"/>
       <c r="Y312" s="7" t="n"/>
       <c r="AB312" s="7" t="n"/>
+      <c r="AC312" s="7" t="n"/>
     </row>
     <row r="313">
       <c r="C313" s="7" t="n"/>
@@ -4812,6 +5129,7 @@
       <c r="V313" s="7" t="n"/>
       <c r="Y313" s="7" t="n"/>
       <c r="AB313" s="7" t="n"/>
+      <c r="AC313" s="7" t="n"/>
     </row>
     <row r="314">
       <c r="C314" s="7" t="n"/>
@@ -4825,6 +5143,7 @@
       <c r="V314" s="7" t="n"/>
       <c r="Y314" s="7" t="n"/>
       <c r="AB314" s="7" t="n"/>
+      <c r="AC314" s="7" t="n"/>
     </row>
     <row r="315">
       <c r="C315" s="7" t="n"/>
@@ -4838,6 +5157,7 @@
       <c r="V315" s="7" t="n"/>
       <c r="Y315" s="7" t="n"/>
       <c r="AB315" s="7" t="n"/>
+      <c r="AC315" s="7" t="n"/>
     </row>
     <row r="316">
       <c r="C316" s="7" t="n"/>
@@ -4851,6 +5171,7 @@
       <c r="V316" s="7" t="n"/>
       <c r="Y316" s="7" t="n"/>
       <c r="AB316" s="7" t="n"/>
+      <c r="AC316" s="7" t="n"/>
     </row>
     <row r="317">
       <c r="C317" s="7" t="n"/>
@@ -4864,6 +5185,7 @@
       <c r="V317" s="7" t="n"/>
       <c r="Y317" s="7" t="n"/>
       <c r="AB317" s="7" t="n"/>
+      <c r="AC317" s="7" t="n"/>
     </row>
     <row r="318">
       <c r="C318" s="7" t="n"/>
@@ -4877,6 +5199,7 @@
       <c r="V318" s="7" t="n"/>
       <c r="Y318" s="7" t="n"/>
       <c r="AB318" s="7" t="n"/>
+      <c r="AC318" s="7" t="n"/>
     </row>
     <row r="319">
       <c r="C319" s="7" t="n"/>
@@ -4890,6 +5213,7 @@
       <c r="V319" s="7" t="n"/>
       <c r="Y319" s="7" t="n"/>
       <c r="AB319" s="7" t="n"/>
+      <c r="AC319" s="7" t="n"/>
     </row>
     <row r="320">
       <c r="C320" s="7" t="n"/>
@@ -4903,6 +5227,7 @@
       <c r="V320" s="7" t="n"/>
       <c r="Y320" s="7" t="n"/>
       <c r="AB320" s="7" t="n"/>
+      <c r="AC320" s="7" t="n"/>
     </row>
     <row r="321">
       <c r="C321" s="7" t="n"/>
@@ -4916,6 +5241,7 @@
       <c r="V321" s="7" t="n"/>
       <c r="Y321" s="7" t="n"/>
       <c r="AB321" s="7" t="n"/>
+      <c r="AC321" s="7" t="n"/>
     </row>
     <row r="322">
       <c r="C322" s="7" t="n"/>
@@ -4929,6 +5255,7 @@
       <c r="V322" s="7" t="n"/>
       <c r="Y322" s="7" t="n"/>
       <c r="AB322" s="7" t="n"/>
+      <c r="AC322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="C323" s="7" t="n"/>
@@ -4942,6 +5269,7 @@
       <c r="V323" s="7" t="n"/>
       <c r="Y323" s="7" t="n"/>
       <c r="AB323" s="7" t="n"/>
+      <c r="AC323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="C324" s="7" t="n"/>
@@ -4955,6 +5283,7 @@
       <c r="V324" s="7" t="n"/>
       <c r="Y324" s="7" t="n"/>
       <c r="AB324" s="7" t="n"/>
+      <c r="AC324" s="7" t="n"/>
     </row>
     <row r="325">
       <c r="C325" s="7" t="n"/>
@@ -4968,6 +5297,7 @@
       <c r="V325" s="7" t="n"/>
       <c r="Y325" s="7" t="n"/>
       <c r="AB325" s="7" t="n"/>
+      <c r="AC325" s="7" t="n"/>
     </row>
     <row r="326">
       <c r="C326" s="7" t="n"/>
@@ -4981,6 +5311,7 @@
       <c r="V326" s="7" t="n"/>
       <c r="Y326" s="7" t="n"/>
       <c r="AB326" s="7" t="n"/>
+      <c r="AC326" s="7" t="n"/>
     </row>
     <row r="327">
       <c r="C327" s="7" t="n"/>
@@ -4994,6 +5325,7 @@
       <c r="V327" s="7" t="n"/>
       <c r="Y327" s="7" t="n"/>
       <c r="AB327" s="7" t="n"/>
+      <c r="AC327" s="7" t="n"/>
     </row>
     <row r="328">
       <c r="C328" s="7" t="n"/>
@@ -5007,6 +5339,7 @@
       <c r="V328" s="7" t="n"/>
       <c r="Y328" s="7" t="n"/>
       <c r="AB328" s="7" t="n"/>
+      <c r="AC328" s="7" t="n"/>
     </row>
     <row r="329">
       <c r="C329" s="7" t="n"/>
@@ -5020,6 +5353,7 @@
       <c r="V329" s="7" t="n"/>
       <c r="Y329" s="7" t="n"/>
       <c r="AB329" s="7" t="n"/>
+      <c r="AC329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="C330" s="7" t="n"/>
@@ -5033,6 +5367,7 @@
       <c r="V330" s="7" t="n"/>
       <c r="Y330" s="7" t="n"/>
       <c r="AB330" s="7" t="n"/>
+      <c r="AC330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="C331" s="7" t="n"/>
@@ -5046,6 +5381,7 @@
       <c r="V331" s="7" t="n"/>
       <c r="Y331" s="7" t="n"/>
       <c r="AB331" s="7" t="n"/>
+      <c r="AC331" s="7" t="n"/>
     </row>
     <row r="332">
       <c r="C332" s="7" t="n"/>
@@ -5059,6 +5395,7 @@
       <c r="V332" s="7" t="n"/>
       <c r="Y332" s="7" t="n"/>
       <c r="AB332" s="7" t="n"/>
+      <c r="AC332" s="7" t="n"/>
     </row>
     <row r="333">
       <c r="C333" s="7" t="n"/>
@@ -5072,6 +5409,7 @@
       <c r="V333" s="7" t="n"/>
       <c r="Y333" s="7" t="n"/>
       <c r="AB333" s="7" t="n"/>
+      <c r="AC333" s="7" t="n"/>
     </row>
     <row r="334">
       <c r="C334" s="7" t="n"/>
@@ -5085,6 +5423,7 @@
       <c r="V334" s="7" t="n"/>
       <c r="Y334" s="7" t="n"/>
       <c r="AB334" s="7" t="n"/>
+      <c r="AC334" s="7" t="n"/>
     </row>
     <row r="335">
       <c r="C335" s="7" t="n"/>
@@ -5098,6 +5437,7 @@
       <c r="V335" s="7" t="n"/>
       <c r="Y335" s="7" t="n"/>
       <c r="AB335" s="7" t="n"/>
+      <c r="AC335" s="7" t="n"/>
     </row>
     <row r="336">
       <c r="C336" s="7" t="n"/>
@@ -5111,6 +5451,7 @@
       <c r="V336" s="7" t="n"/>
       <c r="Y336" s="7" t="n"/>
       <c r="AB336" s="7" t="n"/>
+      <c r="AC336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="C337" s="7" t="n"/>
@@ -5124,6 +5465,7 @@
       <c r="V337" s="7" t="n"/>
       <c r="Y337" s="7" t="n"/>
       <c r="AB337" s="7" t="n"/>
+      <c r="AC337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="C338" s="7" t="n"/>
@@ -5137,6 +5479,7 @@
       <c r="V338" s="7" t="n"/>
       <c r="Y338" s="7" t="n"/>
       <c r="AB338" s="7" t="n"/>
+      <c r="AC338" s="7" t="n"/>
     </row>
     <row r="339">
       <c r="C339" s="7" t="n"/>
@@ -5150,6 +5493,7 @@
       <c r="V339" s="7" t="n"/>
       <c r="Y339" s="7" t="n"/>
       <c r="AB339" s="7" t="n"/>
+      <c r="AC339" s="7" t="n"/>
     </row>
     <row r="340">
       <c r="C340" s="7" t="n"/>
@@ -5163,6 +5507,7 @@
       <c r="V340" s="7" t="n"/>
       <c r="Y340" s="7" t="n"/>
       <c r="AB340" s="7" t="n"/>
+      <c r="AC340" s="7" t="n"/>
     </row>
     <row r="341">
       <c r="C341" s="7" t="n"/>
@@ -5176,6 +5521,7 @@
       <c r="V341" s="7" t="n"/>
       <c r="Y341" s="7" t="n"/>
       <c r="AB341" s="7" t="n"/>
+      <c r="AC341" s="7" t="n"/>
     </row>
     <row r="342">
       <c r="C342" s="7" t="n"/>
@@ -5189,6 +5535,7 @@
       <c r="V342" s="7" t="n"/>
       <c r="Y342" s="7" t="n"/>
       <c r="AB342" s="7" t="n"/>
+      <c r="AC342" s="7" t="n"/>
     </row>
     <row r="343">
       <c r="C343" s="7" t="n"/>
@@ -5202,6 +5549,7 @@
       <c r="V343" s="7" t="n"/>
       <c r="Y343" s="7" t="n"/>
       <c r="AB343" s="7" t="n"/>
+      <c r="AC343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="C344" s="7" t="n"/>
@@ -5215,6 +5563,7 @@
       <c r="V344" s="7" t="n"/>
       <c r="Y344" s="7" t="n"/>
       <c r="AB344" s="7" t="n"/>
+      <c r="AC344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="C345" s="7" t="n"/>
@@ -5228,6 +5577,7 @@
       <c r="V345" s="7" t="n"/>
       <c r="Y345" s="7" t="n"/>
       <c r="AB345" s="7" t="n"/>
+      <c r="AC345" s="7" t="n"/>
     </row>
     <row r="346">
       <c r="C346" s="7" t="n"/>
@@ -5241,6 +5591,7 @@
       <c r="V346" s="7" t="n"/>
       <c r="Y346" s="7" t="n"/>
       <c r="AB346" s="7" t="n"/>
+      <c r="AC346" s="7" t="n"/>
     </row>
     <row r="347">
       <c r="C347" s="7" t="n"/>
@@ -5254,6 +5605,7 @@
       <c r="V347" s="7" t="n"/>
       <c r="Y347" s="7" t="n"/>
       <c r="AB347" s="7" t="n"/>
+      <c r="AC347" s="7" t="n"/>
     </row>
     <row r="348">
       <c r="C348" s="7" t="n"/>
@@ -5267,6 +5619,7 @@
       <c r="V348" s="7" t="n"/>
       <c r="Y348" s="7" t="n"/>
       <c r="AB348" s="7" t="n"/>
+      <c r="AC348" s="7" t="n"/>
     </row>
     <row r="349">
       <c r="C349" s="7" t="n"/>
@@ -5280,6 +5633,7 @@
       <c r="V349" s="7" t="n"/>
       <c r="Y349" s="7" t="n"/>
       <c r="AB349" s="7" t="n"/>
+      <c r="AC349" s="7" t="n"/>
     </row>
     <row r="350">
       <c r="C350" s="7" t="n"/>
@@ -5293,6 +5647,7 @@
       <c r="V350" s="7" t="n"/>
       <c r="Y350" s="7" t="n"/>
       <c r="AB350" s="7" t="n"/>
+      <c r="AC350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="C351" s="7" t="n"/>
@@ -5306,6 +5661,7 @@
       <c r="V351" s="7" t="n"/>
       <c r="Y351" s="7" t="n"/>
       <c r="AB351" s="7" t="n"/>
+      <c r="AC351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="C352" s="7" t="n"/>
@@ -5319,6 +5675,7 @@
       <c r="V352" s="7" t="n"/>
       <c r="Y352" s="7" t="n"/>
       <c r="AB352" s="7" t="n"/>
+      <c r="AC352" s="7" t="n"/>
     </row>
     <row r="353">
       <c r="C353" s="7" t="n"/>
@@ -5332,6 +5689,7 @@
       <c r="V353" s="7" t="n"/>
       <c r="Y353" s="7" t="n"/>
       <c r="AB353" s="7" t="n"/>
+      <c r="AC353" s="7" t="n"/>
     </row>
     <row r="354">
       <c r="C354" s="7" t="n"/>
@@ -5345,6 +5703,7 @@
       <c r="V354" s="7" t="n"/>
       <c r="Y354" s="7" t="n"/>
       <c r="AB354" s="7" t="n"/>
+      <c r="AC354" s="7" t="n"/>
     </row>
     <row r="355">
       <c r="C355" s="7" t="n"/>
@@ -5358,6 +5717,7 @@
       <c r="V355" s="7" t="n"/>
       <c r="Y355" s="7" t="n"/>
       <c r="AB355" s="7" t="n"/>
+      <c r="AC355" s="7" t="n"/>
     </row>
     <row r="356">
       <c r="C356" s="7" t="n"/>
@@ -5371,6 +5731,7 @@
       <c r="V356" s="7" t="n"/>
       <c r="Y356" s="7" t="n"/>
       <c r="AB356" s="7" t="n"/>
+      <c r="AC356" s="7" t="n"/>
     </row>
     <row r="357">
       <c r="C357" s="7" t="n"/>
@@ -5384,6 +5745,7 @@
       <c r="V357" s="7" t="n"/>
       <c r="Y357" s="7" t="n"/>
       <c r="AB357" s="7" t="n"/>
+      <c r="AC357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="C358" s="7" t="n"/>
@@ -5397,6 +5759,7 @@
       <c r="V358" s="7" t="n"/>
       <c r="Y358" s="7" t="n"/>
       <c r="AB358" s="7" t="n"/>
+      <c r="AC358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="C359" s="7" t="n"/>
@@ -5410,6 +5773,7 @@
       <c r="V359" s="7" t="n"/>
       <c r="Y359" s="7" t="n"/>
       <c r="AB359" s="7" t="n"/>
+      <c r="AC359" s="7" t="n"/>
     </row>
     <row r="360">
       <c r="C360" s="7" t="n"/>
@@ -5423,6 +5787,7 @@
       <c r="V360" s="7" t="n"/>
       <c r="Y360" s="7" t="n"/>
       <c r="AB360" s="7" t="n"/>
+      <c r="AC360" s="7" t="n"/>
     </row>
     <row r="361">
       <c r="C361" s="7" t="n"/>
@@ -5436,6 +5801,7 @@
       <c r="V361" s="7" t="n"/>
       <c r="Y361" s="7" t="n"/>
       <c r="AB361" s="7" t="n"/>
+      <c r="AC361" s="7" t="n"/>
     </row>
     <row r="362">
       <c r="C362" s="7" t="n"/>
@@ -5449,6 +5815,7 @@
       <c r="V362" s="7" t="n"/>
       <c r="Y362" s="7" t="n"/>
       <c r="AB362" s="7" t="n"/>
+      <c r="AC362" s="7" t="n"/>
     </row>
     <row r="363">
       <c r="C363" s="7" t="n"/>
@@ -5462,6 +5829,7 @@
       <c r="V363" s="7" t="n"/>
       <c r="Y363" s="7" t="n"/>
       <c r="AB363" s="7" t="n"/>
+      <c r="AC363" s="7" t="n"/>
     </row>
     <row r="364">
       <c r="C364" s="7" t="n"/>
@@ -5475,6 +5843,7 @@
       <c r="V364" s="7" t="n"/>
       <c r="Y364" s="7" t="n"/>
       <c r="AB364" s="7" t="n"/>
+      <c r="AC364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="C365" s="7" t="n"/>
@@ -5488,6 +5857,7 @@
       <c r="V365" s="7" t="n"/>
       <c r="Y365" s="7" t="n"/>
       <c r="AB365" s="7" t="n"/>
+      <c r="AC365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="C366" s="7" t="n"/>
@@ -5501,6 +5871,7 @@
       <c r="V366" s="7" t="n"/>
       <c r="Y366" s="7" t="n"/>
       <c r="AB366" s="7" t="n"/>
+      <c r="AC366" s="7" t="n"/>
     </row>
     <row r="367">
       <c r="C367" s="7" t="n"/>
@@ -5514,6 +5885,7 @@
       <c r="V367" s="7" t="n"/>
       <c r="Y367" s="7" t="n"/>
       <c r="AB367" s="7" t="n"/>
+      <c r="AC367" s="7" t="n"/>
     </row>
     <row r="368">
       <c r="C368" s="7" t="n"/>
@@ -5527,6 +5899,7 @@
       <c r="V368" s="7" t="n"/>
       <c r="Y368" s="7" t="n"/>
       <c r="AB368" s="7" t="n"/>
+      <c r="AC368" s="7" t="n"/>
     </row>
     <row r="369">
       <c r="C369" s="7" t="n"/>
@@ -5540,6 +5913,7 @@
       <c r="V369" s="7" t="n"/>
       <c r="Y369" s="7" t="n"/>
       <c r="AB369" s="7" t="n"/>
+      <c r="AC369" s="7" t="n"/>
     </row>
     <row r="370">
       <c r="C370" s="7" t="n"/>
@@ -5553,6 +5927,7 @@
       <c r="V370" s="7" t="n"/>
       <c r="Y370" s="7" t="n"/>
       <c r="AB370" s="7" t="n"/>
+      <c r="AC370" s="7" t="n"/>
     </row>
     <row r="371">
       <c r="C371" s="7" t="n"/>
@@ -5566,6 +5941,7 @@
       <c r="V371" s="7" t="n"/>
       <c r="Y371" s="7" t="n"/>
       <c r="AB371" s="7" t="n"/>
+      <c r="AC371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="C372" s="7" t="n"/>
@@ -5579,6 +5955,7 @@
       <c r="V372" s="7" t="n"/>
       <c r="Y372" s="7" t="n"/>
       <c r="AB372" s="7" t="n"/>
+      <c r="AC372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="C373" s="7" t="n"/>
@@ -5592,6 +5969,7 @@
       <c r="V373" s="7" t="n"/>
       <c r="Y373" s="7" t="n"/>
       <c r="AB373" s="7" t="n"/>
+      <c r="AC373" s="7" t="n"/>
     </row>
     <row r="374">
       <c r="C374" s="7" t="n"/>
@@ -5605,6 +5983,7 @@
       <c r="V374" s="7" t="n"/>
       <c r="Y374" s="7" t="n"/>
       <c r="AB374" s="7" t="n"/>
+      <c r="AC374" s="7" t="n"/>
     </row>
     <row r="375">
       <c r="C375" s="7" t="n"/>
@@ -5618,6 +5997,7 @@
       <c r="V375" s="7" t="n"/>
       <c r="Y375" s="7" t="n"/>
       <c r="AB375" s="7" t="n"/>
+      <c r="AC375" s="7" t="n"/>
     </row>
     <row r="376">
       <c r="C376" s="7" t="n"/>
@@ -5631,6 +6011,7 @@
       <c r="V376" s="7" t="n"/>
       <c r="Y376" s="7" t="n"/>
       <c r="AB376" s="7" t="n"/>
+      <c r="AC376" s="7" t="n"/>
     </row>
     <row r="377">
       <c r="C377" s="7" t="n"/>
@@ -5644,6 +6025,7 @@
       <c r="V377" s="7" t="n"/>
       <c r="Y377" s="7" t="n"/>
       <c r="AB377" s="7" t="n"/>
+      <c r="AC377" s="7" t="n"/>
     </row>
     <row r="378">
       <c r="C378" s="7" t="n"/>
@@ -5657,6 +6039,7 @@
       <c r="V378" s="7" t="n"/>
       <c r="Y378" s="7" t="n"/>
       <c r="AB378" s="7" t="n"/>
+      <c r="AC378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="C379" s="7" t="n"/>
@@ -5670,6 +6053,7 @@
       <c r="V379" s="7" t="n"/>
       <c r="Y379" s="7" t="n"/>
       <c r="AB379" s="7" t="n"/>
+      <c r="AC379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="C380" s="7" t="n"/>
@@ -5683,6 +6067,7 @@
       <c r="V380" s="7" t="n"/>
       <c r="Y380" s="7" t="n"/>
       <c r="AB380" s="7" t="n"/>
+      <c r="AC380" s="7" t="n"/>
     </row>
     <row r="381">
       <c r="C381" s="7" t="n"/>
@@ -5696,6 +6081,7 @@
       <c r="V381" s="7" t="n"/>
       <c r="Y381" s="7" t="n"/>
       <c r="AB381" s="7" t="n"/>
+      <c r="AC381" s="7" t="n"/>
     </row>
     <row r="382">
       <c r="C382" s="7" t="n"/>
@@ -5709,6 +6095,7 @@
       <c r="V382" s="7" t="n"/>
       <c r="Y382" s="7" t="n"/>
       <c r="AB382" s="7" t="n"/>
+      <c r="AC382" s="7" t="n"/>
     </row>
     <row r="383">
       <c r="C383" s="7" t="n"/>
@@ -5722,6 +6109,7 @@
       <c r="V383" s="7" t="n"/>
       <c r="Y383" s="7" t="n"/>
       <c r="AB383" s="7" t="n"/>
+      <c r="AC383" s="7" t="n"/>
     </row>
     <row r="384">
       <c r="C384" s="7" t="n"/>
@@ -5735,6 +6123,7 @@
       <c r="V384" s="7" t="n"/>
       <c r="Y384" s="7" t="n"/>
       <c r="AB384" s="7" t="n"/>
+      <c r="AC384" s="7" t="n"/>
     </row>
     <row r="385">
       <c r="C385" s="7" t="n"/>
@@ -5748,6 +6137,7 @@
       <c r="V385" s="7" t="n"/>
       <c r="Y385" s="7" t="n"/>
       <c r="AB385" s="7" t="n"/>
+      <c r="AC385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="C386" s="7" t="n"/>
@@ -5761,6 +6151,7 @@
       <c r="V386" s="7" t="n"/>
       <c r="Y386" s="7" t="n"/>
       <c r="AB386" s="7" t="n"/>
+      <c r="AC386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="C387" s="7" t="n"/>
@@ -5774,6 +6165,7 @@
       <c r="V387" s="7" t="n"/>
       <c r="Y387" s="7" t="n"/>
       <c r="AB387" s="7" t="n"/>
+      <c r="AC387" s="7" t="n"/>
     </row>
     <row r="388">
       <c r="C388" s="7" t="n"/>
@@ -5787,6 +6179,7 @@
       <c r="V388" s="7" t="n"/>
       <c r="Y388" s="7" t="n"/>
       <c r="AB388" s="7" t="n"/>
+      <c r="AC388" s="7" t="n"/>
     </row>
     <row r="389">
       <c r="C389" s="7" t="n"/>
@@ -5800,6 +6193,7 @@
       <c r="V389" s="7" t="n"/>
       <c r="Y389" s="7" t="n"/>
       <c r="AB389" s="7" t="n"/>
+      <c r="AC389" s="7" t="n"/>
     </row>
     <row r="390">
       <c r="C390" s="7" t="n"/>
@@ -5813,6 +6207,7 @@
       <c r="V390" s="7" t="n"/>
       <c r="Y390" s="7" t="n"/>
       <c r="AB390" s="7" t="n"/>
+      <c r="AC390" s="7" t="n"/>
     </row>
     <row r="391">
       <c r="C391" s="7" t="n"/>
@@ -5826,6 +6221,7 @@
       <c r="V391" s="7" t="n"/>
       <c r="Y391" s="7" t="n"/>
       <c r="AB391" s="7" t="n"/>
+      <c r="AC391" s="7" t="n"/>
     </row>
     <row r="392">
       <c r="C392" s="7" t="n"/>
@@ -5839,6 +6235,7 @@
       <c r="V392" s="7" t="n"/>
       <c r="Y392" s="7" t="n"/>
       <c r="AB392" s="7" t="n"/>
+      <c r="AC392" s="7" t="n"/>
     </row>
     <row r="393">
       <c r="C393" s="7" t="n"/>
@@ -5852,6 +6249,7 @@
       <c r="V393" s="7" t="n"/>
       <c r="Y393" s="7" t="n"/>
       <c r="AB393" s="7" t="n"/>
+      <c r="AC393" s="7" t="n"/>
     </row>
     <row r="394">
       <c r="C394" s="7" t="n"/>
@@ -5865,6 +6263,7 @@
       <c r="V394" s="7" t="n"/>
       <c r="Y394" s="7" t="n"/>
       <c r="AB394" s="7" t="n"/>
+      <c r="AC394" s="7" t="n"/>
     </row>
     <row r="395">
       <c r="C395" s="7" t="n"/>
@@ -5878,6 +6277,7 @@
       <c r="V395" s="7" t="n"/>
       <c r="Y395" s="7" t="n"/>
       <c r="AB395" s="7" t="n"/>
+      <c r="AC395" s="7" t="n"/>
     </row>
     <row r="396">
       <c r="C396" s="7" t="n"/>
@@ -5891,6 +6291,7 @@
       <c r="V396" s="7" t="n"/>
       <c r="Y396" s="7" t="n"/>
       <c r="AB396" s="7" t="n"/>
+      <c r="AC396" s="7" t="n"/>
     </row>
     <row r="397">
       <c r="C397" s="7" t="n"/>
@@ -5904,6 +6305,7 @@
       <c r="V397" s="7" t="n"/>
       <c r="Y397" s="7" t="n"/>
       <c r="AB397" s="7" t="n"/>
+      <c r="AC397" s="7" t="n"/>
     </row>
     <row r="398">
       <c r="C398" s="7" t="n"/>
@@ -5917,6 +6319,7 @@
       <c r="V398" s="7" t="n"/>
       <c r="Y398" s="7" t="n"/>
       <c r="AB398" s="7" t="n"/>
+      <c r="AC398" s="7" t="n"/>
     </row>
     <row r="399">
       <c r="C399" s="7" t="n"/>
@@ -5930,6 +6333,7 @@
       <c r="V399" s="7" t="n"/>
       <c r="Y399" s="7" t="n"/>
       <c r="AB399" s="7" t="n"/>
+      <c r="AC399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="C400" s="7" t="n"/>
@@ -5943,6 +6347,7 @@
       <c r="V400" s="7" t="n"/>
       <c r="Y400" s="7" t="n"/>
       <c r="AB400" s="7" t="n"/>
+      <c r="AC400" s="7" t="n"/>
     </row>
     <row r="401">
       <c r="C401" s="7" t="n"/>
@@ -5956,6 +6361,7 @@
       <c r="V401" s="7" t="n"/>
       <c r="Y401" s="7" t="n"/>
       <c r="AB401" s="7" t="n"/>
+      <c r="AC401" s="7" t="n"/>
     </row>
     <row r="402">
       <c r="C402" s="7" t="n"/>
@@ -5969,6 +6375,7 @@
       <c r="V402" s="7" t="n"/>
       <c r="Y402" s="7" t="n"/>
       <c r="AB402" s="7" t="n"/>
+      <c r="AC402" s="7" t="n"/>
     </row>
     <row r="403">
       <c r="C403" s="7" t="n"/>
@@ -5982,6 +6389,7 @@
       <c r="V403" s="7" t="n"/>
       <c r="Y403" s="7" t="n"/>
       <c r="AB403" s="7" t="n"/>
+      <c r="AC403" s="7" t="n"/>
     </row>
     <row r="404">
       <c r="C404" s="7" t="n"/>
@@ -5995,6 +6403,7 @@
       <c r="V404" s="7" t="n"/>
       <c r="Y404" s="7" t="n"/>
       <c r="AB404" s="7" t="n"/>
+      <c r="AC404" s="7" t="n"/>
     </row>
     <row r="405">
       <c r="C405" s="7" t="n"/>
@@ -6008,6 +6417,7 @@
       <c r="V405" s="7" t="n"/>
       <c r="Y405" s="7" t="n"/>
       <c r="AB405" s="7" t="n"/>
+      <c r="AC405" s="7" t="n"/>
     </row>
     <row r="406">
       <c r="C406" s="7" t="n"/>
@@ -6021,6 +6431,7 @@
       <c r="V406" s="7" t="n"/>
       <c r="Y406" s="7" t="n"/>
       <c r="AB406" s="7" t="n"/>
+      <c r="AC406" s="7" t="n"/>
     </row>
     <row r="407">
       <c r="C407" s="7" t="n"/>
@@ -6034,6 +6445,7 @@
       <c r="V407" s="7" t="n"/>
       <c r="Y407" s="7" t="n"/>
       <c r="AB407" s="7" t="n"/>
+      <c r="AC407" s="7" t="n"/>
     </row>
     <row r="408">
       <c r="C408" s="7" t="n"/>
@@ -6047,6 +6459,7 @@
       <c r="V408" s="7" t="n"/>
       <c r="Y408" s="7" t="n"/>
       <c r="AB408" s="7" t="n"/>
+      <c r="AC408" s="7" t="n"/>
     </row>
     <row r="409">
       <c r="C409" s="7" t="n"/>
@@ -6060,6 +6473,7 @@
       <c r="V409" s="7" t="n"/>
       <c r="Y409" s="7" t="n"/>
       <c r="AB409" s="7" t="n"/>
+      <c r="AC409" s="7" t="n"/>
     </row>
     <row r="410">
       <c r="C410" s="7" t="n"/>
@@ -6073,6 +6487,7 @@
       <c r="V410" s="7" t="n"/>
       <c r="Y410" s="7" t="n"/>
       <c r="AB410" s="7" t="n"/>
+      <c r="AC410" s="7" t="n"/>
     </row>
     <row r="411">
       <c r="C411" s="7" t="n"/>
@@ -6086,6 +6501,7 @@
       <c r="V411" s="7" t="n"/>
       <c r="Y411" s="7" t="n"/>
       <c r="AB411" s="7" t="n"/>
+      <c r="AC411" s="7" t="n"/>
     </row>
     <row r="412">
       <c r="C412" s="7" t="n"/>
@@ -6099,6 +6515,7 @@
       <c r="V412" s="7" t="n"/>
       <c r="Y412" s="7" t="n"/>
       <c r="AB412" s="7" t="n"/>
+      <c r="AC412" s="7" t="n"/>
     </row>
     <row r="413">
       <c r="C413" s="7" t="n"/>
@@ -6112,6 +6529,7 @@
       <c r="V413" s="7" t="n"/>
       <c r="Y413" s="7" t="n"/>
       <c r="AB413" s="7" t="n"/>
+      <c r="AC413" s="7" t="n"/>
     </row>
     <row r="414">
       <c r="C414" s="7" t="n"/>
@@ -6125,6 +6543,7 @@
       <c r="V414" s="7" t="n"/>
       <c r="Y414" s="7" t="n"/>
       <c r="AB414" s="7" t="n"/>
+      <c r="AC414" s="7" t="n"/>
     </row>
     <row r="415">
       <c r="C415" s="7" t="n"/>
@@ -6138,6 +6557,7 @@
       <c r="V415" s="7" t="n"/>
       <c r="Y415" s="7" t="n"/>
       <c r="AB415" s="7" t="n"/>
+      <c r="AC415" s="7" t="n"/>
     </row>
     <row r="416">
       <c r="C416" s="7" t="n"/>
@@ -6151,6 +6571,7 @@
       <c r="V416" s="7" t="n"/>
       <c r="Y416" s="7" t="n"/>
       <c r="AB416" s="7" t="n"/>
+      <c r="AC416" s="7" t="n"/>
     </row>
     <row r="417">
       <c r="C417" s="7" t="n"/>
@@ -6164,6 +6585,7 @@
       <c r="V417" s="7" t="n"/>
       <c r="Y417" s="7" t="n"/>
       <c r="AB417" s="7" t="n"/>
+      <c r="AC417" s="7" t="n"/>
     </row>
     <row r="418">
       <c r="C418" s="7" t="n"/>
@@ -6177,6 +6599,7 @@
       <c r="V418" s="7" t="n"/>
       <c r="Y418" s="7" t="n"/>
       <c r="AB418" s="7" t="n"/>
+      <c r="AC418" s="7" t="n"/>
     </row>
     <row r="419">
       <c r="C419" s="7" t="n"/>
@@ -6190,6 +6613,7 @@
       <c r="V419" s="7" t="n"/>
       <c r="Y419" s="7" t="n"/>
       <c r="AB419" s="7" t="n"/>
+      <c r="AC419" s="7" t="n"/>
     </row>
     <row r="420">
       <c r="C420" s="7" t="n"/>
@@ -6203,6 +6627,7 @@
       <c r="V420" s="7" t="n"/>
       <c r="Y420" s="7" t="n"/>
       <c r="AB420" s="7" t="n"/>
+      <c r="AC420" s="7" t="n"/>
     </row>
     <row r="421">
       <c r="C421" s="7" t="n"/>
@@ -6216,6 +6641,7 @@
       <c r="V421" s="7" t="n"/>
       <c r="Y421" s="7" t="n"/>
       <c r="AB421" s="7" t="n"/>
+      <c r="AC421" s="7" t="n"/>
     </row>
     <row r="422">
       <c r="C422" s="7" t="n"/>
@@ -6229,6 +6655,7 @@
       <c r="V422" s="7" t="n"/>
       <c r="Y422" s="7" t="n"/>
       <c r="AB422" s="7" t="n"/>
+      <c r="AC422" s="7" t="n"/>
     </row>
     <row r="423">
       <c r="C423" s="7" t="n"/>
@@ -6242,6 +6669,7 @@
       <c r="V423" s="7" t="n"/>
       <c r="Y423" s="7" t="n"/>
       <c r="AB423" s="7" t="n"/>
+      <c r="AC423" s="7" t="n"/>
     </row>
     <row r="424">
       <c r="C424" s="7" t="n"/>
@@ -6255,6 +6683,7 @@
       <c r="V424" s="7" t="n"/>
       <c r="Y424" s="7" t="n"/>
       <c r="AB424" s="7" t="n"/>
+      <c r="AC424" s="7" t="n"/>
     </row>
     <row r="425">
       <c r="C425" s="7" t="n"/>
@@ -6268,6 +6697,7 @@
       <c r="V425" s="7" t="n"/>
       <c r="Y425" s="7" t="n"/>
       <c r="AB425" s="7" t="n"/>
+      <c r="AC425" s="7" t="n"/>
     </row>
     <row r="426">
       <c r="C426" s="7" t="n"/>
@@ -6281,6 +6711,7 @@
       <c r="V426" s="7" t="n"/>
       <c r="Y426" s="7" t="n"/>
       <c r="AB426" s="7" t="n"/>
+      <c r="AC426" s="7" t="n"/>
     </row>
     <row r="427">
       <c r="C427" s="7" t="n"/>
@@ -6294,6 +6725,7 @@
       <c r="V427" s="7" t="n"/>
       <c r="Y427" s="7" t="n"/>
       <c r="AB427" s="7" t="n"/>
+      <c r="AC427" s="7" t="n"/>
     </row>
     <row r="428">
       <c r="C428" s="7" t="n"/>
@@ -6307,6 +6739,7 @@
       <c r="V428" s="7" t="n"/>
       <c r="Y428" s="7" t="n"/>
       <c r="AB428" s="7" t="n"/>
+      <c r="AC428" s="7" t="n"/>
     </row>
     <row r="429">
       <c r="C429" s="7" t="n"/>
@@ -6320,6 +6753,7 @@
       <c r="V429" s="7" t="n"/>
       <c r="Y429" s="7" t="n"/>
       <c r="AB429" s="7" t="n"/>
+      <c r="AC429" s="7" t="n"/>
     </row>
     <row r="430">
       <c r="C430" s="7" t="n"/>
@@ -6333,6 +6767,7 @@
       <c r="V430" s="7" t="n"/>
       <c r="Y430" s="7" t="n"/>
       <c r="AB430" s="7" t="n"/>
+      <c r="AC430" s="7" t="n"/>
     </row>
     <row r="431">
       <c r="C431" s="7" t="n"/>
@@ -6346,6 +6781,7 @@
       <c r="V431" s="7" t="n"/>
       <c r="Y431" s="7" t="n"/>
       <c r="AB431" s="7" t="n"/>
+      <c r="AC431" s="7" t="n"/>
     </row>
     <row r="432">
       <c r="C432" s="7" t="n"/>
@@ -6359,6 +6795,7 @@
       <c r="V432" s="7" t="n"/>
       <c r="Y432" s="7" t="n"/>
       <c r="AB432" s="7" t="n"/>
+      <c r="AC432" s="7" t="n"/>
     </row>
     <row r="433">
       <c r="C433" s="7" t="n"/>
@@ -6372,6 +6809,7 @@
       <c r="V433" s="7" t="n"/>
       <c r="Y433" s="7" t="n"/>
       <c r="AB433" s="7" t="n"/>
+      <c r="AC433" s="7" t="n"/>
     </row>
     <row r="434">
       <c r="C434" s="7" t="n"/>
@@ -6385,6 +6823,7 @@
       <c r="V434" s="7" t="n"/>
       <c r="Y434" s="7" t="n"/>
       <c r="AB434" s="7" t="n"/>
+      <c r="AC434" s="7" t="n"/>
     </row>
     <row r="435">
       <c r="C435" s="7" t="n"/>
@@ -6398,6 +6837,7 @@
       <c r="V435" s="7" t="n"/>
       <c r="Y435" s="7" t="n"/>
       <c r="AB435" s="7" t="n"/>
+      <c r="AC435" s="7" t="n"/>
     </row>
     <row r="436">
       <c r="C436" s="7" t="n"/>
@@ -6411,6 +6851,7 @@
       <c r="V436" s="7" t="n"/>
       <c r="Y436" s="7" t="n"/>
       <c r="AB436" s="7" t="n"/>
+      <c r="AC436" s="7" t="n"/>
     </row>
     <row r="437">
       <c r="C437" s="7" t="n"/>
@@ -6424,6 +6865,7 @@
       <c r="V437" s="7" t="n"/>
       <c r="Y437" s="7" t="n"/>
       <c r="AB437" s="7" t="n"/>
+      <c r="AC437" s="7" t="n"/>
     </row>
     <row r="438">
       <c r="C438" s="7" t="n"/>
@@ -6437,6 +6879,7 @@
       <c r="V438" s="7" t="n"/>
       <c r="Y438" s="7" t="n"/>
       <c r="AB438" s="7" t="n"/>
+      <c r="AC438" s="7" t="n"/>
     </row>
     <row r="439">
       <c r="C439" s="7" t="n"/>
@@ -6450,6 +6893,7 @@
       <c r="V439" s="7" t="n"/>
       <c r="Y439" s="7" t="n"/>
       <c r="AB439" s="7" t="n"/>
+      <c r="AC439" s="7" t="n"/>
     </row>
     <row r="440">
       <c r="C440" s="7" t="n"/>
@@ -6463,6 +6907,7 @@
       <c r="V440" s="7" t="n"/>
       <c r="Y440" s="7" t="n"/>
       <c r="AB440" s="7" t="n"/>
+      <c r="AC440" s="7" t="n"/>
     </row>
     <row r="441">
       <c r="C441" s="7" t="n"/>
@@ -6476,6 +6921,7 @@
       <c r="V441" s="7" t="n"/>
       <c r="Y441" s="7" t="n"/>
       <c r="AB441" s="7" t="n"/>
+      <c r="AC441" s="7" t="n"/>
     </row>
     <row r="442">
       <c r="C442" s="7" t="n"/>
@@ -6489,6 +6935,7 @@
       <c r="V442" s="7" t="n"/>
       <c r="Y442" s="7" t="n"/>
       <c r="AB442" s="7" t="n"/>
+      <c r="AC442" s="7" t="n"/>
     </row>
     <row r="443">
       <c r="C443" s="7" t="n"/>
@@ -6502,6 +6949,7 @@
       <c r="V443" s="7" t="n"/>
       <c r="Y443" s="7" t="n"/>
       <c r="AB443" s="7" t="n"/>
+      <c r="AC443" s="7" t="n"/>
     </row>
     <row r="444">
       <c r="C444" s="7" t="n"/>
@@ -6515,6 +6963,7 @@
       <c r="V444" s="7" t="n"/>
       <c r="Y444" s="7" t="n"/>
       <c r="AB444" s="7" t="n"/>
+      <c r="AC444" s="7" t="n"/>
     </row>
     <row r="445">
       <c r="C445" s="7" t="n"/>
@@ -6528,6 +6977,7 @@
       <c r="V445" s="7" t="n"/>
       <c r="Y445" s="7" t="n"/>
       <c r="AB445" s="7" t="n"/>
+      <c r="AC445" s="7" t="n"/>
     </row>
     <row r="446">
       <c r="C446" s="7" t="n"/>
@@ -6541,6 +6991,7 @@
       <c r="V446" s="7" t="n"/>
       <c r="Y446" s="7" t="n"/>
       <c r="AB446" s="7" t="n"/>
+      <c r="AC446" s="7" t="n"/>
     </row>
     <row r="447">
       <c r="C447" s="7" t="n"/>
@@ -6554,6 +7005,7 @@
       <c r="V447" s="7" t="n"/>
       <c r="Y447" s="7" t="n"/>
       <c r="AB447" s="7" t="n"/>
+      <c r="AC447" s="7" t="n"/>
     </row>
     <row r="448">
       <c r="C448" s="7" t="n"/>
@@ -6567,6 +7019,7 @@
       <c r="V448" s="7" t="n"/>
       <c r="Y448" s="7" t="n"/>
       <c r="AB448" s="7" t="n"/>
+      <c r="AC448" s="7" t="n"/>
     </row>
     <row r="449">
       <c r="C449" s="7" t="n"/>
@@ -6580,6 +7033,7 @@
       <c r="V449" s="7" t="n"/>
       <c r="Y449" s="7" t="n"/>
       <c r="AB449" s="7" t="n"/>
+      <c r="AC449" s="7" t="n"/>
     </row>
     <row r="450">
       <c r="C450" s="7" t="n"/>
@@ -6593,6 +7047,7 @@
       <c r="V450" s="7" t="n"/>
       <c r="Y450" s="7" t="n"/>
       <c r="AB450" s="7" t="n"/>
+      <c r="AC450" s="7" t="n"/>
     </row>
     <row r="451">
       <c r="C451" s="7" t="n"/>
@@ -6606,6 +7061,7 @@
       <c r="V451" s="7" t="n"/>
       <c r="Y451" s="7" t="n"/>
       <c r="AB451" s="7" t="n"/>
+      <c r="AC451" s="7" t="n"/>
     </row>
     <row r="452">
       <c r="C452" s="7" t="n"/>
@@ -6619,6 +7075,7 @@
       <c r="V452" s="7" t="n"/>
       <c r="Y452" s="7" t="n"/>
       <c r="AB452" s="7" t="n"/>
+      <c r="AC452" s="7" t="n"/>
     </row>
     <row r="453">
       <c r="C453" s="7" t="n"/>
@@ -6632,6 +7089,7 @@
       <c r="V453" s="7" t="n"/>
       <c r="Y453" s="7" t="n"/>
       <c r="AB453" s="7" t="n"/>
+      <c r="AC453" s="7" t="n"/>
     </row>
     <row r="454">
       <c r="C454" s="7" t="n"/>
@@ -6645,6 +7103,7 @@
       <c r="V454" s="7" t="n"/>
       <c r="Y454" s="7" t="n"/>
       <c r="AB454" s="7" t="n"/>
+      <c r="AC454" s="7" t="n"/>
     </row>
     <row r="455">
       <c r="C455" s="7" t="n"/>
@@ -6658,6 +7117,7 @@
       <c r="V455" s="7" t="n"/>
       <c r="Y455" s="7" t="n"/>
       <c r="AB455" s="7" t="n"/>
+      <c r="AC455" s="7" t="n"/>
     </row>
     <row r="456">
       <c r="C456" s="7" t="n"/>
@@ -6671,6 +7131,7 @@
       <c r="V456" s="7" t="n"/>
       <c r="Y456" s="7" t="n"/>
       <c r="AB456" s="7" t="n"/>
+      <c r="AC456" s="7" t="n"/>
     </row>
     <row r="457">
       <c r="C457" s="7" t="n"/>
@@ -6684,6 +7145,7 @@
       <c r="V457" s="7" t="n"/>
       <c r="Y457" s="7" t="n"/>
       <c r="AB457" s="7" t="n"/>
+      <c r="AC457" s="7" t="n"/>
     </row>
     <row r="458">
       <c r="C458" s="7" t="n"/>
@@ -6697,6 +7159,7 @@
       <c r="V458" s="7" t="n"/>
       <c r="Y458" s="7" t="n"/>
       <c r="AB458" s="7" t="n"/>
+      <c r="AC458" s="7" t="n"/>
     </row>
     <row r="459">
       <c r="C459" s="7" t="n"/>
@@ -6710,6 +7173,7 @@
       <c r="V459" s="7" t="n"/>
       <c r="Y459" s="7" t="n"/>
       <c r="AB459" s="7" t="n"/>
+      <c r="AC459" s="7" t="n"/>
     </row>
     <row r="460">
       <c r="C460" s="7" t="n"/>
@@ -6723,6 +7187,7 @@
       <c r="V460" s="7" t="n"/>
       <c r="Y460" s="7" t="n"/>
       <c r="AB460" s="7" t="n"/>
+      <c r="AC460" s="7" t="n"/>
     </row>
     <row r="461">
       <c r="C461" s="7" t="n"/>
@@ -6736,6 +7201,7 @@
       <c r="V461" s="7" t="n"/>
       <c r="Y461" s="7" t="n"/>
       <c r="AB461" s="7" t="n"/>
+      <c r="AC461" s="7" t="n"/>
     </row>
     <row r="462">
       <c r="C462" s="7" t="n"/>
@@ -6749,6 +7215,7 @@
       <c r="V462" s="7" t="n"/>
       <c r="Y462" s="7" t="n"/>
       <c r="AB462" s="7" t="n"/>
+      <c r="AC462" s="7" t="n"/>
     </row>
     <row r="463">
       <c r="C463" s="7" t="n"/>
@@ -6762,6 +7229,7 @@
       <c r="V463" s="7" t="n"/>
       <c r="Y463" s="7" t="n"/>
       <c r="AB463" s="7" t="n"/>
+      <c r="AC463" s="7" t="n"/>
     </row>
     <row r="464">
       <c r="C464" s="7" t="n"/>
@@ -6775,6 +7243,7 @@
       <c r="V464" s="7" t="n"/>
       <c r="Y464" s="7" t="n"/>
       <c r="AB464" s="7" t="n"/>
+      <c r="AC464" s="7" t="n"/>
     </row>
     <row r="465">
       <c r="C465" s="7" t="n"/>
@@ -6788,6 +7257,7 @@
       <c r="V465" s="7" t="n"/>
       <c r="Y465" s="7" t="n"/>
       <c r="AB465" s="7" t="n"/>
+      <c r="AC465" s="7" t="n"/>
     </row>
     <row r="466">
       <c r="C466" s="7" t="n"/>
@@ -6801,6 +7271,7 @@
       <c r="V466" s="7" t="n"/>
       <c r="Y466" s="7" t="n"/>
       <c r="AB466" s="7" t="n"/>
+      <c r="AC466" s="7" t="n"/>
     </row>
     <row r="467">
       <c r="C467" s="7" t="n"/>
@@ -6814,6 +7285,7 @@
       <c r="V467" s="7" t="n"/>
       <c r="Y467" s="7" t="n"/>
       <c r="AB467" s="7" t="n"/>
+      <c r="AC467" s="7" t="n"/>
     </row>
     <row r="468">
       <c r="C468" s="7" t="n"/>
@@ -6827,6 +7299,7 @@
       <c r="V468" s="7" t="n"/>
       <c r="Y468" s="7" t="n"/>
       <c r="AB468" s="7" t="n"/>
+      <c r="AC468" s="7" t="n"/>
     </row>
     <row r="469">
       <c r="C469" s="7" t="n"/>
@@ -6840,6 +7313,7 @@
       <c r="V469" s="7" t="n"/>
       <c r="Y469" s="7" t="n"/>
       <c r="AB469" s="7" t="n"/>
+      <c r="AC469" s="7" t="n"/>
     </row>
     <row r="470">
       <c r="C470" s="7" t="n"/>
@@ -6853,6 +7327,7 @@
       <c r="V470" s="7" t="n"/>
       <c r="Y470" s="7" t="n"/>
       <c r="AB470" s="7" t="n"/>
+      <c r="AC470" s="7" t="n"/>
     </row>
     <row r="471">
       <c r="C471" s="7" t="n"/>
@@ -6866,6 +7341,7 @@
       <c r="V471" s="7" t="n"/>
       <c r="Y471" s="7" t="n"/>
       <c r="AB471" s="7" t="n"/>
+      <c r="AC471" s="7" t="n"/>
     </row>
     <row r="472">
       <c r="C472" s="7" t="n"/>
@@ -6879,6 +7355,7 @@
       <c r="V472" s="7" t="n"/>
       <c r="Y472" s="7" t="n"/>
       <c r="AB472" s="7" t="n"/>
+      <c r="AC472" s="7" t="n"/>
     </row>
     <row r="473">
       <c r="C473" s="7" t="n"/>
@@ -6892,6 +7369,7 @@
       <c r="V473" s="7" t="n"/>
       <c r="Y473" s="7" t="n"/>
       <c r="AB473" s="7" t="n"/>
+      <c r="AC473" s="7" t="n"/>
     </row>
     <row r="474">
       <c r="C474" s="7" t="n"/>
@@ -6905,6 +7383,7 @@
       <c r="V474" s="7" t="n"/>
       <c r="Y474" s="7" t="n"/>
       <c r="AB474" s="7" t="n"/>
+      <c r="AC474" s="7" t="n"/>
     </row>
     <row r="475">
       <c r="C475" s="7" t="n"/>
@@ -6918,6 +7397,7 @@
       <c r="V475" s="7" t="n"/>
       <c r="Y475" s="7" t="n"/>
       <c r="AB475" s="7" t="n"/>
+      <c r="AC475" s="7" t="n"/>
     </row>
     <row r="476">
       <c r="C476" s="7" t="n"/>
@@ -6931,6 +7411,7 @@
       <c r="V476" s="7" t="n"/>
       <c r="Y476" s="7" t="n"/>
       <c r="AB476" s="7" t="n"/>
+      <c r="AC476" s="7" t="n"/>
     </row>
     <row r="477">
       <c r="C477" s="7" t="n"/>
@@ -6944,6 +7425,7 @@
       <c r="V477" s="7" t="n"/>
       <c r="Y477" s="7" t="n"/>
       <c r="AB477" s="7" t="n"/>
+      <c r="AC477" s="7" t="n"/>
     </row>
     <row r="478">
       <c r="C478" s="7" t="n"/>
@@ -6957,6 +7439,7 @@
       <c r="V478" s="7" t="n"/>
       <c r="Y478" s="7" t="n"/>
       <c r="AB478" s="7" t="n"/>
+      <c r="AC478" s="7" t="n"/>
     </row>
     <row r="479">
       <c r="C479" s="7" t="n"/>
@@ -6970,6 +7453,7 @@
       <c r="V479" s="7" t="n"/>
       <c r="Y479" s="7" t="n"/>
       <c r="AB479" s="7" t="n"/>
+      <c r="AC479" s="7" t="n"/>
     </row>
     <row r="480">
       <c r="C480" s="7" t="n"/>
@@ -6983,6 +7467,7 @@
       <c r="V480" s="7" t="n"/>
       <c r="Y480" s="7" t="n"/>
       <c r="AB480" s="7" t="n"/>
+      <c r="AC480" s="7" t="n"/>
     </row>
     <row r="481">
       <c r="C481" s="7" t="n"/>
@@ -6996,6 +7481,7 @@
       <c r="V481" s="7" t="n"/>
       <c r="Y481" s="7" t="n"/>
       <c r="AB481" s="7" t="n"/>
+      <c r="AC481" s="7" t="n"/>
     </row>
     <row r="482">
       <c r="C482" s="7" t="n"/>
@@ -7009,6 +7495,7 @@
       <c r="V482" s="7" t="n"/>
       <c r="Y482" s="7" t="n"/>
       <c r="AB482" s="7" t="n"/>
+      <c r="AC482" s="7" t="n"/>
     </row>
     <row r="483">
       <c r="C483" s="7" t="n"/>
@@ -7022,6 +7509,7 @@
       <c r="V483" s="7" t="n"/>
       <c r="Y483" s="7" t="n"/>
       <c r="AB483" s="7" t="n"/>
+      <c r="AC483" s="7" t="n"/>
     </row>
     <row r="484">
       <c r="C484" s="7" t="n"/>
@@ -7035,6 +7523,7 @@
       <c r="V484" s="7" t="n"/>
       <c r="Y484" s="7" t="n"/>
       <c r="AB484" s="7" t="n"/>
+      <c r="AC484" s="7" t="n"/>
     </row>
     <row r="485">
       <c r="C485" s="7" t="n"/>
@@ -7048,6 +7537,7 @@
       <c r="V485" s="7" t="n"/>
       <c r="Y485" s="7" t="n"/>
       <c r="AB485" s="7" t="n"/>
+      <c r="AC485" s="7" t="n"/>
     </row>
     <row r="486">
       <c r="C486" s="7" t="n"/>
@@ -7061,6 +7551,7 @@
       <c r="V486" s="7" t="n"/>
       <c r="Y486" s="7" t="n"/>
       <c r="AB486" s="7" t="n"/>
+      <c r="AC486" s="7" t="n"/>
     </row>
     <row r="487">
       <c r="C487" s="7" t="n"/>
@@ -7074,6 +7565,7 @@
       <c r="V487" s="7" t="n"/>
       <c r="Y487" s="7" t="n"/>
       <c r="AB487" s="7" t="n"/>
+      <c r="AC487" s="7" t="n"/>
     </row>
     <row r="488">
       <c r="C488" s="7" t="n"/>
@@ -7087,6 +7579,7 @@
       <c r="V488" s="7" t="n"/>
       <c r="Y488" s="7" t="n"/>
       <c r="AB488" s="7" t="n"/>
+      <c r="AC488" s="7" t="n"/>
     </row>
     <row r="489">
       <c r="C489" s="7" t="n"/>
@@ -7100,6 +7593,7 @@
       <c r="V489" s="7" t="n"/>
       <c r="Y489" s="7" t="n"/>
       <c r="AB489" s="7" t="n"/>
+      <c r="AC489" s="7" t="n"/>
     </row>
     <row r="490">
       <c r="C490" s="7" t="n"/>
@@ -7113,6 +7607,7 @@
       <c r="V490" s="7" t="n"/>
       <c r="Y490" s="7" t="n"/>
       <c r="AB490" s="7" t="n"/>
+      <c r="AC490" s="7" t="n"/>
     </row>
     <row r="491">
       <c r="C491" s="7" t="n"/>
@@ -7126,6 +7621,7 @@
       <c r="V491" s="7" t="n"/>
       <c r="Y491" s="7" t="n"/>
       <c r="AB491" s="7" t="n"/>
+      <c r="AC491" s="7" t="n"/>
     </row>
     <row r="492">
       <c r="C492" s="7" t="n"/>
@@ -7139,6 +7635,7 @@
       <c r="V492" s="7" t="n"/>
       <c r="Y492" s="7" t="n"/>
       <c r="AB492" s="7" t="n"/>
+      <c r="AC492" s="7" t="n"/>
     </row>
     <row r="493">
       <c r="C493" s="7" t="n"/>
@@ -7152,6 +7649,7 @@
       <c r="V493" s="7" t="n"/>
       <c r="Y493" s="7" t="n"/>
       <c r="AB493" s="7" t="n"/>
+      <c r="AC493" s="7" t="n"/>
     </row>
     <row r="494">
       <c r="C494" s="7" t="n"/>
@@ -7165,6 +7663,7 @@
       <c r="V494" s="7" t="n"/>
       <c r="Y494" s="7" t="n"/>
       <c r="AB494" s="7" t="n"/>
+      <c r="AC494" s="7" t="n"/>
     </row>
     <row r="495">
       <c r="C495" s="7" t="n"/>
@@ -7178,6 +7677,7 @@
       <c r="V495" s="7" t="n"/>
       <c r="Y495" s="7" t="n"/>
       <c r="AB495" s="7" t="n"/>
+      <c r="AC495" s="7" t="n"/>
     </row>
     <row r="496">
       <c r="C496" s="7" t="n"/>
@@ -7191,6 +7691,7 @@
       <c r="V496" s="7" t="n"/>
       <c r="Y496" s="7" t="n"/>
       <c r="AB496" s="7" t="n"/>
+      <c r="AC496" s="7" t="n"/>
     </row>
     <row r="497">
       <c r="C497" s="7" t="n"/>
@@ -7204,6 +7705,7 @@
       <c r="V497" s="7" t="n"/>
       <c r="Y497" s="7" t="n"/>
       <c r="AB497" s="7" t="n"/>
+      <c r="AC497" s="7" t="n"/>
     </row>
     <row r="498">
       <c r="C498" s="7" t="n"/>
@@ -7217,6 +7719,7 @@
       <c r="V498" s="7" t="n"/>
       <c r="Y498" s="7" t="n"/>
       <c r="AB498" s="7" t="n"/>
+      <c r="AC498" s="7" t="n"/>
     </row>
     <row r="499">
       <c r="C499" s="7" t="n"/>
@@ -7230,6 +7733,7 @@
       <c r="V499" s="7" t="n"/>
       <c r="Y499" s="7" t="n"/>
       <c r="AB499" s="7" t="n"/>
+      <c r="AC499" s="7" t="n"/>
     </row>
     <row r="500">
       <c r="C500" s="7" t="n"/>
@@ -7243,6 +7747,7 @@
       <c r="V500" s="7" t="n"/>
       <c r="Y500" s="7" t="n"/>
       <c r="AB500" s="7" t="n"/>
+      <c r="AC500" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7255,7 +7760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -7362,6 +7867,13 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Grade: only for classes that have grades (for example Aftercare with Gr R to Gr 12). Type it as Gr 3, Grade 3 or just 3. Leave it blank for any other class.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
